--- a/data/5.R_pakh_hoan_thanh.xlsx
+++ b/data/5.R_pakh_hoan_thanh.xlsx
@@ -668,7 +668,7 @@
         <v>46183</v>
       </c>
       <c r="AA2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
         <v>46183</v>
       </c>
       <c r="AA3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         <v>46183</v>
       </c>
       <c r="AA4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>46183</v>
       </c>
       <c r="AA5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>46183</v>
       </c>
       <c r="AA6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>46183</v>
       </c>
       <c r="AA7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         <v>46183</v>
       </c>
       <c r="AA8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>46183</v>
       </c>
       <c r="AA9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>46183</v>
       </c>
       <c r="AA10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
@@ -2095,7 +2095,7 @@
         <v>46183</v>
       </c>
       <c r="AA11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>46183</v>
       </c>
       <c r="AA12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>46183</v>
       </c>
       <c r="AA13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         <v>46183</v>
       </c>
       <c r="AA14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
@@ -2727,7 +2727,7 @@
         <v>46183</v>
       </c>
       <c r="AA15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         <v>46183</v>
       </c>
       <c r="AA16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         <v>46182</v>
       </c>
       <c r="AA17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
@@ -3208,7 +3208,7 @@
         <v>46182</v>
       </c>
       <c r="AA18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>46182</v>
       </c>
       <c r="AA19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
         <v>46182</v>
       </c>
       <c r="AA20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         <v>46182</v>
       </c>
       <c r="AA21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         <v>46183</v>
       </c>
       <c r="AA22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
@@ -4012,7 +4012,7 @@
         <v>46182</v>
       </c>
       <c r="AA23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>46182</v>
       </c>
       <c r="AA24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
@@ -4324,7 +4324,7 @@
         <v>46182</v>
       </c>
       <c r="AA25">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
@@ -4487,7 +4487,7 @@
         <v>46182</v>
       </c>
       <c r="AA26">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
         <v>46182</v>
       </c>
       <c r="AA27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
@@ -4813,7 +4813,7 @@
         <v>46182</v>
       </c>
       <c r="AA28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
@@ -4976,7 +4976,7 @@
         <v>46182</v>
       </c>
       <c r="AA29">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
@@ -5139,7 +5139,7 @@
         <v>46182</v>
       </c>
       <c r="AA30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
@@ -5306,7 +5306,7 @@
         <v>46182</v>
       </c>
       <c r="AA31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
@@ -5467,7 +5467,7 @@
         <v>46181</v>
       </c>
       <c r="AA32">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
@@ -5624,7 +5624,7 @@
         <v>46181</v>
       </c>
       <c r="AA33">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
@@ -5780,7 +5780,7 @@
         <v>46181</v>
       </c>
       <c r="AA34">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
@@ -5938,7 +5938,7 @@
         <v>46181</v>
       </c>
       <c r="AA35">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
@@ -6100,7 +6100,7 @@
         <v>46181</v>
       </c>
       <c r="AA36">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         <v>46182</v>
       </c>
       <c r="AA37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
@@ -6416,7 +6416,7 @@
         <v>46181</v>
       </c>
       <c r="AA38">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
@@ -6572,7 +6572,7 @@
         <v>46181</v>
       </c>
       <c r="AA39">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
@@ -6735,7 +6735,7 @@
         <v>46181</v>
       </c>
       <c r="AA40">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
@@ -6898,7 +6898,7 @@
         <v>46181</v>
       </c>
       <c r="AA41">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
@@ -7054,7 +7054,7 @@
         <v>46181</v>
       </c>
       <c r="AA42">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         <v>46181</v>
       </c>
       <c r="AA43">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
@@ -7380,7 +7380,7 @@
         <v>46181</v>
       </c>
       <c r="AA44">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
@@ -7542,7 +7542,7 @@
         <v>46181</v>
       </c>
       <c r="AA45">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
@@ -7700,7 +7700,7 @@
         <v>46181</v>
       </c>
       <c r="AA46">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
@@ -7858,7 +7858,7 @@
         <v>46181</v>
       </c>
       <c r="AA47">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
@@ -8014,7 +8014,7 @@
         <v>46181</v>
       </c>
       <c r="AA48">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
@@ -8177,7 +8177,7 @@
         <v>46181</v>
       </c>
       <c r="AA49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
@@ -8334,7 +8334,7 @@
         <v>46181</v>
       </c>
       <c r="AA50">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
@@ -8490,7 +8490,7 @@
         <v>46181</v>
       </c>
       <c r="AA51">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
@@ -8646,7 +8646,7 @@
         <v>46181</v>
       </c>
       <c r="AA52">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
@@ -8809,7 +8809,7 @@
         <v>46181</v>
       </c>
       <c r="AA53">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
@@ -8966,7 +8966,7 @@
         <v>46181</v>
       </c>
       <c r="AA54">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
@@ -9123,7 +9123,7 @@
         <v>46181</v>
       </c>
       <c r="AA55">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         <v>46181</v>
       </c>
       <c r="AA56">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         <v>46181</v>
       </c>
       <c r="AA57">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
@@ -9605,7 +9605,7 @@
         <v>46181</v>
       </c>
       <c r="AA58">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
@@ -9766,7 +9766,7 @@
         <v>46181</v>
       </c>
       <c r="AA59">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
@@ -9929,7 +9929,7 @@
         <v>46181</v>
       </c>
       <c r="AA60">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
@@ -10092,7 +10092,7 @@
         <v>46181</v>
       </c>
       <c r="AA61">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
@@ -10253,7 +10253,7 @@
         <v>46181</v>
       </c>
       <c r="AA62">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
@@ -10411,7 +10411,7 @@
         <v>46181</v>
       </c>
       <c r="AA63">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
@@ -10574,7 +10574,7 @@
         <v>46181</v>
       </c>
       <c r="AA64">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
@@ -10732,7 +10732,7 @@
         <v>46181</v>
       </c>
       <c r="AA65">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
@@ -10888,7 +10888,7 @@
         <v>46181</v>
       </c>
       <c r="AA66">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
@@ -11051,7 +11051,7 @@
         <v>46181</v>
       </c>
       <c r="AA67">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
@@ -11214,7 +11214,7 @@
         <v>46181</v>
       </c>
       <c r="AA68">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
@@ -11376,7 +11376,7 @@
         <v>46181</v>
       </c>
       <c r="AA69">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
@@ -11539,7 +11539,7 @@
         <v>46181</v>
       </c>
       <c r="AA70">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
@@ -11702,7 +11702,7 @@
         <v>46181</v>
       </c>
       <c r="AA71">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
@@ -11863,7 +11863,7 @@
         <v>46181</v>
       </c>
       <c r="AA72">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
@@ -12026,7 +12026,7 @@
         <v>46181</v>
       </c>
       <c r="AA73">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
@@ -12189,7 +12189,7 @@
         <v>46181</v>
       </c>
       <c r="AA74">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
@@ -12352,7 +12352,7 @@
         <v>46181</v>
       </c>
       <c r="AA75">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
@@ -12510,7 +12510,7 @@
         <v>46181</v>
       </c>
       <c r="AA76">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
@@ -12674,7 +12674,7 @@
         <v>46181</v>
       </c>
       <c r="AA77">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
@@ -12835,7 +12835,7 @@
         <v>46181</v>
       </c>
       <c r="AA78">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
@@ -12996,7 +12996,7 @@
         <v>46181</v>
       </c>
       <c r="AA79">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
@@ -13159,7 +13159,7 @@
         <v>46181</v>
       </c>
       <c r="AA80">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
@@ -13322,7 +13322,7 @@
         <v>46181</v>
       </c>
       <c r="AA81">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
@@ -13485,7 +13485,7 @@
         <v>46181</v>
       </c>
       <c r="AA82">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
@@ -13643,7 +13643,7 @@
         <v>46181</v>
       </c>
       <c r="AA83">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
@@ -13805,7 +13805,7 @@
         <v>46181</v>
       </c>
       <c r="AA84">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
@@ -13961,7 +13961,7 @@
         <v>46181</v>
       </c>
       <c r="AA85">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
@@ -14117,7 +14117,7 @@
         <v>46181</v>
       </c>
       <c r="AA86">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
@@ -14278,7 +14278,7 @@
         <v>46181</v>
       </c>
       <c r="AA87">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
@@ -14441,7 +14441,7 @@
         <v>46181</v>
       </c>
       <c r="AA88">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
@@ -14599,7 +14599,7 @@
         <v>46181</v>
       </c>
       <c r="AA89">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
@@ -14762,7 +14762,7 @@
         <v>46181</v>
       </c>
       <c r="AA90">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
@@ -14925,7 +14925,7 @@
         <v>46181</v>
       </c>
       <c r="AA91">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
@@ -15082,7 +15082,7 @@
         <v>46181</v>
       </c>
       <c r="AA92">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
@@ -15238,7 +15238,7 @@
         <v>46181</v>
       </c>
       <c r="AA93">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
@@ -15400,7 +15400,7 @@
         <v>46178</v>
       </c>
       <c r="AA94">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
@@ -15562,7 +15562,7 @@
         <v>46178</v>
       </c>
       <c r="AA95">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
@@ -15720,7 +15720,7 @@
         <v>46178</v>
       </c>
       <c r="AA96">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
@@ -15883,7 +15883,7 @@
         <v>46178</v>
       </c>
       <c r="AA97">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
@@ -16039,7 +16039,7 @@
         <v>46178</v>
       </c>
       <c r="AA98">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
@@ -16202,7 +16202,7 @@
         <v>46178</v>
       </c>
       <c r="AA99">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
@@ -16365,7 +16365,7 @@
         <v>46178</v>
       </c>
       <c r="AA100">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
@@ -16526,7 +16526,7 @@
         <v>46178</v>
       </c>
       <c r="AA101">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
@@ -16689,7 +16689,7 @@
         <v>46178</v>
       </c>
       <c r="AA102">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
@@ -16846,7 +16846,7 @@
         <v>46178</v>
       </c>
       <c r="AA103">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
@@ -17009,7 +17009,7 @@
         <v>46178</v>
       </c>
       <c r="AA104">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
@@ -17172,7 +17172,7 @@
         <v>46178</v>
       </c>
       <c r="AA105">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
@@ -17335,7 +17335,7 @@
         <v>46178</v>
       </c>
       <c r="AA106">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
@@ -17492,7 +17492,7 @@
         <v>46178</v>
       </c>
       <c r="AA107">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
@@ -17655,7 +17655,7 @@
         <v>46178</v>
       </c>
       <c r="AA108">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
@@ -17818,7 +17818,7 @@
         <v>46178</v>
       </c>
       <c r="AA109">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
@@ -17974,7 +17974,7 @@
         <v>46178</v>
       </c>
       <c r="AA110">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
@@ -18132,7 +18132,7 @@
         <v>46181</v>
       </c>
       <c r="AA111">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB111" t="inlineStr">
         <is>
@@ -18290,7 +18290,7 @@
         <v>46178</v>
       </c>
       <c r="AA112">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB112" t="inlineStr">
         <is>
@@ -18453,7 +18453,7 @@
         <v>46178</v>
       </c>
       <c r="AA113">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB113" t="inlineStr">
         <is>
@@ -18616,7 +18616,7 @@
         <v>46178</v>
       </c>
       <c r="AA114">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB114" t="inlineStr">
         <is>
@@ -18779,7 +18779,7 @@
         <v>46178</v>
       </c>
       <c r="AA115">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB115" t="inlineStr">
         <is>
@@ -18936,7 +18936,7 @@
         <v>46178</v>
       </c>
       <c r="AA116">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB116" t="inlineStr">
         <is>
@@ -19099,7 +19099,7 @@
         <v>46178</v>
       </c>
       <c r="AA117">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB117" t="inlineStr">
         <is>
@@ -19262,7 +19262,7 @@
         <v>46178</v>
       </c>
       <c r="AA118">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB118" t="inlineStr">
         <is>
@@ -19425,7 +19425,7 @@
         <v>46177</v>
       </c>
       <c r="AA119">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB119" t="inlineStr">
         <is>
@@ -19583,7 +19583,7 @@
         <v>46177</v>
       </c>
       <c r="AA120">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB120" t="inlineStr">
         <is>
@@ -19746,7 +19746,7 @@
         <v>46177</v>
       </c>
       <c r="AA121">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB121" t="inlineStr">
         <is>
@@ -19909,7 +19909,7 @@
         <v>46177</v>
       </c>
       <c r="AA122">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB122" t="inlineStr">
         <is>
@@ -20067,7 +20067,7 @@
         <v>46177</v>
       </c>
       <c r="AA123">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB123" t="inlineStr">
         <is>
@@ -20224,7 +20224,7 @@
         <v>46177</v>
       </c>
       <c r="AA124">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB124" t="inlineStr">
         <is>
@@ -20387,7 +20387,7 @@
         <v>46177</v>
       </c>
       <c r="AA125">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB125" t="inlineStr">
         <is>
@@ -20544,7 +20544,7 @@
         <v>46177</v>
       </c>
       <c r="AA126">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB126" t="inlineStr">
         <is>
@@ -20707,7 +20707,7 @@
         <v>46177</v>
       </c>
       <c r="AA127">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB127" t="inlineStr">
         <is>
@@ -20864,7 +20864,7 @@
         <v>46177</v>
       </c>
       <c r="AA128">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB128" t="inlineStr">
         <is>
@@ -21027,7 +21027,7 @@
         <v>46177</v>
       </c>
       <c r="AA129">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB129" t="inlineStr">
         <is>
@@ -21184,7 +21184,7 @@
         <v>46177</v>
       </c>
       <c r="AA130">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB130" t="inlineStr">
         <is>
@@ -21347,7 +21347,7 @@
         <v>46177</v>
       </c>
       <c r="AA131">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB131" t="inlineStr">
         <is>
@@ -21510,7 +21510,7 @@
         <v>46178</v>
       </c>
       <c r="AA132">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB132" t="inlineStr">
         <is>
@@ -21675,7 +21675,7 @@
         <v>46178</v>
       </c>
       <c r="AA133">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB133" t="inlineStr">
         <is>
@@ -21834,7 +21834,7 @@
         <v>46177</v>
       </c>
       <c r="AA134">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB134" t="inlineStr">
         <is>
@@ -21997,7 +21997,7 @@
         <v>46177</v>
       </c>
       <c r="AA135">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB135" t="inlineStr">
         <is>
@@ -22154,7 +22154,7 @@
         <v>46177</v>
       </c>
       <c r="AA136">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB136" t="inlineStr">
         <is>
@@ -22317,7 +22317,7 @@
         <v>46177</v>
       </c>
       <c r="AA137">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB137" t="inlineStr">
         <is>
@@ -22480,7 +22480,7 @@
         <v>46177</v>
       </c>
       <c r="AA138">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB138" t="inlineStr">
         <is>
@@ -22643,7 +22643,7 @@
         <v>46177</v>
       </c>
       <c r="AA139">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB139" t="inlineStr">
         <is>
@@ -22807,7 +22807,7 @@
         <v>46177</v>
       </c>
       <c r="AA140">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB140" t="inlineStr">
         <is>
@@ -22970,7 +22970,7 @@
         <v>46177</v>
       </c>
       <c r="AA141">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB141" t="inlineStr">
         <is>
@@ -23127,7 +23127,7 @@
         <v>46177</v>
       </c>
       <c r="AA142">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB142" t="inlineStr">
         <is>
@@ -23290,7 +23290,7 @@
         <v>46177</v>
       </c>
       <c r="AA143">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB143" t="inlineStr">
         <is>
@@ -23453,7 +23453,7 @@
         <v>46177</v>
       </c>
       <c r="AA144">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB144" t="inlineStr">
         <is>
@@ -23610,7 +23610,7 @@
         <v>46177</v>
       </c>
       <c r="AA145">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB145" t="inlineStr">
         <is>
@@ -23773,7 +23773,7 @@
         <v>46176</v>
       </c>
       <c r="AA146">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB146" t="inlineStr">
         <is>
@@ -23936,7 +23936,7 @@
         <v>46176</v>
       </c>
       <c r="AA147">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB147" t="inlineStr">
         <is>
@@ -24099,7 +24099,7 @@
         <v>46176</v>
       </c>
       <c r="AA148">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB148" t="inlineStr">
         <is>
@@ -24262,7 +24262,7 @@
         <v>46176</v>
       </c>
       <c r="AA149">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB149" t="inlineStr">
         <is>
@@ -24425,7 +24425,7 @@
         <v>46176</v>
       </c>
       <c r="AA150">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB150" t="inlineStr">
         <is>
@@ -24586,7 +24586,7 @@
         <v>46176</v>
       </c>
       <c r="AA151">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB151" t="inlineStr">
         <is>
@@ -24742,7 +24742,7 @@
         <v>46176</v>
       </c>
       <c r="AA152">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB152" t="inlineStr">
         <is>
@@ -24905,7 +24905,7 @@
         <v>46176</v>
       </c>
       <c r="AA153">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB153" t="inlineStr">
         <is>
@@ -25068,7 +25068,7 @@
         <v>46176</v>
       </c>
       <c r="AA154">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB154" t="inlineStr">
         <is>
@@ -25225,7 +25225,7 @@
         <v>46176</v>
       </c>
       <c r="AA155">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB155" t="inlineStr">
         <is>
@@ -25381,7 +25381,7 @@
         <v>46176</v>
       </c>
       <c r="AA156">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB156" t="inlineStr">
         <is>
@@ -25539,7 +25539,7 @@
         <v>46176</v>
       </c>
       <c r="AA157">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB157" t="inlineStr">
         <is>
@@ -25702,7 +25702,7 @@
         <v>46176</v>
       </c>
       <c r="AA158">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB158" t="inlineStr">
         <is>
@@ -25865,7 +25865,7 @@
         <v>46177</v>
       </c>
       <c r="AA159">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB159" t="inlineStr">
         <is>
@@ -26030,7 +26030,7 @@
         <v>46177</v>
       </c>
       <c r="AA160">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB160" t="inlineStr">
         <is>
@@ -26193,7 +26193,7 @@
         <v>46177</v>
       </c>
       <c r="AA161">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB161" t="inlineStr">
         <is>
@@ -26356,7 +26356,7 @@
         <v>46176</v>
       </c>
       <c r="AA162">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB162" t="inlineStr">
         <is>
@@ -26518,7 +26518,7 @@
         <v>46176</v>
       </c>
       <c r="AA163">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB163" t="inlineStr">
         <is>
@@ -26681,7 +26681,7 @@
         <v>46176</v>
       </c>
       <c r="AA164">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB164" t="inlineStr">
         <is>
@@ -26844,7 +26844,7 @@
         <v>46176</v>
       </c>
       <c r="AA165">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB165" t="inlineStr">
         <is>
@@ -27007,7 +27007,7 @@
         <v>46176</v>
       </c>
       <c r="AA166">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB166" t="inlineStr">
         <is>
@@ -27170,7 +27170,7 @@
         <v>46176</v>
       </c>
       <c r="AA167">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB167" t="inlineStr">
         <is>
@@ -27333,7 +27333,7 @@
         <v>46176</v>
       </c>
       <c r="AA168">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB168" t="inlineStr">
         <is>
@@ -27489,7 +27489,7 @@
         <v>46175</v>
       </c>
       <c r="AA169">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB169" t="inlineStr">
         <is>
@@ -27646,7 +27646,7 @@
         <v>46175</v>
       </c>
       <c r="AA170">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB170" t="inlineStr">
         <is>
@@ -27803,7 +27803,7 @@
         <v>46175</v>
       </c>
       <c r="AA171">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB171" t="inlineStr">
         <is>
@@ -27966,7 +27966,7 @@
         <v>46175</v>
       </c>
       <c r="AA172">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB172" t="inlineStr">
         <is>
@@ -28128,7 +28128,7 @@
         <v>46175</v>
       </c>
       <c r="AA173">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB173" t="inlineStr">
         <is>
@@ -28285,7 +28285,7 @@
         <v>46175</v>
       </c>
       <c r="AA174">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB174" t="inlineStr">
         <is>
@@ -28443,7 +28443,7 @@
         <v>46175</v>
       </c>
       <c r="AA175">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB175" t="inlineStr">
         <is>
@@ -28606,7 +28606,7 @@
         <v>46175</v>
       </c>
       <c r="AA176">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB176" t="inlineStr">
         <is>
@@ -28769,7 +28769,7 @@
         <v>46175</v>
       </c>
       <c r="AA177">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB177" t="inlineStr">
         <is>
@@ -28932,7 +28932,7 @@
         <v>46175</v>
       </c>
       <c r="AA178">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB178" t="inlineStr">
         <is>
@@ -29095,7 +29095,7 @@
         <v>46175</v>
       </c>
       <c r="AA179">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB179" t="inlineStr">
         <is>
@@ -29258,7 +29258,7 @@
         <v>46175</v>
       </c>
       <c r="AA180">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB180" t="inlineStr">
         <is>
@@ -29421,7 +29421,7 @@
         <v>46175</v>
       </c>
       <c r="AA181">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB181" t="inlineStr">
         <is>
@@ -29577,7 +29577,7 @@
         <v>46175</v>
       </c>
       <c r="AA182">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB182" t="inlineStr">
         <is>
@@ -29734,7 +29734,7 @@
         <v>46174</v>
       </c>
       <c r="AA183">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AB183" t="inlineStr">
         <is>
@@ -29897,7 +29897,7 @@
         <v>46174</v>
       </c>
       <c r="AA184">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AB184" t="inlineStr">
         <is>
@@ -30055,7 +30055,7 @@
         <v>46174</v>
       </c>
       <c r="AA185">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AB185" t="inlineStr">
         <is>
@@ -30212,7 +30212,7 @@
         <v>46174</v>
       </c>
       <c r="AA186">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AB186" t="inlineStr">
         <is>
@@ -30369,7 +30369,7 @@
         <v>46174</v>
       </c>
       <c r="AA187">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AB187" t="inlineStr">
         <is>
@@ -30531,7 +30531,7 @@
         <v>46174</v>
       </c>
       <c r="AA188">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AB188" t="inlineStr">
         <is>
@@ -30694,7 +30694,7 @@
         <v>46174</v>
       </c>
       <c r="AA189">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AB189" t="inlineStr">
         <is>
@@ -30857,7 +30857,7 @@
         <v>46174</v>
       </c>
       <c r="AA190">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AB190" t="inlineStr">
         <is>
@@ -31014,7 +31014,7 @@
         <v>46175</v>
       </c>
       <c r="AA191">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB191" t="inlineStr">
         <is>
@@ -31177,7 +31177,7 @@
         <v>46175</v>
       </c>
       <c r="AA192">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB192" t="inlineStr">
         <is>
@@ -31340,7 +31340,7 @@
         <v>46174</v>
       </c>
       <c r="AA193">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AB193" t="inlineStr">
         <is>
@@ -31497,7 +31497,7 @@
         <v>46174</v>
       </c>
       <c r="AA194">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AB194" t="inlineStr">
         <is>
@@ -31653,7 +31653,7 @@
         <v>46174</v>
       </c>
       <c r="AA195">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AB195" t="inlineStr">
         <is>
@@ -31811,7 +31811,7 @@
         <v>46174</v>
       </c>
       <c r="AA196">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AB196" t="inlineStr">
         <is>
@@ -31974,7 +31974,7 @@
         <v>46174</v>
       </c>
       <c r="AA197">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AB197" t="inlineStr">
         <is>
@@ -32137,7 +32137,7 @@
         <v>46174</v>
       </c>
       <c r="AA198">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AB198" t="inlineStr">
         <is>
@@ -32300,7 +32300,7 @@
         <v>46174</v>
       </c>
       <c r="AA199">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AB199" t="inlineStr">
         <is>
@@ -32463,7 +32463,7 @@
         <v>46174</v>
       </c>
       <c r="AA200">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AB200" t="inlineStr">
         <is>
@@ -32626,7 +32626,7 @@
         <v>46174</v>
       </c>
       <c r="AA201">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AB201" t="inlineStr">
         <is>
@@ -32782,7 +32782,7 @@
         <v>46174</v>
       </c>
       <c r="AA202">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AB202" t="inlineStr">
         <is>
@@ -32940,7 +32940,7 @@
         <v>46174</v>
       </c>
       <c r="AA203">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AB203" t="inlineStr">
         <is>
@@ -33103,7 +33103,7 @@
         <v>46174</v>
       </c>
       <c r="AA204">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AB204" t="inlineStr">
         <is>
@@ -33266,7 +33266,7 @@
         <v>46174</v>
       </c>
       <c r="AA205">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AB205" t="inlineStr">
         <is>
@@ -33423,7 +33423,7 @@
         <v>46174</v>
       </c>
       <c r="AA206">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AB206" t="inlineStr">
         <is>
@@ -33586,7 +33586,7 @@
         <v>46174</v>
       </c>
       <c r="AA207">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AB207" t="inlineStr">
         <is>
@@ -33750,7 +33750,7 @@
         <v>46174</v>
       </c>
       <c r="AA208">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AB208" t="inlineStr">
         <is>
@@ -33913,7 +33913,7 @@
         <v>46174</v>
       </c>
       <c r="AA209">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AB209" t="inlineStr">
         <is>
@@ -34070,7 +34070,7 @@
         <v>46174</v>
       </c>
       <c r="AA210">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AB210" t="inlineStr">
         <is>
@@ -34233,7 +34233,7 @@
         <v>46174</v>
       </c>
       <c r="AA211">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AB211" t="inlineStr">
         <is>
@@ -34391,7 +34391,7 @@
         <v>46174</v>
       </c>
       <c r="AA212">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AB212" t="inlineStr">
         <is>
@@ -34553,7 +34553,7 @@
         <v>46174</v>
       </c>
       <c r="AA213">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AB213" t="inlineStr">
         <is>
@@ -34714,7 +34714,7 @@
         <v>46174</v>
       </c>
       <c r="AA214">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AB214" t="inlineStr">
         <is>
@@ -34877,7 +34877,7 @@
         <v>46174</v>
       </c>
       <c r="AA215">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AB215" t="inlineStr">
         <is>
@@ -35040,7 +35040,7 @@
         <v>46174</v>
       </c>
       <c r="AA216">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AB216" t="inlineStr">
         <is>
@@ -35202,7 +35202,7 @@
         <v>46174</v>
       </c>
       <c r="AA217">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AB217" t="inlineStr">
         <is>
@@ -35365,7 +35365,7 @@
         <v>46174</v>
       </c>
       <c r="AA218">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AB218" t="inlineStr">
         <is>
@@ -35526,7 +35526,7 @@
         <v>46174</v>
       </c>
       <c r="AA219">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AB219" t="inlineStr">
         <is>
@@ -35683,7 +35683,7 @@
         <v>46174</v>
       </c>
       <c r="AA220">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AB220" t="inlineStr">
         <is>
@@ -35846,7 +35846,7 @@
         <v>46174</v>
       </c>
       <c r="AA221">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AB221" t="inlineStr">
         <is>
@@ -36011,7 +36011,7 @@
         <v>46174</v>
       </c>
       <c r="AA222">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AB222" t="inlineStr">
         <is>
@@ -36174,7 +36174,7 @@
         <v>46174</v>
       </c>
       <c r="AA223">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AB223" t="inlineStr">
         <is>
@@ -36337,7 +36337,7 @@
         <v>46174</v>
       </c>
       <c r="AA224">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AB224" t="inlineStr">
         <is>
@@ -36500,7 +36500,7 @@
         <v>46174</v>
       </c>
       <c r="AA225">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AB225" t="inlineStr">
         <is>
@@ -36656,7 +36656,7 @@
         <v>46174</v>
       </c>
       <c r="AA226">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AB226" t="inlineStr">
         <is>
@@ -36819,7 +36819,7 @@
         <v>46174</v>
       </c>
       <c r="AA227">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AB227" t="inlineStr">
         <is>
@@ -36982,7 +36982,7 @@
         <v>46174</v>
       </c>
       <c r="AA228">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AB228" t="inlineStr">
         <is>
@@ -37148,7 +37148,7 @@
         <v>46174</v>
       </c>
       <c r="AA229">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AB229" t="inlineStr">
         <is>
@@ -37313,7 +37313,7 @@
         <v>46174</v>
       </c>
       <c r="AA230">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AB230" t="inlineStr">
         <is>
@@ -37476,7 +37476,7 @@
         <v>46174</v>
       </c>
       <c r="AA231">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AB231" t="inlineStr">
         <is>
@@ -37632,7 +37632,7 @@
         <v>46174</v>
       </c>
       <c r="AA232">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AB232" t="inlineStr">
         <is>
@@ -37795,7 +37795,7 @@
         <v>46174</v>
       </c>
       <c r="AA233">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AB233" t="inlineStr">
         <is>
@@ -37953,7 +37953,7 @@
         <v>46174</v>
       </c>
       <c r="AA234">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AB234" t="inlineStr">
         <is>
@@ -38116,7 +38116,7 @@
         <v>46174</v>
       </c>
       <c r="AA235">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AB235" t="inlineStr">
         <is>
@@ -38279,7 +38279,7 @@
         <v>46174</v>
       </c>
       <c r="AA236">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AB236" t="inlineStr">
         <is>
@@ -38442,7 +38442,7 @@
         <v>46174</v>
       </c>
       <c r="AA237">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AB237" t="inlineStr">
         <is>
@@ -38606,7 +38606,7 @@
         <v>46174</v>
       </c>
       <c r="AA238">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AB238" t="inlineStr">
         <is>
@@ -38767,7 +38767,7 @@
         <v>46174</v>
       </c>
       <c r="AA239">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AB239" t="inlineStr">
         <is>
@@ -38930,7 +38930,7 @@
         <v>46174</v>
       </c>
       <c r="AA240">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AB240" t="inlineStr">
         <is>
@@ -39093,7 +39093,7 @@
         <v>46174</v>
       </c>
       <c r="AA241">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AB241" t="inlineStr">
         <is>
@@ -39256,7 +39256,7 @@
         <v>46174</v>
       </c>
       <c r="AA242">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AB242" t="inlineStr">
         <is>
@@ -39419,7 +39419,7 @@
         <v>46174</v>
       </c>
       <c r="AA243">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AB243" t="inlineStr">
         <is>
@@ -39577,7 +39577,7 @@
         <v>46171</v>
       </c>
       <c r="AA244">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AB244" t="inlineStr">
         <is>
@@ -39741,7 +39741,7 @@
         <v>46171</v>
       </c>
       <c r="AA245">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AB245" t="inlineStr">
         <is>
@@ -39904,7 +39904,7 @@
         <v>46171</v>
       </c>
       <c r="AA246">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AB246" t="inlineStr">
         <is>
@@ -40062,7 +40062,7 @@
         <v>46171</v>
       </c>
       <c r="AA247">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AB247" t="inlineStr">
         <is>
@@ -40225,7 +40225,7 @@
         <v>46171</v>
       </c>
       <c r="AA248">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AB248" t="inlineStr">
         <is>
@@ -40388,7 +40388,7 @@
         <v>46171</v>
       </c>
       <c r="AA249">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AB249" t="inlineStr">
         <is>
@@ -40551,7 +40551,7 @@
         <v>46171</v>
       </c>
       <c r="AA250">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AB250" t="inlineStr">
         <is>
@@ -40714,7 +40714,7 @@
         <v>46171</v>
       </c>
       <c r="AA251">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AB251" t="inlineStr">
         <is>
@@ -40877,7 +40877,7 @@
         <v>46171</v>
       </c>
       <c r="AA252">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AB252" t="inlineStr">
         <is>
@@ -41035,7 +41035,7 @@
         <v>46171</v>
       </c>
       <c r="AA253">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AB253" t="inlineStr">
         <is>
@@ -41198,7 +41198,7 @@
         <v>46171</v>
       </c>
       <c r="AA254">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AB254" t="inlineStr">
         <is>
@@ -41360,7 +41360,7 @@
         <v>46171</v>
       </c>
       <c r="AA255">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AB255" t="inlineStr">
         <is>
@@ -41516,7 +41516,7 @@
         <v>46171</v>
       </c>
       <c r="AA256">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AB256" t="inlineStr">
         <is>
@@ -41674,7 +41674,7 @@
         <v>46171</v>
       </c>
       <c r="AA257">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AB257" t="inlineStr">
         <is>
@@ -41837,7 +41837,7 @@
         <v>46171</v>
       </c>
       <c r="AA258">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AB258" t="inlineStr">
         <is>
@@ -42000,7 +42000,7 @@
         <v>46171</v>
       </c>
       <c r="AA259">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AB259" t="inlineStr">
         <is>
@@ -42161,7 +42161,7 @@
         <v>46170</v>
       </c>
       <c r="AA260">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AB260" t="inlineStr">
         <is>
@@ -42319,7 +42319,7 @@
         <v>46170</v>
       </c>
       <c r="AA261">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AB261" t="inlineStr">
         <is>
@@ -42478,7 +42478,7 @@
         <v>46170</v>
       </c>
       <c r="AA262">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AB262" t="inlineStr">
         <is>
@@ -42641,7 +42641,7 @@
         <v>46169</v>
       </c>
       <c r="AA263">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AB263" t="inlineStr">
         <is>
@@ -42804,7 +42804,7 @@
         <v>46170</v>
       </c>
       <c r="AA264">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AB264" t="inlineStr">
         <is>
@@ -42967,7 +42967,7 @@
         <v>46170</v>
       </c>
       <c r="AA265">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AB265" t="inlineStr">
         <is>
@@ -43130,7 +43130,7 @@
         <v>46170</v>
       </c>
       <c r="AA266">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AB266" t="inlineStr">
         <is>
@@ -43293,7 +43293,7 @@
         <v>46169</v>
       </c>
       <c r="AA267">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AB267" t="inlineStr">
         <is>
@@ -43456,7 +43456,7 @@
         <v>46169</v>
       </c>
       <c r="AA268">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AB268" t="inlineStr">
         <is>
@@ -43620,7 +43620,7 @@
         <v>46169</v>
       </c>
       <c r="AA269">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AB269" t="inlineStr">
         <is>
@@ -43783,7 +43783,7 @@
         <v>46169</v>
       </c>
       <c r="AA270">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AB270" t="inlineStr">
         <is>
@@ -43946,7 +43946,7 @@
         <v>46169</v>
       </c>
       <c r="AA271">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AB271" t="inlineStr">
         <is>
@@ -44109,7 +44109,7 @@
         <v>46169</v>
       </c>
       <c r="AA272">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AB272" t="inlineStr">
         <is>
@@ -44272,7 +44272,7 @@
         <v>46169</v>
       </c>
       <c r="AA273">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AB273" t="inlineStr">
         <is>
@@ -44435,7 +44435,7 @@
         <v>46168</v>
       </c>
       <c r="AA274">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AB274" t="inlineStr">
         <is>
@@ -44599,7 +44599,7 @@
         <v>46168</v>
       </c>
       <c r="AA275">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AB275" t="inlineStr">
         <is>
@@ -44762,7 +44762,7 @@
         <v>46168</v>
       </c>
       <c r="AA276">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AB276" t="inlineStr">
         <is>
@@ -44925,7 +44925,7 @@
         <v>46168</v>
       </c>
       <c r="AA277">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AB277" t="inlineStr">
         <is>
@@ -45088,7 +45088,7 @@
         <v>46168</v>
       </c>
       <c r="AA278">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AB278" t="inlineStr">
         <is>
@@ -45251,7 +45251,7 @@
         <v>46168</v>
       </c>
       <c r="AA279">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AB279" t="inlineStr">
         <is>
@@ -45414,7 +45414,7 @@
         <v>46167</v>
       </c>
       <c r="AA280">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AB280" t="inlineStr">
         <is>
@@ -45577,7 +45577,7 @@
         <v>46167</v>
       </c>
       <c r="AA281">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AB281" t="inlineStr">
         <is>
@@ -45740,7 +45740,7 @@
         <v>46167</v>
       </c>
       <c r="AA282">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AB282" t="inlineStr">
         <is>
@@ -45903,7 +45903,7 @@
         <v>46167</v>
       </c>
       <c r="AA283">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AB283" t="inlineStr">
         <is>
@@ -46066,7 +46066,7 @@
         <v>46167</v>
       </c>
       <c r="AA284">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AB284" t="inlineStr">
         <is>
@@ -46229,7 +46229,7 @@
         <v>46167</v>
       </c>
       <c r="AA285">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AB285" t="inlineStr">
         <is>
@@ -46387,7 +46387,7 @@
         <v>46167</v>
       </c>
       <c r="AA286">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AB286" t="inlineStr">
         <is>
@@ -46545,7 +46545,7 @@
         <v>46167</v>
       </c>
       <c r="AA287">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AB287" t="inlineStr">
         <is>
@@ -46707,7 +46707,7 @@
         <v>46167</v>
       </c>
       <c r="AA288">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AB288" t="inlineStr">
         <is>
@@ -46870,7 +46870,7 @@
         <v>46167</v>
       </c>
       <c r="AA289">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AB289" t="inlineStr">
         <is>
@@ -47033,7 +47033,7 @@
         <v>46164</v>
       </c>
       <c r="AA290">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AB290" t="inlineStr">
         <is>
@@ -47196,7 +47196,7 @@
         <v>46163</v>
       </c>
       <c r="AA291">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AB291" t="inlineStr">
         <is>
@@ -47359,7 +47359,7 @@
         <v>46164</v>
       </c>
       <c r="AA292">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AB292" t="inlineStr">
         <is>
@@ -47522,7 +47522,7 @@
         <v>46162</v>
       </c>
       <c r="AA293">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AB293" t="inlineStr">
         <is>
@@ -47685,7 +47685,7 @@
         <v>46162</v>
       </c>
       <c r="AA294">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AB294" t="inlineStr">
         <is>
@@ -47849,7 +47849,7 @@
         <v>46161</v>
       </c>
       <c r="AA295">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AB295" t="inlineStr">
         <is>
@@ -48012,7 +48012,7 @@
         <v>46160</v>
       </c>
       <c r="AA296">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AB296" t="inlineStr">
         <is>
@@ -48175,7 +48175,7 @@
         <v>46160</v>
       </c>
       <c r="AA297">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AB297" t="inlineStr">
         <is>
@@ -48338,7 +48338,7 @@
         <v>46156</v>
       </c>
       <c r="AA298">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AB298" t="inlineStr">
         <is>
@@ -48501,7 +48501,7 @@
         <v>46155</v>
       </c>
       <c r="AA299">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AB299" t="inlineStr">
         <is>
@@ -48664,7 +48664,7 @@
         <v>46154</v>
       </c>
       <c r="AA300">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AB300" t="inlineStr">
         <is>
@@ -48822,7 +48822,7 @@
         <v>46146</v>
       </c>
       <c r="AA301">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AB301" t="inlineStr">
         <is>
@@ -48985,7 +48985,7 @@
         <v>46146</v>
       </c>
       <c r="AA302">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AB302" t="inlineStr">
         <is>
@@ -49143,7 +49143,7 @@
         <v>46140</v>
       </c>
       <c r="AA303">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AB303" t="inlineStr">
         <is>
@@ -49305,7 +49305,7 @@
         <v>46135</v>
       </c>
       <c r="AA304">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AB304" t="inlineStr">
         <is>
@@ -49468,7 +49468,7 @@
         <v>46125</v>
       </c>
       <c r="AA305">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AB305" t="inlineStr">
         <is>
@@ -49630,7 +49630,7 @@
         <v>46118</v>
       </c>
       <c r="AA306">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AB306" t="inlineStr">
         <is>
@@ -49794,7 +49794,7 @@
         <v>46104</v>
       </c>
       <c r="AA307">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AB307" t="inlineStr">
         <is>
@@ -49953,7 +49953,7 @@
         <v>46001</v>
       </c>
       <c r="AA308">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AB308" t="inlineStr">
         <is>

--- a/data/5.R_pakh_hoan_thanh.xlsx
+++ b/data/5.R_pakh_hoan_thanh.xlsx
@@ -357,7 +357,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AI30"/>
+  <dimension ref="A1:AI49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="19" max="19" width="20.7109375" style="2" customWidth="1"/>
@@ -546,1048 +546,2332 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>KV1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>HNI</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Hệ thống NLMT</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_HNI_1641398</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Diamond</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Hoàng Việt Thanh</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0984736666</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Xã Cẩm Thanh</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Sự cố</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>1. KH đã báo CN: A Tín
+2. KH phản ánh: nhảy áp liên tục, đóng áp thì nhảy, đẩy lên thì nhảy, KH đang nghi do mấy hôm nay mưa
+3. KH yêu cầu: KT ở gần đây qua kiểm tra, xử lý tình trạng này</t>
+        </is>
+      </c>
+      <c r="S2" s="2">
+        <v>46205.67013888889</v>
+      </c>
+      <c r="T2" s="2">
+        <v>46206.67013888889</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Hoàn thành</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Đặng Văn Tài</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>469009</t>
+        </is>
+      </c>
+      <c r="Y2" s="2">
+        <v>46206.32847222222</v>
+      </c>
+      <c r="Z2" s="3">
+        <v>46205</v>
+      </c>
+      <c r="AA2">
+        <v>1</v>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>N1 - Truongdv17, Congnd15</t>
+        </is>
+      </c>
+      <c r="AE2">
+        <v>15.79972222222222</v>
+      </c>
+      <c r="AF2">
+        <v>0.6583217592592593</v>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="AH2">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>KV1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>BNH</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Hệ thống NLMT</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>VCC_YCTX_BNH_1782612643202</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Nguyễn Chí Công</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0941541386</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>phường Nếnh</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Trước bán</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Khiếu nại</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Liên hệ tư vấn chậm</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>KH có YCTX NLMT từ ngày 28/06 chưa có ai liên hệ và tư vấn</t>
+        </is>
+      </c>
+      <c r="S3" s="2">
+        <v>46205.4625</v>
+      </c>
+      <c r="T3" s="2">
+        <v>46206.4625</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Hoàn thành</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Nguyễn Đức Ngọc</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>068757</t>
+        </is>
+      </c>
+      <c r="Y3" s="2">
+        <v>46206.32569444444</v>
+      </c>
+      <c r="Z3" s="3">
+        <v>46205</v>
+      </c>
+      <c r="AA3">
+        <v>1</v>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>IOC</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>P.KDNLMT</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>N1 - Truongdv17, Congnd15</t>
+        </is>
+      </c>
+      <c r="AE3">
+        <v>20.71638888888889</v>
+      </c>
+      <c r="AF3">
+        <v>0.8631828703703704</v>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="AH3">
+        <v>3.283333333333333</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>KV2</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>DNG</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>DVKT</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Home Service</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Bảo dưỡng Điều hòa treo tường (9.000BTU ÷ 12.000 BTU)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>DH_B2C_DNG_1782913112337</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Member</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Nguyễn Văn Liêm</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0913494405</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>21/9 Ông Ích Khiêm, P Hải Châu, ĐNang,, Thành phố Đà Nẵng</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Trước bán</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Khiếu nại</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Liên hệ chậm</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>KH đặt đơn DVKT từ ngày 01/07 chưa có KT liên hệ và đến hỗ trợ
+KH cần KT đến hỗ trợ sớm</t>
+        </is>
+      </c>
+      <c r="S4" s="2">
+        <v>46205.40555555555</v>
+      </c>
+      <c r="T4" s="2">
+        <v>46205.57222222222</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Đóng</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Tăng Thanh Châu</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>433381</t>
+        </is>
+      </c>
+      <c r="Y4" s="2">
+        <v>46205.47777777778</v>
+      </c>
+      <c r="Z4" s="3">
+        <v>46205</v>
+      </c>
+      <c r="AA4">
+        <v>1</v>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>IOC</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>N2 - Tienvt16, Anhnt631</t>
+        </is>
+      </c>
+      <c r="AE4">
+        <v>1.733333333333333</v>
+      </c>
+      <c r="AF4">
+        <v>0.07222222222222223</v>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="AH4">
+        <v>2.266666666666667</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>KV1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>HNI</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Hệ thống NLMT</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_HNI_1701119</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Diamond</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Nguyễn Tiến Đạt</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0868020995</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>số 10 ngõ 101 Yến Vỹ</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Sự cố</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>1. KH  chưa liên hệ CN
+2. Hiện nhà KH đã mất điện lưới và điện NLMT, Điện lưới vẫn đang có nhưng không chuyển vào hệ thông để sử dụng được, App theo dõi hiệu suất báo ngoại tuyến
+3. KH cần CN đến kiểm tra và hỗ trợ gấp do đang không có điện để sử dụng</t>
+        </is>
+      </c>
+      <c r="S5" s="2">
+        <v>46205.35347222222</v>
+      </c>
+      <c r="T5" s="2">
+        <v>46206.375</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Đóng</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Trần Văn Tuấn</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>471823</t>
+        </is>
+      </c>
+      <c r="Y5" s="2">
+        <v>46205.61041666666</v>
+      </c>
+      <c r="Z5" s="3">
+        <v>46205</v>
+      </c>
+      <c r="AA5">
+        <v>1</v>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>N1 - Truongdv17, Congnd15</t>
+        </is>
+      </c>
+      <c r="AE5">
+        <v>6.166666666666667</v>
+      </c>
+      <c r="AF5">
+        <v>0.2569444444444445</v>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="AH5">
+        <v>18.34972222222222</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>KV1</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>BNH</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Hệ thống NLMT</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>VCC_YCTX_BNH_1780640531321</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Nguyễn Văn Tiến</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0964880815</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Tdp đông hương</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Trước bán</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hỗ trợ</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Tư vấn sản phẩm/dịch vụ</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>KH có YCTX NLMT cần CN liên hệ và tư vấn lại</t>
+        </is>
+      </c>
+      <c r="S6" s="2">
+        <v>46205.70486111111</v>
+      </c>
+      <c r="T6" s="2">
+        <v>46206.70486111111</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Đóng</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Nguyễn Thị Nhị</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>239095</t>
+        </is>
+      </c>
+      <c r="Y6" s="2">
+        <v>46205.72083333333</v>
+      </c>
+      <c r="Z6" s="3">
+        <v>46205</v>
+      </c>
+      <c r="AA6">
+        <v>1</v>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>IOC</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>P.KDNLMT</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>N1 - Truongdv17, Congnd15</t>
+        </is>
+      </c>
+      <c r="AE6">
+        <v>0.08305555555555555</v>
+      </c>
+      <c r="AF6">
+        <v>0.003460648148148148</v>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="AH6">
+        <v>23.61638888888889</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>KV3</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>VLG</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_VLG_1659623</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>Cao Thanh Tùng</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>0913847139</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Số 40C, Hoàng Lam khu phố 13</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Nhân viên nội bộ VCC</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>Hỗ trợ</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Cài đặt hệ thống (APP/Mật khẩu)</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>1. CN báo sự cố cho KH
 2. KH cần CN hỗ trợ Up Firmware cho HT NLMT do Ăc quy lưu trữ của KH đang chưa nhận sạc
 3. KH cần CN đến kiểm tra và hỗ trợ sớm</t>
         </is>
       </c>
-      <c r="S2" s="2">
+      <c r="S7" s="2">
         <v>46204.72152777778</v>
       </c>
-      <c r="T2" s="2">
+      <c r="T7" s="2">
         <v>46205.72152777778</v>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Đóng</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
         <is>
           <t>Phạm Quốc Duy</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>447517</t>
         </is>
       </c>
-      <c r="Y2" s="2">
+      <c r="Y7" s="2">
         <v>46204.73819444445</v>
       </c>
-      <c r="Z2" s="3">
+      <c r="Z7" s="3">
         <v>46204</v>
       </c>
-      <c r="AA2">
-        <v>1</v>
-      </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AA7">
+        <v>2</v>
+      </c>
+      <c r="AB7" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>N3 - Thikd, Ducnt84</t>
         </is>
       </c>
-      <c r="AE2">
+      <c r="AE7">
         <v>0</v>
       </c>
-      <c r="AF2">
+      <c r="AF7">
         <v>0</v>
       </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="AH2">
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="AH7">
         <v>23.59972222222222</v>
       </c>
-      <c r="AI2" t="inlineStr">
+      <c r="AI7" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>KV3</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>TNH</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>KHCN_NLMT_LAN_0239382</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>Member</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>Trương Phú Quý</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>0973878004</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>24a Nguyễn Văn Chánh KP Xuân Hoà 2</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>Hỗ trợ</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Cài đặt hệ thống (APP/Mật khẩu)</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>1. KH chưa báo CN (đã liên hệ với nhân sự phụ trách lắp đặt nhưng chuyển công tác)
 2. KH phản ánh và yêu cầu: KH đổi điện thoại, ko nhớ tên app nên cần hỗ trợ cài app NLMT theo dõi hiệu suất</t>
         </is>
       </c>
-      <c r="S3" s="2">
+      <c r="S8" s="2">
         <v>46204.47083333333</v>
       </c>
-      <c r="T3" s="2">
+      <c r="T8" s="2">
         <v>46205.71180555555</v>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Đóng</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
         <is>
           <t>Trần Văn Phi Anh</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>464495</t>
         </is>
       </c>
-      <c r="Y3" s="2">
+      <c r="Y8" s="2">
         <v>46204.60416666667</v>
       </c>
-      <c r="Z3" s="3">
+      <c r="Z8" s="3">
         <v>46204</v>
       </c>
-      <c r="AA3">
-        <v>1</v>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AA8">
+        <v>2</v>
+      </c>
+      <c r="AB8" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>N3 - Thikd, Ducnt84</t>
         </is>
       </c>
-      <c r="AE3">
+      <c r="AE8">
         <v>3.2</v>
       </c>
-      <c r="AF3">
+      <c r="AF8">
         <v>0.1333333333333333</v>
       </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="AH3">
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="AH8">
         <v>26.58305555555555</v>
       </c>
-      <c r="AI3" t="inlineStr">
+      <c r="AI8" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>NAN</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>VCC_YCTX_NAN_1782697575907</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>Trần Văn Tam</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>0964485912</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>tương dương</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Trước bán</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>Hỗ trợ</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Tư vấn sản phẩm/dịch vụ</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>YCTX NLMT lịch hẹn 30/06 KH chưa thấy có KT liên hệ tư vấn khảo sát</t>
         </is>
       </c>
-      <c r="S4" s="2">
+      <c r="S9" s="2">
         <v>46204.40347222222</v>
       </c>
-      <c r="T4" s="2">
+      <c r="T9" s="2">
         <v>46205.40347222222</v>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>Đóng</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
         <is>
           <t>Trần Trọng Hiếu</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>069197</t>
         </is>
       </c>
-      <c r="Y4" s="2">
+      <c r="Y9" s="2">
         <v>46204.76319444444</v>
       </c>
-      <c r="Z4" s="3">
+      <c r="Z9" s="3">
         <v>46204</v>
       </c>
-      <c r="AA4">
-        <v>1</v>
-      </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AA9">
+        <v>2</v>
+      </c>
+      <c r="AB9" t="inlineStr">
         <is>
           <t>IOC</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>P.KDNLMT</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>N2 - Tienvt16, Anhnt631</t>
         </is>
       </c>
-      <c r="AE4">
+      <c r="AE9">
         <v>7.316388888888889</v>
       </c>
-      <c r="AF4">
+      <c r="AF9">
         <v>0.304849537037037</v>
       </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="AH4">
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="AH9">
         <v>15.36638888888889</v>
       </c>
-      <c r="AI4" t="inlineStr">
+      <c r="AI9" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>KV3</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>CTO</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>VCC_YCTX_CTO_1782465732430</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>Trần Trường Thành</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>0939464545</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Hòa An</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Trước bán</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>Hỗ trợ</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Tư vấn sản phẩm/dịch vụ</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>YCTX NLMT lịch hẹn 30/6 KH chưa được liên hệ tư vấn NLMT</t>
         </is>
       </c>
-      <c r="S5" s="2">
+      <c r="S10" s="2">
         <v>46204.38611111111</v>
       </c>
-      <c r="T5" s="2">
+      <c r="T10" s="2">
         <v>46205.38611111111</v>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>Đóng</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
         <is>
           <t>phạm đức trí</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>489704</t>
         </is>
       </c>
-      <c r="Y5" s="2">
+      <c r="Y10" s="2">
         <v>46204.40277777778</v>
       </c>
-      <c r="Z5" s="3">
+      <c r="Z10" s="3">
         <v>46204</v>
       </c>
-      <c r="AA5">
-        <v>1</v>
-      </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AA10">
+        <v>2</v>
+      </c>
+      <c r="AB10" t="inlineStr">
         <is>
           <t>IOC</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>P.KDNLMT</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>N3 - Thikd, Ducnt84</t>
         </is>
       </c>
-      <c r="AE5">
+      <c r="AE10">
         <v>0.4</v>
       </c>
-      <c r="AF5">
+      <c r="AF10">
         <v>0.01666666666666667</v>
       </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="AH5">
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="AH10">
         <v>23.59972222222222</v>
       </c>
-      <c r="AI5" t="inlineStr">
+      <c r="AI10" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>KV3</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>AGG</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_AGG_1625605</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>Phạm Thị Thu Thủy</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>0984767917</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Ấp Vĩnh Lộc</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Nhân viên nội bộ VCC</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>CN 0384989610 báo sự cố hộ KH
 1.	KH phản ánh: cúp điện nlmt
 2.	KH yêu cầu: KT qua kiểm tra, xử lý tình trạng này</t>
         </is>
       </c>
-      <c r="S6" s="2">
+      <c r="S11" s="2">
         <v>46204.38055555556</v>
       </c>
-      <c r="T6" s="2">
+      <c r="T11" s="2">
         <v>46205.38055555556</v>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>Đóng</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
         <is>
           <t>Nguyễn Nhật Hiếu</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>442802</t>
         </is>
       </c>
-      <c r="Y6" s="2">
+      <c r="Y11" s="2">
         <v>46204.38611111111</v>
       </c>
-      <c r="Z6" s="3">
+      <c r="Z11" s="3">
         <v>46204</v>
       </c>
-      <c r="AA6">
-        <v>1</v>
-      </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AA11">
+        <v>2</v>
+      </c>
+      <c r="AB11" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AD11" t="inlineStr">
         <is>
           <t>N3 - Thikd, Ducnt84</t>
         </is>
       </c>
-      <c r="AE6">
+      <c r="AE11">
         <v>0.1333333333333333</v>
       </c>
-      <c r="AF6">
+      <c r="AF11">
         <v>0.005555555555555556</v>
       </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="AH6">
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="AH11">
         <v>23.86638888888889</v>
       </c>
-      <c r="AI6" t="inlineStr">
+      <c r="AI11" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>KV1</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>NBH</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Hệ thống NLMT</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>060125-GPTH/HĐMB-2025/CNCTNDH-HOANGDUNG</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>B2B</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Khách hàng doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH DỆT - MAY HOÀNG DŨNG</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0905606661</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>KCN Hòa Xá</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Sự cố</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Không kết nối được app/Wifi và không theo dõi được hiệu suất</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>1. KH chưa báo CN 
+2. KH phản ánh: ko kết nối được hệ thống nlmt, báo offline KH theo dõi trên app thì thấy con đo meter nlmt trong 1 khu đang ko đo được nlmt sản sinh ra.
+3. KH yêu cầu: KT qua kiểm tra, khắc phục tình trạng này</t>
+        </is>
+      </c>
+      <c r="S12" s="2">
+        <v>46204.36319444445</v>
+      </c>
+      <c r="T12" s="2">
+        <v>46206.6875</v>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Đóng</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Bùi Quốc Mạnh</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>292174</t>
+        </is>
+      </c>
+      <c r="Y12" s="2">
+        <v>46205.61527777778</v>
+      </c>
+      <c r="Z12" s="3">
+        <v>46204</v>
+      </c>
+      <c r="AA12">
+        <v>2</v>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>IOC</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>P.Triển khai</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>N1 - Truongdv17, Congnd15</t>
+        </is>
+      </c>
+      <c r="AE12">
+        <v>30.04972222222222</v>
+      </c>
+      <c r="AF12">
+        <v>1.252071759259259</v>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="AH12">
+        <v>25.73305555555556</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>KV3</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Hệ thống NLMT</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_DNI_1669491</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Diamond</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Hoàng Công Trình</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0972421575</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>ấp 4</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Sự cố</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Kh chưa báo CN
+KH báo sự cố hệ thống NLMT không nhận điện không sản xuất ra điện pin  hiển thị chế độ chờ hiện không hoạt động 
+Yêu cầu CN cho KT qua ktra cho KH..</t>
+        </is>
+      </c>
+      <c r="S13" s="2">
+        <v>46204.35069444445</v>
+      </c>
+      <c r="T13" s="2">
+        <v>46205.35069444445</v>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Đóng</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ngô Minh Hoàng</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>119059</t>
+        </is>
+      </c>
+      <c r="Y13" s="2">
+        <v>46205.34166666667</v>
+      </c>
+      <c r="Z13" s="3">
+        <v>46204</v>
+      </c>
+      <c r="AA13">
+        <v>2</v>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>N3 - Thikd, Ducnt84</t>
+        </is>
+      </c>
+      <c r="AE13">
+        <v>23.78305555555556</v>
+      </c>
+      <c r="AF13">
+        <v>0.9909606481481482</v>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="AH13">
+        <v>0.2166666666666667</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>KV3</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
         <is>
           <t>HCM</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>Tấm pin NLMT</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>041001-KD/HĐMB-2021/BDG-VANCHUONG</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>Lê Văn Chương</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>0907344470</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>Phường Lái Thiêu</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>Zalo</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>Tấm pin bị rò rỉ/ Lỗi</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>1. KH chưa liên hệ CN
 2. Hiện một tấm pin của KH đang gặp sự cố
 3. KH cần CN hỗ trợ đến kiểm tra sớm</t>
         </is>
       </c>
-      <c r="S7" s="2">
+      <c r="S14" s="2">
         <v>46204.33333333333</v>
       </c>
-      <c r="T7" s="2">
+      <c r="T14" s="2">
         <v>46205.375</v>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Đóng</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Phạm Đình Tuân</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>442050</t>
+        </is>
+      </c>
+      <c r="Y14" s="2">
+        <v>46205.31597222222</v>
+      </c>
+      <c r="Z14" s="3">
+        <v>46204</v>
+      </c>
+      <c r="AA14">
+        <v>2</v>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>IOC</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>P.Triển khai</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>N3 - Thikd, Ducnt84</t>
+        </is>
+      </c>
+      <c r="AE14">
+        <v>23.58305555555556</v>
+      </c>
+      <c r="AF14">
+        <v>0.9826273148148149</v>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="AH14">
+        <v>1.416666666666667</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>KV2</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>LDG</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Hệ thống NLMT</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_LDG_1677590</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Diamond</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Nguyễn Tấn Cường</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0932112328</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Trại Mát</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Life Care</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Sự cố</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>1. KH chưa liên hệ CN
+2. KH tham khảo hộ gia đình khác được KH giới thiệu lắp hệ NLMT cùng công suất, số lượng tấm pin, và thiết bị biến tần khi đạt công suất tối đa có thể đặt 9.8-&gt;10Kw diện NLMT, trong khi HT NLMT của KH đạt hiệu suát tối đâ chỉ tới 8.5KW, dù ngày nắng to cũng không sạc đầy Ắc quy lưu trữ.
+3. KH cần CN đến kiểm tra giúp cho KH</t>
+        </is>
+      </c>
+      <c r="S15" s="2">
+        <v>46205.34236111111</v>
+      </c>
+      <c r="T15" s="2">
+        <v>46206.34236111111</v>
+      </c>
+      <c r="U15" t="inlineStr">
         <is>
           <t>Hoàn thành</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Phạm Đình Tuân</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>442050</t>
-        </is>
-      </c>
-      <c r="Y7" s="2">
-        <v>46205.31597222222</v>
-      </c>
-      <c r="Z7" s="3">
-        <v>46204</v>
-      </c>
-      <c r="AA7">
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Nguyễn Văn Toàn</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>197916</t>
+        </is>
+      </c>
+      <c r="Y15" s="2">
+        <v>46205.63125</v>
+      </c>
+      <c r="Z15" s="3">
+        <v>46205</v>
+      </c>
+      <c r="AA15">
         <v>1</v>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>IOC</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>P.Triển khai</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
         <is>
           <t>N3 - Thikd, Ducnt84</t>
         </is>
       </c>
-      <c r="AE7">
-        <v>23.58305555555556</v>
-      </c>
-      <c r="AF7">
-        <v>0.9826273148148149</v>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="AH7">
-        <v>1.416666666666667</v>
-      </c>
-      <c r="AI7" t="inlineStr">
+      <c r="AE15">
+        <v>6.933333333333334</v>
+      </c>
+      <c r="AF15">
+        <v>0.2888888888888889</v>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="AH15">
+        <v>17.06638888888889</v>
+      </c>
+      <c r="AI15" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>HNI</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_HNI_1695850</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>Member</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>Nguyễn Mạnh Tùng</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>0961955569</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>Số 63 ngõ 101 Thanh Nhàn</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>Hỗ trợ</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>Thủ tục/giấy tờ/ Hóa đơn/ Hồ sơ lắp đặt</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="R16" t="inlineStr">
         <is>
           <t>1. KH đã liên hệ tới CN
 2. HT NLMT của KH đã hoàn thiện lắp đặt và đưa vào sử dụng tuy nhiên chi nhánh chưa cung cấp cho KH các chứng từ:
@@ -1597,326 +2881,326 @@
 3. KH cần chi nhánh liên hệ, hướng dẫn KH sử dụng , cung cấp các chứng từ liên quan và có đề xuất hướng xử lý về việc chậm hợp đồng cho KH</t>
         </is>
       </c>
-      <c r="S8" s="2">
+      <c r="S16" s="2">
         <v>46204.33333333333</v>
       </c>
-      <c r="T8" s="2">
+      <c r="T16" s="2">
         <v>46205.375</v>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>Hoàn thành</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
         <is>
           <t>Ngô Thị Thu Hường</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>842314</t>
         </is>
       </c>
-      <c r="Y8" s="2">
+      <c r="Y16" s="2">
         <v>46204.74166666667</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="Z16" s="3">
         <v>46204</v>
       </c>
-      <c r="AA8">
-        <v>1</v>
-      </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AA16">
+        <v>2</v>
+      </c>
+      <c r="AB16" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AC16" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AD16" t="inlineStr">
         <is>
           <t>N1 - Truongdv17, Congnd15</t>
         </is>
       </c>
-      <c r="AE8">
+      <c r="AE16">
         <v>8.999722222222223</v>
       </c>
-      <c r="AF8">
+      <c r="AF16">
         <v>0.374988425925926</v>
       </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="AH8">
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="AH16">
         <v>15.19972222222222</v>
       </c>
-      <c r="AI8" t="inlineStr">
+      <c r="AI16" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>NAN</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_NAN_1686618</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>Nguyễn Đức Tài</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>0974213814</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>Xóm 16 Phúc Lộc</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t>1. KH chưa liên hệ CN
 2. HT NLMT của KH bị giảm hiệu suất nhiều thời gian gần đây,  hiện tại sản xuất được 2,9Kw, so sánh với hộ gia đình khác cùng lắp HT NLMT sản xuất được 4,3Kw
 3. KH cần CN đến hỗ trợ kiểm tra giúp</t>
         </is>
       </c>
-      <c r="S9" s="2">
+      <c r="S17" s="2">
         <v>46203.60555555555</v>
       </c>
-      <c r="T9" s="2">
+      <c r="T17" s="2">
         <v>46204.60555555555</v>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>Đóng</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
         <is>
           <t>Nguyễn Kim Sơn</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>490042</t>
         </is>
       </c>
-      <c r="Y9" s="2">
+      <c r="Y17" s="2">
         <v>46204.40833333333</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="Z17" s="3">
         <v>46203</v>
       </c>
-      <c r="AA9">
-        <v>2</v>
-      </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AA17">
+        <v>3</v>
+      </c>
+      <c r="AB17" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AC17" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AD17" t="inlineStr">
         <is>
           <t>N2 - Tienvt16, Anhnt631</t>
         </is>
       </c>
-      <c r="AE9">
+      <c r="AE17">
         <v>19.26638888888889</v>
       </c>
-      <c r="AF9">
+      <c r="AF17">
         <v>0.8027662037037038</v>
       </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="AH9">
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="AH17">
         <v>4.733333333333333</v>
       </c>
-      <c r="AI9" t="inlineStr">
+      <c r="AI17" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>KV3</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>VLG</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_VLG_1679600</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>Nguyễn Tài Năng</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>0916001008</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>ấp 1 xã bình chánh hcm</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>Life Care</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>Hỗ trợ</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>Thủ tục/giấy tờ/ Hóa đơn/ Hồ sơ lắp đặt</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="R18" t="inlineStr">
         <is>
           <t>KH đã báo KT nhưng chưa được hỗ trợ 
  KH phản ánh Viettel  Vinh Long vẫn không cung cấp tài liệu hay bất hoá đơn chứng từ cho khách hàng sau khi lắp bình lưu trữ và biến tần.
@@ -1924,2273 +3208,3724 @@
 Yêu cầu CN cho KT hỗ trợ KH</t>
         </is>
       </c>
-      <c r="S10" s="2">
+      <c r="S18" s="2">
         <v>46203.60486111111</v>
       </c>
-      <c r="T10" s="2">
+      <c r="T18" s="2">
         <v>46204.60486111111</v>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>Hoàn thành</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
         <is>
           <t>Lê Minh Tường</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>465829</t>
         </is>
       </c>
-      <c r="Y10" s="2">
+      <c r="Y18" s="2">
         <v>46204.56944444445</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="Z18" s="3">
         <v>46203</v>
       </c>
-      <c r="AA10">
-        <v>2</v>
-      </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AA18">
+        <v>3</v>
+      </c>
+      <c r="AB18" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AC18" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AD18" t="inlineStr">
         <is>
           <t>N3 - Thikd, Ducnt84</t>
         </is>
       </c>
-      <c r="AE10">
+      <c r="AE18">
         <v>23.14972222222222</v>
       </c>
-      <c r="AF10">
+      <c r="AF18">
         <v>0.9645717592592593</v>
       </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="AH10">
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="AH18">
         <v>0.85</v>
       </c>
-      <c r="AI10" t="inlineStr">
+      <c r="AI18" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>KV1</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>NAN</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>M&amp;E</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Máy giặt</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_NAN_1681265</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Nguyễn Văn Thắng</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0333111015</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Khối 1</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Nhân viên nội bộ VCC</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Sự cố</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>1.KH là nhân viên nội bộ VCC
+2. Thiết bị máy giặt của KH gặp sự cố giặt được nhưng không vắt được
+Địa chỉ đặt thiết bị : Thôn Long Sơn 10 Xã Yên Xuân, Tỉnh Nghệ An
+3. KH cần CN hỗ trợ kiểm tra và khắc phục sớm</t>
+        </is>
+      </c>
+      <c r="S19" s="2">
+        <v>46205.33333333333</v>
+      </c>
+      <c r="T19" s="2">
+        <v>46206.375</v>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Hoàn thành</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Nguyễn Đình Thương</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>268414</t>
+        </is>
+      </c>
+      <c r="Y19" s="2">
+        <v>46205.67569444445</v>
+      </c>
+      <c r="Z19" s="3">
+        <v>46205</v>
+      </c>
+      <c r="AA19">
+        <v>1</v>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>P.Triển khai</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>N2 - Tienvt16, Anhnt631</t>
+        </is>
+      </c>
+      <c r="AE19">
+        <v>8.216666666666667</v>
+      </c>
+      <c r="AF19">
+        <v>0.3423611111111111</v>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="AH19">
+        <v>16.78305555555556</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>KV3</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>DNI</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>DVKT</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>Home Service</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>Bảo dưỡng Điều hòa treo tường (9.000BTU ÷ 12.000 BTU)</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>VCC_HS_DNI_1778210462306</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>Member</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>Anhh Thanh</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>0365728728</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>22 đường c2 kp phước bình, Phường Bình Phước, Tỉnh Đồng Nai</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>Hỗ trợ</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>Khác</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="R20" t="inlineStr">
         <is>
           <t>1. KH phản ánh: Đơn hàng của KH làm xong từ 9/5 sau đó 1 máy lạnh ko đóng được và có liên hệ với a Ngọc trong thời gian bảo hành, KH có kb zalo để trao đổi. CN cũng đã đến kiểm tra nhưng chưa khắc phục được tình trạng giờ 2 cái bị hư còn 1 cái bị chảy nước.
 2. KH yêu cầu: Chiều mai 3h 2/3 đến kiểm tra xử lý tình trạng này. KH có sẵn thông tin hình ảnh nhắn tin với a Ngọ trong zalo đến làm việc KH sẽ cung cấp</t>
         </is>
       </c>
-      <c r="S11" s="2">
+      <c r="S20" s="2">
         <v>46204.62569444445</v>
       </c>
-      <c r="T11" s="2">
+      <c r="T20" s="2">
         <v>46205.62569444445</v>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>Hoàn thành</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
         <is>
           <t>Nguyễn Văn Ngọ</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>410194</t>
         </is>
       </c>
-      <c r="Y11" s="2">
+      <c r="Y20" s="2">
         <v>46204.87152777778</v>
       </c>
-      <c r="Z11" s="3">
+      <c r="Z20" s="3">
         <v>46204</v>
       </c>
-      <c r="AA11">
-        <v>1</v>
-      </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AA20">
+        <v>2</v>
+      </c>
+      <c r="AB20" t="inlineStr">
         <is>
           <t>HS</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AC20" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AD20" t="inlineStr">
         <is>
           <t>N3 - Thikd, Ducnt84</t>
         </is>
       </c>
-      <c r="AE11">
+      <c r="AE20">
         <v>1.983055555555556</v>
       </c>
-      <c r="AF11">
+      <c r="AF20">
         <v>0.08262731481481482</v>
       </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="AH11">
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="AH20">
         <v>18.09972222222222</v>
       </c>
-      <c r="AI11" t="inlineStr">
+      <c r="AI20" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>KV2</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>GLI</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Hệ thống NLMT</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_BDH_1224352</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Member</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Lê Tấn Dũng</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0985979282</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Đại An,Xã Cát Nhơn</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Zalo</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Sự cố</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>1. KH đã báo CN sự cố trước TT_1782705022714
+2. KH phản ánh: 1 tấm pin bị bạc màu CN có hẹn là đầu tháng qua kiểm tra nhưng đến 1/7 ko thấy có thông tin hay qua kiểm tra gì.
+3. KH yêu cầu: KT qua kiểm tra, xử lý tình trạng này.</t>
+        </is>
+      </c>
+      <c r="S21" s="2">
+        <v>46204.59444444445</v>
+      </c>
+      <c r="T21" s="2">
+        <v>46205.59444444445</v>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Đóng</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Nguyễn Hồng Vũ</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>461991</t>
+        </is>
+      </c>
+      <c r="Y21" s="2">
+        <v>46205.50277777778</v>
+      </c>
+      <c r="Z21" s="3">
+        <v>46204</v>
+      </c>
+      <c r="AA21">
+        <v>2</v>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>N3 - Thikd, Ducnt84</t>
+        </is>
+      </c>
+      <c r="AE21">
+        <v>21.79972222222222</v>
+      </c>
+      <c r="AF21">
+        <v>0.9083217592592593</v>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="AH21">
+        <v>2.2</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>HNI</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_HNI_1701343</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>Nguyễn Hoàng Quân</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>0973624210</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>1/4 Quang Trung</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>Trước bán</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="R22" t="inlineStr">
         <is>
           <t>hệ thống lỗi không hoạt động</t>
         </is>
       </c>
-      <c r="S12" s="2">
+      <c r="S22" s="2">
         <v>46204.47291666667</v>
       </c>
-      <c r="T12" s="2">
+      <c r="T22" s="2">
         <v>46205.47291666667</v>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Đóng</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Phạm Văn Tình</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>463011</t>
+        </is>
+      </c>
+      <c r="Y22" s="2">
+        <v>46204.66388888888</v>
+      </c>
+      <c r="Z22" s="3">
+        <v>46204</v>
+      </c>
+      <c r="AA22">
+        <v>2</v>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>P.KDNLMT</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>N1 - Truongdv17, Congnd15</t>
+        </is>
+      </c>
+      <c r="AE22">
+        <v>4.583333333333333</v>
+      </c>
+      <c r="AF22">
+        <v>0.1909722222222222</v>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="AH22">
+        <v>19.41638888888889</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>KV1</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>BNH</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Hệ thống NLMT</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_BNH_1612190</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Nguyễn Thạc Công</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0399676299</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Trung Hòa, Phường Đình Bảng</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Sự cố</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>KH phản ánh pin lưu không hoạt động trên màn hình báo lỗi  màn hình có chữ  ALAN màu đỏ, Kh muốn KT liên hệ và đến kiểm tra cho KH</t>
+        </is>
+      </c>
+      <c r="S23" s="2">
+        <v>46204.3875</v>
+      </c>
+      <c r="T23" s="2">
+        <v>46208.5</v>
+      </c>
+      <c r="U23" t="inlineStr">
         <is>
           <t>Hoàn thành</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>Phạm Văn Tình</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>463011</t>
-        </is>
-      </c>
-      <c r="Y12" s="2">
-        <v>46204.66388888888</v>
-      </c>
-      <c r="Z12" s="3">
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Nguyễn Thế Hưng</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>464101</t>
+        </is>
+      </c>
+      <c r="Y23" s="2">
+        <v>46205.44166666667</v>
+      </c>
+      <c r="Z23" s="3">
         <v>46204</v>
       </c>
-      <c r="AA12">
-        <v>1</v>
-      </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AA23">
+        <v>2</v>
+      </c>
+      <c r="AB23" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>P.KDNLMT</t>
-        </is>
-      </c>
-      <c r="AD12" t="inlineStr">
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
         <is>
           <t>N1 - Truongdv17, Congnd15</t>
         </is>
       </c>
-      <c r="AE12">
-        <v>4.583333333333333</v>
-      </c>
-      <c r="AF12">
-        <v>0.1909722222222222</v>
-      </c>
-      <c r="AG12" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="AH12">
-        <v>19.41638888888889</v>
-      </c>
-      <c r="AI12" t="inlineStr">
+      <c r="AE23">
+        <v>25.29972222222222</v>
+      </c>
+      <c r="AF23">
+        <v>1.054155092592593</v>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="AH23">
+        <v>37.39944444444444</v>
+      </c>
+      <c r="AI23" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>HYN</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_HYN_1699601</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>Member</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>Nguyễn Văn Thuần</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>0987622153</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>Thôn Đào Dương</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>Happycall</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="Q24" t="inlineStr">
         <is>
           <t>Lắp đặt sai quy cách, thiếu vật tư, thiết bị, phụ kiện đi kèm</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="R24" t="inlineStr">
         <is>
           <t>1. KH  đã báo KT CN
 2. Cục biến tần lắp chưa chuẩn, KT đã đến hỗ trợ cài đặt lại nhưng chưa xử lí triệt để.
 3. Yêu cầu CN hỗ trợ KH</t>
         </is>
       </c>
-      <c r="S13" s="2">
+      <c r="S24" s="2">
         <v>46204.36458333333</v>
       </c>
-      <c r="T13" s="2">
+      <c r="T24" s="2">
         <v>46205.36458333333</v>
       </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>Hoàn thành</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Đóng</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
         <is>
           <t>Đỗ Đức Huỳnh</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>436625</t>
         </is>
       </c>
-      <c r="Y13" s="2">
+      <c r="Y24" s="2">
         <v>46204.46736111111</v>
       </c>
-      <c r="Z13" s="3">
+      <c r="Z24" s="3">
         <v>46204</v>
       </c>
-      <c r="AA13">
-        <v>1</v>
-      </c>
-      <c r="AB13" t="inlineStr">
+      <c r="AA24">
+        <v>2</v>
+      </c>
+      <c r="AB24" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
+      <c r="AC24" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AD13" t="inlineStr">
+      <c r="AD24" t="inlineStr">
         <is>
           <t>N1 - Truongdv17, Congnd15</t>
         </is>
       </c>
-      <c r="AE13">
+      <c r="AE24">
         <v>2.466666666666667</v>
       </c>
-      <c r="AF13">
+      <c r="AF24">
         <v>0.1027777777777778</v>
       </c>
-      <c r="AG13" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="AH13">
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="AH24">
         <v>21.53305555555556</v>
       </c>
-      <c r="AI13" t="inlineStr">
+      <c r="AI24" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>KV3</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>DTP</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_DTP_1619705</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>Nguyễn Văn Ly</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>0977749451</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>Ấp Mỹ An A</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>Hot</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="Q25" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="R25" t="inlineStr">
         <is>
           <t>Kh đã báo KT
 KH báo sự cố NLMT biến tần không nhận điện, chỉ có dùng điện NLMT 
 Yêu cầu CN cho KT qua ktra cho KH..</t>
         </is>
       </c>
-      <c r="S14" s="2">
+      <c r="S25" s="2">
         <v>46204.34027777778</v>
       </c>
-      <c r="T14" s="2">
+      <c r="T25" s="2">
         <v>46205.34027777778</v>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="U25" t="inlineStr">
         <is>
           <t>Hoàn thành</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
         <is>
           <t>Lê Văn Lanh</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>075650</t>
         </is>
       </c>
-      <c r="Y14" s="2">
+      <c r="Y25" s="2">
         <v>46204.81875</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="Z25" s="3">
         <v>46204</v>
       </c>
-      <c r="AA14">
-        <v>1</v>
-      </c>
-      <c r="AB14" t="inlineStr">
+      <c r="AA25">
+        <v>2</v>
+      </c>
+      <c r="AB25" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
+      <c r="AC25" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AD14" t="inlineStr">
+      <c r="AD25" t="inlineStr">
         <is>
           <t>N3 - Thikd, Ducnt84</t>
         </is>
       </c>
-      <c r="AE14">
+      <c r="AE25">
         <v>8.833055555555555</v>
       </c>
-      <c r="AF14">
+      <c r="AF25">
         <v>0.3680439814814815</v>
       </c>
-      <c r="AG14" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="AH14">
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="AH25">
         <v>12.51638888888889</v>
       </c>
-      <c r="AI14" t="inlineStr">
+      <c r="AI25" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>KV2</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>DNG</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Hệ thống NLMT</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_DNG_1698222</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Diamond</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Trần Duy Hưng</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0775518365</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Thôn 1</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Sự cố</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>KH phản ánh CT bị lỗi chạy không ổn định, bị chập chờn, các buổi trong ngày điện NLMT vẫn còn nhưng vẫn lấy điện lưới, khoảng 2 tuần nay
+Yêu cầu quản lí điều kĩ thuật liên hệ và xuống kiểm tra cho KH</t>
+        </is>
+      </c>
+      <c r="S26" s="2">
+        <v>46203.57222222222</v>
+      </c>
+      <c r="T26" s="2">
+        <v>46206.42361111111</v>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Đóng</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Phan Thế Tỉnh</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>069542</t>
+        </is>
+      </c>
+      <c r="Y26" s="2">
+        <v>46205.46597222222</v>
+      </c>
+      <c r="Z26" s="3">
+        <v>46203</v>
+      </c>
+      <c r="AA26">
+        <v>3</v>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>N2 - Tienvt16, Anhnt631</t>
+        </is>
+      </c>
+      <c r="AE26">
+        <v>45.44944444444444</v>
+      </c>
+      <c r="AF26">
+        <v>1.893726851851852</v>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="AH26">
+        <v>22.98305555555556</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>HNI</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>DVKT</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>Home Service</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>Bảo dưỡng Điều hòa treo tường (9.000BTU ÷ 12.000 BTU)</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>VCC_HS_HNI_1782617276241</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>Member</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>Binh An</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>0979024582</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>Đội 8 ngọc hồi thanh trì hà nội, gần nhà văn hóa, Xã Ngọc Hồi, Thành phố Hà Nội</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="Q27" t="inlineStr">
         <is>
           <t>Sau bảo dưỡng thiết bị vẫn bẩn</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="R27" t="inlineStr">
         <is>
           <t>Đơn hàng 28/6 vẫn đang trong hạn bảo hành
 1. KH phản ánh: vẫn còn mùi ở thiết bị
 2. KH yêu cầu: KT qua kiểm tra lại</t>
         </is>
       </c>
-      <c r="S15" s="2">
+      <c r="S27" s="2">
         <v>46202.45069444444</v>
       </c>
-      <c r="T15" s="2">
+      <c r="T27" s="2">
         <v>46204.83333333333</v>
       </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Hoàn thành</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Đóng</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
         <is>
           <t>Lê Duy Tuấn</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
+      <c r="X27" t="inlineStr">
         <is>
           <t>293859</t>
         </is>
       </c>
-      <c r="Y15" s="2">
+      <c r="Y27" s="2">
         <v>46204.69513888888</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="Z27" s="3">
         <v>46202</v>
       </c>
-      <c r="AA15">
-        <v>3</v>
-      </c>
-      <c r="AB15" t="inlineStr">
+      <c r="AA27">
+        <v>4</v>
+      </c>
+      <c r="AB27" t="inlineStr">
         <is>
           <t>HS</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
+      <c r="AC27" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AD15" t="inlineStr">
+      <c r="AD27" t="inlineStr">
         <is>
           <t>N1 - Truongdv17, Congnd15</t>
         </is>
       </c>
-      <c r="AE15">
+      <c r="AE27">
         <v>53.86611111111111</v>
       </c>
-      <c r="AF15">
+      <c r="AF27">
         <v>2.244421296296296</v>
       </c>
-      <c r="AG15" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="AH15">
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="AH27">
         <v>3.316666666666667</v>
       </c>
-      <c r="AI15" t="inlineStr">
+      <c r="AI27" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>HPG</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_HPG_1698592</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>Vũ Thanh Hướng</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>0384276150</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>số 56 Tổ dân phố Ngọ Dương 5</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>Happycall</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="P28" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="Q28" t="inlineStr">
         <is>
           <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="R28" t="inlineStr">
         <is>
           <t>1. KH đã báo CN
 2. KH khi sửa dụng vào mùa nắng nong thì tiền điện giảm không nhiều chỉ giảm chưa đên 700.000, hệ thống pin chỉ thu dược tầm 60-70% vào mùa nắng trong khi KH lắp hệ 12.4KWP
 3. KH muốn CN hỗ trợ và khảo sát lại xem có phải tăng tấm pin để cải thiện không</t>
         </is>
       </c>
-      <c r="S16" s="2">
+      <c r="S28" s="2">
         <v>46202.425</v>
       </c>
-      <c r="T16" s="2">
+      <c r="T28" s="2">
         <v>46204.77083333333</v>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="U28" t="inlineStr">
         <is>
           <t>Đóng</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
         <is>
           <t>Phạm Thế Hùng</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
+      <c r="X28" t="inlineStr">
         <is>
           <t>413728</t>
         </is>
       </c>
-      <c r="Y16" s="2">
+      <c r="Y28" s="2">
         <v>46204.72916666667</v>
       </c>
-      <c r="Z16" s="3">
+      <c r="Z28" s="3">
         <v>46202</v>
       </c>
-      <c r="AA16">
-        <v>3</v>
-      </c>
-      <c r="AB16" t="inlineStr">
+      <c r="AA28">
+        <v>4</v>
+      </c>
+      <c r="AB28" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
+      <c r="AC28" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AD16" t="inlineStr">
+      <c r="AD28" t="inlineStr">
         <is>
           <t>N1 - Truongdv17, Congnd15</t>
         </is>
       </c>
-      <c r="AE16">
+      <c r="AE28">
         <v>54.79916666666666</v>
       </c>
-      <c r="AF16">
+      <c r="AF28">
         <v>2.283298611111111</v>
       </c>
-      <c r="AG16" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="AH16">
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="AH28">
         <v>1</v>
       </c>
-      <c r="AI16" t="inlineStr">
+      <c r="AI28" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>KV3</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>VLG</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_VLG_1699538</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>Nguyễn Thành Nam</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>0981847986</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>Ấp Đại An</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>Happycall</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="P29" t="inlineStr">
         <is>
           <t>Hỗ trợ</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="Q29" t="inlineStr">
         <is>
           <t>Thủ tục/giấy tờ/ Hóa đơn/ Hồ sơ lắp đặt</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="R29" t="inlineStr">
         <is>
           <t>1. KH đã báo CN
 2. KH muốn hoàn thiện hồ sơ để nộp điện lực vì bên điện lực đã đến kiểm tra, KH đã đưa giấy tờ nhưng bị sai mẫu 
 3. Yêu cầu CN hỗ trợ KH</t>
         </is>
       </c>
-      <c r="S17" s="2">
+      <c r="S29" s="2">
         <v>46203.39444444445</v>
       </c>
-      <c r="T17" s="2">
+      <c r="T29" s="2">
         <v>46204.39444444445</v>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="U29" t="inlineStr">
         <is>
           <t>Đóng</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
         <is>
           <t>Lê Phước Nhựt</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
+      <c r="X29" t="inlineStr">
         <is>
           <t>436203</t>
         </is>
       </c>
-      <c r="Y17" s="2">
+      <c r="Y29" s="2">
         <v>46204.33680555555</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="Z29" s="3">
         <v>46203</v>
       </c>
-      <c r="AA17">
-        <v>2</v>
-      </c>
-      <c r="AB17" t="inlineStr">
+      <c r="AA29">
+        <v>3</v>
+      </c>
+      <c r="AB29" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
+      <c r="AC29" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AD17" t="inlineStr">
+      <c r="AD29" t="inlineStr">
         <is>
           <t>N3 - Thikd, Ducnt84</t>
         </is>
       </c>
-      <c r="AE17">
+      <c r="AE29">
         <v>22.61638888888889</v>
       </c>
-      <c r="AF17">
+      <c r="AF29">
         <v>0.9423495370370371</v>
       </c>
-      <c r="AG17" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="AH17">
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="AH29">
         <v>1.383333333333333</v>
       </c>
-      <c r="AI17" t="inlineStr">
+      <c r="AI29" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>KV2</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>DNG</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Hệ thống NLMT</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>VCC_YCTX_DNG_1782352514072</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Lê Quốc Khánh</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>0905388543</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>an khê</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Trước bán</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Hỗ trợ</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>Tư vấn sản phẩm/dịch vụ</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>KH có YCTX NLMT cần chi nhánh liên hệ đến hỗ trợ tư vấn KH</t>
+        </is>
+      </c>
+      <c r="S30" s="2">
+        <v>46203.33333333333</v>
+      </c>
+      <c r="T30" s="2">
+        <v>46206.70833333333</v>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Đóng</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Trần Văn Tư</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>071636</t>
+        </is>
+      </c>
+      <c r="Y30" s="2">
+        <v>46205.41041666667</v>
+      </c>
+      <c r="Z30" s="3">
+        <v>46203</v>
+      </c>
+      <c r="AA30">
+        <v>3</v>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>IOC</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>P.KDNLMT</t>
+        </is>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>N2 - Tienvt16, Anhnt631</t>
+        </is>
+      </c>
+      <c r="AE30">
+        <v>49.84944444444444</v>
+      </c>
+      <c r="AF30">
+        <v>2.077060185185185</v>
+      </c>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="AH30">
+        <v>31.14972222222222</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>TNN</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_TNN_1621964</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>Phan Đình Tuệ</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>0912805116</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>quyết thắng</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>Hot</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Sự cố</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>Không kết nối được app/Wifi và không theo dõi được hiệu suất</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Bảo hành</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
         <is>
           <t>Kh chưa báo CN
 KH báo sự cố hệ thống NLMT đang không theo dõi được qua App, không báo thông số , hiện HT đang không sản sinh điện NLMT
 Yêu cầu CN cho KT qua ktra cho KH</t>
         </is>
       </c>
-      <c r="S18" s="2">
+      <c r="S31" s="2">
         <v>46202.35972222222</v>
       </c>
-      <c r="T18" s="2">
-        <v>46205.65277777778</v>
-      </c>
-      <c r="U18" t="inlineStr">
+      <c r="T31" s="2">
+        <v>46220.56527777778</v>
+      </c>
+      <c r="U31" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
         <is>
           <t>Nguyễn Văn Thao</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
+      <c r="X31" t="inlineStr">
         <is>
           <t>289758</t>
         </is>
       </c>
-      <c r="Y18" s="2">
+      <c r="Y31" s="2">
         <v>46205.3</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="Z31" s="3">
         <v>46202</v>
       </c>
-      <c r="AA18">
-        <v>3</v>
-      </c>
-      <c r="AB18" t="inlineStr">
+      <c r="AA31">
+        <v>4</v>
+      </c>
+      <c r="AB31" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
+      <c r="AC31" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AD18" t="inlineStr">
+      <c r="AD31" t="inlineStr">
         <is>
           <t>N1 - Truongdv17, Congnd15</t>
         </is>
       </c>
-      <c r="AE18">
+      <c r="AE31">
         <v>70.56583333333333</v>
       </c>
-      <c r="AF18">
+      <c r="AF31">
         <v>2.940243055555555</v>
       </c>
-      <c r="AG18" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="AH18">
-        <v>8.466666666666667</v>
-      </c>
-      <c r="AI18" t="inlineStr">
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="AH31">
+        <v>270.3636111111111</v>
+      </c>
+      <c r="AI31" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>HNI</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_HNI_1658523</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>Nguyễn Kim Trung</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>0961897878</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>Số nhà 46 ngõ 163 Đường Phạm Văn Đồng</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="P32" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="Q32" t="inlineStr">
         <is>
           <t>Không kết nối được app/Wifi và không theo dõi được hiệu suất</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="R32" t="inlineStr">
         <is>
           <t>1. KH chưa báo CN
 2. KH phản ánh: KH theo dõi trên app ko thấy có thông số hiệu suất
 3. KH yêu cầu: KT qua kiểm tra, hỗ trợ KH tình trạng này</t>
         </is>
       </c>
-      <c r="S19" s="2">
+      <c r="S32" s="2">
         <v>46202.42430555556</v>
       </c>
-      <c r="T19" s="2">
+      <c r="T32" s="2">
         <v>46208.36458333333</v>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="U32" t="inlineStr">
         <is>
           <t>Đóng</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
         <is>
           <t>Nguyễn Tiến Lực</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
+      <c r="X32" t="inlineStr">
         <is>
           <t>285897</t>
         </is>
       </c>
-      <c r="Y19" s="2">
+      <c r="Y32" s="2">
         <v>46204.40486111111</v>
       </c>
-      <c r="Z19" s="3">
+      <c r="Z32" s="3">
         <v>46202</v>
       </c>
-      <c r="AA19">
-        <v>3</v>
-      </c>
-      <c r="AB19" t="inlineStr">
+      <c r="AA32">
+        <v>4</v>
+      </c>
+      <c r="AB32" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
+      <c r="AC32" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AD19" t="inlineStr">
+      <c r="AD32" t="inlineStr">
         <is>
           <t>N1 - Truongdv17, Congnd15</t>
         </is>
       </c>
-      <c r="AE19">
+      <c r="AE32">
         <v>47.53277777777777</v>
       </c>
-      <c r="AF19">
+      <c r="AF32">
         <v>1.980532407407407</v>
       </c>
-      <c r="AG19" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="AH19">
+      <c r="AG32" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="AH32">
         <v>62.2825</v>
       </c>
-      <c r="AI19" t="inlineStr">
+      <c r="AI32" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>TNN</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>DVKT</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>Home Service</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>Bảo dưỡng vệ sinh máy giặt lồng ngang</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>VCC_HS_TNN_1781839465427</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>Member</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>Trần Đức Thiện</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>0847771131</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>Tdp mỏ chè- phường bách quang - tỉnh thái nguyên, Phường Bách Quang, Tỉnh Thái Nguyên</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>Facebook</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>Hot</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="P33" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="Q33" t="inlineStr">
         <is>
           <t>Sau bảo dưỡng thiết bị vẫn bẩn</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="R33" t="inlineStr">
         <is>
           <t>Đơn hàng làm xong từ 26/6 vẫn trong hạn bảo hành 72h
 1. KH phản ánh: giờ giặt quần áo ra nhiều mùn rất bẩn
 2. KH yêu cầu: qua kiểm tra, xử lý tình trạng này nếu cần thiết thì thay phần ba chảng máy giặt</t>
         </is>
       </c>
-      <c r="S20" s="2">
+      <c r="S33" s="2">
         <v>46202.33333333333</v>
       </c>
-      <c r="T20" s="2">
+      <c r="T33" s="2">
         <v>46204.72222222222</v>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="U33" t="inlineStr">
         <is>
           <t>Đóng</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
         <is>
           <t>Nguyễn Văn Thao</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
+      <c r="X33" t="inlineStr">
         <is>
           <t>289758</t>
         </is>
       </c>
-      <c r="Y20" s="2">
+      <c r="Y33" s="2">
         <v>46204.67430555556</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="Z33" s="3">
         <v>46202</v>
       </c>
-      <c r="AA20">
-        <v>3</v>
-      </c>
-      <c r="AB20" t="inlineStr">
+      <c r="AA33">
+        <v>4</v>
+      </c>
+      <c r="AB33" t="inlineStr">
         <is>
           <t>HS</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
+      <c r="AC33" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AD20" t="inlineStr">
+      <c r="AD33" t="inlineStr">
         <is>
           <t>N1 - Truongdv17, Congnd15</t>
         </is>
       </c>
-      <c r="AE20">
+      <c r="AE33">
         <v>56.18277777777777</v>
       </c>
-      <c r="AF20">
+      <c r="AF33">
         <v>2.340949074074074</v>
       </c>
-      <c r="AG20" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="AH20">
+      <c r="AG33" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="AH33">
         <v>1.15</v>
       </c>
-      <c r="AI20" t="inlineStr">
+      <c r="AI33" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>HNI</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_HNI_1703908</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>Vũ Nam Thái</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>0934685885</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>5b/8 ngõ 1074 đường Láng</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>Hot</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>Trong bán</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="P34" t="inlineStr">
         <is>
           <t>Khiếu nại</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="Q34" t="inlineStr">
         <is>
           <t>Nghiệp vụ chuyên môn kém</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="R34" t="inlineStr">
         <is>
           <t>1. KH đã báo CN
 2. KH phản ánh: Từ phản ánh trước TT_1782300958053 về việc tập kết vật tư đủ hơn 1 tuần trời nhưng ko triển khai lắp đặt và hẹn KH khất hất lần này đến lần khác là lắp đặt. KH ko còn sự tin tưởng, bức xúc và thất vọng.
 3. KH yêu cầu: đến dọn dẹp đồ đạc và làm thủ tục hủy HĐ, yêu cầu người có thẩm quyền phản hồi xử lý trước 12h. Nếu ko KH sẽ tự xử lý theo cách của KH</t>
         </is>
       </c>
-      <c r="S21" s="2">
+      <c r="S34" s="2">
         <v>46202.33333333333</v>
       </c>
-      <c r="T21" s="2">
+      <c r="T34" s="2">
         <v>46204.75347222222</v>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="U34" t="inlineStr">
         <is>
           <t>Hoàn thành</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
         <is>
           <t>Trình Văn Quân</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
+      <c r="X34" t="inlineStr">
         <is>
           <t>428952</t>
         </is>
       </c>
-      <c r="Y21" s="2">
+      <c r="Y34" s="2">
         <v>46204.43055555555</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="Z34" s="3">
         <v>46202</v>
       </c>
-      <c r="AA21">
-        <v>3</v>
-      </c>
-      <c r="AB21" t="inlineStr">
+      <c r="AA34">
+        <v>4</v>
+      </c>
+      <c r="AB34" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
+      <c r="AC34" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AD21" t="inlineStr">
+      <c r="AD34" t="inlineStr">
         <is>
           <t>N1 - Truongdv17, Congnd15</t>
         </is>
       </c>
-      <c r="AE21">
+      <c r="AE34">
         <v>50.33277777777778</v>
       </c>
-      <c r="AF21">
+      <c r="AF34">
         <v>2.097199074074074</v>
       </c>
-      <c r="AG21" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="AH21">
+      <c r="AG34" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="AH34">
         <v>7.75</v>
       </c>
-      <c r="AI21" t="inlineStr">
+      <c r="AI34" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>KV3</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>HCM</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>DVKT</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Home Service</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Bảo dưỡng Điều hòa treo tường (9.000BTU ÷ 12.000 BTU)</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>VCC_HS_HCM_1780623178350</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Đỗ Nhật Minh</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>0359953838</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>26 đường số 2, khu dân cư 6B Intresco, Xã Bình Hưng, Thành phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Sự cố</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>Sau sửa chữa thiết bị hỏng lại</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>Về khiếu nại từ trước của KH TT_1781177607618 CN có hẹn KH qua kiểm tra xử lý thiết bị nhưng KH thấy thiết bị ko có vấn đề gì lắm nên từ chối. Đến giờ KH lại thấy có tình trạng rỉ nước, chảy nước. KH mong muốn KT chính thức của viettel đến kiểm tra xử lý, KH có thể đợi nhưng phải là KT chính thức đến.</t>
+        </is>
+      </c>
+      <c r="S35" s="2">
+        <v>46202.33333333333</v>
+      </c>
+      <c r="T35" s="2">
+        <v>46206.5625</v>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Hoàn thành</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Trương Lê Thái Ngọc</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>455623</t>
+        </is>
+      </c>
+      <c r="Y35" s="2">
+        <v>46205.58680555555</v>
+      </c>
+      <c r="Z35" s="3">
+        <v>46202</v>
+      </c>
+      <c r="AA35">
+        <v>4</v>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>HS</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t>N3 - Thikd, Ducnt84</t>
+        </is>
+      </c>
+      <c r="AE35">
+        <v>78.0825</v>
+      </c>
+      <c r="AF35">
+        <v>3.2534375</v>
+      </c>
+      <c r="AG35" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="AH35">
+        <v>23.41638888888889</v>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>KV3</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>CMU</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Hệ thống NLMT</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_CMU_1651109</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Diamond</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Nguyễn Thị Kiều Oanh</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>0868975552</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Khóm 2</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Sự cố</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>KH chưa báo CN
+KH báo sự cố hệ thống NLMT hiện tại sạc không vào điện dù trời nắng to, cả ngày chỉ sạc vào dưới 50% pin
+Yêu cầu CN cho KT qua Ktra cho KH</t>
+        </is>
+      </c>
+      <c r="S36" s="2">
+        <v>46202.33333333333</v>
+      </c>
+      <c r="T36" s="2">
+        <v>46205.53125</v>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Hoàn thành</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Phạm Văn Tính</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>063084</t>
+        </is>
+      </c>
+      <c r="Y36" s="2">
+        <v>46205.47361111111</v>
+      </c>
+      <c r="Z36" s="3">
+        <v>46202</v>
+      </c>
+      <c r="AA36">
+        <v>4</v>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AD36" t="inlineStr">
+        <is>
+          <t>N3 - Thikd, Ducnt84</t>
+        </is>
+      </c>
+      <c r="AE36">
+        <v>75.36583333333334</v>
+      </c>
+      <c r="AF36">
+        <v>3.140243055555556</v>
+      </c>
+      <c r="AG36" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="AH36">
+        <v>1.383333333333333</v>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>HNI</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>M&amp;E</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Thang máy</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>10092025-GP&amp;DVKT/HĐMBLĐ-2025/HNI-NGUYENNGOCDUONG</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Diamond</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Nguyễn Ngọc Dương</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>0909289598</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>vân canh</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Khiếu nại</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>Nghiệp vụ chuyên môn kém</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>1. KH đã báo CN
+2. KH phản ánh: KH rất bức xúc trong quá trình thi công làm sai rất nhiều, ko hề giám sát, KH yêu cầu rất nhiều trên nhóm zalo đo cửa thang máy cho thông tin thiết kế nhưng ko thực hiện. Trong quá trình làm nhân viên đi wc ko đúng chỗ, làm hỏng công trình như khoan thủng tường, vỡ gạch. Đến giờ vi phạm rất nhiều như này cũng ko lập biên bản trong khi KH yêu cầu và KH cũng sẽ ko ký BBNT. Ngoài ra việc bảo dưỡng thang máy 1 năm 4 lần KH yêu cầu CN cũng ko đến làm cũng ko thông tin lại.
+3. KH yêu cầu: phản hồi lại thông tin cho KH trong ngày hôm nay hoặc ngày mai và đưa ra phương án xử lý.</t>
+        </is>
+      </c>
+      <c r="S37" s="2">
+        <v>46202.33333333333</v>
+      </c>
+      <c r="T37" s="2">
+        <v>46205.77777777778</v>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Hoàn thành</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Ngô Đức Tân</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>484844</t>
+        </is>
+      </c>
+      <c r="Y37" s="2">
+        <v>46205.37986111111</v>
+      </c>
+      <c r="Z37" s="3">
+        <v>46202</v>
+      </c>
+      <c r="AA37">
+        <v>4</v>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>IOC</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>P.Triển khai</t>
+        </is>
+      </c>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t>N1 - Truongdv17, Congnd15</t>
+        </is>
+      </c>
+      <c r="AE37">
+        <v>73.11583333333334</v>
+      </c>
+      <c r="AF37">
+        <v>3.046493055555556</v>
+      </c>
+      <c r="AG37" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="AH37">
+        <v>9.550000000000001</v>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>KV1</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
         <is>
           <t>HPG</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_HPG_1695987</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>Trần Văn Đức</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="K38" t="inlineStr">
         <is>
           <t>0328775232</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="L38" t="inlineStr">
         <is>
           <t>Số 99 đường số 2 tổ 9 - Tổ dân phố Cái Tắt</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="N38" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="O38" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="P38" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="Q38" t="inlineStr">
         <is>
           <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr">
+      <c r="R38" t="inlineStr">
         <is>
           <t>CN báo sự cố hộ KH 0393188966
 KH gặp sự cố NLMT tiền điện hàng tháng chỉ khoảng 2-2,5tr. Tuy nhiên sau khi lắp đặt và sử dụng hệ thống NLMT của VCC cung cấp từ ngày 11/6 thì tiền điện tăng vọt lên 6,4tr, mặc dù trên App theo dõi vẫn hoạt động bình thường
 Yêu cầu Cn cho KT qua Ktra cho KH</t>
         </is>
       </c>
-      <c r="S22" s="2">
+      <c r="S38" s="2">
         <v>46202.33333333333</v>
       </c>
-      <c r="T22" s="2">
+      <c r="T38" s="2">
         <v>46205.32291666667</v>
       </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>Hoàn thành</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Đóng</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
         <is>
           <t>Đào Văn Sơn</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
+      <c r="X38" t="inlineStr">
         <is>
           <t>079457</t>
         </is>
       </c>
-      <c r="Y22" s="2">
+      <c r="Y38" s="2">
         <v>46204.72083333333</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="Z38" s="3">
         <v>46202</v>
       </c>
-      <c r="AA22">
-        <v>3</v>
-      </c>
-      <c r="AB22" t="inlineStr">
+      <c r="AA38">
+        <v>4</v>
+      </c>
+      <c r="AB38" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
+      <c r="AC38" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AD22" t="inlineStr">
+      <c r="AD38" t="inlineStr">
         <is>
           <t>N1 - Truongdv17, Congnd15</t>
         </is>
       </c>
-      <c r="AE22">
+      <c r="AE38">
         <v>56.99916666666667</v>
       </c>
-      <c r="AF22">
+      <c r="AF38">
         <v>2.374965277777778</v>
       </c>
-      <c r="AG22" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="AH22">
+      <c r="AG38" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="AH38">
         <v>14.44972222222222</v>
       </c>
-      <c r="AI22" t="inlineStr">
+      <c r="AI38" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>HNI</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_HNI_1675916</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>Mạnh Chính</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t>0946111696</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="L39" t="inlineStr">
         <is>
           <t>Số 70 tổ 2, xóm 3, Thôn Long Phú, Đường 58</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="N39" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="O39" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="P39" t="inlineStr">
         <is>
           <t>Bảo hành</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr">
+      <c r="Q39" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr">
+      <c r="R39" t="inlineStr">
         <is>
           <t>Kh phản ánh hệ thống NLMT bị sập điện, sập luôn cả điện lưới không hoạt động được, bị từ sáng
 Yêu cầu quản lí điều kĩ thuật liên hệ và xuống kiểm tra gấp</t>
         </is>
       </c>
-      <c r="S23" s="2">
+      <c r="S39" s="2">
         <v>46198.56527777778</v>
       </c>
-      <c r="T23" s="2">
+      <c r="T39" s="2">
         <v>46219.43402777778</v>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="U39" t="inlineStr">
         <is>
           <t>Đóng</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
         <is>
           <t>Phạm Văn Tình</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
+      <c r="X39" t="inlineStr">
         <is>
           <t>463011</t>
         </is>
       </c>
-      <c r="Y23" s="2">
+      <c r="Y39" s="2">
         <v>46204.43263888889</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="Z39" s="3">
         <v>46198</v>
       </c>
-      <c r="AA23">
-        <v>7</v>
-      </c>
-      <c r="AB23" t="inlineStr">
+      <c r="AA39">
+        <v>8</v>
+      </c>
+      <c r="AB39" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
+      <c r="AC39" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AD23" t="inlineStr">
+      <c r="AD39" t="inlineStr">
         <is>
           <t>N1 - Truongdv17, Congnd15</t>
         </is>
       </c>
-      <c r="AE23">
+      <c r="AE39">
         <v>92.81555555555556</v>
       </c>
-      <c r="AF23">
+      <c r="AF39">
         <v>3.867314814814815</v>
       </c>
-      <c r="AG23" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="AH23">
+      <c r="AG39" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="AH39">
         <v>264.0302777777778</v>
       </c>
-      <c r="AI23" t="inlineStr">
+      <c r="AI39" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>BNH</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Hệ thống NLMT</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_BNH_1677775</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Diamond</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Trần Văn Luyện</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>0978295850</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Thôn An Ninh</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Bảo hành</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>1. KH chưa báo CN
+2. KH phản ánh: Có gọi bên điện lực kiểm tra sửa điện thì phát hiện điện nlmt đang cắt pha mát chứ ko cắt pha lửa và thấy nguy hiểm. 
+3. KH yêu cầu: Qua kiểm tra, đấu nối lại đường điện</t>
+        </is>
+      </c>
+      <c r="S40" s="2">
+        <v>46196.4875</v>
+      </c>
+      <c r="T40" s="2">
+        <v>46215.47291666667</v>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Đóng</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Phạm Văn Huy</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>408869</t>
+        </is>
+      </c>
+      <c r="Y40" s="2">
+        <v>46205.37847222222</v>
+      </c>
+      <c r="Z40" s="3">
+        <v>46196</v>
+      </c>
+      <c r="AA40">
+        <v>10</v>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AD40" t="inlineStr">
+        <is>
+          <t>N1 - Truongdv17, Congnd15</t>
+        </is>
+      </c>
+      <c r="AE40">
+        <v>165.3813888888889</v>
+      </c>
+      <c r="AF40">
+        <v>6.890891203703704</v>
+      </c>
+      <c r="AG40" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="AH40">
+        <v>158.9147222222222</v>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>KV1</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
         <is>
           <t>HNI</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_HNI_1559163</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>Nguyễn Phi Quang</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t>0989269569</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="L41" t="inlineStr">
         <is>
           <t>44 nguyễn công hoan</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t>Hot</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="O41" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="P41" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
+      <c r="Q41" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr">
+      <c r="R41" t="inlineStr">
         <is>
           <t>1. KH đã báo CN
 2. KH phản ánh: nắng nhưng ko thấy sản xuất ra điện toàn thấy sử dụng điện lưới tiền điện tăng cao bất thường, 1 tháng 3tr5 tiền điện. 
@@ -4198,1049 +6933,1369 @@
 ***Địa chỉ KH cung cấp: 44 nguyễn công hoàn, phường giảng võ, hà nội</t>
         </is>
       </c>
-      <c r="S24" s="2">
+      <c r="S41" s="2">
         <v>46196.33333333333</v>
       </c>
-      <c r="T24" s="2">
+      <c r="T41" s="2">
         <v>46202.70833333333</v>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="U41" t="inlineStr">
         <is>
           <t>Hoàn thành</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr">
+      <c r="V41" t="inlineStr">
         <is>
           <t>Quá hạn</t>
         </is>
       </c>
-      <c r="W24" t="inlineStr">
+      <c r="W41" t="inlineStr">
         <is>
           <t>Vũ Bá Mạnh</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
+      <c r="X41" t="inlineStr">
         <is>
           <t>463951</t>
         </is>
       </c>
-      <c r="Y24" s="2">
+      <c r="Y41" s="2">
         <v>46204.63680555555</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="Z41" s="3">
         <v>46196</v>
       </c>
-      <c r="AA24">
-        <v>9</v>
-      </c>
-      <c r="AB24" t="inlineStr">
+      <c r="AA41">
+        <v>10</v>
+      </c>
+      <c r="AB41" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
+      <c r="AC41" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AD24" t="inlineStr">
+      <c r="AD41" t="inlineStr">
         <is>
           <t>N1 - Truongdv17, Congnd15</t>
         </is>
       </c>
-      <c r="AE24">
+      <c r="AE41">
         <v>151.2816666666667</v>
       </c>
-      <c r="AF24">
+      <c r="AF41">
         <v>6.303402777777777</v>
       </c>
-      <c r="AG24" t="inlineStr">
+      <c r="AG41" t="inlineStr">
         <is>
           <t>Quá hạn</t>
         </is>
       </c>
-      <c r="AH24">
+      <c r="AH41">
         <v>-1</v>
       </c>
-      <c r="AI24" t="inlineStr">
+      <c r="AI41" t="inlineStr">
         <is>
           <t>Quá hạn</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>KV1</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>NBH</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Hệ thống NLMT</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>KHCN_DVNLMT_HNM_0254674</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Nguyễn Hữu Nghĩa</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>0963144889</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>xóm 3, thôn Tống Xá</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Sự cố</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>Hiệu suất sản phẩm kém</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>KH phản ánh Hiệu quả sản phẩm kém, tiền điện tăng lên 700-1tr, công mức xả điện yếu hơn so với lúc đầu sử dụng
+Yêu cầu quản lí điều kĩ thuật liên hệ qua số 0397422358 - chị Nga ( vợ ) và xuống kiểm tra cho KH</t>
+        </is>
+      </c>
+      <c r="S42" s="2">
+        <v>46195.33333333333</v>
+      </c>
+      <c r="T42" s="2">
+        <v>46207.34375</v>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Đóng</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Trần Duy Ngọc</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>416520</t>
+        </is>
+      </c>
+      <c r="Y42" s="2">
+        <v>46205.75347222222</v>
+      </c>
+      <c r="Z42" s="3">
+        <v>46195</v>
+      </c>
+      <c r="AA42">
+        <v>11</v>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AD42" t="inlineStr">
+        <is>
+          <t>N1 - Truongdv17, Congnd15</t>
+        </is>
+      </c>
+      <c r="AE42">
+        <v>200.9975</v>
+      </c>
+      <c r="AF42">
+        <v>8.374895833333335</v>
+      </c>
+      <c r="AG42" t="inlineStr">
+        <is>
+          <t>Quá hạn</t>
+        </is>
+      </c>
+      <c r="AH42">
+        <v>29.91611111111111</v>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
         <is>
           <t>KV3</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>DNI</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_DNI_1679345</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t>Nguyễn Hữu Hùng</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="K43" t="inlineStr">
         <is>
           <t>0984304228</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="L43" t="inlineStr">
         <is>
           <t>Âp Ngọc Lâm 5</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="N43" t="inlineStr">
         <is>
           <t>Hot</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="O43" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="P43" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr">
+      <c r="Q43" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr">
+      <c r="R43" t="inlineStr">
         <is>
           <t>KH đã báo KT
 Kh báo sự cố NLMT đã lắp pin lưu trữ nhưng hiện tại điện vẫn bị sập
 Yêu cầu CN cho KT qua ktra cho KH</t>
         </is>
       </c>
-      <c r="S25" s="2">
+      <c r="S43" s="2">
         <v>46195.33333333333</v>
       </c>
-      <c r="T25" s="2">
+      <c r="T43" s="2">
         <v>46204.83333333333</v>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Đóng</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Trần Quốc Khang</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>459729</t>
+        </is>
+      </c>
+      <c r="Y43" s="2">
+        <v>46204.81527777778</v>
+      </c>
+      <c r="Z43" s="3">
+        <v>46195</v>
+      </c>
+      <c r="AA43">
+        <v>11</v>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AD43" t="inlineStr">
+        <is>
+          <t>N3 - Thikd, Ducnt84</t>
+        </is>
+      </c>
+      <c r="AE43">
+        <v>176.9977777777778</v>
+      </c>
+      <c r="AF43">
+        <v>7.374907407407409</v>
+      </c>
+      <c r="AG43" t="inlineStr">
+        <is>
+          <t>Quá hạn</t>
+        </is>
+      </c>
+      <c r="AH43">
+        <v>0.4333333333333333</v>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>KV1</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>HNI</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Hệ thống NLMT</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_HNI_1702060</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Hộ Kinh Doanh Đỗ Duy Diệu</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>0971454500</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Mst 001090060710, Đồng Nanh</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Trong bán</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Khiếu nại</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>Tiến độ triển khai chậm</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>KH chưa báo CN 
+KH phản ánh tiến độ triển khai chậm, chưa có ai mang linh kiện đến và lắp đặt cho KH
+Yêu cầu quản lí điều kĩ thuật liên hệ và xuống lắp đặt cho KH gấp</t>
+        </is>
+      </c>
+      <c r="S44" s="2">
+        <v>46191.58333333333</v>
+      </c>
+      <c r="T44" s="2">
+        <v>46205.70833333333</v>
+      </c>
+      <c r="U44" t="inlineStr">
         <is>
           <t>Hoàn thành</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>Trần Quốc Khang</t>
-        </is>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>459729</t>
-        </is>
-      </c>
-      <c r="Y25" s="2">
-        <v>46204.81527777778</v>
-      </c>
-      <c r="Z25" s="3">
-        <v>46195</v>
-      </c>
-      <c r="AA25">
-        <v>10</v>
-      </c>
-      <c r="AB25" t="inlineStr">
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Nguyễn Thành Vinh</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>413306</t>
+        </is>
+      </c>
+      <c r="Y44" s="2">
+        <v>46205.37152777778</v>
+      </c>
+      <c r="Z44" s="3">
+        <v>46191</v>
+      </c>
+      <c r="AA44">
+        <v>15</v>
+      </c>
+      <c r="AB44" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AD25" t="inlineStr">
-        <is>
-          <t>N3 - Thikd, Ducnt84</t>
-        </is>
-      </c>
-      <c r="AE25">
-        <v>176.9977777777778</v>
-      </c>
-      <c r="AF25">
-        <v>7.374907407407409</v>
-      </c>
-      <c r="AG25" t="inlineStr">
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>P.Triển khai</t>
+        </is>
+      </c>
+      <c r="AD44" t="inlineStr">
+        <is>
+          <t>N1 - Truongdv17, Congnd15</t>
+        </is>
+      </c>
+      <c r="AE44">
+        <v>234.9138888888889</v>
+      </c>
+      <c r="AF44">
+        <v>9.788078703703704</v>
+      </c>
+      <c r="AG44" t="inlineStr">
         <is>
           <t>Quá hạn</t>
         </is>
       </c>
-      <c r="AH25">
-        <v>0.4333333333333333</v>
-      </c>
-      <c r="AI25" t="inlineStr">
+      <c r="AH44">
+        <v>8.083333333333334</v>
+      </c>
+      <c r="AI44" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="45">
+      <c r="A45" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>BNH</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>Inverter</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_BGG_1550653</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>Nguyễn Văn Trường</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="K45" t="inlineStr">
         <is>
           <t>0983678890</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t>Phúc Hòa</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="N45" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="O45" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="P45" t="inlineStr">
         <is>
           <t>Bảo hành</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="Q45" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr">
+      <c r="R45" t="inlineStr">
         <is>
           <t>1. KH đã liên hệ CN
 2. Biến tần của KH đang không hiển thị thông tin tải điện của nhà KH khoảng 2 ngày nay
 3. KH cần CN liên hệ và đến hỗ trợ kiểm tra sớm</t>
         </is>
       </c>
-      <c r="S26" s="2">
+      <c r="S45" s="2">
         <v>46191.33333333333</v>
       </c>
-      <c r="T26" s="2">
+      <c r="T45" s="2">
         <v>46206.63055555556</v>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="U45" t="inlineStr">
         <is>
           <t>Đóng</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
         <is>
           <t>Nguyễn Văn Trường</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
+      <c r="X45" t="inlineStr">
         <is>
           <t>121999</t>
         </is>
       </c>
-      <c r="Y26" s="2">
+      <c r="Y45" s="2">
         <v>46204.28125</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="Z45" s="3">
         <v>46191</v>
       </c>
-      <c r="AA26">
-        <v>14</v>
-      </c>
-      <c r="AB26" t="inlineStr">
+      <c r="AA45">
+        <v>15</v>
+      </c>
+      <c r="AB45" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
+      <c r="AC45" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AD26" t="inlineStr">
+      <c r="AD45" t="inlineStr">
         <is>
           <t>N1 - Truongdv17, Congnd15</t>
         </is>
       </c>
-      <c r="AE26">
+      <c r="AE45">
         <v>214.7475</v>
       </c>
-      <c r="AF26">
+      <c r="AF45">
         <v>8.947812500000001</v>
       </c>
-      <c r="AG26" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="AH26">
+      <c r="AG45" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="AH45">
         <v>56.38277777777778</v>
       </c>
-      <c r="AI26" t="inlineStr">
+      <c r="AI45" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="46">
+      <c r="A46" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>TNN</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_TNN_1686396</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t>Lê Trung Hiếu</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="K46" t="inlineStr">
         <is>
           <t>0986238792</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t>KDT Cosi T5 phường Gia Sàng</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="N46" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="O46" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="P46" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="Q46" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr">
+      <c r="R46" t="inlineStr">
         <is>
           <t>1. KH đã liên hệ CN 
 2. Trên App theo dõi hiệu suất HT NLMT của KH thông báo lấy 5Kw điện lưới, thực tế Đồng hồ điện lưới thông báo lấy 50Kw điện lưới
 3.KH cần CN liên hệ và đến kiểm tra sớm</t>
         </is>
       </c>
-      <c r="S27" s="2">
+      <c r="S46" s="2">
         <v>46190.67986111112</v>
       </c>
-      <c r="T27" s="2">
+      <c r="T46" s="2">
         <v>46207.77777777778</v>
       </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>Hoàn thành</t>
-        </is>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr">
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Đóng</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
         <is>
           <t>Nguyễn Văn Thao</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
+      <c r="X46" t="inlineStr">
         <is>
           <t>289758</t>
         </is>
       </c>
-      <c r="Y27" s="2">
+      <c r="Y46" s="2">
         <v>46204.67430555556</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="Z46" s="3">
         <v>46190</v>
       </c>
-      <c r="AA27">
-        <v>15</v>
-      </c>
-      <c r="AB27" t="inlineStr">
+      <c r="AA46">
+        <v>16</v>
+      </c>
+      <c r="AB46" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
+      <c r="AC46" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AD27" t="inlineStr">
+      <c r="AD46" t="inlineStr">
         <is>
           <t>N1 - Truongdv17, Congnd15</t>
         </is>
       </c>
-      <c r="AE27">
+      <c r="AE46">
         <v>239.8638888888889</v>
       </c>
-      <c r="AF27">
+      <c r="AF46">
         <v>9.994328703703705</v>
       </c>
-      <c r="AG27" t="inlineStr">
+      <c r="AG46" t="inlineStr">
         <is>
           <t>Quá hạn</t>
         </is>
       </c>
-      <c r="AH27">
+      <c r="AH46">
         <v>55.81583333333333</v>
       </c>
-      <c r="AI27" t="inlineStr">
+      <c r="AI46" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+    <row r="47">
+      <c r="A47" t="inlineStr">
         <is>
           <t>KV3</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>TNH</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_TNH_1624898</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>Nguyễn Nhật Long</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="K47" t="inlineStr">
         <is>
           <t>0979714497</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="L47" t="inlineStr">
         <is>
           <t>hẻm 53, Phường Ninh Thạnh</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="N47" t="inlineStr">
         <is>
           <t>VIP</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="O47" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="P47" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="Q47" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr">
+      <c r="R47" t="inlineStr">
         <is>
           <t>KH chưa báo CN 
 khách hàng báo pin lưu trữ bị chớp đỏ, ko sử dụng được.
 Yêu cầu quản lí điều kỹ thuật hỗ trợ kiểm tra gấp</t>
         </is>
       </c>
-      <c r="S28" s="2">
+      <c r="S47" s="2">
         <v>46188.49097222222</v>
       </c>
-      <c r="T28" s="2">
+      <c r="T47" s="2">
         <v>46207.72916666667</v>
       </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>Hoàn thành</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr">
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Đóng</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
         <is>
           <t>Nguyễn Đặng Vĩnh Phát</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
+      <c r="X47" t="inlineStr">
         <is>
           <t>455619</t>
         </is>
       </c>
-      <c r="Y28" s="2">
+      <c r="Y47" s="2">
         <v>46204.79513888889</v>
       </c>
-      <c r="Z28" s="3">
+      <c r="Z47" s="3">
         <v>46188</v>
       </c>
-      <c r="AA28">
-        <v>17</v>
-      </c>
-      <c r="AB28" t="inlineStr">
+      <c r="AA47">
+        <v>18</v>
+      </c>
+      <c r="AB47" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
+      <c r="AC47" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AD28" t="inlineStr">
+      <c r="AD47" t="inlineStr">
         <is>
           <t>N3 - Thikd, Ducnt84</t>
         </is>
       </c>
-      <c r="AE28">
+      <c r="AE47">
         <v>293.2130555555556</v>
       </c>
-      <c r="AF28">
+      <c r="AF47">
         <v>12.21721064814815</v>
       </c>
-      <c r="AG28" t="inlineStr">
+      <c r="AG47" t="inlineStr">
         <is>
           <t>Quá hạn</t>
         </is>
       </c>
-      <c r="AH28">
+      <c r="AH47">
         <v>52.91583333333333</v>
       </c>
-      <c r="AI28" t="inlineStr">
+      <c r="AI47" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+    <row r="48">
+      <c r="A48" t="inlineStr">
         <is>
           <t>KV2</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>DLK</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>Tấm pin NLMT</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_DLK_1594905</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t>Bùi Văn Thông</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="K48" t="inlineStr">
         <is>
           <t>0945267979</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t>Buôn Lê B, , Ea H’leo, Đắk Lắk, Việt Nam.</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="N48" t="inlineStr">
         <is>
           <t>VIP</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="O48" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="P48" t="inlineStr">
         <is>
           <t>Bảo hành</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
+      <c r="Q48" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr">
+      <c r="R48" t="inlineStr">
         <is>
           <t>Đã báo CN: Đã báo
 KH báo sự cố: Hiện tại 1 tấm pin nhà KH có hiện tượng bị không sử dụng được 
 KH yêu cầu: KT qua kiểm tra cho Kh</t>
         </is>
       </c>
-      <c r="S29" s="2">
+      <c r="S48" s="2">
         <v>46176.60138888888</v>
       </c>
-      <c r="T29" s="2">
+      <c r="T48" s="2">
         <v>46217.38958333334</v>
       </c>
-      <c r="U29" t="inlineStr">
+      <c r="U48" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr">
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
         <is>
           <t>Phạm Duy Bộ</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
+      <c r="X48" t="inlineStr">
         <is>
           <t>411337</t>
         </is>
       </c>
-      <c r="Y29" s="2">
+      <c r="Y48" s="2">
         <v>46204.7</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="Z48" s="3">
         <v>46176</v>
       </c>
-      <c r="AA29">
-        <v>29</v>
-      </c>
-      <c r="AB29" t="inlineStr">
+      <c r="AA48">
+        <v>30</v>
+      </c>
+      <c r="AB48" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
+      <c r="AC48" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AD29" t="inlineStr">
+      <c r="AD48" t="inlineStr">
         <is>
           <t>N3 - Thikd, Ducnt84</t>
         </is>
       </c>
-      <c r="AE29">
+      <c r="AE48">
         <v>482.361111111111</v>
       </c>
-      <c r="AF29">
+      <c r="AF48">
         <v>20.09837962962962</v>
       </c>
-      <c r="AG29" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="AH29">
+      <c r="AG48" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="AH48">
         <v>208.5475</v>
       </c>
-      <c r="AI29" t="inlineStr">
+      <c r="AI48" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+    <row r="49">
+      <c r="A49" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>HNI</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_HBH_1559029</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t>Phạm Công Chính</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="K49" t="inlineStr">
         <is>
           <t>0985511119</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="L49" t="inlineStr">
         <is>
           <t>Thôn 6</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="N49" t="inlineStr">
         <is>
           <t>Hot</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="O49" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="P49" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr">
+      <c r="Q49" t="inlineStr">
         <is>
           <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr">
+      <c r="R49" t="inlineStr">
         <is>
           <t>Chưa báo chi nhánh
 Lỗi cảnh báo ác quy hiệu suất ko đạt 
 Yêu cầu kt qua ktra</t>
         </is>
       </c>
-      <c r="S30" s="2">
+      <c r="S49" s="2">
         <v>46140.33333333333</v>
       </c>
-      <c r="T30" s="2">
+      <c r="T49" s="2">
         <v>46213.71180555555</v>
       </c>
-      <c r="U30" t="inlineStr">
+      <c r="U49" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr">
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
         <is>
           <t>Nguyễn Ngọc Duy</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
+      <c r="X49" t="inlineStr">
         <is>
           <t>286240</t>
         </is>
       </c>
-      <c r="Y30" s="2">
+      <c r="Y49" s="2">
         <v>46204.62152777778</v>
       </c>
-      <c r="Z30" s="3">
+      <c r="Z49" s="3">
         <v>46140</v>
       </c>
-      <c r="AA30">
-        <v>65</v>
-      </c>
-      <c r="AB30" t="inlineStr">
+      <c r="AA49">
+        <v>66</v>
+      </c>
+      <c r="AB49" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
+      <c r="AC49" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AD30" t="inlineStr">
+      <c r="AD49" t="inlineStr">
         <is>
           <t>N1 - Truongdv17, Congnd15</t>
         </is>
       </c>
-      <c r="AE30">
+      <c r="AE49">
         <v>1062.904444444444</v>
       </c>
-      <c r="AF30">
+      <c r="AF49">
         <v>44.28768518518518</v>
       </c>
-      <c r="AG30" t="inlineStr">
+      <c r="AG49" t="inlineStr">
         <is>
           <t>Quá hạn</t>
         </is>
       </c>
-      <c r="AH30">
+      <c r="AH49">
         <v>170.1647222222222</v>
       </c>
-      <c r="AI30" t="inlineStr">
+      <c r="AI49" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>

--- a/data/5.R_pakh_hoan_thanh.xlsx
+++ b/data/5.R_pakh_hoan_thanh.xlsx
@@ -676,7 +676,7 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE2">
@@ -837,7 +837,7 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE3">
@@ -995,7 +995,7 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE4">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE5">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE6">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>N2 - Tienvt16, Anhnt631</t>
+          <t>N1 - Congnd15, Tienvt16</t>
         </is>
       </c>
       <c r="AE7">
@@ -1645,7 +1645,7 @@
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N1 - Congnd15, Tienvt16</t>
         </is>
       </c>
       <c r="AE8">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>N2 - Tienvt16, Anhnt631</t>
+          <t>N4 - Nhungntt27, Anhnt631</t>
         </is>
       </c>
       <c r="AE9">
@@ -1969,7 +1969,7 @@
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE10">
@@ -2127,7 +2127,7 @@
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE11">
@@ -2285,7 +2285,7 @@
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N1 - Congnd15, Tienvt16</t>
         </is>
       </c>
       <c r="AE12">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE13">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>N2 - Tienvt16, Anhnt631</t>
+          <t>N4 - Nhungntt27, Anhnt631</t>
         </is>
       </c>
       <c r="AE14">
@@ -2767,7 +2767,7 @@
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>N2 - Tienvt16, Anhnt631</t>
+          <t>N4 - Nhungntt27, Anhnt631</t>
         </is>
       </c>
       <c r="AE15">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE16">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE17">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N1 - Congnd15, Tienvt16</t>
         </is>
       </c>
       <c r="AE18">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE19">
@@ -3577,7 +3577,7 @@
       </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE20">
@@ -3733,7 +3733,7 @@
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE21">
@@ -3896,7 +3896,7 @@
       </c>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE22">
@@ -4058,7 +4058,7 @@
       </c>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE23">
@@ -4215,7 +4215,7 @@
       </c>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE24">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE25">
@@ -4534,7 +4534,7 @@
       </c>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE26">
@@ -4690,7 +4690,7 @@
       </c>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE27">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE28">
@@ -5009,7 +5009,7 @@
       </c>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE29">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>N2 - Tienvt16, Anhnt631</t>
+          <t>N1 - Congnd15, Tienvt16</t>
         </is>
       </c>
       <c r="AE30">
@@ -5330,7 +5330,7 @@
       </c>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE31">
@@ -5493,7 +5493,7 @@
       </c>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N4 - Nhungntt27, Anhnt631</t>
         </is>
       </c>
       <c r="AE32">
@@ -5656,7 +5656,7 @@
       </c>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE33">
@@ -5819,7 +5819,7 @@
       </c>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE34">
@@ -5977,7 +5977,7 @@
       </c>
       <c r="AD35" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE35">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="AD36" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE36">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="AD37" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE37">
@@ -6453,7 +6453,7 @@
       </c>
       <c r="AD38" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE38">
@@ -6616,7 +6616,7 @@
       </c>
       <c r="AD39" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE39">
@@ -6779,7 +6779,7 @@
       </c>
       <c r="AD40" t="inlineStr">
         <is>
-          <t>N2 - Tienvt16, Anhnt631</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE40">
@@ -6937,7 +6937,7 @@
       </c>
       <c r="AD41" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE41">
@@ -7099,7 +7099,7 @@
       </c>
       <c r="AD42" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE42">
@@ -7255,7 +7255,7 @@
       </c>
       <c r="AD43" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE43">
@@ -7411,7 +7411,7 @@
       </c>
       <c r="AD44" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE44">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="AD45" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE45">
@@ -7737,7 +7737,7 @@
       </c>
       <c r="AD46" t="inlineStr">
         <is>
-          <t>N2 - Tienvt16, Anhnt631</t>
+          <t>N1 - Congnd15, Tienvt16</t>
         </is>
       </c>
       <c r="AE46">
@@ -7893,7 +7893,7 @@
       </c>
       <c r="AD47" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE47">
@@ -8056,7 +8056,7 @@
       </c>
       <c r="AD48" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N4 - Nhungntt27, Anhnt631</t>
         </is>
       </c>
       <c r="AE48">
@@ -8217,7 +8217,7 @@
       </c>
       <c r="AD49" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE49">
@@ -8380,7 +8380,7 @@
       </c>
       <c r="AD50" t="inlineStr">
         <is>
-          <t>N2 - Tienvt16, Anhnt631</t>
+          <t>N1 - Congnd15, Tienvt16</t>
         </is>
       </c>
       <c r="AE50">
@@ -8543,7 +8543,7 @@
       </c>
       <c r="AD51" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N1 - Congnd15, Tienvt16</t>
         </is>
       </c>
       <c r="AE51">
@@ -8706,7 +8706,7 @@
       </c>
       <c r="AD52" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N1 - Congnd15, Tienvt16</t>
         </is>
       </c>
       <c r="AE52">
@@ -8864,7 +8864,7 @@
       </c>
       <c r="AD53" t="inlineStr">
         <is>
-          <t>N2 - Tienvt16, Anhnt631</t>
+          <t>N1 - Congnd15, Tienvt16</t>
         </is>
       </c>
       <c r="AE53">
@@ -9022,7 +9022,7 @@
       </c>
       <c r="AD54" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE54">
@@ -9185,7 +9185,7 @@
       </c>
       <c r="AD55" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE55">
@@ -9348,7 +9348,7 @@
       </c>
       <c r="AD56" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE56">
@@ -9511,7 +9511,7 @@
       </c>
       <c r="AD57" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE57">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="AD58" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE58">
@@ -9836,7 +9836,7 @@
       </c>
       <c r="AD59" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE59">
@@ -9999,7 +9999,7 @@
       </c>
       <c r="AD60" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE60">
@@ -10161,7 +10161,7 @@
       </c>
       <c r="AD61" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE61">
@@ -10319,7 +10319,7 @@
       </c>
       <c r="AD62" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE62">
@@ -10482,7 +10482,7 @@
       </c>
       <c r="AD63" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N4 - Nhungntt27, Anhnt631</t>
         </is>
       </c>
       <c r="AE63">
@@ -10645,7 +10645,7 @@
       </c>
       <c r="AD64" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE64">
@@ -10801,7 +10801,7 @@
       </c>
       <c r="AD65" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE65">
@@ -10960,7 +10960,7 @@
       </c>
       <c r="AD66" t="inlineStr">
         <is>
-          <t>N2 - Tienvt16, Anhnt631</t>
+          <t>N4 - Nhungntt27, Anhnt631</t>
         </is>
       </c>
       <c r="AE66">
@@ -11118,7 +11118,7 @@
       </c>
       <c r="AD67" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE67">
@@ -11281,7 +11281,7 @@
       </c>
       <c r="AD68" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE68">
@@ -11444,7 +11444,7 @@
       </c>
       <c r="AD69" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N4 - Nhungntt27, Anhnt631</t>
         </is>
       </c>
       <c r="AE69">
@@ -11602,7 +11602,7 @@
       </c>
       <c r="AD70" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE70">
@@ -11765,7 +11765,7 @@
       </c>
       <c r="AD71" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N4 - Nhungntt27, Anhnt631</t>
         </is>
       </c>
       <c r="AE71">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="AD72" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE72">
@@ -12091,7 +12091,7 @@
       </c>
       <c r="AD73" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE73">
@@ -12249,7 +12249,7 @@
       </c>
       <c r="AD74" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N1 - Congnd15, Tienvt16</t>
         </is>
       </c>
       <c r="AE74">
@@ -12412,7 +12412,7 @@
       </c>
       <c r="AD75" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE75">
@@ -12570,7 +12570,7 @@
       </c>
       <c r="AD76" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N1 - Congnd15, Tienvt16</t>
         </is>
       </c>
       <c r="AE76">
@@ -12726,7 +12726,7 @@
       </c>
       <c r="AD77" t="inlineStr">
         <is>
-          <t>N2 - Tienvt16, Anhnt631</t>
+          <t>N1 - Congnd15, Tienvt16</t>
         </is>
       </c>
       <c r="AE77">
@@ -12889,7 +12889,7 @@
       </c>
       <c r="AD78" t="inlineStr">
         <is>
-          <t>N2 - Tienvt16, Anhnt631</t>
+          <t>N1 - Congnd15, Tienvt16</t>
         </is>
       </c>
       <c r="AE78">
@@ -13052,7 +13052,7 @@
       </c>
       <c r="AD79" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE79">
@@ -13215,7 +13215,7 @@
       </c>
       <c r="AD80" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE80">
@@ -13378,7 +13378,7 @@
       </c>
       <c r="AD81" t="inlineStr">
         <is>
-          <t>N2 - Tienvt16, Anhnt631</t>
+          <t>N4 - Nhungntt27, Anhnt631</t>
         </is>
       </c>
       <c r="AE81">
@@ -13536,7 +13536,7 @@
       </c>
       <c r="AD82" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE82">
@@ -13699,7 +13699,7 @@
       </c>
       <c r="AD83" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE83">
@@ -13862,7 +13862,7 @@
       </c>
       <c r="AD84" t="inlineStr">
         <is>
-          <t>N2 - Tienvt16, Anhnt631</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE84">
@@ -14025,7 +14025,7 @@
       </c>
       <c r="AD85" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE85">
@@ -14181,7 +14181,7 @@
       </c>
       <c r="AD86" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE86">
@@ -14344,7 +14344,7 @@
       </c>
       <c r="AD87" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N1 - Congnd15, Tienvt16</t>
         </is>
       </c>
       <c r="AE87">
@@ -14506,7 +14506,7 @@
       </c>
       <c r="AD88" t="inlineStr">
         <is>
-          <t>N2 - Tienvt16, Anhnt631</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE88">
@@ -14669,7 +14669,7 @@
       </c>
       <c r="AD89" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE89">
@@ -14832,7 +14832,7 @@
       </c>
       <c r="AD90" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N1 - Congnd15, Tienvt16</t>
         </is>
       </c>
       <c r="AE90">
@@ -14995,7 +14995,7 @@
       </c>
       <c r="AD91" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N1 - Congnd15, Tienvt16</t>
         </is>
       </c>
       <c r="AE91">
@@ -15151,7 +15151,7 @@
       </c>
       <c r="AD92" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N1 - Congnd15, Tienvt16</t>
         </is>
       </c>
       <c r="AE92">
@@ -15309,7 +15309,7 @@
       </c>
       <c r="AD93" t="inlineStr">
         <is>
-          <t>N2 - Tienvt16, Anhnt631</t>
+          <t>N4 - Nhungntt27, Anhnt631</t>
         </is>
       </c>
       <c r="AE93">
@@ -15471,7 +15471,7 @@
       </c>
       <c r="AD94" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE94">
@@ -15627,7 +15627,7 @@
       </c>
       <c r="AD95" t="inlineStr">
         <is>
-          <t>N2 - Tienvt16, Anhnt631</t>
+          <t>N4 - Nhungntt27, Anhnt631</t>
         </is>
       </c>
       <c r="AE95">
@@ -15785,7 +15785,7 @@
       </c>
       <c r="AD96" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE96">
@@ -15948,7 +15948,7 @@
       </c>
       <c r="AD97" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE97">
@@ -16104,7 +16104,7 @@
       </c>
       <c r="AD98" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE98">
@@ -16262,7 +16262,7 @@
       </c>
       <c r="AD99" t="inlineStr">
         <is>
-          <t>N2 - Tienvt16, Anhnt631</t>
+          <t>N4 - Nhungntt27, Anhnt631</t>
         </is>
       </c>
       <c r="AE99">
@@ -16425,7 +16425,7 @@
       </c>
       <c r="AD100" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE100">
@@ -16588,7 +16588,7 @@
       </c>
       <c r="AD101" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE101">
@@ -16751,7 +16751,7 @@
       </c>
       <c r="AD102" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N1 - Congnd15, Tienvt16</t>
         </is>
       </c>
       <c r="AE102">
@@ -16914,7 +16914,7 @@
       </c>
       <c r="AD103" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N1 - Congnd15, Tienvt16</t>
         </is>
       </c>
       <c r="AE103">
@@ -17070,7 +17070,7 @@
       </c>
       <c r="AD104" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE104">
@@ -17228,7 +17228,7 @@
       </c>
       <c r="AD105" t="inlineStr">
         <is>
-          <t>N2 - Tienvt16, Anhnt631</t>
+          <t>N1 - Congnd15, Tienvt16</t>
         </is>
       </c>
       <c r="AE105">
@@ -17391,7 +17391,7 @@
       </c>
       <c r="AD106" t="inlineStr">
         <is>
-          <t>N2 - Tienvt16, Anhnt631</t>
+          <t>N4 - Nhungntt27, Anhnt631</t>
         </is>
       </c>
       <c r="AE106">
@@ -17549,7 +17549,7 @@
       </c>
       <c r="AD107" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE107">
@@ -17712,7 +17712,7 @@
       </c>
       <c r="AD108" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE108">
@@ -17875,7 +17875,7 @@
       </c>
       <c r="AD109" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE109">
@@ -18038,7 +18038,7 @@
       </c>
       <c r="AD110" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE110">
@@ -18196,7 +18196,7 @@
       </c>
       <c r="AD111" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N1 - Congnd15, Tienvt16</t>
         </is>
       </c>
       <c r="AE111">
@@ -18359,7 +18359,7 @@
       </c>
       <c r="AD112" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE112">
@@ -18522,7 +18522,7 @@
       </c>
       <c r="AD113" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE113">
@@ -18685,7 +18685,7 @@
       </c>
       <c r="AD114" t="inlineStr">
         <is>
-          <t>N2 - Tienvt16, Anhnt631</t>
+          <t>N4 - Nhungntt27, Anhnt631</t>
         </is>
       </c>
       <c r="AE114">
@@ -18848,7 +18848,7 @@
       </c>
       <c r="AD115" t="inlineStr">
         <is>
-          <t>N2 - Tienvt16, Anhnt631</t>
+          <t>N4 - Nhungntt27, Anhnt631</t>
         </is>
       </c>
       <c r="AE115">
@@ -19006,7 +19006,7 @@
       </c>
       <c r="AD116" t="inlineStr">
         <is>
-          <t>N2 - Tienvt16, Anhnt631</t>
+          <t>N4 - Nhungntt27, Anhnt631</t>
         </is>
       </c>
       <c r="AE116">
@@ -19162,7 +19162,7 @@
       </c>
       <c r="AD117" t="inlineStr">
         <is>
-          <t>N2 - Tienvt16, Anhnt631</t>
+          <t>N1 - Congnd15, Tienvt16</t>
         </is>
       </c>
       <c r="AE117">
@@ -19318,7 +19318,7 @@
       </c>
       <c r="AD118" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE118">
@@ -19481,7 +19481,7 @@
       </c>
       <c r="AD119" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE119">
@@ -19644,7 +19644,7 @@
       </c>
       <c r="AD120" t="inlineStr">
         <is>
-          <t>N2 - Tienvt16, Anhnt631</t>
+          <t>N4 - Nhungntt27, Anhnt631</t>
         </is>
       </c>
       <c r="AE120">
@@ -19807,7 +19807,7 @@
       </c>
       <c r="AD121" t="inlineStr">
         <is>
-          <t>N2 - Tienvt16, Anhnt631</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE121">
@@ -19965,7 +19965,7 @@
       </c>
       <c r="AD122" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE122">
@@ -20128,7 +20128,7 @@
       </c>
       <c r="AD123" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE123">
@@ -20286,7 +20286,7 @@
       </c>
       <c r="AD124" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE124">
@@ -20442,7 +20442,7 @@
       </c>
       <c r="AD125" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE125">
@@ -20605,7 +20605,7 @@
       </c>
       <c r="AD126" t="inlineStr">
         <is>
-          <t>N2 - Tienvt16, Anhnt631</t>
+          <t>N4 - Nhungntt27, Anhnt631</t>
         </is>
       </c>
       <c r="AE126">
@@ -20768,7 +20768,7 @@
       </c>
       <c r="AD127" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE127">
@@ -20926,7 +20926,7 @@
       </c>
       <c r="AD128" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE128">
@@ -21089,7 +21089,7 @@
       </c>
       <c r="AD129" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N1 - Congnd15, Tienvt16</t>
         </is>
       </c>
       <c r="AE129">
@@ -21252,7 +21252,7 @@
       </c>
       <c r="AD130" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N1 - Congnd15, Tienvt16</t>
         </is>
       </c>
       <c r="AE130">
@@ -21410,7 +21410,7 @@
       </c>
       <c r="AD131" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE131">
@@ -21568,7 +21568,7 @@
       </c>
       <c r="AD132" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE132">
@@ -21731,7 +21731,7 @@
       </c>
       <c r="AD133" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE133">
@@ -21894,7 +21894,7 @@
       </c>
       <c r="AD134" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE134">
@@ -22057,7 +22057,7 @@
       </c>
       <c r="AD135" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N1 - Congnd15, Tienvt16</t>
         </is>
       </c>
       <c r="AE135">
@@ -22218,7 +22218,7 @@
       </c>
       <c r="AD136" t="inlineStr">
         <is>
-          <t>N2 - Tienvt16, Anhnt631</t>
+          <t>N1 - Congnd15, Tienvt16</t>
         </is>
       </c>
       <c r="AE136">
@@ -22376,7 +22376,7 @@
       </c>
       <c r="AD137" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE137">
@@ -22528,7 +22528,7 @@
       </c>
       <c r="AD138" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE138">
@@ -22691,7 +22691,7 @@
       </c>
       <c r="AD139" t="inlineStr">
         <is>
-          <t>N2 - Tienvt16, Anhnt631</t>
+          <t>N4 - Nhungntt27, Anhnt631</t>
         </is>
       </c>
       <c r="AE139">
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AD140" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N1 - Congnd15, Tienvt16</t>
         </is>
       </c>
       <c r="AE140">
@@ -23017,7 +23017,7 @@
       </c>
       <c r="AD141" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE141">
@@ -23180,7 +23180,7 @@
       </c>
       <c r="AD142" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE142">
@@ -23338,7 +23338,7 @@
       </c>
       <c r="AD143" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE143">
@@ -23499,7 +23499,7 @@
       </c>
       <c r="AD144" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N4 - Nhungntt27, Anhnt631</t>
         </is>
       </c>
       <c r="AE144">
@@ -23662,7 +23662,7 @@
       </c>
       <c r="AD145" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE145">
@@ -23825,7 +23825,7 @@
       </c>
       <c r="AD146" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N1 - Congnd15, Tienvt16</t>
         </is>
       </c>
       <c r="AE146">
@@ -23983,7 +23983,7 @@
       </c>
       <c r="AD147" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE147">
@@ -24145,7 +24145,7 @@
       </c>
       <c r="AD148" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE148">
@@ -24308,7 +24308,7 @@
       </c>
       <c r="AD149" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE149">
@@ -24466,7 +24466,7 @@
       </c>
       <c r="AD150" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE150">
@@ -24629,7 +24629,7 @@
       </c>
       <c r="AD151" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE151">
@@ -24792,7 +24792,7 @@
       </c>
       <c r="AD152" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE152">
@@ -24953,7 +24953,7 @@
       </c>
       <c r="AD153" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE153">
@@ -25116,7 +25116,7 @@
       </c>
       <c r="AD154" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE154">
@@ -25274,7 +25274,7 @@
       </c>
       <c r="AD155" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE155">
@@ -25430,7 +25430,7 @@
       </c>
       <c r="AD156" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE156">
@@ -25591,7 +25591,7 @@
       </c>
       <c r="AD157" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE157">
@@ -25754,7 +25754,7 @@
       </c>
       <c r="AD158" t="inlineStr">
         <is>
-          <t>N2 - Tienvt16, Anhnt631</t>
+          <t>N4 - Nhungntt27, Anhnt631</t>
         </is>
       </c>
       <c r="AE158">
@@ -25912,7 +25912,7 @@
       </c>
       <c r="AD159" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE159">
@@ -26075,7 +26075,7 @@
       </c>
       <c r="AD160" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE160">
@@ -26237,7 +26237,7 @@
       </c>
       <c r="AD161" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE161">
@@ -26400,7 +26400,7 @@
       </c>
       <c r="AD162" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE162">
@@ -26561,7 +26561,7 @@
       </c>
       <c r="AD163" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE163">
@@ -26722,7 +26722,7 @@
       </c>
       <c r="AD164" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N1 - Congnd15, Tienvt16</t>
         </is>
       </c>
       <c r="AE164">
@@ -26885,7 +26885,7 @@
       </c>
       <c r="AD165" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE165">
@@ -27048,7 +27048,7 @@
       </c>
       <c r="AD166" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE166">
@@ -27210,7 +27210,7 @@
       </c>
       <c r="AD167" t="inlineStr">
         <is>
-          <t>N2 - Tienvt16, Anhnt631</t>
+          <t>N4 - Nhungntt27, Anhnt631</t>
         </is>
       </c>
       <c r="AE167">
@@ -27367,7 +27367,7 @@
       </c>
       <c r="AD168" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE168">
@@ -27530,7 +27530,7 @@
       </c>
       <c r="AD169" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE169">
@@ -27688,7 +27688,7 @@
       </c>
       <c r="AD170" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE170">
@@ -27851,7 +27851,7 @@
       </c>
       <c r="AD171" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE171">
@@ -28008,7 +28008,7 @@
       </c>
       <c r="AD172" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE172">
@@ -28172,7 +28172,7 @@
       </c>
       <c r="AD173" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE173">
@@ -28329,7 +28329,7 @@
       </c>
       <c r="AD174" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE174">
@@ -28492,7 +28492,7 @@
       </c>
       <c r="AD175" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE175">
@@ -28655,7 +28655,7 @@
       </c>
       <c r="AD176" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE176">
@@ -28816,7 +28816,7 @@
       </c>
       <c r="AD177" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE177">
@@ -28979,7 +28979,7 @@
       </c>
       <c r="AD178" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE178">
@@ -29141,7 +29141,7 @@
       </c>
       <c r="AD179" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE179">
@@ -29297,7 +29297,7 @@
       </c>
       <c r="AD180" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE180">
@@ -29460,7 +29460,7 @@
       </c>
       <c r="AD181" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE181">
@@ -29621,7 +29621,7 @@
       </c>
       <c r="AD182" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE182">
@@ -29784,7 +29784,7 @@
       </c>
       <c r="AD183" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE183">
@@ -29947,7 +29947,7 @@
       </c>
       <c r="AD184" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE184">
@@ -30103,7 +30103,7 @@
       </c>
       <c r="AD185" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE185">
@@ -30266,7 +30266,7 @@
       </c>
       <c r="AD186" t="inlineStr">
         <is>
-          <t>N2 - Tienvt16, Anhnt631</t>
+          <t>N4 - Nhungntt27, Anhnt631</t>
         </is>
       </c>
       <c r="AE186">
@@ -30429,7 +30429,7 @@
       </c>
       <c r="AD187" t="inlineStr">
         <is>
-          <t>N2 - Tienvt16, Anhnt631</t>
+          <t>N1 - Congnd15, Tienvt16</t>
         </is>
       </c>
       <c r="AE187">
@@ -30587,7 +30587,7 @@
       </c>
       <c r="AD188" t="inlineStr">
         <is>
-          <t>N2 - Tienvt16, Anhnt631</t>
+          <t>N1 - Congnd15, Tienvt16</t>
         </is>
       </c>
       <c r="AE188">
@@ -30750,7 +30750,7 @@
       </c>
       <c r="AD189" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE189">
@@ -30913,7 +30913,7 @@
       </c>
       <c r="AD190" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE190">
@@ -31069,7 +31069,7 @@
       </c>
       <c r="AD191" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE191">
@@ -31232,7 +31232,7 @@
       </c>
       <c r="AD192" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE192">
@@ -31394,7 +31394,7 @@
       </c>
       <c r="AD193" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE193">
@@ -31557,7 +31557,7 @@
       </c>
       <c r="AD194" t="inlineStr">
         <is>
-          <t>N2 - Tienvt16, Anhnt631</t>
+          <t>N4 - Nhungntt27, Anhnt631</t>
         </is>
       </c>
       <c r="AE194">
@@ -31713,7 +31713,7 @@
       </c>
       <c r="AD195" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE195">
@@ -31876,7 +31876,7 @@
       </c>
       <c r="AD196" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE196">
@@ -32032,7 +32032,7 @@
       </c>
       <c r="AD197" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE197">
@@ -32195,7 +32195,7 @@
       </c>
       <c r="AD198" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N1 - Congnd15, Tienvt16</t>
         </is>
       </c>
       <c r="AE198">
@@ -32358,7 +32358,7 @@
       </c>
       <c r="AD199" t="inlineStr">
         <is>
-          <t>N2 - Tienvt16, Anhnt631</t>
+          <t>N4 - Nhungntt27, Anhnt631</t>
         </is>
       </c>
       <c r="AE199">
@@ -32521,7 +32521,7 @@
       </c>
       <c r="AD200" t="inlineStr">
         <is>
-          <t>N2 - Tienvt16, Anhnt631</t>
+          <t>N1 - Congnd15, Tienvt16</t>
         </is>
       </c>
       <c r="AE200">
@@ -32684,7 +32684,7 @@
       </c>
       <c r="AD201" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE201">
@@ -32847,7 +32847,7 @@
       </c>
       <c r="AD202" t="inlineStr">
         <is>
-          <t>N2 - Tienvt16, Anhnt631</t>
+          <t>N1 - Congnd15, Tienvt16</t>
         </is>
       </c>
       <c r="AE202">
@@ -33010,7 +33010,7 @@
       </c>
       <c r="AD203" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE203">
@@ -33166,7 +33166,7 @@
       </c>
       <c r="AD204" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE204">
@@ -33322,7 +33322,7 @@
       </c>
       <c r="AD205" t="inlineStr">
         <is>
-          <t>N2 - Tienvt16, Anhnt631</t>
+          <t>N1 - Congnd15, Tienvt16</t>
         </is>
       </c>
       <c r="AE205">
@@ -33478,7 +33478,7 @@
       </c>
       <c r="AD206" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE206">
@@ -33641,7 +33641,7 @@
       </c>
       <c r="AD207" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE207">
@@ -33804,7 +33804,7 @@
       </c>
       <c r="AD208" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE208">
@@ -33967,7 +33967,7 @@
       </c>
       <c r="AD209" t="inlineStr">
         <is>
-          <t>N2 - Tienvt16, Anhnt631</t>
+          <t>N4 - Nhungntt27, Anhnt631</t>
         </is>
       </c>
       <c r="AE209">
@@ -34123,7 +34123,7 @@
       </c>
       <c r="AD210" t="inlineStr">
         <is>
-          <t>N2 - Tienvt16, Anhnt631</t>
+          <t>N1 - Congnd15, Tienvt16</t>
         </is>
       </c>
       <c r="AE210">
@@ -34285,7 +34285,7 @@
       </c>
       <c r="AD211" t="inlineStr">
         <is>
-          <t>N2 - Tienvt16, Anhnt631</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE211">
@@ -34448,7 +34448,7 @@
       </c>
       <c r="AD212" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE212">
@@ -34606,7 +34606,7 @@
       </c>
       <c r="AD213" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE213">
@@ -34764,7 +34764,7 @@
       </c>
       <c r="AD214" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE214">
@@ -34927,7 +34927,7 @@
       </c>
       <c r="AD215" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE215">
@@ -35089,7 +35089,7 @@
       </c>
       <c r="AD216" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE216">
@@ -35245,7 +35245,7 @@
       </c>
       <c r="AD217" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE217">
@@ -35407,7 +35407,7 @@
       </c>
       <c r="AD218" t="inlineStr">
         <is>
-          <t>N2 - Tienvt16, Anhnt631</t>
+          <t>N1 - Congnd15, Tienvt16</t>
         </is>
       </c>
       <c r="AE218">
@@ -35570,7 +35570,7 @@
       </c>
       <c r="AD219" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE219">
@@ -35726,7 +35726,7 @@
       </c>
       <c r="AD220" t="inlineStr">
         <is>
-          <t>N2 - Tienvt16, Anhnt631</t>
+          <t>N1 - Congnd15, Tienvt16</t>
         </is>
       </c>
       <c r="AE220">
@@ -35889,7 +35889,7 @@
       </c>
       <c r="AD221" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N1 - Congnd15, Tienvt16</t>
         </is>
       </c>
       <c r="AE221">
@@ -36052,7 +36052,7 @@
       </c>
       <c r="AD222" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE222">
@@ -36215,7 +36215,7 @@
       </c>
       <c r="AD223" t="inlineStr">
         <is>
-          <t>N2 - Tienvt16, Anhnt631</t>
+          <t>N1 - Congnd15, Tienvt16</t>
         </is>
       </c>
       <c r="AE223">
@@ -36374,7 +36374,7 @@
       </c>
       <c r="AD224" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE224">
@@ -36530,7 +36530,7 @@
       </c>
       <c r="AD225" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE225">
@@ -36689,7 +36689,7 @@
       </c>
       <c r="AD226" t="inlineStr">
         <is>
-          <t>N2 - Tienvt16, Anhnt631</t>
+          <t>N1 - Congnd15, Tienvt16</t>
         </is>
       </c>
       <c r="AE226">
@@ -36852,7 +36852,7 @@
       </c>
       <c r="AD227" t="inlineStr">
         <is>
-          <t>N2 - Tienvt16, Anhnt631</t>
+          <t>N4 - Nhungntt27, Anhnt631</t>
         </is>
       </c>
       <c r="AE227">
@@ -37010,7 +37010,7 @@
       </c>
       <c r="AD228" t="inlineStr">
         <is>
-          <t>N2 - Tienvt16, Anhnt631</t>
+          <t>N4 - Nhungntt27, Anhnt631</t>
         </is>
       </c>
       <c r="AE228">
@@ -37173,7 +37173,7 @@
       </c>
       <c r="AD229" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE229">
@@ -37329,7 +37329,7 @@
       </c>
       <c r="AD230" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE230">
@@ -37492,7 +37492,7 @@
       </c>
       <c r="AD231" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE231">
@@ -37648,7 +37648,7 @@
       </c>
       <c r="AD232" t="inlineStr">
         <is>
-          <t>N2 - Tienvt16, Anhnt631</t>
+          <t>N4 - Nhungntt27, Anhnt631</t>
         </is>
       </c>
       <c r="AE232">
@@ -37806,7 +37806,7 @@
       </c>
       <c r="AD233" t="inlineStr">
         <is>
-          <t>N2 - Tienvt16, Anhnt631</t>
+          <t>N1 - Congnd15, Tienvt16</t>
         </is>
       </c>
       <c r="AE233">
@@ -37969,7 +37969,7 @@
       </c>
       <c r="AD234" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE234">
@@ -38132,7 +38132,7 @@
       </c>
       <c r="AD235" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE235">
@@ -38295,7 +38295,7 @@
       </c>
       <c r="AD236" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE236">
@@ -38452,7 +38452,7 @@
       </c>
       <c r="AD237" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE237">
@@ -38614,7 +38614,7 @@
       </c>
       <c r="AD238" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE238">
@@ -38770,7 +38770,7 @@
       </c>
       <c r="AD239" t="inlineStr">
         <is>
-          <t>N2 - Tienvt16, Anhnt631</t>
+          <t>N4 - Nhungntt27, Anhnt631</t>
         </is>
       </c>
       <c r="AE239">
@@ -38926,7 +38926,7 @@
       </c>
       <c r="AD240" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N1 - Congnd15, Tienvt16</t>
         </is>
       </c>
       <c r="AE240">
@@ -39089,7 +39089,7 @@
       </c>
       <c r="AD241" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE241">
@@ -39252,7 +39252,7 @@
       </c>
       <c r="AD242" t="inlineStr">
         <is>
-          <t>N2 - Tienvt16, Anhnt631</t>
+          <t>N4 - Nhungntt27, Anhnt631</t>
         </is>
       </c>
       <c r="AE242">
@@ -39410,7 +39410,7 @@
       </c>
       <c r="AD243" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE243">
@@ -39573,7 +39573,7 @@
       </c>
       <c r="AD244" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE244">
@@ -39734,7 +39734,7 @@
       </c>
       <c r="AD245" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE245">
@@ -39892,7 +39892,7 @@
       </c>
       <c r="AD246" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE246">
@@ -40055,7 +40055,7 @@
       </c>
       <c r="AD247" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE247">
@@ -40221,7 +40221,7 @@
       </c>
       <c r="AD248" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE248">
@@ -40384,7 +40384,7 @@
       </c>
       <c r="AD249" t="inlineStr">
         <is>
-          <t>N2 - Tienvt16, Anhnt631</t>
+          <t>N4 - Nhungntt27, Anhnt631</t>
         </is>
       </c>
       <c r="AE249">
@@ -40548,7 +40548,7 @@
       </c>
       <c r="AD250" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE250">
@@ -40711,7 +40711,7 @@
       </c>
       <c r="AD251" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE251">
@@ -40875,7 +40875,7 @@
       </c>
       <c r="AD252" t="inlineStr">
         <is>
-          <t>N2 - Tienvt16, Anhnt631</t>
+          <t>N4 - Nhungntt27, Anhnt631</t>
         </is>
       </c>
       <c r="AE252">
@@ -41037,7 +41037,7 @@
       </c>
       <c r="AD253" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE253">
@@ -41200,7 +41200,7 @@
       </c>
       <c r="AD254" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE254">
@@ -41361,7 +41361,7 @@
       </c>
       <c r="AD255" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE255">
@@ -41520,7 +41520,7 @@
       </c>
       <c r="AD256" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE256">
@@ -41681,7 +41681,7 @@
       </c>
       <c r="AD257" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE257">
@@ -41844,7 +41844,7 @@
       </c>
       <c r="AD258" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N4 - Nhungntt27, Anhnt631</t>
         </is>
       </c>
       <c r="AE258">
@@ -42007,7 +42007,7 @@
       </c>
       <c r="AD259" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N1 - Congnd15, Tienvt16</t>
         </is>
       </c>
       <c r="AE259">
@@ -42169,7 +42169,7 @@
       </c>
       <c r="AD260" t="inlineStr">
         <is>
-          <t>N2 - Tienvt16, Anhnt631</t>
+          <t>N1 - Congnd15, Tienvt16</t>
         </is>
       </c>
       <c r="AE260">
@@ -42332,7 +42332,7 @@
       </c>
       <c r="AD261" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE261">
@@ -42494,7 +42494,7 @@
       </c>
       <c r="AD262" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE262">
@@ -42657,7 +42657,7 @@
       </c>
       <c r="AD263" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE263">
@@ -42820,7 +42820,7 @@
       </c>
       <c r="AD264" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE264">
@@ -42983,7 +42983,7 @@
       </c>
       <c r="AD265" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE265">
@@ -43139,7 +43139,7 @@
       </c>
       <c r="AD266" t="inlineStr">
         <is>
-          <t>N2 - Tienvt16, Anhnt631</t>
+          <t>N1 - Congnd15, Tienvt16</t>
         </is>
       </c>
       <c r="AE266">
@@ -43301,7 +43301,7 @@
       </c>
       <c r="AD267" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE267">
@@ -43464,7 +43464,7 @@
       </c>
       <c r="AD268" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N4 - Nhungntt27, Anhnt631</t>
         </is>
       </c>
       <c r="AE268">
@@ -43627,7 +43627,7 @@
       </c>
       <c r="AD269" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE269">
@@ -43790,7 +43790,7 @@
       </c>
       <c r="AD270" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE270">
@@ -43953,7 +43953,7 @@
       </c>
       <c r="AD271" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N4 - Nhungntt27, Anhnt631</t>
         </is>
       </c>
       <c r="AE271">
@@ -44116,7 +44116,7 @@
       </c>
       <c r="AD272" t="inlineStr">
         <is>
-          <t>N2 - Tienvt16, Anhnt631</t>
+          <t>N1 - Congnd15, Tienvt16</t>
         </is>
       </c>
       <c r="AE272">
@@ -44279,7 +44279,7 @@
       </c>
       <c r="AD273" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE273">
@@ -44436,7 +44436,7 @@
       </c>
       <c r="AD274" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE274">
@@ -44594,7 +44594,7 @@
       </c>
       <c r="AD275" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE275">
@@ -44755,7 +44755,7 @@
       </c>
       <c r="AD276" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N1 - Congnd15, Tienvt16</t>
         </is>
       </c>
       <c r="AE276">
@@ -44911,7 +44911,7 @@
       </c>
       <c r="AD277" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE277">
@@ -45074,7 +45074,7 @@
       </c>
       <c r="AD278" t="inlineStr">
         <is>
-          <t>N2 - Tienvt16, Anhnt631</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE278">
@@ -45237,7 +45237,7 @@
       </c>
       <c r="AD279" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE279">
@@ -45400,7 +45400,7 @@
       </c>
       <c r="AD280" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE280">
@@ -45562,7 +45562,7 @@
       </c>
       <c r="AD281" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE281">
@@ -45725,7 +45725,7 @@
       </c>
       <c r="AD282" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE282">
@@ -45888,7 +45888,7 @@
       </c>
       <c r="AD283" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE283">
@@ -46051,7 +46051,7 @@
       </c>
       <c r="AD284" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE284">
@@ -46214,7 +46214,7 @@
       </c>
       <c r="AD285" t="inlineStr">
         <is>
-          <t>N2 - Tienvt16, Anhnt631</t>
+          <t>N1 - Congnd15, Tienvt16</t>
         </is>
       </c>
       <c r="AE285">
@@ -46376,7 +46376,7 @@
       </c>
       <c r="AD286" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE286">
@@ -46539,7 +46539,7 @@
       </c>
       <c r="AD287" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE287">
@@ -46702,7 +46702,7 @@
       </c>
       <c r="AD288" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE288">
@@ -46866,7 +46866,7 @@
       </c>
       <c r="AD289" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE289">
@@ -47029,7 +47029,7 @@
       </c>
       <c r="AD290" t="inlineStr">
         <is>
-          <t>N2 - Tienvt16, Anhnt631</t>
+          <t>N1 - Congnd15, Tienvt16</t>
         </is>
       </c>
       <c r="AE290">
@@ -47192,7 +47192,7 @@
       </c>
       <c r="AD291" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE291">
@@ -47355,7 +47355,7 @@
       </c>
       <c r="AD292" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE292">
@@ -47519,7 +47519,7 @@
       </c>
       <c r="AD293" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE293">
@@ -47682,7 +47682,7 @@
       </c>
       <c r="AD294" t="inlineStr">
         <is>
-          <t>N2 - Tienvt16, Anhnt631</t>
+          <t>N4 - Nhungntt27, Anhnt631</t>
         </is>
       </c>
       <c r="AE294">
@@ -47840,7 +47840,7 @@
       </c>
       <c r="AD295" t="inlineStr">
         <is>
-          <t>N2 - Tienvt16, Anhnt631</t>
+          <t>N1 - Congnd15, Tienvt16</t>
         </is>
       </c>
       <c r="AE295">
@@ -48003,7 +48003,7 @@
       </c>
       <c r="AD296" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE296">
@@ -48166,7 +48166,7 @@
       </c>
       <c r="AD297" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE297">
@@ -48328,7 +48328,7 @@
       </c>
       <c r="AD298" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE298">
@@ -48491,7 +48491,7 @@
       </c>
       <c r="AD299" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N4 - Nhungntt27, Anhnt631</t>
         </is>
       </c>
       <c r="AE299">
@@ -48654,7 +48654,7 @@
       </c>
       <c r="AD300" t="inlineStr">
         <is>
-          <t>N2 - Tienvt16, Anhnt631</t>
+          <t>N4 - Nhungntt27, Anhnt631</t>
         </is>
       </c>
       <c r="AE300">
@@ -48817,7 +48817,7 @@
       </c>
       <c r="AD301" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE301">
@@ -48980,7 +48980,7 @@
       </c>
       <c r="AD302" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE302">
@@ -49138,7 +49138,7 @@
       </c>
       <c r="AD303" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE303">
@@ -49301,7 +49301,7 @@
       </c>
       <c r="AD304" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE304">
@@ -49464,7 +49464,7 @@
       </c>
       <c r="AD305" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N4 - Nhungntt27, Anhnt631</t>
         </is>
       </c>
       <c r="AE305">
@@ -49627,7 +49627,7 @@
       </c>
       <c r="AD306" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE306">
@@ -49785,7 +49785,7 @@
       </c>
       <c r="AD307" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE307">
@@ -49948,7 +49948,7 @@
       </c>
       <c r="AD308" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE308">
@@ -50111,7 +50111,7 @@
       </c>
       <c r="AD309" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE309">
@@ -50274,7 +50274,7 @@
       </c>
       <c r="AD310" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE310">
@@ -50438,7 +50438,7 @@
       </c>
       <c r="AD311" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE311">
@@ -50601,7 +50601,7 @@
       </c>
       <c r="AD312" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE312">
@@ -50764,7 +50764,7 @@
       </c>
       <c r="AD313" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE313">
@@ -50927,7 +50927,7 @@
       </c>
       <c r="AD314" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE314">
@@ -51090,7 +51090,7 @@
       </c>
       <c r="AD315" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE315">
@@ -51253,7 +51253,7 @@
       </c>
       <c r="AD316" t="inlineStr">
         <is>
-          <t>N2 - Tienvt16, Anhnt631</t>
+          <t>N1 - Congnd15, Tienvt16</t>
         </is>
       </c>
       <c r="AE316">
@@ -51411,7 +51411,7 @@
       </c>
       <c r="AD317" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE317">
@@ -51574,7 +51574,7 @@
       </c>
       <c r="AD318" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE318">
@@ -51737,7 +51737,7 @@
       </c>
       <c r="AD319" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE319">
@@ -51898,7 +51898,7 @@
       </c>
       <c r="AD320" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AE320">
@@ -52061,7 +52061,7 @@
       </c>
       <c r="AD321" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE321">
@@ -52227,7 +52227,7 @@
       </c>
       <c r="AD322" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AE322">

--- a/data/5.R_pakh_hoan_thanh.xlsx
+++ b/data/5.R_pakh_hoan_thanh.xlsx
@@ -662,7 +662,7 @@
         <v>46217</v>
       </c>
       <c r="AA2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>46217</v>
       </c>
       <c r="AA3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>46217</v>
       </c>
       <c r="AA4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         <v>46217</v>
       </c>
       <c r="AA5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>46217</v>
       </c>
       <c r="AA6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>46217</v>
       </c>
       <c r="AA7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>46217</v>
       </c>
       <c r="AA8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>46217</v>
       </c>
       <c r="AA9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>46216</v>
       </c>
       <c r="AA10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
@@ -2113,7 +2113,7 @@
         <v>46216</v>
       </c>
       <c r="AA11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>46216</v>
       </c>
       <c r="AA12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>46216</v>
       </c>
       <c r="AA13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>46216</v>
       </c>
       <c r="AA14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
@@ -2753,7 +2753,7 @@
         <v>46216</v>
       </c>
       <c r="AA15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         <v>46216</v>
       </c>
       <c r="AA16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>46216</v>
       </c>
       <c r="AA17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>46216</v>
       </c>
       <c r="AA18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
@@ -3400,7 +3400,7 @@
         <v>46216</v>
       </c>
       <c r="AA19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
@@ -3563,7 +3563,7 @@
         <v>46216</v>
       </c>
       <c r="AA20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         <v>46216</v>
       </c>
       <c r="AA21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
@@ -3882,7 +3882,7 @@
         <v>46216</v>
       </c>
       <c r="AA22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
@@ -4044,7 +4044,7 @@
         <v>46217</v>
       </c>
       <c r="AA23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>46217</v>
       </c>
       <c r="AA24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
         <v>46217</v>
       </c>
       <c r="AA25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
@@ -4520,7 +4520,7 @@
         <v>46216</v>
       </c>
       <c r="AA26">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
@@ -4676,7 +4676,7 @@
         <v>46216</v>
       </c>
       <c r="AA27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         <v>46216</v>
       </c>
       <c r="AA28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
@@ -4995,7 +4995,7 @@
         <v>46216</v>
       </c>
       <c r="AA29">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         <v>46216</v>
       </c>
       <c r="AA30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
@@ -5316,7 +5316,7 @@
         <v>46216</v>
       </c>
       <c r="AA31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
@@ -5479,7 +5479,7 @@
         <v>46216</v>
       </c>
       <c r="AA32">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
@@ -5642,7 +5642,7 @@
         <v>46216</v>
       </c>
       <c r="AA33">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
@@ -5805,7 +5805,7 @@
         <v>46216</v>
       </c>
       <c r="AA34">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>46216</v>
       </c>
       <c r="AA35">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
@@ -6119,7 +6119,7 @@
         <v>46216</v>
       </c>
       <c r="AA36">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
@@ -6282,7 +6282,7 @@
         <v>46216</v>
       </c>
       <c r="AA37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
@@ -6439,7 +6439,7 @@
         <v>46216</v>
       </c>
       <c r="AA38">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         <v>46216</v>
       </c>
       <c r="AA39">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
@@ -6765,7 +6765,7 @@
         <v>46216</v>
       </c>
       <c r="AA40">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
@@ -6923,7 +6923,7 @@
         <v>46216</v>
       </c>
       <c r="AA41">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
@@ -7085,7 +7085,7 @@
         <v>46216</v>
       </c>
       <c r="AA42">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
@@ -7241,7 +7241,7 @@
         <v>46216</v>
       </c>
       <c r="AA43">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
@@ -7397,7 +7397,7 @@
         <v>46216</v>
       </c>
       <c r="AA44">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
@@ -7560,7 +7560,7 @@
         <v>46216</v>
       </c>
       <c r="AA45">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
@@ -7723,7 +7723,7 @@
         <v>46216</v>
       </c>
       <c r="AA46">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         <v>46216</v>
       </c>
       <c r="AA47">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
@@ -8042,7 +8042,7 @@
         <v>46216</v>
       </c>
       <c r="AA48">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
@@ -8203,7 +8203,7 @@
         <v>46216</v>
       </c>
       <c r="AA49">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         <v>46216</v>
       </c>
       <c r="AA50">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         <v>46216</v>
       </c>
       <c r="AA51">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
@@ -8692,7 +8692,7 @@
         <v>46216</v>
       </c>
       <c r="AA52">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
@@ -8850,7 +8850,7 @@
         <v>46216</v>
       </c>
       <c r="AA53">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
@@ -9008,7 +9008,7 @@
         <v>46216</v>
       </c>
       <c r="AA54">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
@@ -9171,7 +9171,7 @@
         <v>46216</v>
       </c>
       <c r="AA55">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         <v>46216</v>
       </c>
       <c r="AA56">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
@@ -9497,7 +9497,7 @@
         <v>46216</v>
       </c>
       <c r="AA57">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
@@ -9660,7 +9660,7 @@
         <v>46216</v>
       </c>
       <c r="AA58">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
@@ -9822,7 +9822,7 @@
         <v>46216</v>
       </c>
       <c r="AA59">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
@@ -9985,7 +9985,7 @@
         <v>46216</v>
       </c>
       <c r="AA60">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
@@ -10147,7 +10147,7 @@
         <v>46216</v>
       </c>
       <c r="AA61">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
@@ -10305,7 +10305,7 @@
         <v>46213</v>
       </c>
       <c r="AA62">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
@@ -10468,7 +10468,7 @@
         <v>46213</v>
       </c>
       <c r="AA63">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
@@ -10631,7 +10631,7 @@
         <v>46213</v>
       </c>
       <c r="AA64">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
@@ -10787,7 +10787,7 @@
         <v>46213</v>
       </c>
       <c r="AA65">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
@@ -10946,7 +10946,7 @@
         <v>46213</v>
       </c>
       <c r="AA66">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
@@ -11104,7 +11104,7 @@
         <v>46213</v>
       </c>
       <c r="AA67">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
@@ -11267,7 +11267,7 @@
         <v>46216</v>
       </c>
       <c r="AA68">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
@@ -11430,7 +11430,7 @@
         <v>46213</v>
       </c>
       <c r="AA69">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
@@ -11588,7 +11588,7 @@
         <v>46213</v>
       </c>
       <c r="AA70">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
@@ -11751,7 +11751,7 @@
         <v>46213</v>
       </c>
       <c r="AA71">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
@@ -11914,7 +11914,7 @@
         <v>46213</v>
       </c>
       <c r="AA72">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
@@ -12077,7 +12077,7 @@
         <v>46213</v>
       </c>
       <c r="AA73">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
@@ -12235,7 +12235,7 @@
         <v>46213</v>
       </c>
       <c r="AA74">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
@@ -12398,7 +12398,7 @@
         <v>46213</v>
       </c>
       <c r="AA75">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
@@ -12556,7 +12556,7 @@
         <v>46213</v>
       </c>
       <c r="AA76">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
@@ -12712,7 +12712,7 @@
         <v>46213</v>
       </c>
       <c r="AA77">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
@@ -12875,7 +12875,7 @@
         <v>46213</v>
       </c>
       <c r="AA78">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
@@ -13038,7 +13038,7 @@
         <v>46213</v>
       </c>
       <c r="AA79">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
@@ -13201,7 +13201,7 @@
         <v>46213</v>
       </c>
       <c r="AA80">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
@@ -13364,7 +13364,7 @@
         <v>46213</v>
       </c>
       <c r="AA81">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
@@ -13522,7 +13522,7 @@
         <v>46213</v>
       </c>
       <c r="AA82">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
@@ -13685,7 +13685,7 @@
         <v>46213</v>
       </c>
       <c r="AA83">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
@@ -13848,7 +13848,7 @@
         <v>46212</v>
       </c>
       <c r="AA84">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
@@ -14011,7 +14011,7 @@
         <v>46212</v>
       </c>
       <c r="AA85">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
@@ -14167,7 +14167,7 @@
         <v>46212</v>
       </c>
       <c r="AA86">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
@@ -14330,7 +14330,7 @@
         <v>46212</v>
       </c>
       <c r="AA87">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
@@ -14492,7 +14492,7 @@
         <v>46212</v>
       </c>
       <c r="AA88">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
@@ -14655,7 +14655,7 @@
         <v>46212</v>
       </c>
       <c r="AA89">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
@@ -14818,7 +14818,7 @@
         <v>46212</v>
       </c>
       <c r="AA90">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
@@ -14981,7 +14981,7 @@
         <v>46213</v>
       </c>
       <c r="AA91">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
@@ -15137,7 +15137,7 @@
         <v>46212</v>
       </c>
       <c r="AA92">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
@@ -15295,7 +15295,7 @@
         <v>46212</v>
       </c>
       <c r="AA93">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
@@ -15457,7 +15457,7 @@
         <v>46212</v>
       </c>
       <c r="AA94">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
@@ -15613,7 +15613,7 @@
         <v>46212</v>
       </c>
       <c r="AA95">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
@@ -15771,7 +15771,7 @@
         <v>46212</v>
       </c>
       <c r="AA96">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
@@ -15934,7 +15934,7 @@
         <v>46212</v>
       </c>
       <c r="AA97">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
@@ -16090,7 +16090,7 @@
         <v>46212</v>
       </c>
       <c r="AA98">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
@@ -16248,7 +16248,7 @@
         <v>46212</v>
       </c>
       <c r="AA99">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
@@ -16411,7 +16411,7 @@
         <v>46212</v>
       </c>
       <c r="AA100">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
@@ -16574,7 +16574,7 @@
         <v>46212</v>
       </c>
       <c r="AA101">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
@@ -16737,7 +16737,7 @@
         <v>46212</v>
       </c>
       <c r="AA102">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
@@ -16900,7 +16900,7 @@
         <v>46211</v>
       </c>
       <c r="AA103">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
@@ -17056,7 +17056,7 @@
         <v>46211</v>
       </c>
       <c r="AA104">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
@@ -17214,7 +17214,7 @@
         <v>46211</v>
       </c>
       <c r="AA105">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
@@ -17377,7 +17377,7 @@
         <v>46211</v>
       </c>
       <c r="AA106">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
@@ -17535,7 +17535,7 @@
         <v>46211</v>
       </c>
       <c r="AA107">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
@@ -17698,7 +17698,7 @@
         <v>46211</v>
       </c>
       <c r="AA108">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
@@ -17861,7 +17861,7 @@
         <v>46211</v>
       </c>
       <c r="AA109">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
@@ -18024,7 +18024,7 @@
         <v>46211</v>
       </c>
       <c r="AA110">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
@@ -18182,7 +18182,7 @@
         <v>46212</v>
       </c>
       <c r="AA111">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB111" t="inlineStr">
         <is>
@@ -18345,7 +18345,7 @@
         <v>46212</v>
       </c>
       <c r="AA112">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB112" t="inlineStr">
         <is>
@@ -18508,7 +18508,7 @@
         <v>46212</v>
       </c>
       <c r="AA113">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB113" t="inlineStr">
         <is>
@@ -18671,7 +18671,7 @@
         <v>46212</v>
       </c>
       <c r="AA114">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB114" t="inlineStr">
         <is>
@@ -18834,7 +18834,7 @@
         <v>46212</v>
       </c>
       <c r="AA115">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB115" t="inlineStr">
         <is>
@@ -18992,7 +18992,7 @@
         <v>46211</v>
       </c>
       <c r="AA116">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB116" t="inlineStr">
         <is>
@@ -19148,7 +19148,7 @@
         <v>46211</v>
       </c>
       <c r="AA117">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB117" t="inlineStr">
         <is>
@@ -19304,7 +19304,7 @@
         <v>46211</v>
       </c>
       <c r="AA118">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB118" t="inlineStr">
         <is>
@@ -19467,7 +19467,7 @@
         <v>46211</v>
       </c>
       <c r="AA119">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB119" t="inlineStr">
         <is>
@@ -19630,7 +19630,7 @@
         <v>46211</v>
       </c>
       <c r="AA120">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB120" t="inlineStr">
         <is>
@@ -19793,7 +19793,7 @@
         <v>46211</v>
       </c>
       <c r="AA121">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB121" t="inlineStr">
         <is>
@@ -19951,7 +19951,7 @@
         <v>46211</v>
       </c>
       <c r="AA122">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB122" t="inlineStr">
         <is>
@@ -20114,7 +20114,7 @@
         <v>46211</v>
       </c>
       <c r="AA123">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB123" t="inlineStr">
         <is>
@@ -20272,7 +20272,7 @@
         <v>46211</v>
       </c>
       <c r="AA124">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB124" t="inlineStr">
         <is>
@@ -20428,7 +20428,7 @@
         <v>46211</v>
       </c>
       <c r="AA125">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB125" t="inlineStr">
         <is>
@@ -20591,7 +20591,7 @@
         <v>46211</v>
       </c>
       <c r="AA126">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB126" t="inlineStr">
         <is>
@@ -20754,7 +20754,7 @@
         <v>46211</v>
       </c>
       <c r="AA127">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB127" t="inlineStr">
         <is>
@@ -20912,7 +20912,7 @@
         <v>46211</v>
       </c>
       <c r="AA128">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB128" t="inlineStr">
         <is>
@@ -21075,7 +21075,7 @@
         <v>46211</v>
       </c>
       <c r="AA129">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB129" t="inlineStr">
         <is>
@@ -21238,7 +21238,7 @@
         <v>46210</v>
       </c>
       <c r="AA130">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB130" t="inlineStr">
         <is>
@@ -21396,7 +21396,7 @@
         <v>46211</v>
       </c>
       <c r="AA131">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB131" t="inlineStr">
         <is>
@@ -21554,7 +21554,7 @@
         <v>46210</v>
       </c>
       <c r="AA132">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB132" t="inlineStr">
         <is>
@@ -21717,7 +21717,7 @@
         <v>46210</v>
       </c>
       <c r="AA133">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB133" t="inlineStr">
         <is>
@@ -21880,7 +21880,7 @@
         <v>46210</v>
       </c>
       <c r="AA134">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB134" t="inlineStr">
         <is>
@@ -22043,7 +22043,7 @@
         <v>46210</v>
       </c>
       <c r="AA135">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB135" t="inlineStr">
         <is>
@@ -22204,7 +22204,7 @@
         <v>46210</v>
       </c>
       <c r="AA136">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB136" t="inlineStr">
         <is>
@@ -22362,7 +22362,7 @@
         <v>46210</v>
       </c>
       <c r="AA137">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB137" t="inlineStr">
         <is>
@@ -22677,7 +22677,7 @@
         <v>46210</v>
       </c>
       <c r="AA139">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB139" t="inlineStr">
         <is>
@@ -22840,7 +22840,7 @@
         <v>46210</v>
       </c>
       <c r="AA140">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB140" t="inlineStr">
         <is>
@@ -23003,7 +23003,7 @@
         <v>46210</v>
       </c>
       <c r="AA141">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB141" t="inlineStr">
         <is>
@@ -23166,7 +23166,7 @@
         <v>46210</v>
       </c>
       <c r="AA142">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB142" t="inlineStr">
         <is>
@@ -23324,7 +23324,7 @@
         <v>46209</v>
       </c>
       <c r="AA143">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB143" t="inlineStr">
         <is>
@@ -23485,7 +23485,7 @@
         <v>46209</v>
       </c>
       <c r="AA144">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB144" t="inlineStr">
         <is>
@@ -23648,7 +23648,7 @@
         <v>46209</v>
       </c>
       <c r="AA145">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB145" t="inlineStr">
         <is>
@@ -23811,7 +23811,7 @@
         <v>46209</v>
       </c>
       <c r="AA146">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB146" t="inlineStr">
         <is>
@@ -23969,7 +23969,7 @@
         <v>46209</v>
       </c>
       <c r="AA147">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB147" t="inlineStr">
         <is>
@@ -24131,7 +24131,7 @@
         <v>46210</v>
       </c>
       <c r="AA148">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB148" t="inlineStr">
         <is>
@@ -24294,7 +24294,7 @@
         <v>46210</v>
       </c>
       <c r="AA149">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB149" t="inlineStr">
         <is>
@@ -24452,7 +24452,7 @@
         <v>46210</v>
       </c>
       <c r="AA150">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB150" t="inlineStr">
         <is>
@@ -24615,7 +24615,7 @@
         <v>46210</v>
       </c>
       <c r="AA151">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB151" t="inlineStr">
         <is>
@@ -24778,7 +24778,7 @@
         <v>46210</v>
       </c>
       <c r="AA152">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB152" t="inlineStr">
         <is>
@@ -24939,7 +24939,7 @@
         <v>46210</v>
       </c>
       <c r="AA153">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB153" t="inlineStr">
         <is>
@@ -25102,7 +25102,7 @@
         <v>46209</v>
       </c>
       <c r="AA154">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB154" t="inlineStr">
         <is>
@@ -25260,7 +25260,7 @@
         <v>46209</v>
       </c>
       <c r="AA155">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB155" t="inlineStr">
         <is>
@@ -25416,7 +25416,7 @@
         <v>46209</v>
       </c>
       <c r="AA156">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB156" t="inlineStr">
         <is>
@@ -25577,7 +25577,7 @@
         <v>46209</v>
       </c>
       <c r="AA157">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB157" t="inlineStr">
         <is>
@@ -25740,7 +25740,7 @@
         <v>46209</v>
       </c>
       <c r="AA158">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB158" t="inlineStr">
         <is>
@@ -25898,7 +25898,7 @@
         <v>46209</v>
       </c>
       <c r="AA159">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB159" t="inlineStr">
         <is>
@@ -26061,7 +26061,7 @@
         <v>46209</v>
       </c>
       <c r="AA160">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB160" t="inlineStr">
         <is>
@@ -26223,7 +26223,7 @@
         <v>46209</v>
       </c>
       <c r="AA161">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB161" t="inlineStr">
         <is>
@@ -26386,7 +26386,7 @@
         <v>46209</v>
       </c>
       <c r="AA162">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB162" t="inlineStr">
         <is>
@@ -26547,7 +26547,7 @@
         <v>46209</v>
       </c>
       <c r="AA163">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB163" t="inlineStr">
         <is>
@@ -26708,7 +26708,7 @@
         <v>46209</v>
       </c>
       <c r="AA164">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB164" t="inlineStr">
         <is>
@@ -26871,7 +26871,7 @@
         <v>46209</v>
       </c>
       <c r="AA165">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB165" t="inlineStr">
         <is>
@@ -27034,7 +27034,7 @@
         <v>46209</v>
       </c>
       <c r="AA166">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB166" t="inlineStr">
         <is>
@@ -27196,7 +27196,7 @@
         <v>46209</v>
       </c>
       <c r="AA167">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB167" t="inlineStr">
         <is>
@@ -27353,7 +27353,7 @@
         <v>46209</v>
       </c>
       <c r="AA168">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB168" t="inlineStr">
         <is>
@@ -27516,7 +27516,7 @@
         <v>46209</v>
       </c>
       <c r="AA169">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB169" t="inlineStr">
         <is>
@@ -27674,7 +27674,7 @@
         <v>46209</v>
       </c>
       <c r="AA170">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB170" t="inlineStr">
         <is>
@@ -27837,7 +27837,7 @@
         <v>46209</v>
       </c>
       <c r="AA171">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB171" t="inlineStr">
         <is>
@@ -27994,7 +27994,7 @@
         <v>46209</v>
       </c>
       <c r="AA172">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB172" t="inlineStr">
         <is>
@@ -28158,7 +28158,7 @@
         <v>46209</v>
       </c>
       <c r="AA173">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB173" t="inlineStr">
         <is>
@@ -28315,7 +28315,7 @@
         <v>46209</v>
       </c>
       <c r="AA174">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB174" t="inlineStr">
         <is>
@@ -28478,7 +28478,7 @@
         <v>46209</v>
       </c>
       <c r="AA175">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB175" t="inlineStr">
         <is>
@@ -28641,7 +28641,7 @@
         <v>46209</v>
       </c>
       <c r="AA176">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB176" t="inlineStr">
         <is>
@@ -28802,7 +28802,7 @@
         <v>46209</v>
       </c>
       <c r="AA177">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB177" t="inlineStr">
         <is>
@@ -28965,7 +28965,7 @@
         <v>46209</v>
       </c>
       <c r="AA178">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB178" t="inlineStr">
         <is>
@@ -29127,7 +29127,7 @@
         <v>46209</v>
       </c>
       <c r="AA179">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB179" t="inlineStr">
         <is>
@@ -29283,7 +29283,7 @@
         <v>46209</v>
       </c>
       <c r="AA180">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB180" t="inlineStr">
         <is>
@@ -29446,7 +29446,7 @@
         <v>46209</v>
       </c>
       <c r="AA181">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB181" t="inlineStr">
         <is>
@@ -29607,7 +29607,7 @@
         <v>46209</v>
       </c>
       <c r="AA182">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB182" t="inlineStr">
         <is>
@@ -29770,7 +29770,7 @@
         <v>46209</v>
       </c>
       <c r="AA183">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB183" t="inlineStr">
         <is>
@@ -29933,7 +29933,7 @@
         <v>46209</v>
       </c>
       <c r="AA184">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB184" t="inlineStr">
         <is>
@@ -30089,7 +30089,7 @@
         <v>46209</v>
       </c>
       <c r="AA185">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB185" t="inlineStr">
         <is>
@@ -30252,7 +30252,7 @@
         <v>46209</v>
       </c>
       <c r="AA186">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB186" t="inlineStr">
         <is>
@@ -30415,7 +30415,7 @@
         <v>46209</v>
       </c>
       <c r="AA187">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB187" t="inlineStr">
         <is>
@@ -30573,7 +30573,7 @@
         <v>46209</v>
       </c>
       <c r="AA188">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB188" t="inlineStr">
         <is>
@@ -30736,7 +30736,7 @@
         <v>46209</v>
       </c>
       <c r="AA189">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB189" t="inlineStr">
         <is>
@@ -30899,7 +30899,7 @@
         <v>46209</v>
       </c>
       <c r="AA190">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB190" t="inlineStr">
         <is>
@@ -31055,7 +31055,7 @@
         <v>46209</v>
       </c>
       <c r="AA191">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB191" t="inlineStr">
         <is>
@@ -31218,7 +31218,7 @@
         <v>46209</v>
       </c>
       <c r="AA192">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB192" t="inlineStr">
         <is>
@@ -31380,7 +31380,7 @@
         <v>46209</v>
       </c>
       <c r="AA193">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB193" t="inlineStr">
         <is>
@@ -31543,7 +31543,7 @@
         <v>46209</v>
       </c>
       <c r="AA194">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB194" t="inlineStr">
         <is>
@@ -31699,7 +31699,7 @@
         <v>46209</v>
       </c>
       <c r="AA195">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB195" t="inlineStr">
         <is>
@@ -31862,7 +31862,7 @@
         <v>46209</v>
       </c>
       <c r="AA196">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB196" t="inlineStr">
         <is>
@@ -32018,7 +32018,7 @@
         <v>46209</v>
       </c>
       <c r="AA197">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB197" t="inlineStr">
         <is>
@@ -32181,7 +32181,7 @@
         <v>46209</v>
       </c>
       <c r="AA198">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB198" t="inlineStr">
         <is>
@@ -32344,7 +32344,7 @@
         <v>46209</v>
       </c>
       <c r="AA199">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB199" t="inlineStr">
         <is>
@@ -32507,7 +32507,7 @@
         <v>46209</v>
       </c>
       <c r="AA200">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB200" t="inlineStr">
         <is>
@@ -32670,7 +32670,7 @@
         <v>46209</v>
       </c>
       <c r="AA201">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB201" t="inlineStr">
         <is>
@@ -32833,7 +32833,7 @@
         <v>46206</v>
       </c>
       <c r="AA202">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AB202" t="inlineStr">
         <is>
@@ -32996,7 +32996,7 @@
         <v>46206</v>
       </c>
       <c r="AA203">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AB203" t="inlineStr">
         <is>
@@ -33152,7 +33152,7 @@
         <v>46206</v>
       </c>
       <c r="AA204">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AB204" t="inlineStr">
         <is>
@@ -33308,7 +33308,7 @@
         <v>46209</v>
       </c>
       <c r="AA205">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB205" t="inlineStr">
         <is>
@@ -33464,7 +33464,7 @@
         <v>46209</v>
       </c>
       <c r="AA206">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB206" t="inlineStr">
         <is>
@@ -33627,7 +33627,7 @@
         <v>46206</v>
       </c>
       <c r="AA207">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AB207" t="inlineStr">
         <is>
@@ -33790,7 +33790,7 @@
         <v>46206</v>
       </c>
       <c r="AA208">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AB208" t="inlineStr">
         <is>
@@ -33953,7 +33953,7 @@
         <v>46206</v>
       </c>
       <c r="AA209">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AB209" t="inlineStr">
         <is>
@@ -34109,7 +34109,7 @@
         <v>46206</v>
       </c>
       <c r="AA210">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AB210" t="inlineStr">
         <is>
@@ -34271,7 +34271,7 @@
         <v>46206</v>
       </c>
       <c r="AA211">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AB211" t="inlineStr">
         <is>
@@ -34434,7 +34434,7 @@
         <v>46205</v>
       </c>
       <c r="AA212">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AB212" t="inlineStr">
         <is>
@@ -34592,7 +34592,7 @@
         <v>46205</v>
       </c>
       <c r="AA213">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AB213" t="inlineStr">
         <is>
@@ -34750,7 +34750,7 @@
         <v>46205</v>
       </c>
       <c r="AA214">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AB214" t="inlineStr">
         <is>
@@ -34913,7 +34913,7 @@
         <v>46205</v>
       </c>
       <c r="AA215">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AB215" t="inlineStr">
         <is>
@@ -35075,7 +35075,7 @@
         <v>46205</v>
       </c>
       <c r="AA216">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AB216" t="inlineStr">
         <is>
@@ -35231,7 +35231,7 @@
         <v>46205</v>
       </c>
       <c r="AA217">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AB217" t="inlineStr">
         <is>
@@ -35393,7 +35393,7 @@
         <v>46205</v>
       </c>
       <c r="AA218">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AB218" t="inlineStr">
         <is>
@@ -35556,7 +35556,7 @@
         <v>46205</v>
       </c>
       <c r="AA219">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AB219" t="inlineStr">
         <is>
@@ -35712,7 +35712,7 @@
         <v>46206</v>
       </c>
       <c r="AA220">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AB220" t="inlineStr">
         <is>
@@ -35875,7 +35875,7 @@
         <v>46206</v>
       </c>
       <c r="AA221">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AB221" t="inlineStr">
         <is>
@@ -36038,7 +36038,7 @@
         <v>46206</v>
       </c>
       <c r="AA222">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AB222" t="inlineStr">
         <is>
@@ -36201,7 +36201,7 @@
         <v>46206</v>
       </c>
       <c r="AA223">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AB223" t="inlineStr">
         <is>
@@ -36360,7 +36360,7 @@
         <v>46206</v>
       </c>
       <c r="AA224">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AB224" t="inlineStr">
         <is>
@@ -36516,7 +36516,7 @@
         <v>46206</v>
       </c>
       <c r="AA225">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AB225" t="inlineStr">
         <is>
@@ -36675,7 +36675,7 @@
         <v>46206</v>
       </c>
       <c r="AA226">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AB226" t="inlineStr">
         <is>
@@ -36838,7 +36838,7 @@
         <v>46206</v>
       </c>
       <c r="AA227">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AB227" t="inlineStr">
         <is>
@@ -36996,7 +36996,7 @@
         <v>46206</v>
       </c>
       <c r="AA228">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AB228" t="inlineStr">
         <is>
@@ -37159,7 +37159,7 @@
         <v>46206</v>
       </c>
       <c r="AA229">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AB229" t="inlineStr">
         <is>
@@ -37315,7 +37315,7 @@
         <v>46205</v>
       </c>
       <c r="AA230">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AB230" t="inlineStr">
         <is>
@@ -37478,7 +37478,7 @@
         <v>46205</v>
       </c>
       <c r="AA231">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AB231" t="inlineStr">
         <is>
@@ -37634,7 +37634,7 @@
         <v>46205</v>
       </c>
       <c r="AA232">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AB232" t="inlineStr">
         <is>
@@ -37792,7 +37792,7 @@
         <v>46205</v>
       </c>
       <c r="AA233">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AB233" t="inlineStr">
         <is>
@@ -37955,7 +37955,7 @@
         <v>46205</v>
       </c>
       <c r="AA234">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AB234" t="inlineStr">
         <is>
@@ -38118,7 +38118,7 @@
         <v>46205</v>
       </c>
       <c r="AA235">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AB235" t="inlineStr">
         <is>
@@ -38281,7 +38281,7 @@
         <v>46204</v>
       </c>
       <c r="AA236">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AB236" t="inlineStr">
         <is>
@@ -38438,7 +38438,7 @@
         <v>46204</v>
       </c>
       <c r="AA237">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AB237" t="inlineStr">
         <is>
@@ -38600,7 +38600,7 @@
         <v>46204</v>
       </c>
       <c r="AA238">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AB238" t="inlineStr">
         <is>
@@ -38756,7 +38756,7 @@
         <v>46204</v>
       </c>
       <c r="AA239">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AB239" t="inlineStr">
         <is>
@@ -38912,7 +38912,7 @@
         <v>46204</v>
       </c>
       <c r="AA240">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AB240" t="inlineStr">
         <is>
@@ -39075,7 +39075,7 @@
         <v>46204</v>
       </c>
       <c r="AA241">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AB241" t="inlineStr">
         <is>
@@ -39238,7 +39238,7 @@
         <v>46204</v>
       </c>
       <c r="AA242">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AB242" t="inlineStr">
         <is>
@@ -39396,7 +39396,7 @@
         <v>46204</v>
       </c>
       <c r="AA243">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AB243" t="inlineStr">
         <is>
@@ -39559,7 +39559,7 @@
         <v>46204</v>
       </c>
       <c r="AA244">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AB244" t="inlineStr">
         <is>
@@ -39720,7 +39720,7 @@
         <v>46204</v>
       </c>
       <c r="AA245">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AB245" t="inlineStr">
         <is>
@@ -39878,7 +39878,7 @@
         <v>46204</v>
       </c>
       <c r="AA246">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AB246" t="inlineStr">
         <is>
@@ -40041,7 +40041,7 @@
         <v>46205</v>
       </c>
       <c r="AA247">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AB247" t="inlineStr">
         <is>
@@ -40207,7 +40207,7 @@
         <v>46204</v>
       </c>
       <c r="AA248">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AB248" t="inlineStr">
         <is>
@@ -40370,7 +40370,7 @@
         <v>46203</v>
       </c>
       <c r="AA249">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AB249" t="inlineStr">
         <is>
@@ -40534,7 +40534,7 @@
         <v>46203</v>
       </c>
       <c r="AA250">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AB250" t="inlineStr">
         <is>
@@ -40697,7 +40697,7 @@
         <v>46203</v>
       </c>
       <c r="AA251">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AB251" t="inlineStr">
         <is>
@@ -40861,7 +40861,7 @@
         <v>46205</v>
       </c>
       <c r="AA252">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AB252" t="inlineStr">
         <is>
@@ -41023,7 +41023,7 @@
         <v>46204</v>
       </c>
       <c r="AA253">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AB253" t="inlineStr">
         <is>
@@ -41186,7 +41186,7 @@
         <v>46204</v>
       </c>
       <c r="AA254">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AB254" t="inlineStr">
         <is>
@@ -41347,7 +41347,7 @@
         <v>46204</v>
       </c>
       <c r="AA255">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AB255" t="inlineStr">
         <is>
@@ -41506,7 +41506,7 @@
         <v>46204</v>
       </c>
       <c r="AA256">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AB256" t="inlineStr">
         <is>
@@ -41667,7 +41667,7 @@
         <v>46204</v>
       </c>
       <c r="AA257">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AB257" t="inlineStr">
         <is>
@@ -41830,7 +41830,7 @@
         <v>46204</v>
       </c>
       <c r="AA258">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AB258" t="inlineStr">
         <is>
@@ -41993,7 +41993,7 @@
         <v>46204</v>
       </c>
       <c r="AA259">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AB259" t="inlineStr">
         <is>
@@ -42155,7 +42155,7 @@
         <v>46203</v>
       </c>
       <c r="AA260">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AB260" t="inlineStr">
         <is>
@@ -42318,7 +42318,7 @@
         <v>46202</v>
       </c>
       <c r="AA261">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AB261" t="inlineStr">
         <is>
@@ -42480,7 +42480,7 @@
         <v>46202</v>
       </c>
       <c r="AA262">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AB262" t="inlineStr">
         <is>
@@ -42643,7 +42643,7 @@
         <v>46202</v>
       </c>
       <c r="AA263">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AB263" t="inlineStr">
         <is>
@@ -42806,7 +42806,7 @@
         <v>46203</v>
       </c>
       <c r="AA264">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AB264" t="inlineStr">
         <is>
@@ -42969,7 +42969,7 @@
         <v>46203</v>
       </c>
       <c r="AA265">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AB265" t="inlineStr">
         <is>
@@ -43125,7 +43125,7 @@
         <v>46203</v>
       </c>
       <c r="AA266">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AB266" t="inlineStr">
         <is>
@@ -43287,7 +43287,7 @@
         <v>46202</v>
       </c>
       <c r="AA267">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AB267" t="inlineStr">
         <is>
@@ -43450,7 +43450,7 @@
         <v>46202</v>
       </c>
       <c r="AA268">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AB268" t="inlineStr">
         <is>
@@ -43613,7 +43613,7 @@
         <v>46202</v>
       </c>
       <c r="AA269">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AB269" t="inlineStr">
         <is>
@@ -43776,7 +43776,7 @@
         <v>46202</v>
       </c>
       <c r="AA270">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AB270" t="inlineStr">
         <is>
@@ -43939,7 +43939,7 @@
         <v>46202</v>
       </c>
       <c r="AA271">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AB271" t="inlineStr">
         <is>
@@ -44102,7 +44102,7 @@
         <v>46202</v>
       </c>
       <c r="AA272">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AB272" t="inlineStr">
         <is>
@@ -44265,7 +44265,7 @@
         <v>46202</v>
       </c>
       <c r="AA273">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AB273" t="inlineStr">
         <is>
@@ -44422,7 +44422,7 @@
         <v>46202</v>
       </c>
       <c r="AA274">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AB274" t="inlineStr">
         <is>
@@ -44580,7 +44580,7 @@
         <v>46202</v>
       </c>
       <c r="AA275">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AB275" t="inlineStr">
         <is>
@@ -44741,7 +44741,7 @@
         <v>46202</v>
       </c>
       <c r="AA276">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AB276" t="inlineStr">
         <is>
@@ -44897,7 +44897,7 @@
         <v>46202</v>
       </c>
       <c r="AA277">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AB277" t="inlineStr">
         <is>
@@ -45060,7 +45060,7 @@
         <v>46202</v>
       </c>
       <c r="AA278">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AB278" t="inlineStr">
         <is>
@@ -45223,7 +45223,7 @@
         <v>46202</v>
       </c>
       <c r="AA279">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AB279" t="inlineStr">
         <is>
@@ -45386,7 +45386,7 @@
         <v>46202</v>
       </c>
       <c r="AA280">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AB280" t="inlineStr">
         <is>
@@ -45548,7 +45548,7 @@
         <v>46202</v>
       </c>
       <c r="AA281">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AB281" t="inlineStr">
         <is>
@@ -45711,7 +45711,7 @@
         <v>46202</v>
       </c>
       <c r="AA282">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AB282" t="inlineStr">
         <is>
@@ -45874,7 +45874,7 @@
         <v>46202</v>
       </c>
       <c r="AA283">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AB283" t="inlineStr">
         <is>
@@ -46037,7 +46037,7 @@
         <v>46199</v>
       </c>
       <c r="AA284">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AB284" t="inlineStr">
         <is>
@@ -46200,7 +46200,7 @@
         <v>46199</v>
       </c>
       <c r="AA285">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AB285" t="inlineStr">
         <is>
@@ -46362,7 +46362,7 @@
         <v>46198</v>
       </c>
       <c r="AA286">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AB286" t="inlineStr">
         <is>
@@ -46525,7 +46525,7 @@
         <v>46198</v>
       </c>
       <c r="AA287">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AB287" t="inlineStr">
         <is>
@@ -46688,7 +46688,7 @@
         <v>46198</v>
       </c>
       <c r="AA288">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AB288" t="inlineStr">
         <is>
@@ -46852,7 +46852,7 @@
         <v>46198</v>
       </c>
       <c r="AA289">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AB289" t="inlineStr">
         <is>
@@ -47015,7 +47015,7 @@
         <v>46197</v>
       </c>
       <c r="AA290">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AB290" t="inlineStr">
         <is>
@@ -47178,7 +47178,7 @@
         <v>46196</v>
       </c>
       <c r="AA291">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AB291" t="inlineStr">
         <is>
@@ -47341,7 +47341,7 @@
         <v>46196</v>
       </c>
       <c r="AA292">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AB292" t="inlineStr">
         <is>
@@ -47505,7 +47505,7 @@
         <v>46196</v>
       </c>
       <c r="AA293">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AB293" t="inlineStr">
         <is>
@@ -47668,7 +47668,7 @@
         <v>46195</v>
       </c>
       <c r="AA294">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AB294" t="inlineStr">
         <is>
@@ -47826,7 +47826,7 @@
         <v>46195</v>
       </c>
       <c r="AA295">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AB295" t="inlineStr">
         <is>
@@ -47989,7 +47989,7 @@
         <v>46195</v>
       </c>
       <c r="AA296">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AB296" t="inlineStr">
         <is>
@@ -48152,7 +48152,7 @@
         <v>46195</v>
       </c>
       <c r="AA297">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AB297" t="inlineStr">
         <is>
@@ -48314,7 +48314,7 @@
         <v>46195</v>
       </c>
       <c r="AA298">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AB298" t="inlineStr">
         <is>
@@ -48477,7 +48477,7 @@
         <v>46195</v>
       </c>
       <c r="AA299">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AB299" t="inlineStr">
         <is>
@@ -48640,7 +48640,7 @@
         <v>46195</v>
       </c>
       <c r="AA300">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AB300" t="inlineStr">
         <is>
@@ -48803,7 +48803,7 @@
         <v>46195</v>
       </c>
       <c r="AA301">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AB301" t="inlineStr">
         <is>
@@ -48966,7 +48966,7 @@
         <v>46191</v>
       </c>
       <c r="AA302">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AB302" t="inlineStr">
         <is>
@@ -49124,7 +49124,7 @@
         <v>46191</v>
       </c>
       <c r="AA303">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AB303" t="inlineStr">
         <is>
@@ -49287,7 +49287,7 @@
         <v>46191</v>
       </c>
       <c r="AA304">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AB304" t="inlineStr">
         <is>
@@ -49450,7 +49450,7 @@
         <v>46190</v>
       </c>
       <c r="AA305">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AB305" t="inlineStr">
         <is>
@@ -49613,7 +49613,7 @@
         <v>46190</v>
       </c>
       <c r="AA306">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AB306" t="inlineStr">
         <is>
@@ -49771,7 +49771,7 @@
         <v>46190</v>
       </c>
       <c r="AA307">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AB307" t="inlineStr">
         <is>
@@ -49934,7 +49934,7 @@
         <v>46190</v>
       </c>
       <c r="AA308">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AB308" t="inlineStr">
         <is>
@@ -50097,7 +50097,7 @@
         <v>46188</v>
       </c>
       <c r="AA309">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AB309" t="inlineStr">
         <is>
@@ -50260,7 +50260,7 @@
         <v>46188</v>
       </c>
       <c r="AA310">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AB310" t="inlineStr">
         <is>
@@ -50424,7 +50424,7 @@
         <v>46184</v>
       </c>
       <c r="AA311">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AB311" t="inlineStr">
         <is>
@@ -50587,7 +50587,7 @@
         <v>46181</v>
       </c>
       <c r="AA312">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="AB312" t="inlineStr">
         <is>
@@ -50750,7 +50750,7 @@
         <v>46178</v>
       </c>
       <c r="AA313">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AB313" t="inlineStr">
         <is>
@@ -50913,7 +50913,7 @@
         <v>46176</v>
       </c>
       <c r="AA314">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AB314" t="inlineStr">
         <is>
@@ -51076,7 +51076,7 @@
         <v>46176</v>
       </c>
       <c r="AA315">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AB315" t="inlineStr">
         <is>
@@ -51239,7 +51239,7 @@
         <v>46176</v>
       </c>
       <c r="AA316">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AB316" t="inlineStr">
         <is>
@@ -51397,7 +51397,7 @@
         <v>46174</v>
       </c>
       <c r="AA317">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AB317" t="inlineStr">
         <is>
@@ -51560,7 +51560,7 @@
         <v>46167</v>
       </c>
       <c r="AA318">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AB318" t="inlineStr">
         <is>
@@ -51723,7 +51723,7 @@
         <v>46163</v>
       </c>
       <c r="AA319">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AB319" t="inlineStr">
         <is>
@@ -51884,7 +51884,7 @@
         <v>46148</v>
       </c>
       <c r="AA320">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AB320" t="inlineStr">
         <is>
@@ -52047,7 +52047,7 @@
         <v>46140</v>
       </c>
       <c r="AA321">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AB321" t="inlineStr">
         <is>
@@ -52213,7 +52213,7 @@
         <v>46128</v>
       </c>
       <c r="AA322">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AB322" t="inlineStr">
         <is>

--- a/data/5.R_pakh_hoan_thanh.xlsx
+++ b/data/5.R_pakh_hoan_thanh.xlsx
@@ -3946,7 +3946,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -4122,7 +4122,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
@@ -4996,7 +4996,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Quá hạn</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
@@ -5344,7 +5344,7 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
@@ -6037,7 +6037,7 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
@@ -6207,7 +6207,7 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
@@ -6379,7 +6379,7 @@
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
@@ -6554,7 +6554,7 @@
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
@@ -6904,7 +6904,7 @@
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
@@ -7603,7 +7603,7 @@
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
@@ -7954,7 +7954,7 @@
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
@@ -8131,7 +8131,7 @@
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
@@ -8308,7 +8308,7 @@
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
@@ -8654,7 +8654,7 @@
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
@@ -9008,7 +9008,7 @@
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X50" t="inlineStr">
@@ -9183,7 +9183,7 @@
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
@@ -9360,7 +9360,7 @@
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X52" t="inlineStr">
@@ -9714,7 +9714,7 @@
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X54" t="inlineStr">
@@ -10057,7 +10057,7 @@
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X56" t="inlineStr">
@@ -10230,7 +10230,7 @@
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
@@ -10408,7 +10408,7 @@
       </c>
       <c r="W58" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X58" t="inlineStr">
@@ -10759,7 +10759,7 @@
       </c>
       <c r="W60" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X60" t="inlineStr">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X61" t="inlineStr">
@@ -11111,7 +11111,7 @@
       </c>
       <c r="W62" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X62" t="inlineStr">
@@ -11288,7 +11288,7 @@
       </c>
       <c r="W63" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X63" t="inlineStr">
@@ -11458,7 +11458,7 @@
       </c>
       <c r="W64" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X64" t="inlineStr">
@@ -11630,7 +11630,7 @@
       </c>
       <c r="W65" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X65" t="inlineStr">
@@ -12151,7 +12151,7 @@
       </c>
       <c r="W68" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X68" t="inlineStr">
@@ -12328,7 +12328,7 @@
       </c>
       <c r="W69" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X69" t="inlineStr">
@@ -12677,7 +12677,7 @@
       </c>
       <c r="W71" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X71" t="inlineStr">
@@ -13021,7 +13021,7 @@
       </c>
       <c r="W73" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X73" t="inlineStr">
@@ -13370,7 +13370,7 @@
       </c>
       <c r="W75" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X75" t="inlineStr">
@@ -13721,7 +13721,7 @@
       </c>
       <c r="W77" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X77" t="inlineStr">
@@ -13896,7 +13896,7 @@
       </c>
       <c r="W78" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X78" t="inlineStr">
@@ -14071,7 +14071,7 @@
       </c>
       <c r="W79" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X79" t="inlineStr">
@@ -14248,7 +14248,7 @@
       </c>
       <c r="W80" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X80" t="inlineStr">
@@ -14425,7 +14425,7 @@
       </c>
       <c r="W81" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X81" t="inlineStr">
@@ -14602,7 +14602,7 @@
       </c>
       <c r="W82" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X82" t="inlineStr">
@@ -14779,7 +14779,7 @@
       </c>
       <c r="W83" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X83" t="inlineStr">
@@ -14949,7 +14949,7 @@
       </c>
       <c r="W84" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X84" t="inlineStr">
@@ -15126,7 +15126,7 @@
       </c>
       <c r="W85" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X85" t="inlineStr">
@@ -15641,7 +15641,7 @@
       </c>
       <c r="W88" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X88" t="inlineStr">
@@ -15818,7 +15818,7 @@
       </c>
       <c r="W89" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X89" t="inlineStr">
@@ -15995,7 +15995,7 @@
       </c>
       <c r="W90" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X90" t="inlineStr">
@@ -16170,7 +16170,7 @@
       </c>
       <c r="W91" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X91" t="inlineStr">
@@ -16347,7 +16347,7 @@
       </c>
       <c r="W92" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X92" t="inlineStr">
@@ -16691,7 +16691,7 @@
       </c>
       <c r="W94" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X94" t="inlineStr">
@@ -16868,7 +16868,7 @@
       </c>
       <c r="W95" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X95" t="inlineStr">
@@ -17043,7 +17043,7 @@
       </c>
       <c r="W96" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X96" t="inlineStr">
@@ -17220,7 +17220,7 @@
       </c>
       <c r="W97" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X97" t="inlineStr">
@@ -17397,7 +17397,7 @@
       </c>
       <c r="W98" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X98" t="inlineStr">
@@ -17572,7 +17572,7 @@
       </c>
       <c r="W99" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X99" t="inlineStr">
@@ -17749,7 +17749,7 @@
       </c>
       <c r="W100" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X100" t="inlineStr">
@@ -17926,7 +17926,7 @@
       </c>
       <c r="W101" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X101" t="inlineStr">
@@ -18103,7 +18103,7 @@
       </c>
       <c r="W102" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X102" t="inlineStr">
@@ -18280,7 +18280,7 @@
       </c>
       <c r="W103" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X103" t="inlineStr">
@@ -18457,7 +18457,7 @@
       </c>
       <c r="W104" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X104" t="inlineStr">
@@ -18627,7 +18627,7 @@
       </c>
       <c r="W105" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X105" t="inlineStr">
@@ -18802,7 +18802,7 @@
       </c>
       <c r="W106" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X106" t="inlineStr">
@@ -18979,7 +18979,7 @@
       </c>
       <c r="W107" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X107" t="inlineStr">
@@ -19156,7 +19156,7 @@
       </c>
       <c r="W108" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X108" t="inlineStr">
@@ -19331,7 +19331,7 @@
       </c>
       <c r="W109" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X109" t="inlineStr">
@@ -19508,7 +19508,7 @@
       </c>
       <c r="W110" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X110" t="inlineStr">
@@ -19685,7 +19685,7 @@
       </c>
       <c r="W111" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X111" t="inlineStr">
@@ -19855,7 +19855,7 @@
       </c>
       <c r="W112" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X112" t="inlineStr">
@@ -20032,7 +20032,7 @@
       </c>
       <c r="W113" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X113" t="inlineStr">
@@ -20209,7 +20209,7 @@
       </c>
       <c r="W114" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X114" t="inlineStr">
@@ -20386,7 +20386,7 @@
       </c>
       <c r="W115" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X115" t="inlineStr">
@@ -20558,7 +20558,7 @@
       </c>
       <c r="W116" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X116" t="inlineStr">
@@ -20735,7 +20735,7 @@
       </c>
       <c r="W117" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X117" t="inlineStr">
@@ -20913,7 +20913,7 @@
       </c>
       <c r="W118" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X118" t="inlineStr">
@@ -21090,7 +21090,7 @@
       </c>
       <c r="W119" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X119" t="inlineStr">
@@ -21267,7 +21267,7 @@
       </c>
       <c r="W120" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X120" t="inlineStr">
@@ -21444,7 +21444,7 @@
       </c>
       <c r="W121" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X121" t="inlineStr">
@@ -21621,7 +21621,7 @@
       </c>
       <c r="W122" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X122" t="inlineStr">
@@ -21798,7 +21798,7 @@
       </c>
       <c r="W123" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X123" t="inlineStr">
@@ -21975,7 +21975,7 @@
       </c>
       <c r="W124" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X124" t="inlineStr">
@@ -22315,7 +22315,7 @@
       </c>
       <c r="W126" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X126" t="inlineStr">
@@ -22492,7 +22492,7 @@
       </c>
       <c r="W127" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X127" t="inlineStr">
@@ -22667,7 +22667,7 @@
       </c>
       <c r="W128" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X128" t="inlineStr">
@@ -22837,7 +22837,7 @@
       </c>
       <c r="W129" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X129" t="inlineStr">
@@ -23013,7 +23013,7 @@
       </c>
       <c r="W130" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X130" t="inlineStr">
@@ -23189,7 +23189,7 @@
       </c>
       <c r="W131" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X131" t="inlineStr">
@@ -23366,7 +23366,7 @@
       </c>
       <c r="W132" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X132" t="inlineStr">
@@ -23542,7 +23542,7 @@
       </c>
       <c r="W133" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X133" t="inlineStr">
@@ -23719,7 +23719,7 @@
       </c>
       <c r="W134" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X134" t="inlineStr">
@@ -23896,7 +23896,7 @@
       </c>
       <c r="W135" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X135" t="inlineStr">
@@ -24068,7 +24068,7 @@
       </c>
       <c r="W136" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X136" t="inlineStr">
@@ -24245,7 +24245,7 @@
       </c>
       <c r="W137" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X137" t="inlineStr">
@@ -24420,7 +24420,7 @@
       </c>
       <c r="W138" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X138" t="inlineStr">
@@ -24597,7 +24597,7 @@
       </c>
       <c r="W139" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X139" t="inlineStr">
@@ -24774,7 +24774,7 @@
       </c>
       <c r="W140" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X140" t="inlineStr">
@@ -24950,7 +24950,7 @@
       </c>
       <c r="W141" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X141" t="inlineStr">
@@ -25127,7 +25127,7 @@
       </c>
       <c r="W142" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X142" t="inlineStr">
@@ -25473,7 +25473,7 @@
       </c>
       <c r="W144" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X144" t="inlineStr">
@@ -25650,7 +25650,7 @@
       </c>
       <c r="W145" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X145" t="inlineStr">
@@ -25827,7 +25827,7 @@
       </c>
       <c r="W146" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X146" t="inlineStr">
@@ -26004,7 +26004,7 @@
       </c>
       <c r="W147" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X147" t="inlineStr">
@@ -26174,7 +26174,7 @@
       </c>
       <c r="W148" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X148" t="inlineStr">
@@ -26351,7 +26351,7 @@
       </c>
       <c r="W149" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X149" t="inlineStr">
@@ -26702,7 +26702,7 @@
       </c>
       <c r="W151" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X151" t="inlineStr">
@@ -26879,7 +26879,7 @@
       </c>
       <c r="W152" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X152" t="inlineStr">
@@ -27054,7 +27054,7 @@
       </c>
       <c r="W153" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X153" t="inlineStr">
@@ -27231,7 +27231,7 @@
       </c>
       <c r="W154" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X154" t="inlineStr">
@@ -27408,7 +27408,7 @@
       </c>
       <c r="W155" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X155" t="inlineStr">
@@ -27759,7 +27759,7 @@
       </c>
       <c r="W157" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X157" t="inlineStr">
@@ -27936,7 +27936,7 @@
       </c>
       <c r="W158" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X158" t="inlineStr">
@@ -28113,7 +28113,7 @@
       </c>
       <c r="W159" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X159" t="inlineStr">
@@ -28283,7 +28283,7 @@
       </c>
       <c r="W160" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X160" t="inlineStr">
@@ -28460,7 +28460,7 @@
       </c>
       <c r="W161" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X161" t="inlineStr">
@@ -28637,7 +28637,7 @@
       </c>
       <c r="W162" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X162" t="inlineStr">
@@ -28812,7 +28812,7 @@
       </c>
       <c r="W163" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X163" t="inlineStr">
@@ -28989,7 +28989,7 @@
       </c>
       <c r="W164" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X164" t="inlineStr">
@@ -29161,7 +29161,7 @@
       </c>
       <c r="W165" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X165" t="inlineStr">
@@ -29332,7 +29332,7 @@
       </c>
       <c r="W166" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X166" t="inlineStr">
@@ -29502,7 +29502,7 @@
       </c>
       <c r="W167" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X167" t="inlineStr">
@@ -29672,7 +29672,7 @@
       </c>
       <c r="W168" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X168" t="inlineStr">
@@ -29849,7 +29849,7 @@
       </c>
       <c r="W169" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X169" t="inlineStr">
@@ -30198,7 +30198,7 @@
       </c>
       <c r="W171" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X171" t="inlineStr">
@@ -30375,7 +30375,7 @@
       </c>
       <c r="W172" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X172" t="inlineStr">
@@ -30547,7 +30547,7 @@
       </c>
       <c r="W173" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X173" t="inlineStr">
@@ -30717,7 +30717,7 @@
       </c>
       <c r="W174" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X174" t="inlineStr">
@@ -30892,7 +30892,7 @@
       </c>
       <c r="W175" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X175" t="inlineStr">
@@ -31070,7 +31070,7 @@
       </c>
       <c r="W176" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X176" t="inlineStr">
@@ -31247,7 +31247,7 @@
       </c>
       <c r="W177" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X177" t="inlineStr">
@@ -31424,7 +31424,7 @@
       </c>
       <c r="W178" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X178" t="inlineStr">
@@ -31778,7 +31778,7 @@
       </c>
       <c r="W180" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X180" t="inlineStr">
@@ -31953,7 +31953,7 @@
       </c>
       <c r="W181" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X181" t="inlineStr">
@@ -32299,7 +32299,7 @@
       </c>
       <c r="W183" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X183" t="inlineStr">
@@ -32474,7 +32474,7 @@
       </c>
       <c r="W184" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X184" t="inlineStr">
@@ -32646,7 +32646,7 @@
       </c>
       <c r="W185" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X185" t="inlineStr">
@@ -32823,7 +32823,7 @@
       </c>
       <c r="W186" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X186" t="inlineStr">
@@ -33000,7 +33000,7 @@
       </c>
       <c r="W187" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X187" t="inlineStr">
@@ -33177,7 +33177,7 @@
       </c>
       <c r="W188" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X188" t="inlineStr">
@@ -33354,7 +33354,7 @@
       </c>
       <c r="W189" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X189" t="inlineStr">
@@ -33531,7 +33531,7 @@
       </c>
       <c r="W190" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X190" t="inlineStr">
@@ -33706,7 +33706,7 @@
       </c>
       <c r="W191" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X191" t="inlineStr">
@@ -33885,7 +33885,7 @@
       </c>
       <c r="W192" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X192" t="inlineStr">
@@ -34225,7 +34225,7 @@
       </c>
       <c r="W194" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X194" t="inlineStr">
@@ -34397,7 +34397,7 @@
       </c>
       <c r="W195" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X195" t="inlineStr">
@@ -34567,7 +34567,7 @@
       </c>
       <c r="W196" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X196" t="inlineStr">
@@ -34737,7 +34737,7 @@
       </c>
       <c r="W197" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X197" t="inlineStr">
@@ -35081,7 +35081,7 @@
       </c>
       <c r="W199" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X199" t="inlineStr">
@@ -35258,7 +35258,7 @@
       </c>
       <c r="W200" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X200" t="inlineStr">
@@ -35430,7 +35430,7 @@
       </c>
       <c r="W201" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X201" t="inlineStr">
@@ -35607,7 +35607,7 @@
       </c>
       <c r="W202" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X202" t="inlineStr">
@@ -35782,7 +35782,7 @@
       </c>
       <c r="W203" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X203" t="inlineStr">
@@ -35959,7 +35959,7 @@
       </c>
       <c r="W204" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X204" t="inlineStr">
@@ -36136,7 +36136,7 @@
       </c>
       <c r="W205" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X205" t="inlineStr">
@@ -36313,7 +36313,7 @@
       </c>
       <c r="W206" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X206" t="inlineStr">
@@ -36491,7 +36491,7 @@
       </c>
       <c r="W207" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X207" t="inlineStr">
@@ -36840,7 +36840,7 @@
       </c>
       <c r="W209" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X209" t="inlineStr">
@@ -37017,7 +37017,7 @@
       </c>
       <c r="W210" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X210" t="inlineStr">
@@ -37187,7 +37187,7 @@
       </c>
       <c r="W211" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X211" t="inlineStr">
@@ -37531,7 +37531,7 @@
       </c>
       <c r="W213" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X213" t="inlineStr">
@@ -37701,7 +37701,7 @@
       </c>
       <c r="W214" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X214" t="inlineStr">
@@ -37878,7 +37878,7 @@
       </c>
       <c r="W215" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X215" t="inlineStr">
@@ -38055,7 +38055,7 @@
       </c>
       <c r="W216" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X216" t="inlineStr">
@@ -38406,7 +38406,7 @@
       </c>
       <c r="W218" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X218" t="inlineStr">
@@ -38578,7 +38578,7 @@
       </c>
       <c r="W219" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X219" t="inlineStr">
@@ -38752,7 +38752,7 @@
       </c>
       <c r="W220" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X220" t="inlineStr">
@@ -38924,7 +38924,7 @@
       </c>
       <c r="W221" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X221" t="inlineStr">
@@ -39101,7 +39101,7 @@
       </c>
       <c r="W222" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X222" t="inlineStr">
@@ -39276,7 +39276,7 @@
       </c>
       <c r="W223" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X223" t="inlineStr">
@@ -39453,7 +39453,7 @@
       </c>
       <c r="W224" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X224" t="inlineStr">
@@ -39630,7 +39630,7 @@
       </c>
       <c r="W225" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X225" t="inlineStr">
@@ -39807,7 +39807,7 @@
       </c>
       <c r="W226" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X226" t="inlineStr">
@@ -39982,7 +39982,7 @@
       </c>
       <c r="W227" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X227" t="inlineStr">
@@ -40154,7 +40154,7 @@
       </c>
       <c r="W228" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X228" t="inlineStr">
@@ -40331,7 +40331,7 @@
       </c>
       <c r="W229" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X229" t="inlineStr">
@@ -40503,7 +40503,7 @@
       </c>
       <c r="W230" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X230" t="inlineStr">
@@ -40680,7 +40680,7 @@
       </c>
       <c r="W231" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X231" t="inlineStr">
@@ -40857,7 +40857,7 @@
       </c>
       <c r="W232" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X232" t="inlineStr">
@@ -41034,7 +41034,7 @@
       </c>
       <c r="W233" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X233" t="inlineStr">
@@ -41211,7 +41211,7 @@
       </c>
       <c r="W234" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X234" t="inlineStr">
@@ -41389,7 +41389,7 @@
       </c>
       <c r="W235" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X235" t="inlineStr">
@@ -41564,7 +41564,7 @@
       </c>
       <c r="W236" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X236" t="inlineStr">
@@ -41741,7 +41741,7 @@
       </c>
       <c r="W237" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X237" t="inlineStr">
@@ -41911,7 +41911,7 @@
       </c>
       <c r="W238" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X238" t="inlineStr">
@@ -42088,7 +42088,7 @@
       </c>
       <c r="W239" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X239" t="inlineStr">
@@ -42258,7 +42258,7 @@
       </c>
       <c r="W240" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X240" t="inlineStr">
@@ -42430,7 +42430,7 @@
       </c>
       <c r="W241" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X241" t="inlineStr">
@@ -42606,7 +42606,7 @@
       </c>
       <c r="W242" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X242" t="inlineStr">
@@ -42783,7 +42783,7 @@
       </c>
       <c r="W243" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X243" t="inlineStr">
@@ -42960,7 +42960,7 @@
       </c>
       <c r="W244" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X244" t="inlineStr">
@@ -43137,7 +43137,7 @@
       </c>
       <c r="W245" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X245" t="inlineStr">
@@ -43314,7 +43314,7 @@
       </c>
       <c r="W246" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X246" t="inlineStr">
@@ -43486,7 +43486,7 @@
       </c>
       <c r="W247" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X247" t="inlineStr">
@@ -43657,7 +43657,7 @@
       </c>
       <c r="W248" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X248" t="inlineStr">
@@ -43828,7 +43828,7 @@
       </c>
       <c r="W249" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X249" t="inlineStr">
@@ -44005,7 +44005,7 @@
       </c>
       <c r="W250" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X250" t="inlineStr">
@@ -44177,7 +44177,7 @@
       </c>
       <c r="W251" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X251" t="inlineStr">
@@ -44347,7 +44347,7 @@
       </c>
       <c r="W252" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X252" t="inlineStr">
@@ -44519,7 +44519,7 @@
       </c>
       <c r="W253" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X253" t="inlineStr">
@@ -44696,7 +44696,7 @@
       </c>
       <c r="W254" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X254" t="inlineStr">
@@ -44872,7 +44872,7 @@
       </c>
       <c r="W255" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X255" t="inlineStr">
@@ -45049,7 +45049,7 @@
       </c>
       <c r="W256" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X256" t="inlineStr">
@@ -45226,7 +45226,7 @@
       </c>
       <c r="W257" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X257" t="inlineStr">
@@ -45397,7 +45397,7 @@
       </c>
       <c r="W258" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X258" t="inlineStr">

--- a/data/5.R_pakh_hoan_thanh.xlsx
+++ b/data/5.R_pakh_hoan_thanh.xlsx
@@ -648,7 +648,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Thủ tục/giấy tờ/ Hóa đơn/ Hồ sơ lắp đặt</t>
+          <t>Thủ tục/giấy tờ/ Hóa đơn/ Hồ sơ lắp đặt</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -820,13 +820,13 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1. KH chưa liên hệ CN
-2. HT NLMT của KH không hoạt động và từ 12h trưa ngày 20/08, App theo dõi hiệu suất báo lỗi mạng
+          <t>1. KH chưa liên hệ CN_x000D_
+2. HT NLMT của KH không hoạt động và từ 12h trưa ngày 20/08, App theo dõi hiệu suất báo lỗi mạng_x000D_
 3. KH cần CN đến kiểm tra và khắc phục sớm cho KH</t>
         </is>
       </c>
@@ -999,13 +999,13 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
+          <t>Chất lượng triển khai</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1. KH đã liên hệ CN
-2. Trời đang nắng tuy nhiên trên App theo dõi hiệu suất thông tin chỉ sản xuất hơn 700W trong khi trước đó có thế sản xuất 2 đến 3kw điện
+          <t>1. KH đã liên hệ CN_x000D_
+2. Trời đang nắng tuy nhiên trên App theo dõi hiệu suất thông tin chỉ sản xuất hơn 700W trong khi trước đó có thế sản xuất 2 đến 3kw điện_x000D_
 3. KH cần CN đến hỗ trợ kiểm tra cho KH</t>
         </is>
       </c>
@@ -1178,13 +1178,13 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Tấm pin bị rò rỉ/ Lỗi</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1. CN báo sự cố cho KH
-2. 1 Tấm Pin NLMT của KH có xuất hiện vết ố, ảnh hưởng hiệu suất
+          <t>1. CN báo sự cố cho KH_x000D_
+2. 1 Tấm Pin NLMT của KH có xuất hiện vết ố, ảnh hưởng hiệu suất_x000D_
 3.KH cần CN đến kiêm tra và khắc phục sớm</t>
         </is>
       </c>
@@ -1360,13 +1360,13 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Hướng dẫn, hỗ trợ sử dụng sản phẩm</t>
+          <t>Liên hệ/tư vấn</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1. KH chưa báo CN
-2. KH phản ánh: trước cài đặt pin lưu trữ thấp nhất 10% là xả nhưng hiện tại xả dưới 10%
+          <t>1. KH chưa báo CN_x000D_
+2. KH phản ánh: trước cài đặt pin lưu trữ thấp nhất 10% là xả nhưng hiện tại xả dưới 10%_x000D_
 3. KH yêu cầu: hỗ trợ KH cài đặt lại xả pin lưu trữ</t>
         </is>
       </c>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Chất lượng, dịch vụ, Giá cả</t>
+          <t>Chất lượng triển khai</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Liên hệ / Đặt lịch lại</t>
+          <t>Liên hệ/tư vấn</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Liên hệ chậm</t>
+          <t>Liên hệ/tư vấn</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -2066,13 +2066,13 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Lỗi kết nối giữa thiết bị và hệ thống theo dõi</t>
+          <t>Kết nối hệ thống</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1. KH đã báo CN: a Hội
-2. KH phản ánh: tắt hết tủ điện nhưng trên app theo dõi biểu đồ điện lươi vẫn vào 8-10kw
+          <t>1. KH đã báo CN: a Hội_x000D_
+2. KH phản ánh: tắt hết tủ điện nhưng trên app theo dõi biểu đồ điện lươi vẫn vào 8-10kw_x000D_
 3. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này</t>
         </is>
       </c>
@@ -2425,13 +2425,13 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Hiệu suất sản phẩm kém</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>KH đã báo KT Phụng
-KH báo sự cố hiệu suất NLMT kém đi, KH đã lắp hệ 7,4kw nhưng hiện tại KH vẫn không đủ dùng và vẫn phải lấy của điện lưới hơn 2kw vào mới đủ dùng được
+          <t>KH đã báo KT Phụng_x000D_
+KH báo sự cố hiệu suất NLMT kém đi, KH đã lắp hệ 7,4kw nhưng hiện tại KH vẫn không đủ dùng và vẫn phải lấy của điện lưới hơn 2kw vào mới đủ dùng được_x000D_
 Yêu cầu CN cho KT qua ktra xử lý cho KH</t>
         </is>
       </c>
@@ -2599,7 +2599,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Tư vấn sản phẩm/dịch vụ</t>
+          <t>Liên hệ/tư vấn</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -2779,13 +2779,13 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Lỗi kết nối giữa thiết bị và hệ thống theo dõi</t>
+          <t>Kết nối hệ thống</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1. KH đã báo CN
-2. KH phản ánh: thi thoảng ngắt kết nối app theo dõi nlmt, hiện lỗi "giao tiếp giữa nhà máy và thiết bị bị ngắt kết nối"
+          <t>1. KH đã báo CN_x000D_
+2. KH phản ánh: thi thoảng ngắt kết nối app theo dõi nlmt, hiện lỗi "giao tiếp giữa nhà máy và thiết bị bị ngắt kết nối"_x000D_
 3. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này</t>
         </is>
       </c>
@@ -2958,13 +2958,13 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Hiệu suất sản phẩm kém</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>KH đã báo KT 
-KH báo sự cố:  Biến tần tự động ngắt/dừng hoạt động mỗi khi điện nguồn vào bị tụt xuống dưới 180V. Khi đó, hệ thống tự động chuyển sang dùng 100% điện lưới thay vì dùng điện mặt trời. Hệ thống chỉ chạy điện mặt trời khi ngắt/tắt thủ công nguồn điện lưới. Hệ thống điện mặt trời gần như không có tác dụng (90% thời gian từ lúc lắp đặt vẫn phải dùng điện lưới), tiền điện mỗi tháng không giảm so với trước (vẫn hơn 3 triệu/tháng).
+          <t>KH đã báo KT _x000D_
+KH báo sự cố:  Biến tần tự động ngắt/dừng hoạt động mỗi khi điện nguồn vào bị tụt xuống dưới 180V. Khi đó, hệ thống tự động chuyển sang dùng 100% điện lưới thay vì dùng điện mặt trời. Hệ thống chỉ chạy điện mặt trời khi ngắt/tắt thủ công nguồn điện lưới. Hệ thống điện mặt trời gần như không có tác dụng (90% thời gian từ lúc lắp đặt vẫn phải dùng điện lưới), tiền điện mỗi tháng không giảm so với trước (vẫn hơn 3 triệu/tháng)._x000D_
 Yêu cầu CN cho KT qua ktra lại và xử lý cho KH</t>
         </is>
       </c>
@@ -3137,13 +3137,13 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Sản phẩm không sử dụng được / không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>KH đã báo CN
-KH báo sự cố hệ thống NLMT không sử dụng được điện lưới ko có, điện nhà sung quanh có. Hiện tại nhà KH mất hết điện lưới và điện NLMT 
+          <t>KH đã báo CN_x000D_
+KH báo sự cố hệ thống NLMT không sử dụng được điện lưới ko có, điện nhà sung quanh có. Hiện tại nhà KH mất hết điện lưới và điện NLMT _x000D_
 Yêu cầu Cn cho KT qua ktra xử lý cho KH</t>
         </is>
       </c>
@@ -3319,13 +3319,13 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>Thiếu thiết bị đi kèm/Lắp đặt sai quy cách</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1. KH đã báo CN
-2. KH phản ánh: từ lúc lắp đặt KH đã có báo KT lắp đặt là anh Đàn là về phần tủ điện bị mất 1 ốp nhựa khiến bản lề bị trơn, lỏng. KH đã có trao đổi từ tháng 3, KT hứa qua xử lý nhưng tới nay chưa thấy thông tin gì.
+          <t>1. KH đã báo CN_x000D_
+2. KH phản ánh: từ lúc lắp đặt KH đã có báo KT lắp đặt là anh Đàn là về phần tủ điện bị mất 1 ốp nhựa khiến bản lề bị trơn, lỏng. KH đã có trao đổi từ tháng 3, KT hứa qua xử lý nhưng tới nay chưa thấy thông tin gì._x000D_
 3. KH yêu cầu: qua kiểm tra, hỗ trợ, xử lý phần tủ điện</t>
         </is>
       </c>
@@ -3501,13 +3501,13 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1. KH chưa liên hệ CNCT
-2. Pin lưu trữ của HT NLMT đang không sạc và báo đỏ
+          <t>1. KH chưa liên hệ CNCT_x000D_
+2. Pin lưu trữ của HT NLMT đang không sạc và báo đỏ_x000D_
 3. KH cần CNCT liên hệ và đến hỗ trợ sớm</t>
         </is>
       </c>
@@ -3683,14 +3683,14 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Không kết nối được app/Wifi và không theo dõi được hiệu suất</t>
+          <t>Kết nối hệ thống</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>Người nhà KH 0988138212 báo sự cố
-1. KH chưa báo CN
-2. KH phản ánh: theo dõi trên app ko thấy nguồn, ko thấy biểu đồ, ko rõ là đang hoạt động hay kh
+          <t>Người nhà KH 0988138212 báo sự cố_x000D_
+1. KH chưa báo CN_x000D_
+2. KH phản ánh: theo dõi trên app ko thấy nguồn, ko thấy biểu đồ, ko rõ là đang hoạt động hay kh_x000D_
 3. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này</t>
         </is>
       </c>
@@ -3866,13 +3866,13 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>Sản phẩm bị ngắt quãng/ Không theo dõi và không nghe được</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1. KH đã báo CN: KT Đằng
-2. KH phản ánh: bình thường khi sử dụng pin lưu trữ là điện sử dụng được toàn nhà nhưng hôm nay khi mất điện chỉ 1 vài chỗ sử dụng được điện nlmt
+          <t>1. KH đã báo CN: KT Đằng_x000D_
+2. KH phản ánh: bình thường khi sử dụng pin lưu trữ là điện sử dụng được toàn nhà nhưng hôm nay khi mất điện chỉ 1 vài chỗ sử dụng được điện nlmt_x000D_
 3. KH yêu cầu: qua hỗ trợ, kiểm tra khắc phục tình trạng này</t>
         </is>
       </c>
@@ -4045,14 +4045,14 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>Hỗ trợ lắp đặt</t>
+          <t>Tiến độ triển khai</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1. KH đã báo CN
-2. KH phản ánh: biến tần của KH đã mang về được 4 ngày nhưng ko thấy có ai đến lắp đặt
-3. KH yêu cầu: qua lắp đặt cho KH
+          <t>1. KH đã báo CN_x000D_
+2. KH phản ánh: biến tần của KH đã mang về được 4 ngày nhưng ko thấy có ai đến lắp đặt_x000D_
+3. KH yêu cầu: qua lắp đặt cho KH_x000D_
 *đ/c lắp đặt: Thôn Phù Long 2, Xã Phúc Thọ, Thành phố Hà Nội</t>
         </is>
       </c>
@@ -4228,7 +4228,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>Liên hệ chậm</t>
+          <t>Liên hệ/tư vấn</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -4408,13 +4408,13 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>Cài đặt hệ thống (APP/Mật khẩu)</t>
+          <t>Kết nối hệ thống</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1. KH đã báo CN
-2. KH phản ánh: KH đăng nhập app nlmt điền mật khẩu nhưng lại ra nhà khác
+          <t>1. KH đã báo CN_x000D_
+2. KH phản ánh: KH đăng nhập app nlmt điền mật khẩu nhưng lại ra nhà khác_x000D_
 3. KH yêu cầu: hỗ trợ KH đăng nhập lại app theo dõi nlmt</t>
         </is>
       </c>
@@ -4587,13 +4587,13 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1. KH chưa báo CN
-2. KH phản ánh: từ hôm qua hệ nlmt ko phát ra điện,  KH tưởng hôm qua mưa nên ko phát nhưng đến hôm nay vẫn ko thấy có 
+          <t>1. KH chưa báo CN_x000D_
+2. KH phản ánh: từ hôm qua hệ nlmt ko phát ra điện,  KH tưởng hôm qua mưa nên ko phát nhưng đến hôm nay vẫn ko thấy có _x000D_
 3. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này</t>
         </is>
       </c>
@@ -4769,13 +4769,13 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>Hướng dẫn, hỗ trợ sử dụng sản phẩm</t>
+          <t>Liên hệ/tư vấn</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1. KH đã báo CN (nhưng chuyển công tác)
-2. KH phản ánh: pin lưu trữ KH theo dõi trên app pin chưa đầy nhưng báo 100%
+          <t>1. KH đã báo CN (nhưng chuyển công tác)_x000D_
+2. KH phản ánh: pin lưu trữ KH theo dõi trên app pin chưa đầy nhưng báo 100%_x000D_
 3. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này</t>
         </is>
       </c>
@@ -4943,13 +4943,13 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1. KH chưa báo CN
-2. KH phản ánh: điện lực có thay công tơ nên hiện tại hệ nlmt đang ko có hoạt động
+          <t>1. KH chưa báo CN_x000D_
+2. KH phản ánh: điện lực có thay công tơ nên hiện tại hệ nlmt đang ko có hoạt động_x000D_
 3. KH yêu cầu: KH là hộ kinh doanh nên cần qua kiểm tra, khắc phục tình trạng này sớm</t>
         </is>
       </c>
@@ -5120,12 +5120,12 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>Hỗ trợ lắp đặt</t>
+          <t>Tiến độ triển khai</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1. KH đã liên hệ CN
+          <t>1. KH đã liên hệ CN_x000D_
 2. KH cần hoàn thiện lắp đặt tiếp địa cho tấm pin NLMT sau khi nâng cấp HT NLMT</t>
         </is>
       </c>
@@ -5296,12 +5296,12 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>Đơn bảo dưỡng hết hạn bảo hành</t>
+          <t>Chất lượng bảo dưỡng</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>Đơn hàng từ 8/6 điều hòa gặp tình trạng chảy nước ngay sau khi vệ sinh nhưng chảy ít và KH cũng ko biết SĐT hotline để gọi, giờ điều hòa vẫn gặp tình trạng vậy và chảy nhiều hơn, tìm được số hotline nên 
+          <t>Đơn hàng từ 8/6 điều hòa gặp tình trạng chảy nước ngay sau khi vệ sinh nhưng chảy ít và KH cũng ko biết SĐT hotline để gọi, giờ điều hòa vẫn gặp tình trạng vậy và chảy nhiều hơn, tìm được số hotline nên _x000D_
 KH gọi cần hỗ trợ, khắc phục tình trạng chảy nước.</t>
         </is>
       </c>
@@ -5472,13 +5472,13 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>Không kết nối được app/Wifi và không theo dõi được hiệu suất</t>
+          <t>Kết nối hệ thống</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1. KH đã liên hệ CN
-2. Hiện KH không đăng  nhập được vào App theo dõi hiệu suất NLMT
+          <t>1. KH đã liên hệ CN_x000D_
+2. Hiện KH không đăng  nhập được vào App theo dõi hiệu suất NLMT_x000D_
 3. KH cần CN liên hệ và đến hỗ trợ sớm</t>
         </is>
       </c>
@@ -5644,13 +5644,13 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1. KH đã báo CN: a Dũng
-2. KH phản ánh: toàn bộ sản lượng điện nlmt lên hết điện lưới, có báo CN và KT hỗ trợ cài đặt từ xa nhưng vẫn chưa khắc phục được
+          <t>1. KH đã báo CN: a Dũng_x000D_
+2. KH phản ánh: toàn bộ sản lượng điện nlmt lên hết điện lưới, có báo CN và KT hỗ trợ cài đặt từ xa nhưng vẫn chưa khắc phục được_x000D_
 3. KH yêu cầu: qua kiểm tra trực tiếp và khắc phục tình trạng này</t>
         </is>
       </c>
@@ -5818,13 +5818,13 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1. CN báo sự cố cho KH
-2. Biến tần báo lỗi COM báo đỏ
+          <t>1. CN báo sự cố cho KH_x000D_
+2. Biến tần báo lỗi COM báo đỏ_x000D_
 3. KH cần CN kiểm tra và khăc phục sớm</t>
         </is>
       </c>
@@ -5995,13 +5995,13 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>Hướng dẫn, hỗ trợ sử dụng sản phẩm</t>
+          <t>Liên hệ/tư vấn</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1. KH đã báo CN
-2. KH phản ánh: từ những phản ánh trước CN đã có qua xác định là do phần đấu nối lioa yếu. Nhưng KH báo bên đấu nối lioa 3 pha khẳng định chỉ đấu nối vào cầu dao ko liên quan tới NLMT. Hiện tại thì KH theo dõi app lượng điện sản sinh ra bị loạn, xem điện toàn thấy ra điện lưới
+          <t>1. KH đã báo CN_x000D_
+2. KH phản ánh: từ những phản ánh trước CN đã có qua xác định là do phần đấu nối lioa yếu. Nhưng KH báo bên đấu nối lioa 3 pha khẳng định chỉ đấu nối vào cầu dao ko liên quan tới NLMT. Hiện tại thì KH theo dõi app lượng điện sản sinh ra bị loạn, xem điện toàn thấy ra điện lưới_x000D_
 3. KH yêu cầu: qua kiểm tra tình thực tế, cân đối lại phần đấu nối để khắc phục tình trạng lượng điện sản sinh ra đang không đúng</t>
         </is>
       </c>
@@ -6167,7 +6167,7 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>Xuất hóa đơn</t>
+          <t>Thủ tục/giấy tờ/ Hóa đơn/ Hồ sơ lắp đặt</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -6337,12 +6337,12 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>Cài đặt hệ thống (APP/Mật khẩu)</t>
+          <t>Kết nối hệ thống</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>CN Lâm Quốc Khỏe báo sự cố hộ KH
+          <t>CN Lâm Quốc Khỏe báo sự cố hộ KH_x000D_
 KH doanh nghiệp đã lắp đặt hệ pin NLMT. Cần hỗ trợ cài app giám sát sản lượng.</t>
         </is>
       </c>
@@ -6513,13 +6513,13 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1. KH chưa liên hệ CN 
-2. HT NLMT đang không sản xuất điện, hiện KH đang dùng điện lưới, Chỉ số trên App báo bằng 0
+          <t>1. KH chưa liên hệ CN _x000D_
+2. HT NLMT đang không sản xuất điện, hiện KH đang dùng điện lưới, Chỉ số trên App báo bằng 0_x000D_
 3. KH cần CN liên hệ và đến hỗ trợ sớm</t>
         </is>
       </c>
@@ -6690,13 +6690,13 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1. CN báo sự cố cho KH
-2. Tủ điện HT NLMT hay bị nhảy ATS, có 2 công tơ tuy nhiên 1 công tơ không nhảy, có dấu hiệu không đảo
+          <t>1. CN báo sự cố cho KH_x000D_
+2. Tủ điện HT NLMT hay bị nhảy ATS, có 2 công tơ tuy nhiên 1 công tơ không nhảy, có dấu hiệu không đảo_x000D_
 3. KH cần CN đến hỗ trợ và kiểm tra sớm</t>
         </is>
       </c>
@@ -6867,13 +6867,13 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1. KH đã liên hệ A Kiên
-2. Hiện nhà KH đang mất điện, không có điện lưới và điện NLMT
+          <t>1. KH đã liên hệ A Kiên_x000D_
+2. Hiện nhà KH đang mất điện, không có điện lưới và điện NLMT_x000D_
 3. KH cần CNCT đến kiểm tra và hỗ trợ khắc phục sớm</t>
         </is>
       </c>
@@ -7044,13 +7044,13 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>Thiết bị vỡ, hỏng, chập cháy</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1. KH chưa liên hệ CN
-2. 2 ATS của bộ phận chống sét HT NLMT của KH gặp sự cố chuyển màu đỏ và bị cháy đen
+          <t>1. KH chưa liên hệ CN_x000D_
+2. 2 ATS của bộ phận chống sét HT NLMT của KH gặp sự cố chuyển màu đỏ và bị cháy đen_x000D_
 3.KH cần CN đến kiểm tra và khắc phục sớm cho KH</t>
         </is>
       </c>
@@ -7221,7 +7221,7 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>Xuất hóa đơn</t>
+          <t>Thủ tục/giấy tờ/ Hóa đơn/ Hồ sơ lắp đặt</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -7393,12 +7393,12 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>Thủ tục/giấy tờ/ Hóa đơn/ Hồ sơ lắp đặt</t>
+          <t>Thủ tục/giấy tờ/ Hóa đơn/ Hồ sơ lắp đặt</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1. KH chưa báo chi nhánh
+          <t>1. KH chưa báo chi nhánh_x000D_
 2. KH báo ký HDNLMT với Viettel, theo quy định của nhà nước cần hoàn thiện hồ sơ, thông báo bên điện lực, KH chưa rõ cần hoàn thiện những yêu cầu gì. Cần nhân viên CN liên hệ hỗ trợ các thủ tục cần thiết.</t>
         </is>
       </c>
@@ -7569,13 +7569,13 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>Lắp đặt sai quy cách, thiếu vật tư, thiết bị, phụ kiện đi kèm</t>
+          <t>Chất lượng triển khai</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1. KH đã báo CN: a Giang
-2. KH phản ánh: đã lắp đặt và nghiệm thu đi vào bàn giao nhưng bị thiếu phần tiếp địa trên tấm pin, KH có trao đổi với a Giang 0983276176 thì hứa 3 hôm sau khi bàn giao sẽ đến làm nốt nhưng hiện tại vẫn chưa thấy có đến hỗ trợ.
+          <t>1. KH đã báo CN: a Giang_x000D_
+2. KH phản ánh: đã lắp đặt và nghiệm thu đi vào bàn giao nhưng bị thiếu phần tiếp địa trên tấm pin, KH có trao đổi với a Giang 0983276176 thì hứa 3 hôm sau khi bàn giao sẽ đến làm nốt nhưng hiện tại vẫn chưa thấy có đến hỗ trợ._x000D_
 3. KH yêu cầu: CN hoàn thiện phần tiếp địa cho KH</t>
         </is>
       </c>
@@ -7746,7 +7746,7 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>Đơn bảo dưỡng hết hạn bảo hành</t>
+          <t>Chất lượng bảo dưỡng</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -7918,13 +7918,13 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>Lắp đặt sai quy cách, thiếu vật tư, thiết bị, phụ kiện đi kèm</t>
+          <t>Chất lượng triển khai</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1. KH chưa báo CN
-2. KH phản ánh: các hộ dân xung quanh bị rò điện và điện lực hôm nay có đến kiểm tra thì phát hiện bị hệ nlmt của KH bị đấu nối ngược đường điện, bên điện lực có trao đổi với KH cần nlmt đến kiểm tra phần đấu nối ngay.
+          <t>1. KH chưa báo CN_x000D_
+2. KH phản ánh: các hộ dân xung quanh bị rò điện và điện lực hôm nay có đến kiểm tra thì phát hiện bị hệ nlmt của KH bị đấu nối ngược đường điện, bên điện lực có trao đổi với KH cần nlmt đến kiểm tra phần đấu nối ngay._x000D_
 3. KH yêu cầu: hiện tại đang cắt điện KH yêu cầu là xuống kiểm tra phần đấu nối và khắc phục tình trạng này gấp</t>
         </is>
       </c>
@@ -8090,7 +8090,7 @@
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>Tư vấn sản phẩm/dịch vụ</t>
+          <t>Liên hệ/tư vấn</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -8265,13 +8265,13 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>Thiết bị vỡ, hỏng, chập cháy</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1. KH đã báo chi nhánh - Nhân viên Hải Tùng
-2. Nội dung sự cố: ATS bị cháy cầu trì, đã báo nhân sự Hải Tùng của chi nhánh nhưng chưa được xử lý. CN báo sẽ đổi ATS khác nhưng chưa có hàng, KH đã đợi khoảng hơn 2 tháng nhưng chưa được hỗ trợ.
+          <t>1. KH đã báo chi nhánh - Nhân viên Hải Tùng_x000D_
+2. Nội dung sự cố: ATS bị cháy cầu trì, đã báo nhân sự Hải Tùng của chi nhánh nhưng chưa được xử lý. CN báo sẽ đổi ATS khác nhưng chưa có hàng, KH đã đợi khoảng hơn 2 tháng nhưng chưa được hỗ trợ._x000D_
 3. KHYC: CN hỗ trợ sớm (Viettel  báo giá 12tr KH đồng ý nhưng đợi lâu chưa được thay, KH cần hỗ trợ gấp do gia đình kinh doanh nhà nghỉ KS)</t>
         </is>
       </c>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>Tiến độ triển khai chậm</t>
+          <t>Tiến độ triển khai</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -8609,13 +8609,13 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>Không kết nối được app/Wifi và không theo dõi được hiệu suất</t>
+          <t>Kết nối hệ thống</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1. CNCT báo sự cố cho KH
-2. Logger của KH bị lỗi không kết nối được Wifi
+          <t>1. CNCT báo sự cố cho KH_x000D_
+2. Logger của KH bị lỗi không kết nối được Wifi_x000D_
 3. KH cần CN hỗ trợ khắc phục sớm</t>
         </is>
       </c>
@@ -8786,13 +8786,13 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>Hướng dẫn, hỗ trợ sử dụng sản phẩm</t>
+          <t>Liên hệ/tư vấn</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1. CNCT phản ánh cho KH
-2.Cần thiết lập thời gian sạc, xả của Ắc quy lưu trữ
+          <t>1. CNCT phản ánh cho KH_x000D_
+2.Cần thiết lập thời gian sạc, xả của Ắc quy lưu trữ_x000D_
 3. KH cần CNCT liên hệ và hỗ trợ sớm</t>
         </is>
       </c>
@@ -8963,7 +8963,7 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>Hiệu suất thấp</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -9138,13 +9138,13 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
+          <t>Chất lượng triển khai</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1. KH chưa báo CN
-2. KH phản ánh: hàng tháng KH trả tiền điện 1tr1-1tr3 nhưng tháng gần đây gấp đôi tiền điện là 2tr6-2tr7, KH không biết là do vấn đề đường truyền hay gì
+          <t>1. KH chưa báo CN_x000D_
+2. KH phản ánh: hàng tháng KH trả tiền điện 1tr1-1tr3 nhưng tháng gần đây gấp đôi tiền điện là 2tr6-2tr7, KH không biết là do vấn đề đường truyền hay gì_x000D_
 3. KH yêu cầu: qua kiểm tra phần hiệu suất xem và khắc phục tình trạng này</t>
         </is>
       </c>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>Xuất hóa đơn</t>
+          <t>Thủ tục/giấy tờ/ Hóa đơn/ Hồ sơ lắp đặt</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
@@ -9485,13 +9485,13 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1. KH chưa báo CN
-2. KH phản ánh: tối qua có cài sạc pin lưu trữ, sáng thấy đầy pin nhưng ko thấy xả ra để sử dụng mà toàn dùng điện lưới
+          <t>1. KH chưa báo CN_x000D_
+2. KH phản ánh: tối qua có cài sạc pin lưu trữ, sáng thấy đầy pin nhưng ko thấy xả ra để sử dụng mà toàn dùng điện lưới_x000D_
 3. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này và hướng dẫn KH sạc pin</t>
         </is>
       </c>
@@ -9662,13 +9662,13 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>CN 0982778966 báo sự cố hộ KH
-1. KH phản ánh: nlmt ko vào pin lưu trữ, ko cấp cho tải, phải dùng điện lưới
+          <t>CN 0982778966 báo sự cố hộ KH_x000D_
+1. KH phản ánh: nlmt ko vào pin lưu trữ, ko cấp cho tải, phải dùng điện lưới_x000D_
 2. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này gấp</t>
         </is>
       </c>
@@ -9839,7 +9839,7 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>Tiến độ triển khai chậm</t>
+          <t>Tiến độ triển khai</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
@@ -10011,13 +10011,13 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>Thiết bị vỡ, hỏng, chập cháy</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1. KH đã báo CN: a Tư
-2. KH phản ánh: dây đấu nối từ cục ivt nối ra ngoài bị bục ra dứt dây và xà xuống
+          <t>1. KH đã báo CN: a Tư_x000D_
+2. KH phản ánh: dây đấu nối từ cục ivt nối ra ngoài bị bục ra dứt dây và xà xuống_x000D_
 3. KH yêu cầu: qua kiểm tra, hỗ trợ KH lắp lại đường dây đảm bảo an toàn</t>
         </is>
       </c>
@@ -10188,7 +10188,7 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>Sau bảo dưỡng thiết bị bị hỏng</t>
+          <t>Chất lượng bảo dưỡng</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
@@ -10363,13 +10363,13 @@
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>1. KH chưa báo CN
-2. KH phản ánh: hệ nlmt ko hoạt động, đèn ở pin lưu trữ và cả hệ đều thấy tắt
+          <t>1. KH chưa báo CN_x000D_
+2. KH phản ánh: hệ nlmt ko hoạt động, đèn ở pin lưu trữ và cả hệ đều thấy tắt_x000D_
 3. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này</t>
         </is>
       </c>
@@ -10535,7 +10535,7 @@
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>Tư vấn sản phẩm/dịch vụ</t>
+          <t>Liên hệ/tư vấn</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
@@ -10710,13 +10710,13 @@
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
+          <t>Chất lượng triển khai</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>1. KH đã báo CN: a Quân
-2. KH phản ánh: pin lưu trữ nạp vào ko đủ dùng cho 1 ngày trong khi trời rất nắng, mọi khi chạy sử dụng được đến gần sáng nhưng giờ chỉ đến đêm. Hiện tại đang mất cả điện lưới lẫn nlmt
+          <t>1. KH đã báo CN: a Quân_x000D_
+2. KH phản ánh: pin lưu trữ nạp vào ko đủ dùng cho 1 ngày trong khi trời rất nắng, mọi khi chạy sử dụng được đến gần sáng nhưng giờ chỉ đến đêm. Hiện tại đang mất cả điện lưới lẫn nlmt_x000D_
 3. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này</t>
         </is>
       </c>
@@ -10887,13 +10887,13 @@
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>KH chưa báo CN, KT
-KH báo sự cố hệ thống NLMT liên tục mất điên, sau đó lại có lại và tiếp tục bị mất điện, đã xảy ra tình trạng này 2 ngày nay
+          <t>KH chưa báo CN, KT_x000D_
+KH báo sự cố hệ thống NLMT liên tục mất điên, sau đó lại có lại và tiếp tục bị mất điện, đã xảy ra tình trạng này 2 ngày nay_x000D_
 Yêu cầu CN cho KT qua ktra xử lý cho KH</t>
         </is>
       </c>
@@ -11061,13 +11061,13 @@
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
+          <t>Chất lượng triển khai</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>1. KH đã báo CN: a Phụng
-2. KH phản ánh: CN lúc tư vấn lắp đặt 3 pha là sẽ bớt được 4-5tr tiền điện, nhưng thực tế KH tháng vãn phải đóng 3tr tiền điện chỉ bớt được 1-2tr tiền điện, đã báo CN bảo đến kiểm tra mà chưa thấy
+          <t>1. KH đã báo CN: a Phụng_x000D_
+2. KH phản ánh: CN lúc tư vấn lắp đặt 3 pha là sẽ bớt được 4-5tr tiền điện, nhưng thực tế KH tháng vãn phải đóng 3tr tiền điện chỉ bớt được 1-2tr tiền điện, đã báo CN bảo đến kiểm tra mà chưa thấy_x000D_
 3. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này</t>
         </is>
       </c>
@@ -11233,12 +11233,12 @@
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>Cài đặt hệ thống (APP/Mật khẩu)</t>
+          <t>Kết nối hệ thống</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>1. KH chưa báo CN
+          <t>1. KH chưa báo CN_x000D_
 2. KH phản ánh và yêu cầu: mới thay đt nên cần hỗ trợ đăng nhập lại app theo dõi nlmt, KH có thử TK và MK cũ nhưng ko được</t>
         </is>
       </c>
@@ -11409,12 +11409,12 @@
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>Cài đặt hệ thống (APP/Mật khẩu)</t>
+          <t>Kết nối hệ thống</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>1. KH chưa báo CN
+          <t>1. KH chưa báo CN_x000D_
 2. KH phản ánh và yêu cầu: KH có hệ nlmt ở 2 bên trên 1 mặt bằng, cần hỗ trợ tắt 1 bên hệ nlmt đi vì KH ko cần sử dụng</t>
         </is>
       </c>
@@ -11585,13 +11585,13 @@
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>1. KH đã báo CN: anh Hoàng và phản ánh TT_1786326306315
-2. KH phản ánh: CN hẹn 15/8 xuống bảo hành nhưng hiện tại KH vẫn chưa thấy có xuống hay tháo thiết bị mang đi bảo hành
+          <t>1. KH đã báo CN: anh Hoàng và phản ánh TT_1786326306315_x000D_
+2. KH phản ánh: CN hẹn 15/8 xuống bảo hành nhưng hiện tại KH vẫn chưa thấy có xuống hay tháo thiết bị mang đi bảo hành_x000D_
 3. KH yêu cầu: qua kiểm tra, tháo thiết bị mang đi bảo hành</t>
         </is>
       </c>
@@ -11762,13 +11762,13 @@
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>CN báo sự cố hộ KH
-1.	KH phản ánh: mất điện ko nhảy ats
+          <t>CN báo sự cố hộ KH_x000D_
+1.	KH phản ánh: mất điện ko nhảy ats_x000D_
 2.	KH yêu cầu: qua kiểm tra, khắc phục tình trạng này</t>
         </is>
       </c>
@@ -11939,13 +11939,13 @@
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>Lắp đặt không đảm bảo</t>
+          <t>Chất lượng triển khai</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>1. KH đã báo CN: anh Bang
-2. KH phản ánh: vừa mới đây KH phát hiện ra do thấy có mùi khét và đứt phần dây tiếp địa, KH có ra kiểm tra thì là cọc tiếp địa bằng sắt chứ không phải cọc đồng như trong HĐ. KH có trao đổi với anh Bang thì phản hồi là tính nhầm
+          <t>1. KH đã báo CN: anh Bang_x000D_
+2. KH phản ánh: vừa mới đây KH phát hiện ra do thấy có mùi khét và đứt phần dây tiếp địa, KH có ra kiểm tra thì là cọc tiếp địa bằng sắt chứ không phải cọc đồng như trong HĐ. KH có trao đổi với anh Bang thì phản hồi là tính nhầm_x000D_
 3. KH yêu cầu: thay thế cọc tiếp địa bằng đồng và giải trình vấn đề này cho KH</t>
         </is>
       </c>
@@ -12113,13 +12113,13 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>CN 0346452433 báo sự cố hộ KH qua hệ thống
-1. KH phản ánh: CB tủ nguồn AC bị nhảy
+          <t>CN 0346452433 báo sự cố hộ KH qua hệ thống_x000D_
+1. KH phản ánh: CB tủ nguồn AC bị nhảy_x000D_
 2. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này</t>
         </is>
       </c>
@@ -12290,13 +12290,13 @@
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>1. KH đã báo CN: a Trường
-2. KH phản ánh: pin lưu trữ ko nạp vào ko xả ra
+          <t>1. KH đã báo CN: a Trường_x000D_
+2. KH phản ánh: pin lưu trữ ko nạp vào ko xả ra_x000D_
 3. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này</t>
         </is>
       </c>
@@ -12459,13 +12459,13 @@
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>Thiết bị vỡ, hỏng, chập cháy</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>1. KH đã báo CN
-2. KH phản ánh: 1 tháng trước trời mưa thì KH nghe thấy tiếng nổ, KH có báo KT là a Thông xuống kiểm tra thì xác định bị bể tấm pin, có tháo ra, ngắt nhưng chưa thấy đưa ra phương án xử lý
+          <t>1. KH đã báo CN_x000D_
+2. KH phản ánh: 1 tháng trước trời mưa thì KH nghe thấy tiếng nổ, KH có báo KT là a Thông xuống kiểm tra thì xác định bị bể tấm pin, có tháo ra, ngắt nhưng chưa thấy đưa ra phương án xử lý_x000D_
 3. KH yêu cầu: đưa ra phương án xử lý, hỗ trợ KH về TH này</t>
         </is>
       </c>
@@ -12636,13 +12636,13 @@
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>CN 0364023755 báo sự cố hộ KH
-1. KH phản ánh: 2,3 ngày nay hệ KH 10 tấm pin, 2 string nhưng hiện tại chỉ chạy được 5 tấm, 1 string
+          <t>CN 0364023755 báo sự cố hộ KH_x000D_
+1. KH phản ánh: 2,3 ngày nay hệ KH 10 tấm pin, 2 string nhưng hiện tại chỉ chạy được 5 tấm, 1 string_x000D_
 2. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này gấp</t>
         </is>
       </c>
@@ -12805,7 +12805,7 @@
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>Tư vấn sản phẩm/dịch vụ</t>
+          <t>Liên hệ/tư vấn</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
@@ -12980,13 +12980,13 @@
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>KH đã báo KT
-KH báo sự cố NLMT pin đầy nắng to, lấy điện lưới không lấy điện NLMT hơn 1kw
+          <t>KH đã báo KT_x000D_
+KH báo sự cố NLMT pin đầy nắng to, lấy điện lưới không lấy điện NLMT hơn 1kw_x000D_
 Yêu cầu CN cho KT qua ktra xử lý cho KH</t>
         </is>
       </c>
@@ -13157,13 +13157,13 @@
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>Thiết bị vỡ, hỏng, chập cháy</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>KH đã báo KT
-KH báo sự cố ATS đã thay nhưng được mấy hôm lại bị chập và nay là cháy hẳn 
+          <t>KH đã báo KT_x000D_
+KH báo sự cố ATS đã thay nhưng được mấy hôm lại bị chập và nay là cháy hẳn _x000D_
 Yêu cầu CN cho KT qua ktra xử lý cho KH</t>
         </is>
       </c>
@@ -13334,13 +13334,13 @@
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>Hàng Tổng công ty cấp</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>KH đã báo CN
-Bảo hành INVT, hiện tại iVT không nạp xả điện dược
+          <t>KH đã báo CN_x000D_
+Bảo hành INVT, hiện tại iVT không nạp xả điện dược_x000D_
 Yêu cầu CN cho KT qua ktra xử lý cho KH</t>
         </is>
       </c>
@@ -13511,13 +13511,13 @@
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>KH đã báo GĐKD
-KH báo sự cố nlmt không có xuống điện, bình luư trữ báo lỗi 
+          <t>KH đã báo GĐKD_x000D_
+KH báo sự cố nlmt không có xuống điện, bình luư trữ báo lỗi _x000D_
 Yêu cầu CN cho KT qua ktra xử lý cho KH</t>
         </is>
       </c>
@@ -13683,7 +13683,7 @@
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>Tư vấn sản phẩm/dịch vụ</t>
+          <t>Liên hệ/tư vấn</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
@@ -13858,13 +13858,13 @@
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>Cài đặt hệ thống (APP/Mật khẩu)</t>
+          <t>Kết nối hệ thống</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>KH đã báo KT
-KH cần hỗ trợ cài lại APP theo dõi NLMT
+          <t>KH đã báo KT_x000D_
+KH cần hỗ trợ cài lại APP theo dõi NLMT_x000D_
 Yêu cầu CN cho KT qua hỗ trợ KH</t>
         </is>
       </c>
@@ -14035,13 +14035,13 @@
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>Không kết nối được app/Wifi và không theo dõi được hiệu suất</t>
+          <t>Kết nối hệ thống</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>KH đã báo Anh Mạnh CN 
-KH báo sự cố hiện tại không theo dõi được hiếu suất NLMT trên App
+          <t>KH đã báo Anh Mạnh CN _x000D_
+KH báo sự cố hiện tại không theo dõi được hiếu suất NLMT trên App_x000D_
 Yêu cầu CN cho KT qua ktra hô trợ KH</t>
         </is>
       </c>
@@ -14207,13 +14207,13 @@
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>KH đã báo KT
-KH báo sự cố NLMT đanh bị cháy Atomat 
+          <t>KH đã báo KT_x000D_
+KH báo sự cố NLMT đanh bị cháy Atomat _x000D_
 YÊu cầu CN cho KT qua ktra xử lý cho KH</t>
         </is>
       </c>
@@ -14384,13 +14384,13 @@
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>KH chưa báo CN 
-KH báo sự cố NLMT hiện tại ệ thống lỗi không sản xuất ra điện
+          <t>KH chưa báo CN _x000D_
+KH báo sự cố NLMT hiện tại ệ thống lỗi không sản xuất ra điện_x000D_
 Yêu cầu CN cho KT qua ktra xử lý cho KH</t>
         </is>
       </c>
@@ -14561,14 +14561,14 @@
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>KH đã báo KT
-KH báo sự cố NLMT điện nhảy át nhảy biến tần không lên
-Yêu cầu CN cho KT qua ktra xử lý cho KH
+          <t>KH đã báo KT_x000D_
+KH báo sự cố NLMT điện nhảy át nhảy biến tần không lên_x000D_
+Yêu cầu CN cho KT qua ktra xử lý cho KH_x000D_
 Địa chỉ lắp đặt KM13+800 đường gom đại lộ Thăng Long</t>
         </is>
       </c>
@@ -14739,13 +14739,13 @@
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>Hiệu suất sản phẩm kém</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>KH có báo KT
-KH phản ánh về việc có lắp hệ thống NLMT nhưng vẫn không thấy tiền điện giảm 
+          <t>KH có báo KT_x000D_
+KH phản ánh về việc có lắp hệ thống NLMT nhưng vẫn không thấy tiền điện giảm _x000D_
 Yêu cầu CN cho KT qua ktra cho KH</t>
         </is>
       </c>
@@ -14916,13 +14916,13 @@
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>KH đã báo KT nhưng chưa được hỗ trợ 
-KH báo sự cố hư ats không có bật trên app
+          <t>KH đã báo KT nhưng chưa được hỗ trợ _x000D_
+KH báo sự cố hư ats không có bật trên app_x000D_
 Yêu cầu CN cho KT qua ktra xử lý cho KH</t>
         </is>
       </c>
@@ -15088,7 +15088,7 @@
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>Tư vấn sản phẩm/dịch vụ</t>
+          <t>Liên hệ/tư vấn</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
@@ -15263,7 +15263,7 @@
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>Liên hệ / Đặt lịch lại</t>
+          <t>Liên hệ/tư vấn</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
@@ -15433,13 +15433,13 @@
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>CN báo sự cố hộ KH 0985792828
-KH báo sự cố hiện tại hệ thống NLMT đang bị ngừng hoạt động 
+          <t>CN báo sự cố hộ KH 0985792828_x000D_
+KH báo sự cố hiện tại hệ thống NLMT đang bị ngừng hoạt động _x000D_
 Yêu cầu CN cho KT qua ktra xử ký cho KH</t>
         </is>
       </c>
@@ -15602,13 +15602,13 @@
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>KH đã báo KT nhưng KT đã chuyển công tác
-KH báo sự cố Ivt liên tục báo alam
+          <t>KH đã báo KT nhưng KT đã chuyển công tác_x000D_
+KH báo sự cố Ivt liên tục báo alam_x000D_
 Yêu cầu CN cho KT qua ktra xử lý cho KH</t>
         </is>
       </c>
@@ -15774,13 +15774,13 @@
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>Hiệu suất sản phẩm kém</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>KH chưa báo CN 
-KH báo sự cố thấy hệ thống NLMT hiệu suất giảm kém đi khoảng tầm 30-50% so với trước
+          <t>KH chưa báo CN _x000D_
+KH báo sự cố thấy hệ thống NLMT hiệu suất giảm kém đi khoảng tầm 30-50% so với trước_x000D_
 Yêu cầu CN cho KT qua ktra xử lý cho KH</t>
         </is>
       </c>
@@ -15951,13 +15951,13 @@
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>CN báo sự cố hộ KH 0985792828
-KH gặp sự cố hệ thống đang bị nhảy at mất điện
+          <t>CN báo sự cố hộ KH 0985792828_x000D_
+KH gặp sự cố hệ thống đang bị nhảy at mất điện_x000D_
 Yêu cầu CN cho KT qua ktra xử lý cho KH</t>
         </is>
       </c>
@@ -16128,13 +16128,13 @@
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>KH đã báo KT Anh Hà 
-KH báo sự cố điện NLMT hiện tại mất điện trong khi điện NLMT còn nhưng không dùng được không tự đảo nguồn đươc
+          <t>KH đã báo KT Anh Hà _x000D_
+KH báo sự cố điện NLMT hiện tại mất điện trong khi điện NLMT còn nhưng không dùng được không tự đảo nguồn đươc_x000D_
 Yêu cầu CN cho KT qua ktra xử lý cho KH</t>
         </is>
       </c>
@@ -16305,13 +16305,13 @@
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>KH đã báo KT 
-KH báo sự cố NLMT điện chập chờn ibs chập chờn lỗi, mất điện
+          <t>KH đã báo KT _x000D_
+KH báo sự cố NLMT điện chập chờn ibs chập chờn lỗi, mất điện_x000D_
 Yêu cầu CN cho KT qua ktra xử lý cho KH</t>
         </is>
       </c>
@@ -16479,13 +16479,13 @@
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>Sau bảo dưỡng thiết bị bị hỏng</t>
+          <t>Chất lượng bảo dưỡng</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>1. KH đã liên hệ KT
-2. Đơn hàng bảo dưỡng điều hòa được hỗ trợ ngày 15/08, hiện cửa điều hòa không đóng được
+          <t>1. KH đã liên hệ KT_x000D_
+2. Đơn hàng bảo dưỡng điều hòa được hỗ trợ ngày 15/08, hiện cửa điều hòa không đóng được_x000D_
 3. KH cần CN hỗ trợ khắc phục sớm</t>
         </is>
       </c>
@@ -16656,13 +16656,13 @@
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>1. KH đã liên hệ CN
-2. Ắc quy lưu trữ HT NLMT có điện nhưng không xả
+          <t>1. KH đã liên hệ CN_x000D_
+2. Ắc quy lưu trữ HT NLMT có điện nhưng không xả_x000D_
 3. KH cần CN đến kiêm tra và khắc phục sự cố sớm</t>
         </is>
       </c>
@@ -16833,13 +16833,13 @@
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>KH chưa báo KT
-KH báo sự cố NLMT mất điện và điện nlmt không phát điện không thấy điện chạy vào nhà
+          <t>KH chưa báo KT_x000D_
+KH báo sự cố NLMT mất điện và điện nlmt không phát điện không thấy điện chạy vào nhà_x000D_
 Yêu cầu CN cho KT qua ktra xử lý cho KH</t>
         </is>
       </c>
@@ -17010,13 +17010,13 @@
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>Lỗi kết nối giữa thiết bị và hệ thống theo dõi</t>
+          <t>Kết nối hệ thống</t>
         </is>
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>KH chưa báo Cn 
-KH báo sự cố NLMT hiện tại không báo trên app và không theo dõi được qua App
+          <t>KH chưa báo Cn _x000D_
+KH báo sự cố NLMT hiện tại không báo trên app và không theo dõi được qua App_x000D_
 Yêu cầu CN cho KT qua ktra xử lý cho KH</t>
         </is>
       </c>
@@ -17187,13 +17187,13 @@
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>KH đã báo KT 
-KH báo sự cố NLMT hiện tại không hoạt động, mất điện là điện NLMT cũng mất 
+          <t>KH đã báo KT _x000D_
+KH báo sự cố NLMT hiện tại không hoạt động, mất điện là điện NLMT cũng mất _x000D_
 Yêu cầu CN cho KT qua ktra xử lý cho KH</t>
         </is>
       </c>
@@ -17361,13 +17361,13 @@
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>KH báo KT nhưng chưa được hõ trợ 
-KH báo sự cố NLMT hiện tại không cấp điện không vào điện, theo dõi trên app không thấy có điện 
+          <t>KH báo KT nhưng chưa được hõ trợ _x000D_
+KH báo sự cố NLMT hiện tại không cấp điện không vào điện, theo dõi trên app không thấy có điện _x000D_
 Yêu cầu CN cho KT qua ktra cho KH</t>
         </is>
       </c>
@@ -17535,7 +17535,7 @@
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>Hướng dẫn, hỗ trợ sử dụng sản phẩm</t>
+          <t>Liên hệ/tư vấn</t>
         </is>
       </c>
       <c r="R98" t="inlineStr">
@@ -17705,7 +17705,7 @@
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>Liên hệ / Đặt lịch lại</t>
+          <t>Liên hệ/tư vấn</t>
         </is>
       </c>
       <c r="R99" t="inlineStr">
@@ -17875,7 +17875,7 @@
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>Tư vấn sản phẩm/dịch vụ</t>
+          <t>Liên hệ/tư vấn</t>
         </is>
       </c>
       <c r="R100" t="inlineStr">
@@ -18045,7 +18045,7 @@
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>Liên hệ chậm</t>
+          <t>Liên hệ/tư vấn</t>
         </is>
       </c>
       <c r="R101" t="inlineStr">
@@ -18220,13 +18220,13 @@
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>KH đã báo KT, KT báo gọi TĐ
-KH báo sự cố nlmt không nạp vào pin điện nlmt, hiện tại chỉ còn điện lưới
+          <t>KH đã báo KT, KT báo gọi TĐ_x000D_
+KH báo sự cố nlmt không nạp vào pin điện nlmt, hiện tại chỉ còn điện lưới_x000D_
 Yêu cầu CN cho KT qua ktra xử lý cho KH</t>
         </is>
       </c>
@@ -18389,7 +18389,7 @@
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>Liên hệ chậm</t>
+          <t>Liên hệ/tư vấn</t>
         </is>
       </c>
       <c r="R103" t="inlineStr">
@@ -18559,12 +18559,12 @@
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>Thủ tục/giấy tờ/ Hóa đơn/ Hồ sơ lắp đặt</t>
+          <t>Thủ tục/giấy tờ/ Hóa đơn/ Hồ sơ lắp đặt</t>
         </is>
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>KH báo đã thanh toán xong các chi phí lắp hệ thống NLMT nhưng chưa hề nhận được hóa đơn mua bán lắp đặt, KH có liên hệ bạn sale trước đấy nhưng không liên hệ được
+          <t>KH báo đã thanh toán xong các chi phí lắp hệ thống NLMT nhưng chưa hề nhận được hóa đơn mua bán lắp đặt, KH có liên hệ bạn sale trước đấy nhưng không liên hệ được_x000D_
 Yêu cầu CN lien hệ lại và hỗ trợ cho KH</t>
         </is>
       </c>
@@ -18730,7 +18730,7 @@
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>Liên hệ / Đặt lịch lại</t>
+          <t>Liên hệ/tư vấn</t>
         </is>
       </c>
       <c r="R105" t="inlineStr">
@@ -18905,13 +18905,13 @@
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>KH đã báo KT nhưng chưa được hỗ trợ
-KH báo sự cố hệ thống  có lắp bộ tủ đảo công tơ 15 ngày tự đảo. Gần đây hệ không đảo sau 15 ngày nữa
+          <t>KH đã báo KT nhưng chưa được hỗ trợ_x000D_
+KH báo sự cố hệ thống  có lắp bộ tủ đảo công tơ 15 ngày tự đảo. Gần đây hệ không đảo sau 15 ngày nữa_x000D_
 Yêu cầu CN cho KT qua ktra xử lý cho KH</t>
         </is>
       </c>
@@ -19079,7 +19079,7 @@
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>Đơn bảo dưỡng hết hạn bảo hành</t>
+          <t>Chất lượng bảo dưỡng</t>
         </is>
       </c>
       <c r="R107" t="inlineStr">
@@ -19254,7 +19254,7 @@
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>Đơn bảo dưỡng hết hạn bảo hành</t>
+          <t>Chất lượng bảo dưỡng</t>
         </is>
       </c>
       <c r="R108" t="inlineStr">
@@ -19424,7 +19424,7 @@
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>Liên hệ tư vấn chậm</t>
+          <t>Liên hệ/tư vấn</t>
         </is>
       </c>
       <c r="R109" t="inlineStr">
@@ -19594,7 +19594,7 @@
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>Tư vấn sản phẩm/dịch vụ</t>
+          <t>Liên hệ/tư vấn</t>
         </is>
       </c>
       <c r="R110" t="inlineStr">
@@ -19764,13 +19764,13 @@
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>Inverter không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t>1. KH chưa báo CN
-2. KH phản ánh: ivt gặp trục trặc, quạt tản nhiệt bị hỏng nên biến tần nóng lúc đứng lúc chạy
+          <t>1. KH chưa báo CN_x000D_
+2. KH phản ánh: ivt gặp trục trặc, quạt tản nhiệt bị hỏng nên biến tần nóng lúc đứng lúc chạy_x000D_
 3. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này</t>
         </is>
       </c>
@@ -19938,13 +19938,13 @@
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R112" t="inlineStr">
         <is>
-          <t>1. KH đã liên hệ CN
-2. Từ P/á mã TT_1786152323690, KH phản ánh sau khi CNCT đến kiểm tra và kết luận tủ cháy đã báo giá cho KH chi phí thay tủ là 50%, KH hiện đang không đồng ý do thiết bị vẫn trong hạn bảo hành
+          <t>1. KH đã liên hệ CN_x000D_
+2. Từ P/á mã TT_1786152323690, KH phản ánh sau khi CNCT đến kiểm tra và kết luận tủ cháy đã báo giá cho KH chi phí thay tủ là 50%, KH hiện đang không đồng ý do thiết bị vẫn trong hạn bảo hành_x000D_
 3. KH cần CNCT liên hệ và có hướng khắc phục, xử lý cho KH gấp</t>
         </is>
       </c>
@@ -20112,13 +20112,13 @@
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>Cài đặt hệ thống (APP/Mật khẩu)</t>
+          <t>Kết nối hệ thống</t>
         </is>
       </c>
       <c r="R113" t="inlineStr">
         <is>
-          <t>1. KH chưa báo CN
-2. KH phản ánh: quên mật khẩu đăng nhập app NLMT, ngoài ra hệ nlmt đang gặp trục trặc ko hoạt động được
+          <t>1. KH chưa báo CN_x000D_
+2. KH phản ánh: quên mật khẩu đăng nhập app NLMT, ngoài ra hệ nlmt đang gặp trục trặc ko hoạt động được_x000D_
 3. KH yêu cầu: qua kiểm tra hệ nlmt và hỗ trợ KH đăng nhập lại app</t>
         </is>
       </c>
@@ -20289,13 +20289,13 @@
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R114" t="inlineStr">
         <is>
-          <t>1. KH đã liên hệ CN
-2. Phía điện lực cắt điện để bảo trì từ 6h sáng nay, HT NLMT có pin lưu trữ nhưng không xả, có hiện tượng bốc khói, Điện lực kiểm tra cho KH thấy đang bị mât một pha
+          <t>1. KH đã liên hệ CN_x000D_
+2. Phía điện lực cắt điện để bảo trì từ 6h sáng nay, HT NLMT có pin lưu trữ nhưng không xả, có hiện tượng bốc khói, Điện lực kiểm tra cho KH thấy đang bị mât một pha_x000D_
 3. KH cần CN hỗ trợ khắc phục sớm</t>
         </is>
       </c>
@@ -20466,13 +20466,13 @@
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R115" t="inlineStr">
         <is>
-          <t>1. KH đã liên hệ CN
-2. HT NLMT hiện đang không hoạt động, không có điện NLMT, điện lực đang cắt điện lưới
+          <t>1. KH đã liên hệ CN_x000D_
+2. HT NLMT hiện đang không hoạt động, không có điện NLMT, điện lực đang cắt điện lưới_x000D_
 3. KH cần hỗ trợ khắc phục sớm</t>
         </is>
       </c>
@@ -20643,7 +20643,7 @@
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>Liên hệ chậm</t>
+          <t>Liên hệ/tư vấn</t>
         </is>
       </c>
       <c r="R116" t="inlineStr">
@@ -20818,13 +20818,13 @@
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R117" t="inlineStr">
         <is>
-          <t>1.Khi KH sử dụng HT NLMT, tải nhà tiêu thụ khoảng hơn 3Kw tuy nhiên  khi chuyển sang điện lưới tải tăng lên 9-&gt;10kw
-2. KH đã liên hệ CN và được hướng dẫn xử lý sơ bộ 
+          <t>1.Khi KH sử dụng HT NLMT, tải nhà tiêu thụ khoảng hơn 3Kw tuy nhiên  khi chuyển sang điện lưới tải tăng lên 9-&gt;10kw_x000D_
+2. KH đã liên hệ CN và được hướng dẫn xử lý sơ bộ _x000D_
 3. Hiện KH cần CN hỗ trợ xử lý trong ngày cho KH, tránh trường hợp tải tăng nhiều ảnh hưởng chi phí tiền điện trong tháng</t>
         </is>
       </c>
@@ -20995,14 +20995,15 @@
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R118" t="inlineStr">
         <is>
-          <t>1. KH đã báo CN: a Minh
-2. KH phản ánh: mất điện lưới nhưng ko nhảy sang điện nlmt để sử dụng
-3. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này
+          <t>1. KH đã báo CN: a Minh_x000D_
+2. KH phản ánh: mất điện lưới nhưng ko nhảy sang điện nlmt để sử dụng_x000D_
+3. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này_x000D_
+_x000D_
 Địa chỉ Lắp đặt:5/3 Phường Đình Bảng, Từ Sơn, Bắc Ninh</t>
         </is>
       </c>
@@ -21173,13 +21174,13 @@
       </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>KH chưa báo CN 
-KH báo sự cố NLMT khi mất điện không tự động chuyển từ điện lưới sang điện NLMT
+          <t>KH chưa báo CN _x000D_
+KH báo sự cố NLMT khi mất điện không tự động chuyển từ điện lưới sang điện NLMT_x000D_
 Yêu cầu CN cho KT qua ktra cho KH</t>
         </is>
       </c>
@@ -21350,13 +21351,13 @@
       </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t>KH đã báo KT, KT báo gọi TĐ
-KH báo sự cố NLMT khoản 8h tối là điện nlmt hết, nhưng giờ đến tầm đấy là tụt át, không có điện lưới, mà kêu người qua ktra thì nguồn điện vẫn có điện lưới
+          <t>KH đã báo KT, KT báo gọi TĐ_x000D_
+KH báo sự cố NLMT khoản 8h tối là điện nlmt hết, nhưng giờ đến tầm đấy là tụt át, không có điện lưới, mà kêu người qua ktra thì nguồn điện vẫn có điện lưới_x000D_
 Yêu cầu CN cho KT qua ktra cho KT</t>
         </is>
       </c>
@@ -21522,7 +21523,7 @@
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>Tư vấn sản phẩm/dịch vụ</t>
+          <t>Liên hệ/tư vấn</t>
         </is>
       </c>
       <c r="R121" t="inlineStr">
@@ -21697,7 +21698,7 @@
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>Sau bảo dưỡng thiết bị bị hỏng</t>
+          <t>Chất lượng bảo dưỡng</t>
         </is>
       </c>
       <c r="R122" t="inlineStr">
@@ -21867,7 +21868,7 @@
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>Liên hệ chậm</t>
+          <t>Liên hệ/tư vấn</t>
         </is>
       </c>
       <c r="R123" t="inlineStr">
@@ -22037,7 +22038,7 @@
       </c>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>Tư vấn sản phẩm/dịch vụ</t>
+          <t>Liên hệ/tư vấn</t>
         </is>
       </c>
       <c r="R124" t="inlineStr">
@@ -22212,13 +22213,13 @@
       </c>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>Hỗ trợ lắp đặt</t>
+          <t>Tiến độ triển khai</t>
         </is>
       </c>
       <c r="R125" t="inlineStr">
         <is>
-          <t>1. CN phản ánh cho KH
-2. Khách hàng yêu cầu đo tiếp địa hệ năng lượng mặt trời từ khi lắp đặt xong , nhưng đến nay vẫn chưa thực hiện, 
+          <t>1. CN phản ánh cho KH_x000D_
+2. Khách hàng yêu cầu đo tiếp địa hệ năng lượng mặt trời từ khi lắp đặt xong , nhưng đến nay vẫn chưa thực hiện, _x000D_
 3.Khách hàng yêu cầu kỹ thuật đến thực hiện ngay</t>
         </is>
       </c>
@@ -22384,7 +22385,7 @@
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>Liên hệ chậm</t>
+          <t>Liên hệ/tư vấn</t>
         </is>
       </c>
       <c r="R126" t="inlineStr">
@@ -22554,7 +22555,7 @@
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>Liên hệ chậm</t>
+          <t>Liên hệ/tư vấn</t>
         </is>
       </c>
       <c r="R127" t="inlineStr">
@@ -22724,7 +22725,7 @@
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>Liên hệ / Đặt lịch lại</t>
+          <t>Liên hệ/tư vấn</t>
         </is>
       </c>
       <c r="R128" t="inlineStr">
@@ -22899,13 +22900,13 @@
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R129" t="inlineStr">
         <is>
-          <t>1.KH chưa liên hệ CN
-2. Thiết bị NLMT của KH gặp sự cố, báo lỗi F18
+          <t>1.KH chưa liên hệ CN_x000D_
+2. Thiết bị NLMT của KH gặp sự cố, báo lỗi F18_x000D_
 3. KH cần CN hỗ trợ kiểm tra và khắc phục sớm</t>
         </is>
       </c>
@@ -23076,7 +23077,7 @@
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>Liên hệ tư vấn chậm</t>
+          <t>Liên hệ/tư vấn</t>
         </is>
       </c>
       <c r="R130" t="inlineStr">
@@ -23246,7 +23247,7 @@
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>Chất lượng, dịch vụ, Giá cả</t>
+          <t>Chất lượng triển khai</t>
         </is>
       </c>
       <c r="R131" t="inlineStr">
@@ -23421,13 +23422,13 @@
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>1. KH chưa báo CN
-2. KH phản ánh: hệ nlmt ko chạy được, hệ bám tải, có 2 pha chỉ 1 pha sáng, trên app kiểm tra ko thấy hoạt động
+          <t>1. KH chưa báo CN_x000D_
+2. KH phản ánh: hệ nlmt ko chạy được, hệ bám tải, có 2 pha chỉ 1 pha sáng, trên app kiểm tra ko thấy hoạt động_x000D_
 3. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này gấp</t>
         </is>
       </c>
@@ -23595,7 +23596,7 @@
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>Không kết nối được app/Wifi và không theo dõi được hiệu suất</t>
+          <t>Kết nối hệ thống</t>
         </is>
       </c>
       <c r="R133" t="inlineStr">
@@ -23770,14 +23771,14 @@
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>Thiết bị vỡ, hỏng, chập cháy</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R134" t="inlineStr">
         <is>
-          <t>Người nhà KH 0968755629 báo sự cố
-1. KH chưa báo CN
-2. KH phản ánh: đang dùng điện nlmt thì 11r đêm qua bụp bụp mất điện. Nay KH có cho điện lực, điện nước qua kiểm tra thì thấy bình thường. KH kiểm tra tủ điện ats, chuyển đổi nguồn thì thấy mất át, bị chết và hiện tại đang phải dùng điện lưới
+          <t>Người nhà KH 0968755629 báo sự cố_x000D_
+1. KH chưa báo CN_x000D_
+2. KH phản ánh: đang dùng điện nlmt thì 11r đêm qua bụp bụp mất điện. Nay KH có cho điện lực, điện nước qua kiểm tra thì thấy bình thường. KH kiểm tra tủ điện ats, chuyển đổi nguồn thì thấy mất át, bị chết và hiện tại đang phải dùng điện lưới_x000D_
 3. KH yêu cầu: qua kiểm tra, khắc phục và đấu nối lại</t>
         </is>
       </c>
@@ -23948,7 +23949,7 @@
       </c>
       <c r="Q135" t="inlineStr">
         <is>
-          <t>Liên hệ / Đặt lịch lại</t>
+          <t>Liên hệ/tư vấn</t>
         </is>
       </c>
       <c r="R135" t="inlineStr">
@@ -24123,13 +24124,13 @@
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R136" t="inlineStr">
         <is>
-          <t>CN báo sự cố hộ KH 0986688282 
-KH gặp sự cố NLMT hiện tại không vào được app và không theo dõi được hiệu suất 
+          <t>CN báo sự cố hộ KH 0986688282 _x000D_
+KH gặp sự cố NLMT hiện tại không vào được app và không theo dõi được hiệu suất _x000D_
 Yêu cầu CN cho KT qua ktra cho KH</t>
         </is>
       </c>
@@ -24295,7 +24296,7 @@
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>Liên hệ / Đặt lịch lại</t>
+          <t>Liên hệ/tư vấn</t>
         </is>
       </c>
       <c r="R137" t="inlineStr">
@@ -24470,13 +24471,13 @@
       </c>
       <c r="Q138" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R138" t="inlineStr">
         <is>
-          <t>CN 0384989610 báo sự cố hộ KH
-1. KH phản ánh: pin lưu trữ ko xả
+          <t>CN 0384989610 báo sự cố hộ KH_x000D_
+1. KH phản ánh: pin lưu trữ ko xả_x000D_
 2. KH yêu cầu: qua kiểm tra, xử lý</t>
         </is>
       </c>
@@ -24647,13 +24648,13 @@
       </c>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>Thiết bị vỡ, hỏng, chập cháy</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R139" t="inlineStr">
         <is>
-          <t>CN 0972636399 báo sự cố hộ KH
-1. KH phản ánh: Dây dẫn bị hở ống bảo vệ cọ vào mái tôn khả năng chập chờn
+          <t>CN 0972636399 báo sự cố hộ KH_x000D_
+1. KH phản ánh: Dây dẫn bị hở ống bảo vệ cọ vào mái tôn khả năng chập chờn_x000D_
 2. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này gấp</t>
         </is>
       </c>
@@ -24819,13 +24820,13 @@
       </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>Thiết bị vỡ, hỏng, chập cháy</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R140" t="inlineStr">
         <is>
-          <t>1. KH chưa báo CN
-2. KH phản ánh: tủ điện bị cháy
+          <t>1. KH chưa báo CN_x000D_
+2. KH phản ánh: tủ điện bị cháy_x000D_
 3. KH yêu cầu: qua kiểm tra, khắc phục hoặc đưa ra phương án thay thế cho KH</t>
         </is>
       </c>
@@ -24996,13 +24997,13 @@
       </c>
       <c r="Q141" t="inlineStr">
         <is>
-          <t>Hướng dẫn, hỗ trợ sử dụng sản phẩm</t>
+          <t>Liên hệ/tư vấn</t>
         </is>
       </c>
       <c r="R141" t="inlineStr">
         <is>
-          <t>1. KH chưa báo CN
-2. KH phản ánh: sự cố có xe tông vào đường dây CTY nên KH lo ngại ảnh hưởng đến hệ nlmt
+          <t>1. KH chưa báo CN_x000D_
+2. KH phản ánh: sự cố có xe tông vào đường dây CTY nên KH lo ngại ảnh hưởng đến hệ nlmt_x000D_
 3. KH yêu cầu: qua kiểm tra hệ nlmt xem có vấn đề gì không và khắc phục</t>
         </is>
       </c>
@@ -25173,13 +25174,13 @@
       </c>
       <c r="Q142" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R142" t="inlineStr">
         <is>
-          <t>CN 981168696 báo sự cố hộ KH 
-1. KH phản ánh: hệ thống nlmt báo mất điện, ko sạc ko sản xuất ra điện, trên app báo ko hoạt động, báo lỗi
+          <t>CN 981168696 báo sự cố hộ KH _x000D_
+1. KH phản ánh: hệ thống nlmt báo mất điện, ko sạc ko sản xuất ra điện, trên app báo ko hoạt động, báo lỗi_x000D_
 2. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này sớm</t>
         </is>
       </c>
@@ -25350,13 +25351,13 @@
       </c>
       <c r="Q143" t="inlineStr">
         <is>
-          <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
+          <t>Chất lượng triển khai</t>
         </is>
       </c>
       <c r="R143" t="inlineStr">
         <is>
-          <t>1. KH đã báo CN: anh Việt
-2. KH phản ánh: hiệu suất kém, hệ nlmt ko hoạt động. Từ sáng tới giờ pin lưu trữ bị đứng ở 24%, chỉ có ra được 10 số điện. KT là anh Việt hôm kia có qua kiểm tra rồi, và báo ko có vấn đề gì nhưng đến hôm nay KH thấy hệ ko hoạt động nữa.
+          <t>1. KH đã báo CN: anh Việt_x000D_
+2. KH phản ánh: hiệu suất kém, hệ nlmt ko hoạt động. Từ sáng tới giờ pin lưu trữ bị đứng ở 24%, chỉ có ra được 10 số điện. KT là anh Việt hôm kia có qua kiểm tra rồi, và báo ko có vấn đề gì nhưng đến hôm nay KH thấy hệ ko hoạt động nữa._x000D_
 3. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này</t>
         </is>
       </c>
@@ -25522,7 +25523,7 @@
       </c>
       <c r="Q144" t="inlineStr">
         <is>
-          <t>Liên hệ / Đặt lịch lại</t>
+          <t>Liên hệ/tư vấn</t>
         </is>
       </c>
       <c r="R144" t="inlineStr">
@@ -25697,13 +25698,13 @@
       </c>
       <c r="Q145" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R145" t="inlineStr">
         <is>
-          <t>CN 0967884099 báo sự cố hộ KH 
-1. KH phản ánh: pin lưu trữ bị lỗi ko vào điện
+          <t>CN 0967884099 báo sự cố hộ KH _x000D_
+1. KH phản ánh: pin lưu trữ bị lỗi ko vào điện_x000D_
 2. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này</t>
         </is>
       </c>
@@ -25874,13 +25875,13 @@
       </c>
       <c r="Q146" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R146" t="inlineStr">
         <is>
-          <t>1. KH đã báo CN: a Độ
-2. KH phản ánh: pin lưu trữ đi đến 70% là tự ngắt ko vào nữa, vạch pin cũng bị mất
+          <t>1. KH đã báo CN: a Độ_x000D_
+2. KH phản ánh: pin lưu trữ đi đến 70% là tự ngắt ko vào nữa, vạch pin cũng bị mất_x000D_
 3. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này</t>
         </is>
       </c>
@@ -26051,7 +26052,7 @@
       </c>
       <c r="Q147" t="inlineStr">
         <is>
-          <t>Liên hệ / Đặt lịch lại</t>
+          <t>Liên hệ/tư vấn</t>
         </is>
       </c>
       <c r="R147" t="inlineStr">
@@ -26226,13 +26227,13 @@
       </c>
       <c r="Q148" t="inlineStr">
         <is>
-          <t>Thủ tục/giấy tờ/ Hóa đơn/ Hồ sơ lắp đặt</t>
+          <t>Thủ tục/giấy tờ/ Hóa đơn/ Hồ sơ lắp đặt</t>
         </is>
       </c>
       <c r="R148" t="inlineStr">
         <is>
-          <t>1. KH đã báo CN
-2. KH phản ánh: HĐ của KH đã nghiệm thu trước đó KH có nhu cầu nâng hệ nlmt từ 12 tấm pin &gt; 16 tấm pin và biến tần từ 6kw &gt; 8kw nên HĐ của KH có thay đổi về giá trị HĐ, tổng HĐ KH thanh toán là hơn 147tr nhưng trên hệ thống chỉ có là 123tr hơn. KH theo dõi phần bảo hành thiết bị trên app cũng ko thấy có.
+          <t>1. KH đã báo CN_x000D_
+2. KH phản ánh: HĐ của KH đã nghiệm thu trước đó KH có nhu cầu nâng hệ nlmt từ 12 tấm pin &gt; 16 tấm pin và biến tần từ 6kw &gt; 8kw nên HĐ của KH có thay đổi về giá trị HĐ, tổng HĐ KH thanh toán là hơn 147tr nhưng trên hệ thống chỉ có là 123tr hơn. KH theo dõi phần bảo hành thiết bị trên app cũng ko thấy có._x000D_
 3. KH yêu cầu: Cung cấp bản HĐ cứng cho KH đúng giá trị HĐ KH thanh toán, ghi rõ phần bảo hành các thiết bị, số serial, mã sản phẩm để KH theo dõi</t>
         </is>
       </c>
@@ -26403,13 +26404,13 @@
       </c>
       <c r="Q149" t="inlineStr">
         <is>
-          <t>Inverter không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R149" t="inlineStr">
         <is>
-          <t>CN 0393188966 báo sự cố hộ KH
-1. KH phản ánh: mới bị mất điện xong ivt báo lỗi ko phát ra điện, ko có điện xuống tải
+          <t>CN 0393188966 báo sự cố hộ KH_x000D_
+1. KH phản ánh: mới bị mất điện xong ivt báo lỗi ko phát ra điện, ko có điện xuống tải_x000D_
 2. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này</t>
         </is>
       </c>
@@ -26580,13 +26581,13 @@
       </c>
       <c r="Q150" t="inlineStr">
         <is>
-          <t>Sản phẩm bị ngắt quãng/ Không theo dõi và không nghe được</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R150" t="inlineStr">
         <is>
-          <t>1. KH đã báo CN
-2. KH phản ánh: KH đã có nâng cấp hạ tầng mạng 2 lần nhưng mạng vẫn rất chập chờn nghe zalo đều rất chập chờn, KH ko rõ là phần đấu nối hay đường truyền kém 
+          <t>1. KH đã báo CN_x000D_
+2. KH phản ánh: KH đã có nâng cấp hạ tầng mạng 2 lần nhưng mạng vẫn rất chập chờn nghe zalo đều rất chập chờn, KH ko rõ là phần đấu nối hay đường truyền kém _x000D_
 3. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này</t>
         </is>
       </c>
@@ -26757,13 +26758,13 @@
       </c>
       <c r="Q151" t="inlineStr">
         <is>
-          <t>Inverter không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R151" t="inlineStr">
         <is>
-          <t>1. KH chưa báo CN: có liên hệ người phụ trách lắp đặt nhưng báo chuyển công tác
-2. KH phản ánh: lỗi máy phát điện ở ivt, ivt báo cần khắc phục để đảm bảo điện năng sử dụng
+          <t>1. KH chưa báo CN: có liên hệ người phụ trách lắp đặt nhưng báo chuyển công tác_x000D_
+2. KH phản ánh: lỗi máy phát điện ở ivt, ivt báo cần khắc phục để đảm bảo điện năng sử dụng_x000D_
 3. KH yêu cuầ: qua kiểm tra, khắc phục tình trạng này</t>
         </is>
       </c>
@@ -26934,7 +26935,7 @@
       </c>
       <c r="Q152" t="inlineStr">
         <is>
-          <t>Liên hệ / Đặt lịch lại</t>
+          <t>Liên hệ/tư vấn</t>
         </is>
       </c>
       <c r="R152" t="inlineStr">
@@ -27109,13 +27110,13 @@
       </c>
       <c r="Q153" t="inlineStr">
         <is>
-          <t>Sản phẩm bị ngắt quãng/ Không theo dõi và không nghe được</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R153" t="inlineStr">
         <is>
-          <t>1. KH đã báo CN: a Trướng
-2. KH phản ánh: hệ nlmt đang chạy thì moto ko hoạt động, nửa chừng thì cúp pha. Điện lực đã đến kiểm tra điện vào có điện ra có nên có thể do điện nlmt
+          <t>1. KH đã báo CN: a Trướng_x000D_
+2. KH phản ánh: hệ nlmt đang chạy thì moto ko hoạt động, nửa chừng thì cúp pha. Điện lực đã đến kiểm tra điện vào có điện ra có nên có thể do điện nlmt_x000D_
 3. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này</t>
         </is>
       </c>
@@ -27281,7 +27282,7 @@
       </c>
       <c r="Q154" t="inlineStr">
         <is>
-          <t>Liên hệ / Đặt lịch lại</t>
+          <t>Liên hệ/tư vấn</t>
         </is>
       </c>
       <c r="R154" t="inlineStr">
@@ -27456,13 +27457,13 @@
       </c>
       <c r="Q155" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R155" t="inlineStr">
         <is>
-          <t>1. KH đã báo CN: a Phạm Đức Trí
-2. KH phản ánh: đường dây điện lực bị tắc ảnh hưởng tới điện nlmt và dẫn tới đồ điện trong nhà KH bị hư 
+          <t>1. KH đã báo CN: a Phạm Đức Trí_x000D_
+2. KH phản ánh: đường dây điện lực bị tắc ảnh hưởng tới điện nlmt và dẫn tới đồ điện trong nhà KH bị hư _x000D_
 3. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này gấp</t>
         </is>
       </c>
@@ -27633,13 +27634,13 @@
       </c>
       <c r="Q156" t="inlineStr">
         <is>
-          <t>Lỗi kết nối giữa thiết bị và hệ thống theo dõi</t>
+          <t>Kết nối hệ thống</t>
         </is>
       </c>
       <c r="R156" t="inlineStr">
         <is>
-          <t>1. KH chưa báo CN
-2. KH phản ánh: mất kết nối thiết bị theo dõi
+          <t>1. KH chưa báo CN_x000D_
+2. KH phản ánh: mất kết nối thiết bị theo dõi_x000D_
 3. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này</t>
         </is>
       </c>
@@ -27805,13 +27806,13 @@
       </c>
       <c r="Q157" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R157" t="inlineStr">
         <is>
-          <t>1. KH đã báo CN: a Duy
-2. KH phản ánh: điện nlmt ko vào, KH có trao đổi với CN thì bảo ko hiểu gì về KT và báo điện lực kiểm tra. KH báo điện lực kiểm tra rồi và mọi thứ đều bình thường từ áp đến điện vào nlmt, KH theo dõi thì thấy ko dùng được qua ivt, trên app thì điện báo ko vào. Và phần tủ điện thì KH lại cũng ko kiểm tra được vì khóa, từ lúc làm xong CN ko thấy có bàn giao cho KH
+          <t>1. KH đã báo CN: a Duy_x000D_
+2. KH phản ánh: điện nlmt ko vào, KH có trao đổi với CN thì bảo ko hiểu gì về KT và báo điện lực kiểm tra. KH báo điện lực kiểm tra rồi và mọi thứ đều bình thường từ áp đến điện vào nlmt, KH theo dõi thì thấy ko dùng được qua ivt, trên app thì điện báo ko vào. Và phần tủ điện thì KH lại cũng ko kiểm tra được vì khóa, từ lúc làm xong CN ko thấy có bàn giao cho KH_x000D_
 3. KH yêu cầu: KH hộ là kinh doanh nên cần hỗ trợ kiểm tra sớm, khắc phục phần điện nlmt ko vào để KH có điện để sử dụng</t>
         </is>
       </c>
@@ -27982,13 +27983,13 @@
       </c>
       <c r="Q158" t="inlineStr">
         <is>
-          <t>Inverter không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R158" t="inlineStr">
         <is>
-          <t>1. KH đã báo CN 
-2. KH phản ánh: KH có 2 ivt, hiện tại 1 ivt ko hoạt động
+          <t>1. KH đã báo CN _x000D_
+2. KH phản ánh: KH có 2 ivt, hiện tại 1 ivt ko hoạt động_x000D_
 3. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này</t>
         </is>
       </c>
@@ -28159,13 +28160,13 @@
       </c>
       <c r="Q159" t="inlineStr">
         <is>
-          <t>Hướng dẫn, hỗ trợ sử dụng sản phẩm</t>
+          <t>Liên hệ/tư vấn</t>
         </is>
       </c>
       <c r="R159" t="inlineStr">
         <is>
-          <t>1. KH đã báo CN (KH ko muốn nhắc tên)
-2. KH phản ánh: KH có lịch bảo trì thang máy nhưng chưa thấy có đến ngoài ra phần dầu bôi trơn KH thấy cạn lọ đó rồi cần phải bơm
+          <t>1. KH đã báo CN (KH ko muốn nhắc tên)_x000D_
+2. KH phản ánh: KH có lịch bảo trì thang máy nhưng chưa thấy có đến ngoài ra phần dầu bôi trơn KH thấy cạn lọ đó rồi cần phải bơm_x000D_
 3. KH yêu cầu: cuối tuần khoảng t7 vì trong tuần KH bận đến kiểm tra tổng thể thang máy, và bơm thêm phần dầu bôi trơn</t>
         </is>
       </c>
@@ -28336,13 +28337,13 @@
       </c>
       <c r="Q160" t="inlineStr">
         <is>
-          <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
+          <t>Chất lượng triển khai</t>
         </is>
       </c>
       <c r="R160" t="inlineStr">
         <is>
-          <t>1. KH đã báo CN
-2. KH phản ánh: hiệu suất kém, tăng lên rất nhiều những tháng trước rơi vào 3tr5-4tr nhưng 2,3 tháng gần đây tiền điện tăng 5-6tr5 tiền điện
+          <t>1. KH đã báo CN_x000D_
+2. KH phản ánh: hiệu suất kém, tăng lên rất nhiều những tháng trước rơi vào 3tr5-4tr nhưng 2,3 tháng gần đây tiền điện tăng 5-6tr5 tiền điện_x000D_
 3. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này</t>
         </is>
       </c>
@@ -28513,13 +28514,13 @@
       </c>
       <c r="Q161" t="inlineStr">
         <is>
-          <t>Thiết bị vỡ, hỏng, chập cháy</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R161" t="inlineStr">
         <is>
-          <t>1. KH chưa liên hệ CN
-2. Tủ nguồn của HT NLMT đang có dấu hiệu chập cháy, hở dây đồng, phần băng dính chảy, mùi khét
+          <t>1. KH chưa liên hệ CN_x000D_
+2. Tủ nguồn của HT NLMT đang có dấu hiệu chập cháy, hở dây đồng, phần băng dính chảy, mùi khét_x000D_
 3.KH cần CN liên hệ và hỗ trợ khắc phục sớm</t>
         </is>
       </c>
@@ -28690,13 +28691,13 @@
       </c>
       <c r="Q162" t="inlineStr">
         <is>
-          <t>Hướng dẫn, hỗ trợ sử dụng sản phẩm</t>
+          <t>Liên hệ/tư vấn</t>
         </is>
       </c>
       <c r="R162" t="inlineStr">
         <is>
-          <t>1. KH chưa liên hệ CN
-2. Hiện KH cần hỗ trợ thiết lập thời gian sạc - xẩ của Pin lưu trữ NLMT 
+          <t>1. KH chưa liên hệ CN_x000D_
+2. Hiện KH cần hỗ trợ thiết lập thời gian sạc - xẩ của Pin lưu trữ NLMT _x000D_
 3. KH cần CN liên hệ và hỗ trợ sớm</t>
         </is>
       </c>
@@ -28862,7 +28863,7 @@
       </c>
       <c r="Q163" t="inlineStr">
         <is>
-          <t>Liên hệ chậm</t>
+          <t>Liên hệ/tư vấn</t>
         </is>
       </c>
       <c r="R163" t="inlineStr">
@@ -29037,13 +29038,13 @@
       </c>
       <c r="Q164" t="inlineStr">
         <is>
-          <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
+          <t>Chất lượng triển khai</t>
         </is>
       </c>
       <c r="R164" t="inlineStr">
         <is>
-          <t>1. CN báo sự  cố cho KH (387921791)
-2. Tháng  vừa rồi tiền điện KH cần thanh toán cao bất thường 
+          <t>1. CN báo sự  cố cho KH (387921791)_x000D_
+2. Tháng  vừa rồi tiền điện KH cần thanh toán cao bất thường _x000D_
 3. KH cần CN liên hệ và đến kiểm tra sớm</t>
         </is>
       </c>
@@ -29214,13 +29215,13 @@
       </c>
       <c r="Q165" t="inlineStr">
         <is>
-          <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
+          <t>Chất lượng triển khai</t>
         </is>
       </c>
       <c r="R165" t="inlineStr">
         <is>
-          <t>KH đã  báo KT, KT báo KH gọi TĐ
-KH báo sự cố NLMT KH dùng ít nhưng tiền điện vẫn tăng khá nhiều, trước kia chỉ tầm 1tr6 1tr8/1 tháng nhưng tháng này tiền điện tăng lên 2tr6 và KH cũng không theo dõi được hiệu suất qua App
+          <t>KH đã  báo KT, KT báo KH gọi TĐ_x000D_
+KH báo sự cố NLMT KH dùng ít nhưng tiền điện vẫn tăng khá nhiều, trước kia chỉ tầm 1tr6 1tr8/1 tháng nhưng tháng này tiền điện tăng lên 2tr6 và KH cũng không theo dõi được hiệu suất qua App_x000D_
 Yêu cầu CN cho KT qua ktra cho KH</t>
         </is>
       </c>
@@ -29386,13 +29387,13 @@
       </c>
       <c r="Q166" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R166" t="inlineStr">
         <is>
-          <t>1. KH chưa liên hệ CN
-2. Hiện HT NLMT đang không sản xuất điện, Trên App theo dõi hiệu suất không có thông tin điện NLMT phát sinh, chỉ có điện lưới
+          <t>1. KH chưa liên hệ CN_x000D_
+2. Hiện HT NLMT đang không sản xuất điện, Trên App theo dõi hiệu suất không có thông tin điện NLMT phát sinh, chỉ có điện lưới_x000D_
 3. KH cần CN liên hệ và kiểm tra sớm</t>
         </is>
       </c>
@@ -29563,13 +29564,13 @@
       </c>
       <c r="Q167" t="inlineStr">
         <is>
-          <t>Lỗi kết nối giữa thiết bị và hệ thống theo dõi</t>
+          <t>Kết nối hệ thống</t>
         </is>
       </c>
       <c r="R167" t="inlineStr">
         <is>
-          <t>KH đã báo CN 
-KH phản ánh : Không theo dõi được hiệu suất trên app deye
+          <t>KH đã báo CN _x000D_
+KH phản ánh : Không theo dõi được hiệu suất trên app deye_x000D_
 Yêu cầu CN cho KT qua ktra cho KH</t>
         </is>
       </c>
@@ -29740,13 +29741,13 @@
       </c>
       <c r="Q168" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R168" t="inlineStr">
         <is>
-          <t>1. KH chưa liên hệ CN
-2. Điện mặt trời không hoạt động khi mất điện, Trước đó đã được kiểm tra một lần nhưng chưa khắc phục triệt để
+          <t>1. KH chưa liên hệ CN_x000D_
+2. Điện mặt trời không hoạt động khi mất điện, Trước đó đã được kiểm tra một lần nhưng chưa khắc phục triệt để_x000D_
 3. KH cần CN liên hệ và hỗ trợ sớm</t>
         </is>
       </c>
@@ -29917,13 +29918,13 @@
       </c>
       <c r="Q169" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R169" t="inlineStr">
         <is>
-          <t>1. KH đã liên hệ CN
-2. Nhà KH đang mất điện sáng ngày 13/08, không có điện lưới và điện NLMT
+          <t>1. KH đã liên hệ CN_x000D_
+2. Nhà KH đang mất điện sáng ngày 13/08, không có điện lưới và điện NLMT_x000D_
 3. KH cần CN liên hệ và đến hỗ trợ sớm</t>
         </is>
       </c>
@@ -30089,12 +30090,12 @@
       </c>
       <c r="Q170" t="inlineStr">
         <is>
-          <t>Liên hệ chậm</t>
+          <t>Liên hệ/tư vấn</t>
         </is>
       </c>
       <c r="R170" t="inlineStr">
         <is>
-          <t>KH đặt đơn DVKT hiện chưa được CN liên hệ và đến hỗ trợ thực hiện đơn hàng
+          <t>KH đặt đơn DVKT hiện chưa được CN liên hệ và đến hỗ trợ thực hiện đơn hàng_x000D_
 KH cần hỗ trợ gấp trong sáng ngày 13/08</t>
         </is>
       </c>
@@ -30265,13 +30266,13 @@
       </c>
       <c r="Q171" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R171" t="inlineStr">
         <is>
-          <t>1. CN báo sự cố cho KH (982778966)
-2. HT NLMT đang gặp sự cố đóng ngắt liên tục, một số thời điểm không có điện NLMT
+          <t>1. CN báo sự cố cho KH (982778966)_x000D_
+2. HT NLMT đang gặp sự cố đóng ngắt liên tục, một số thời điểm không có điện NLMT_x000D_
 3. KH cần CN kiểm tra và đề xuất hướng xử lý cho KH</t>
         </is>
       </c>
@@ -30442,7 +30443,7 @@
       </c>
       <c r="Q172" t="inlineStr">
         <is>
-          <t>Liên hệ / Đặt lịch lại</t>
+          <t>Liên hệ/tư vấn</t>
         </is>
       </c>
       <c r="R172" t="inlineStr">
@@ -30612,7 +30613,7 @@
       </c>
       <c r="Q173" t="inlineStr">
         <is>
-          <t>Liên hệ chậm</t>
+          <t>Liên hệ/tư vấn</t>
         </is>
       </c>
       <c r="R173" t="inlineStr">
@@ -30787,13 +30788,13 @@
       </c>
       <c r="Q174" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R174" t="inlineStr">
         <is>
-          <t>1. KH đã liên hệ CN
-2. HT NLMT của KH đang lỗi ATS không điều khiển được qua WIfi, hiện chưa thiết lập được
+          <t>1. KH đã liên hệ CN_x000D_
+2. HT NLMT của KH đang lỗi ATS không điều khiển được qua WIfi, hiện chưa thiết lập được_x000D_
 3. KH cần CN liên hệ và đến hỗ trợ sớm</t>
         </is>
       </c>
@@ -30959,13 +30960,13 @@
       </c>
       <c r="Q175" t="inlineStr">
         <is>
-          <t>Chất lượng, dịch vụ, Giá cả</t>
+          <t>Chất lượng triển khai</t>
         </is>
       </c>
       <c r="R175" t="inlineStr">
         <is>
-          <t>1. KH đã liên hệ CN
-2. Hiện CN đang thông báo các khoản chi phí phát sinh khi lắp đặt HT NLMT khoảng 18.000.000 (Dây AC), trước đó khi nhân sự tư vấn đến khảo sát lăp đăt chưa thông tin cụ thể cho KH
+          <t>1. KH đã liên hệ CN_x000D_
+2. Hiện CN đang thông báo các khoản chi phí phát sinh khi lắp đặt HT NLMT khoảng 18.000.000 (Dây AC), trước đó khi nhân sự tư vấn đến khảo sát lăp đăt chưa thông tin cụ thể cho KH_x000D_
 3. KH không hài lòng với mức chi phí phát sinh cao như vậy và cần CN có hướng giải đáp cho KH</t>
         </is>
       </c>
@@ -31136,13 +31137,13 @@
       </c>
       <c r="Q176" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R176" t="inlineStr">
         <is>
-          <t>1. 3 Ắc quy lưu trữ không nạp trong khi thông số trên App báo ắc quy đầy, hiện KH đang dùng điện lưới
-2. CN đã đến kiểm tra cho KH và thông tin 1 Ăc quy lưu trữ gặp sự cố và cần chuyển bảo hành tuy nhiên hiện tại vẫn chưa hỗ trợ KH
+          <t>1. 3 Ắc quy lưu trữ không nạp trong khi thông số trên App báo ắc quy đầy, hiện KH đang dùng điện lưới_x000D_
+2. CN đã đến kiểm tra cho KH và thông tin 1 Ăc quy lưu trữ gặp sự cố và cần chuyển bảo hành tuy nhiên hiện tại vẫn chưa hỗ trợ KH_x000D_
 3. KH cần CN liên hệ và hỗ trợ gấp cho KH</t>
         </is>
       </c>
@@ -31313,13 +31314,13 @@
       </c>
       <c r="Q177" t="inlineStr">
         <is>
-          <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
+          <t>Chất lượng triển khai</t>
         </is>
       </c>
       <c r="R177" t="inlineStr">
         <is>
-          <t>1. KH đã liên hệ CN
-2. Hiệu suất HT NLMT là 7KW tuy nhiên hiện tại chỉ sản xuất được hơn 2KW
+          <t>1. KH đã liên hệ CN_x000D_
+2. Hiệu suất HT NLMT là 7KW tuy nhiên hiện tại chỉ sản xuất được hơn 2KW_x000D_
 3. KH cần CN hỗ trợ kiểm tra sớm</t>
         </is>
       </c>
@@ -31490,13 +31491,13 @@
       </c>
       <c r="Q178" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R178" t="inlineStr">
         <is>
-          <t>1. KH đã liên hệ CN
-2. KH không thấy có điện NLMT từ tấm pin, Inverter báo đỏ
+          <t>1. KH đã liên hệ CN_x000D_
+2. KH không thấy có điện NLMT từ tấm pin, Inverter báo đỏ_x000D_
 3. KH cần CN đến kiểm tra và khắc phục sớm</t>
         </is>
       </c>
@@ -31667,13 +31668,13 @@
       </c>
       <c r="Q179" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R179" t="inlineStr">
         <is>
-          <t>1. CN báo sự cố cho KH
-2. KH mất kết nối HT NLMT, không theo dõi được hiệu suất qua App, không có điện sử dụng từ đêm qua
+          <t>1. CN báo sự cố cho KH_x000D_
+2. KH mất kết nối HT NLMT, không theo dõi được hiệu suất qua App, không có điện sử dụng từ đêm qua_x000D_
 3. kH cần CN đến hỗ trợ khắc phục gấp</t>
         </is>
       </c>
@@ -32019,7 +32020,7 @@
       </c>
       <c r="Q181" t="inlineStr">
         <is>
-          <t>Chất lượng, dịch vụ, Giá cả</t>
+          <t>Chất lượng triển khai</t>
         </is>
       </c>
       <c r="R181" t="inlineStr">
@@ -32194,12 +32195,12 @@
       </c>
       <c r="Q182" t="inlineStr">
         <is>
-          <t>Thủ tục/giấy tờ/ Hóa đơn/ Hồ sơ lắp đặt</t>
+          <t>Thủ tục/giấy tờ/ Hóa đơn/ Hồ sơ lắp đặt</t>
         </is>
       </c>
       <c r="R182" t="inlineStr">
         <is>
-          <t>1. KH đã báo CN: a Khoa
+          <t>1. KH đã báo CN: a Khoa_x000D_
 2. KH phản ánh và yêu cầu: cần hỗ trợ xuất hóa đơn tổng giá trị HĐ thanh toán gửi qua email: truonghau30495@gmail.com. Ngoài ra KH cần hỗ trợ theo dõi bảo hành các thiết bị, KH sử dụng app AIO và đã vào mục bảo hành nhưng ko thấy có thông tin gì.</t>
         </is>
       </c>
@@ -32370,13 +32371,13 @@
       </c>
       <c r="Q183" t="inlineStr">
         <is>
-          <t>Inverter không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R183" t="inlineStr">
         <is>
-          <t>1. KH chưa báo CN
-2. KH phản ánh: ivt lỗi ko hoạt động
+          <t>1. KH chưa báo CN_x000D_
+2. KH phản ánh: ivt lỗi ko hoạt động_x000D_
 3. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này gấp</t>
         </is>
       </c>
@@ -32542,13 +32543,13 @@
       </c>
       <c r="Q184" t="inlineStr">
         <is>
-          <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
+          <t>Chất lượng triển khai</t>
         </is>
       </c>
       <c r="R184" t="inlineStr">
         <is>
-          <t>1. KH chưa báo CN
-2. KH phản ánh: vẫn về vấn đề hiệu suất kém trước đó đã có thay tấm pin nlmt rồi, hệ của KH 6.3kw mà dạo này chỉ có được 2kw mấy, giảm hơn 50%. KH đang nghi ngờ có vấn đề nguyên nhân chỗ nào đó
+          <t>1. KH chưa báo CN_x000D_
+2. KH phản ánh: vẫn về vấn đề hiệu suất kém trước đó đã có thay tấm pin nlmt rồi, hệ của KH 6.3kw mà dạo này chỉ có được 2kw mấy, giảm hơn 50%. KH đang nghi ngờ có vấn đề nguyên nhân chỗ nào đó_x000D_
 3. KH yêu cầu: qua kiểm tra, khắc phục, xử lý triệt để tình trạng này</t>
         </is>
       </c>
@@ -32716,13 +32717,13 @@
       </c>
       <c r="Q185" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R185" t="inlineStr">
         <is>
-          <t>CN 0366646391 báo sự cố hộ KH
-1. KH phản ánh: CB bị hỏng 1 pha nên ko sử dụng được nlmt
+          <t>CN 0366646391 báo sự cố hộ KH_x000D_
+1. KH phản ánh: CB bị hỏng 1 pha nên ko sử dụng được nlmt_x000D_
 2. KH yêu cầu: qua kiểm tra, khắc phục gấp</t>
         </is>
       </c>
@@ -32893,13 +32894,13 @@
       </c>
       <c r="Q186" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R186" t="inlineStr">
         <is>
-          <t>1. KH chưa báo CN
-2. KH phản ánh: nhảy điện nlmt liên tục, xài được 15p tắt rồi lại có lại
+          <t>1. KH chưa báo CN_x000D_
+2. KH phản ánh: nhảy điện nlmt liên tục, xài được 15p tắt rồi lại có lại_x000D_
 3. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này</t>
         </is>
       </c>
@@ -33070,13 +33071,13 @@
       </c>
       <c r="Q187" t="inlineStr">
         <is>
-          <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
+          <t>Chất lượng triển khai</t>
         </is>
       </c>
       <c r="R187" t="inlineStr">
         <is>
-          <t>1. KH chưa báo CN
-2. KH phản ánh: hiệu suất sản phẩm kém, cảm thấy tiền điện tăng.
+          <t>1. KH chưa báo CN_x000D_
+2. KH phản ánh: hiệu suất sản phẩm kém, cảm thấy tiền điện tăng._x000D_
 3. KH yêu cầu: Qua kiểm tra, khắc phục tình trạng này</t>
         </is>
       </c>
@@ -33247,13 +33248,13 @@
       </c>
       <c r="Q188" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R188" t="inlineStr">
         <is>
-          <t>KH đã báo CN nhưng chưa được hỗ trợ 
-KH báo sự cố NLMT không sạc được pin, mất hết điện lưới 
+          <t>KH đã báo CN nhưng chưa được hỗ trợ _x000D_
+KH báo sự cố NLMT không sạc được pin, mất hết điện lưới _x000D_
 Yêu cầu CN cho KT qua ktra cho KH</t>
         </is>
       </c>
@@ -33424,13 +33425,13 @@
       </c>
       <c r="Q189" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R189" t="inlineStr">
         <is>
-          <t>CN 0986688282 báo sự cố hộ KH 
-KH báo sự cố lỗi hệ thống NLM không hoạt động không sản xuất ra điện 
+          <t>CN 0986688282 báo sự cố hộ KH _x000D_
+KH báo sự cố lỗi hệ thống NLM không hoạt động không sản xuất ra điện _x000D_
 Yêu cầu CN cho KT qua ktra cho KH</t>
         </is>
       </c>
@@ -33596,13 +33597,13 @@
       </c>
       <c r="Q190" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R190" t="inlineStr">
         <is>
-          <t>1. KH đã liên hệ A Được
-2. Thiết bị Camera giám sát rừng hiện đang lỗi Wifi
+          <t>1. KH đã liên hệ A Được_x000D_
+2. Thiết bị Camera giám sát rừng hiện đang lỗi Wifi_x000D_
 3. Kh cần CN hỗ trợ khắc phục sớm</t>
         </is>
       </c>
@@ -33773,13 +33774,13 @@
       </c>
       <c r="Q191" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R191" t="inlineStr">
         <is>
-          <t>1. KH đã liên hệ CN
-2. KH không theo dõi được hiệu suất HT NLMT, Ắc quy lưu trữ hôm nay không nạp, báo Alarm đỏ
+          <t>1. KH đã liên hệ CN_x000D_
+2. KH không theo dõi được hiệu suất HT NLMT, Ắc quy lưu trữ hôm nay không nạp, báo Alarm đỏ_x000D_
 3. KH cần CN hỗ trợ kiểm tra và khắc phục sớm</t>
         </is>
       </c>
@@ -33945,7 +33946,7 @@
       </c>
       <c r="Q192" t="inlineStr">
         <is>
-          <t>Liên hệ chậm</t>
+          <t>Liên hệ/tư vấn</t>
         </is>
       </c>
       <c r="R192" t="inlineStr">
@@ -34120,13 +34121,13 @@
       </c>
       <c r="Q193" t="inlineStr">
         <is>
-          <t>Hướng dẫn, hỗ trợ sử dụng sản phẩm</t>
+          <t>Liên hệ/tư vấn</t>
         </is>
       </c>
       <c r="R193" t="inlineStr">
         <is>
-          <t>1. KH đã báo CN
-2. KH phản ánh: hôm qua mất điện, báo lỗi hệ nlmt ko vào pin KH có liên hệ với CN trước lắp đặt cho KH (KH ko nhớ tên) có 1 KT xuống ko mặc đồng phục điều chỉnh lại pin lưu trữ mà hiện tại pin còn 84% vẫn ưu tiên sử dụng điện lực
+          <t>1. KH đã báo CN_x000D_
+2. KH phản ánh: hôm qua mất điện, báo lỗi hệ nlmt ko vào pin KH có liên hệ với CN trước lắp đặt cho KH (KH ko nhớ tên) có 1 KT xuống ko mặc đồng phục điều chỉnh lại pin lưu trữ mà hiện tại pin còn 84% vẫn ưu tiên sử dụng điện lực_x000D_
 3. KH yêu cầu: qua kiểm tra, điều chỉnh lại hệ thống theo nhu cầu KH sử dụng</t>
         </is>
       </c>
@@ -34292,7 +34293,7 @@
       </c>
       <c r="Q194" t="inlineStr">
         <is>
-          <t>Liên hệ chậm</t>
+          <t>Liên hệ/tư vấn</t>
         </is>
       </c>
       <c r="R194" t="inlineStr">
@@ -34462,13 +34463,13 @@
       </c>
       <c r="Q195" t="inlineStr">
         <is>
-          <t>Inverter không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R195" t="inlineStr">
         <is>
-          <t>1. KH chưa báo CN
-2. KH phản ánh: hệ nlmt ko có ra điện, ivt báo lỗi đỏ ko hoạt động
+          <t>1. KH chưa báo CN_x000D_
+2. KH phản ánh: hệ nlmt ko có ra điện, ivt báo lỗi đỏ ko hoạt động_x000D_
 3. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này</t>
         </is>
       </c>
@@ -34639,7 +34640,7 @@
       </c>
       <c r="Q196" t="inlineStr">
         <is>
-          <t>Liên hệ / Đặt lịch lại</t>
+          <t>Liên hệ/tư vấn</t>
         </is>
       </c>
       <c r="R196" t="inlineStr">
@@ -34814,12 +34815,12 @@
       </c>
       <c r="Q197" t="inlineStr">
         <is>
-          <t>Hướng dẫn, hỗ trợ sử dụng sản phẩm</t>
+          <t>Liên hệ/tư vấn</t>
         </is>
       </c>
       <c r="R197" t="inlineStr">
         <is>
-          <t>1. KH đã báo CN: a Nguyễn Đình Trường
+          <t>1. KH đã báo CN: a Nguyễn Đình Trường_x000D_
 2. KH phản ánh và yêu cầu: do sắp tới mùa mưa bão nên KH cần hỗ trợ đến kiểm tra, theo dõi xem hệ có đang gặp vấn đề gì không và gia cố lại</t>
         </is>
       </c>
@@ -34990,13 +34991,13 @@
       </c>
       <c r="Q198" t="inlineStr">
         <is>
-          <t>Sản phẩm bị ngắt quãng/ Không theo dõi và không nghe được</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R198" t="inlineStr">
         <is>
-          <t>1. KH đã báo CN anh Bảo
-2. KH phản ánh: 1 số điểm wifi bị mất kết nối
+          <t>1. KH đã báo CN anh Bảo_x000D_
+2. KH phản ánh: 1 số điểm wifi bị mất kết nối_x000D_
 3. KH yêu cầu: hỗ trợ gấp thì người dân đang rất đông cần làm thủ tục</t>
         </is>
       </c>
@@ -35162,13 +35163,13 @@
       </c>
       <c r="Q199" t="inlineStr">
         <is>
-          <t>Thủ tục/giấy tờ/ Hóa đơn/ Hồ sơ lắp đặt</t>
+          <t>Thủ tục/giấy tờ/ Hóa đơn/ Hồ sơ lắp đặt</t>
         </is>
       </c>
       <c r="R199" t="inlineStr">
         <is>
-          <t>1. KH đã báo và làm việc với CN
-2. KH phản ánh: cách đây hơn 1 tháng làm HĐ thì đến ngày thi công chưa có thi công được do trời mưa rất to và mái dột rất nặng, KH cũng có phản ánh với đội KT thi công nếu thi công lắp đặt sẽ hỏng toàn bộ phần mái ngói. KH có trao đổi với CN để hỗ trợ hoàn lại cọc rồi và phản hồi là phải chờ 1 HĐ của KH khác với số tiền HĐ tương đương và ck cọc. CN cũng đã gửi mẫu hoàn cọc, nhưng 1 tháng rồi chưa được hỗ trợ tiếp
+          <t>1. KH đã báo và làm việc với CN_x000D_
+2. KH phản ánh: cách đây hơn 1 tháng làm HĐ thì đến ngày thi công chưa có thi công được do trời mưa rất to và mái dột rất nặng, KH cũng có phản ánh với đội KT thi công nếu thi công lắp đặt sẽ hỏng toàn bộ phần mái ngói. KH có trao đổi với CN để hỗ trợ hoàn lại cọc rồi và phản hồi là phải chờ 1 HĐ của KH khác với số tiền HĐ tương đương và ck cọc. CN cũng đã gửi mẫu hoàn cọc, nhưng 1 tháng rồi chưa được hỗ trợ tiếp_x000D_
 3. KH yêu cầu: hỗ trợ KH hoàn cọc</t>
         </is>
       </c>
@@ -35339,13 +35340,13 @@
       </c>
       <c r="Q200" t="inlineStr">
         <is>
-          <t>Inverter không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R200" t="inlineStr">
         <is>
-          <t>1. KH chưa báo CN
-2. KH phản ánh: mới dùng hơn 1 tháng theo dõi trên app thấy báo lỗi biến tần ko hoạt động
+          <t>1. KH chưa báo CN_x000D_
+2. KH phản ánh: mới dùng hơn 1 tháng theo dõi trên app thấy báo lỗi biến tần ko hoạt động_x000D_
 3. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này</t>
         </is>
       </c>
@@ -35516,13 +35517,13 @@
       </c>
       <c r="Q201" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R201" t="inlineStr">
         <is>
-          <t>CN 0973575722 báo sự cố hộ KH
-1. KH phản ánh: có 1 biến tần ko hoạt động, lỗi nhảy màn hình
+          <t>CN 0973575722 báo sự cố hộ KH_x000D_
+1. KH phản ánh: có 1 biến tần ko hoạt động, lỗi nhảy màn hình_x000D_
 2. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này</t>
         </is>
       </c>
@@ -35693,15 +35694,15 @@
       </c>
       <c r="Q202" t="inlineStr">
         <is>
-          <t>Sau bảo dưỡng thiết bị vẫn bẩn</t>
+          <t>Chất lượng bảo dưỡng</t>
         </is>
       </c>
       <c r="R202" t="inlineStr">
         <is>
-          <t>Đơn hàng làm xong 9/8 ngay sau đó KH phản ánh vào 10h35 lên hotline. Trước tiên KH rất ko hài lòng về 2 nhân viên đến làm đã đến muộn 30p rồi còn thái độ ko vui vẻ và loay hoay đổi người khi lắp hộp nhựa xảy ra vấn đề khi bật điều hòa mở cách quạt kêu rất to, KH đã khởi động lại 6,7 lần nhưng đều không được. Khi vừa vệ sinh xong điều hòa thì xung quanh nền nhà tắm KT để lại rất bẩn, ko dọn dẹp sau khi vệ sinh, có mượn rẻ lau ướt nhà KH thì ném ra  chỗ cuộn vệ sinh. 
-KH yêu cầu sau 11h gọi trao đổi với KH 
-+ Về phương án xử lý về sự cố kia và đến kiểm tra vào lúc 6h-6r. KH yêu cầu là nhân viên khác nhỉnh hơn chuyên môn KT vì 2 bạn trước đến làm ko vui vẻ, chuyên môn kém.
-+ Về 2 nhân viên kia có thuộc nhân viên Viettel không, hay có được đào tạo bài bản hay không. KH ko có vấn đề gì về việc thuê ngoài, đại lý nhưng nhân viên có được đào tạo, training về tuân thủ quy định, lịch sự với KH không
+          <t>Đơn hàng làm xong 9/8 ngay sau đó KH phản ánh vào 10h35 lên hotline. Trước tiên KH rất ko hài lòng về 2 nhân viên đến làm đã đến muộn 30p rồi còn thái độ ko vui vẻ và loay hoay đổi người khi lắp hộp nhựa xảy ra vấn đề khi bật điều hòa mở cách quạt kêu rất to, KH đã khởi động lại 6,7 lần nhưng đều không được. Khi vừa vệ sinh xong điều hòa thì xung quanh nền nhà tắm KT để lại rất bẩn, ko dọn dẹp sau khi vệ sinh, có mượn rẻ lau ướt nhà KH thì ném ra  chỗ cuộn vệ sinh. _x000D_
+KH yêu cầu sau 11h gọi trao đổi với KH _x000D_
++ Về phương án xử lý về sự cố kia và đến kiểm tra vào lúc 6h-6r. KH yêu cầu là nhân viên khác nhỉnh hơn chuyên môn KT vì 2 bạn trước đến làm ko vui vẻ, chuyên môn kém._x000D_
++ Về 2 nhân viên kia có thuộc nhân viên Viettel không, hay có được đào tạo bài bản hay không. KH ko có vấn đề gì về việc thuê ngoài, đại lý nhưng nhân viên có được đào tạo, training về tuân thủ quy định, lịch sự với KH không_x000D_
 ***SĐT liên hệ là 0916819868 người nhà của KH vì SĐT KH lên đơn rất bận. Liên hệ trực tiếp với SĐT để liên hệ và làm việc</t>
         </is>
       </c>
@@ -35872,13 +35873,13 @@
       </c>
       <c r="Q203" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R203" t="inlineStr">
         <is>
-          <t>1. KH đã báo CN: a Thảo
-2. KH phản ánh: hệ nlmt ko sử dụng được, trời nắng ko có ra điện
+          <t>1. KH đã báo CN: a Thảo_x000D_
+2. KH phản ánh: hệ nlmt ko sử dụng được, trời nắng ko có ra điện_x000D_
 3. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này sớm</t>
         </is>
       </c>
@@ -36049,13 +36050,13 @@
       </c>
       <c r="Q204" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R204" t="inlineStr">
         <is>
-          <t>1. KH đã báo CN
-2. HT NLMT của KH không tự chuyển sang điện của Ắc quy lưu trữ mà cần thao tác thủ công
+          <t>1. KH đã báo CN_x000D_
+2. HT NLMT của KH không tự chuyển sang điện của Ắc quy lưu trữ mà cần thao tác thủ công_x000D_
 3. KH cần CN hỗ trợ kiểm tra và khắc phục sớm</t>
         </is>
       </c>
@@ -36226,13 +36227,13 @@
       </c>
       <c r="Q205" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R205" t="inlineStr">
         <is>
-          <t>1. KH đã báo CN: Anh Khải
-2. KH phản ánh: PV dư tải nhưng vẫn thấy lấy điện lưới bù vào
+          <t>1. KH đã báo CN: Anh Khải_x000D_
+2. KH phản ánh: PV dư tải nhưng vẫn thấy lấy điện lưới bù vào_x000D_
 3. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này</t>
         </is>
       </c>
@@ -36403,13 +36404,13 @@
       </c>
       <c r="Q206" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R206" t="inlineStr">
         <is>
-          <t>1. KH chưa báo CN
-2. KH phản ánh: KH theo dõi trên app ko thấy có thông số từ đầu giờ chiều tới giờ, KH có 3 pin lưu trữ thì 1 cục chạy 2 cục còn lại không chạy
+          <t>1. KH chưa báo CN_x000D_
+2. KH phản ánh: KH theo dõi trên app ko thấy có thông số từ đầu giờ chiều tới giờ, KH có 3 pin lưu trữ thì 1 cục chạy 2 cục còn lại không chạy_x000D_
 3. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này</t>
         </is>
       </c>
@@ -36580,13 +36581,13 @@
       </c>
       <c r="Q207" t="inlineStr">
         <is>
-          <t>Sản phẩm bị ngắt quãng/ Không theo dõi và không nghe được</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R207" t="inlineStr">
         <is>
-          <t>KH đã báo CN
-KH phản ánh : Kiểm tra ứng dụng thấy ko có sản xuất điện, không theo dõi được hiệu suất trên App
+          <t>KH đã báo CN_x000D_
+KH phản ánh : Kiểm tra ứng dụng thấy ko có sản xuất điện, không theo dõi được hiệu suất trên App_x000D_
 Yêu câu CN cho KT qua ktra cho KH</t>
         </is>
       </c>
@@ -36752,13 +36753,13 @@
       </c>
       <c r="Q208" t="inlineStr">
         <is>
-          <t>Không kết nối được app/Wifi và không theo dõi được hiệu suất</t>
+          <t>Kết nối hệ thống</t>
         </is>
       </c>
       <c r="R208" t="inlineStr">
         <is>
-          <t>1. KH đã liên hệ CN
-2. KH không theo dõi được hiệu suất HT NLMT
+          <t>1. KH đã liên hệ CN_x000D_
+2. KH không theo dõi được hiệu suất HT NLMT_x000D_
 3. KH cần CN hỗ trợ kiểm tra và khắc phục sớm</t>
         </is>
       </c>
@@ -36929,13 +36930,13 @@
       </c>
       <c r="Q209" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R209" t="inlineStr">
         <is>
-          <t>KH đã báo bạn KHẢI CN 
-KH báo sự cố NLMT sạc không đầy pin, pin lưu trữ 16kw sạc chỉ được dưới 90%
+          <t>KH đã báo bạn KHẢI CN _x000D_
+KH báo sự cố NLMT sạc không đầy pin, pin lưu trữ 16kw sạc chỉ được dưới 90%_x000D_
 Yêu cầu CN cho KT qua ktra cho KH</t>
         </is>
       </c>
@@ -37106,13 +37107,13 @@
       </c>
       <c r="Q210" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R210" t="inlineStr">
         <is>
-          <t>1. KH đã báo CN: a Tuy
-2. KH phản ánh: hệ nlmt ko sản sinh ra điện, ko hoạt động
+          <t>1. KH đã báo CN: a Tuy_x000D_
+2. KH phản ánh: hệ nlmt ko sản sinh ra điện, ko hoạt động_x000D_
 3. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này</t>
         </is>
       </c>
@@ -37283,7 +37284,7 @@
       </c>
       <c r="Q211" t="inlineStr">
         <is>
-          <t>Chất lượng, dịch vụ, Giá cả</t>
+          <t>Chất lượng triển khai</t>
         </is>
       </c>
       <c r="R211" t="inlineStr">
@@ -37458,13 +37459,13 @@
       </c>
       <c r="Q212" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R212" t="inlineStr">
         <is>
-          <t>1. KH đã báo CN: anh An 
-2. KH phản ánh: cúp điện lưới ko thấy có điện nlmt để sử dụng, điện lưới nhá lên tí rồi lại ngắt
+          <t>1. KH đã báo CN: anh An _x000D_
+2. KH phản ánh: cúp điện lưới ko thấy có điện nlmt để sử dụng, điện lưới nhá lên tí rồi lại ngắt_x000D_
 3. KH yêu cầu: qua kiểm tra, hỗ trợ khắc phục tình trạng này</t>
         </is>
       </c>
@@ -37635,13 +37636,13 @@
       </c>
       <c r="Q213" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R213" t="inlineStr">
         <is>
-          <t>1. KH chưa liên hệ CN
-2. App theo dõi HT NLMT của KH báo ngoại tuyến
+          <t>1. KH chưa liên hệ CN_x000D_
+2. App theo dõi HT NLMT của KH báo ngoại tuyến_x000D_
 3. KH cần CN liên hệ và đến hỗ trợ sớm</t>
         </is>
       </c>
@@ -37812,13 +37813,13 @@
       </c>
       <c r="Q214" t="inlineStr">
         <is>
-          <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
+          <t>Chất lượng triển khai</t>
         </is>
       </c>
       <c r="R214" t="inlineStr">
         <is>
-          <t>1. KH chưa liên hệ CN
-2. Hiện hiệu suất của HT NLMT giảm mạnh chỉ sản xuất được khoảng 3 số điện, tiền điện tháng trước tăng lên 11tr, App theo dõi HT không báo sự cố
+          <t>1. KH chưa liên hệ CN_x000D_
+2. Hiện hiệu suất của HT NLMT giảm mạnh chỉ sản xuất được khoảng 3 số điện, tiền điện tháng trước tăng lên 11tr, App theo dõi HT không báo sự cố_x000D_
 3. Kh cần CN đến kiểm tra và khắc phục cho KH</t>
         </is>
       </c>
@@ -37989,7 +37990,7 @@
       </c>
       <c r="Q215" t="inlineStr">
         <is>
-          <t>Liên hệ chậm</t>
+          <t>Liên hệ/tư vấn</t>
         </is>
       </c>
       <c r="R215" t="inlineStr">
@@ -38164,12 +38165,12 @@
       </c>
       <c r="Q216" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R216" t="inlineStr">
         <is>
-          <t>KH báo sự cố bị rỉ nước máy nước nóng gần 1 tháng nay, KT trước đấy có qua kiểm tra xử lý nhưng chưa triệt để
+          <t>KH báo sự cố bị rỉ nước máy nước nóng gần 1 tháng nay, KT trước đấy có qua kiểm tra xử lý nhưng chưa triệt để_x000D_
 Yêu cầu CN cho KT qua ktra xử lý lại cho KH</t>
         </is>
       </c>
@@ -38335,14 +38336,14 @@
       </c>
       <c r="Q217" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R217" t="inlineStr">
         <is>
-          <t>1. CN báo sự cố cho KH(0965781379)
-2. HT NLMT của KH đang không hoạt động khoảng 3 ngày nay
-3.KH cần CN hỗ trợ kiểm tra và khắc phục gấp
+          <t>1. CN báo sự cố cho KH(0965781379)_x000D_
+2. HT NLMT của KH đang không hoạt động khoảng 3 ngày nay_x000D_
+3.KH cần CN hỗ trợ kiểm tra và khắc phục gấp_x000D_
 Đ/C : Đường Huỳnh Mẫn Đạt, Phường Bình Thủy, TP Cần Thơ</t>
         </is>
       </c>
@@ -38513,14 +38514,14 @@
       </c>
       <c r="Q218" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R218" t="inlineStr">
         <is>
-          <t>Hiện sản phẩm đã hết hạn bảo hành
-1. KH đã liên hệ CN
-2. Hiện sản phẩm đèn NLMT sáng cả vào ban ngày, KH chưa điều chỉnh được
+          <t>Hiện sản phẩm đã hết hạn bảo hành_x000D_
+1. KH đã liên hệ CN_x000D_
+2. Hiện sản phẩm đèn NLMT sáng cả vào ban ngày, KH chưa điều chỉnh được_x000D_
 3. KH cần CN hỗ trợ kiểm tra và khắc phục, sẽ thanh toán chi phí phát sinh</t>
         </is>
       </c>
@@ -38691,13 +38692,13 @@
       </c>
       <c r="Q219" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R219" t="inlineStr">
         <is>
-          <t>1. KH chưa liên hệ CN
-2.Ăc quy lưu trữ của KH có điện nhưng không xả
+          <t>1. KH chưa liên hệ CN_x000D_
+2.Ăc quy lưu trữ của KH có điện nhưng không xả_x000D_
 3. KH cần CN liên hệ và hỗ trợ sớm</t>
         </is>
       </c>
@@ -38868,13 +38869,13 @@
       </c>
       <c r="Q220" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R220" t="inlineStr">
         <is>
-          <t>1. KH chưa liên hệ CN
-2. Tiền điện KH cần thanh toán đang tăng gấp đôi so với tháng 6, trên App theo dõi hiệu suất không báo lỗi tuy nhiên không hiển thị sản lượng điện NLMT sản xuất được
+          <t>1. KH chưa liên hệ CN_x000D_
+2. Tiền điện KH cần thanh toán đang tăng gấp đôi so với tháng 6, trên App theo dõi hiệu suất không báo lỗi tuy nhiên không hiển thị sản lượng điện NLMT sản xuất được_x000D_
 3. KH cần CN liên hệ và đến kiểm tra sớm</t>
         </is>
       </c>
@@ -39045,7 +39046,7 @@
       </c>
       <c r="Q221" t="inlineStr">
         <is>
-          <t>Liên hệ / Đặt lịch lại</t>
+          <t>Liên hệ/tư vấn</t>
         </is>
       </c>
       <c r="R221" t="inlineStr">
@@ -39220,13 +39221,13 @@
       </c>
       <c r="Q222" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R222" t="inlineStr">
         <is>
-          <t>1. CN báo sự cố cho KH
-2. Nhà KH mất điện, Ăc quy báo đỏ nhấp nháy, có dấu hiệu bị xả kiệt
+          <t>1. CN báo sự cố cho KH_x000D_
+2. Nhà KH mất điện, Ăc quy báo đỏ nhấp nháy, có dấu hiệu bị xả kiệt_x000D_
 3. Kh cần CN liên hệ và đến khắc phục gấp</t>
         </is>
       </c>
@@ -39397,13 +39398,13 @@
       </c>
       <c r="Q223" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R223" t="inlineStr">
         <is>
-          <t>1. CN báo sự cố cho KH (981118000)
-2. Ăc uy lưu trữ báo đỏ, không nạp
+          <t>1. CN báo sự cố cho KH (981118000)_x000D_
+2. Ăc uy lưu trữ báo đỏ, không nạp_x000D_
 3. KH cần CN đến kiểm tra và khắc phục sớm</t>
         </is>
       </c>
@@ -39569,7 +39570,7 @@
       </c>
       <c r="Q224" t="inlineStr">
         <is>
-          <t>Liên hệ chậm</t>
+          <t>Liên hệ/tư vấn</t>
         </is>
       </c>
       <c r="R224" t="inlineStr">
@@ -39739,13 +39740,13 @@
       </c>
       <c r="Q225" t="inlineStr">
         <is>
-          <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
+          <t>Chất lượng triển khai</t>
         </is>
       </c>
       <c r="R225" t="inlineStr">
         <is>
-          <t>1. KH đã liên hệ nhân sự Quang
-2. KH đang bị mất hiệu suất HT NLMT, 2 đường điện hiện chỉ sử dụng được 1 đường 
+          <t>1. KH đã liên hệ nhân sự Quang_x000D_
+2. KH đang bị mất hiệu suất HT NLMT, 2 đường điện hiện chỉ sử dụng được 1 đường _x000D_
 3. KH cần CN đến kiểm tra và khắc phục sớm</t>
         </is>
       </c>
@@ -39916,7 +39917,7 @@
       </c>
       <c r="Q226" t="inlineStr">
         <is>
-          <t>Thực hiện sai quy trình</t>
+          <t>Chất lượng triển khai</t>
         </is>
       </c>
       <c r="R226" t="inlineStr">
@@ -40091,13 +40092,14 @@
       </c>
       <c r="Q227" t="inlineStr">
         <is>
-          <t>Hướng dẫn, hỗ trợ sử dụng sản phẩm</t>
+          <t>Liên hệ/tư vấn</t>
         </is>
       </c>
       <c r="R227" t="inlineStr">
         <is>
-          <t>1. KH chưa liên hệ CN
-2. KH cần hỗ trợ, bảo dưỡng vệ sinh HT NLMT theo điều khoản trong hợp đồng
+          <t>1. KH chưa liên hệ CN_x000D_
+2. KH cần hỗ trợ, bảo dưỡng vệ sinh HT NLMT theo điều khoản trong hợp đồng_x000D_
+_x000D_
 Địa chỉ lắp đặt :C29, Khu Ba Gia, Phường Từ Sơn, Bắc Ninh</t>
         </is>
       </c>
@@ -40268,7 +40270,7 @@
       </c>
       <c r="Q228" t="inlineStr">
         <is>
-          <t>Hướng dẫn, hỗ trợ sử dụng sản phẩm</t>
+          <t>Liên hệ/tư vấn</t>
         </is>
       </c>
       <c r="R228" t="inlineStr">
@@ -40443,13 +40445,13 @@
       </c>
       <c r="Q229" t="inlineStr">
         <is>
-          <t>Cài đặt hệ thống (APP/Mật khẩu)</t>
+          <t>Kết nối hệ thống</t>
         </is>
       </c>
       <c r="R229" t="inlineStr">
         <is>
-          <t>1. KH đã báo CN: a Phụng
-2. KH phản ánh: đăng nhập vào tài khoản app theo dõi ko được, báo sai mật khẩu
+          <t>1. KH đã báo CN: a Phụng_x000D_
+2. KH phản ánh: đăng nhập vào tài khoản app theo dõi ko được, báo sai mật khẩu_x000D_
 3. KH yêu cầu: qua kiểm tra, hỗ trợ KH đăng nhập lại app theo dõi</t>
         </is>
       </c>
@@ -40620,13 +40622,13 @@
       </c>
       <c r="Q230" t="inlineStr">
         <is>
-          <t>Thủ tục/giấy tờ/ Hóa đơn/ Hồ sơ lắp đặt</t>
+          <t>Thủ tục/giấy tờ/ Hóa đơn/ Hồ sơ lắp đặt</t>
         </is>
       </c>
       <c r="R230" t="inlineStr">
         <is>
-          <t>1. KH đã báo CN: a Lê Văn Phụng
-2. KH phản ánh: cần hỗ trợ thủ tục hồ sơ để gửi phía bên điện lực, đã báo CN từ rất lâu rồi mà cứ hứa mãi không thấy làm
+          <t>1. KH đã báo CN: a Lê Văn Phụng_x000D_
+2. KH phản ánh: cần hỗ trợ thủ tục hồ sơ để gửi phía bên điện lực, đã báo CN từ rất lâu rồi mà cứ hứa mãi không thấy làm_x000D_
 3. KH yêu cầu: hỗ trợ, hướng dẫn KH làm thủ tục gửi điện lực</t>
         </is>
       </c>
@@ -40797,7 +40799,7 @@
       </c>
       <c r="Q231" t="inlineStr">
         <is>
-          <t>Liên hệ / Đặt lịch lại</t>
+          <t>Liên hệ/tư vấn</t>
         </is>
       </c>
       <c r="R231" t="inlineStr">
@@ -40967,13 +40969,13 @@
       </c>
       <c r="Q232" t="inlineStr">
         <is>
-          <t>Tiến độ triển khai chậm</t>
+          <t>Tiến độ triển khai</t>
         </is>
       </c>
       <c r="R232" t="inlineStr">
         <is>
-          <t>1. KH đã báo CN
-2. KH phản ánh: KH ký HĐ từ tháng 6 mà hiện tại vẫn chưa thấy có lắp đặt, chưa có tấm pin nlmt. KH có chuyển khoản 40tr qua TK của CN trong HĐ
+          <t>1. KH đã báo CN_x000D_
+2. KH phản ánh: KH ký HĐ từ tháng 6 mà hiện tại vẫn chưa thấy có lắp đặt, chưa có tấm pin nlmt. KH có chuyển khoản 40tr qua TK của CN trong HĐ_x000D_
 3. KH yêu cầu: liên hệ với KH trao đổi và triển khai lắp đặt ngay cho KH</t>
         </is>
       </c>
@@ -41144,7 +41146,7 @@
       </c>
       <c r="Q233" t="inlineStr">
         <is>
-          <t>Không đúng lịch hẹn</t>
+          <t>Liên hệ/tư vấn</t>
         </is>
       </c>
       <c r="R233" t="inlineStr">
@@ -41319,13 +41321,13 @@
       </c>
       <c r="Q234" t="inlineStr">
         <is>
-          <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
+          <t>Chất lượng triển khai</t>
         </is>
       </c>
       <c r="R234" t="inlineStr">
         <is>
-          <t>1. KH đã báo CN
-2. KH phản ánh: hiệu suất sản phẩm kém trước đây 1 ngày nắng đạt được 40kw nhưng giờ chỉ được 1 nửa rơi vào tầm 20kw
+          <t>1. KH đã báo CN_x000D_
+2. KH phản ánh: hiệu suất sản phẩm kém trước đây 1 ngày nắng đạt được 40kw nhưng giờ chỉ được 1 nửa rơi vào tầm 20kw_x000D_
 3. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này</t>
         </is>
       </c>
@@ -41496,7 +41498,7 @@
       </c>
       <c r="Q235" t="inlineStr">
         <is>
-          <t>Tư vấn sản phẩm/dịch vụ</t>
+          <t>Liên hệ/tư vấn</t>
         </is>
       </c>
       <c r="R235" t="inlineStr">
@@ -41671,13 +41673,13 @@
       </c>
       <c r="Q236" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R236" t="inlineStr">
         <is>
-          <t>1.CN báo sự cố cho KH
-2. KH không theo dõi được hiệu suất NLMT trên App, chỉ số =0
+          <t>1.CN báo sự cố cho KH_x000D_
+2. KH không theo dõi được hiệu suất NLMT trên App, chỉ số =0_x000D_
 3. KH cần CN liên hệ và hỗ trợ sớm</t>
         </is>
       </c>
@@ -41848,13 +41850,13 @@
       </c>
       <c r="Q237" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R237" t="inlineStr">
         <is>
-          <t>1. KH chưa báo CN
-2. KH phản ánh: khi mất điện lưới ko thấy có điện nlmt để sử dụng
+          <t>1. KH chưa báo CN_x000D_
+2. KH phản ánh: khi mất điện lưới ko thấy có điện nlmt để sử dụng_x000D_
 3. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này sớm</t>
         </is>
       </c>
@@ -42025,7 +42027,7 @@
       </c>
       <c r="Q238" t="inlineStr">
         <is>
-          <t>Không đúng lịch hẹn</t>
+          <t>Liên hệ/tư vấn</t>
         </is>
       </c>
       <c r="R238" t="inlineStr">
@@ -42200,7 +42202,7 @@
       </c>
       <c r="Q239" t="inlineStr">
         <is>
-          <t>Liên hệ / Đặt lịch lại</t>
+          <t>Liên hệ/tư vấn</t>
         </is>
       </c>
       <c r="R239" t="inlineStr">
@@ -42375,13 +42377,13 @@
       </c>
       <c r="Q240" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R240" t="inlineStr">
         <is>
-          <t>1. KH đã liên hệ CN
-2. Inverter của KH gặp sụ cố báo đỏ, hiện cảnh báo, nhà KH đang không có điện để sử dụng
+          <t>1. KH đã liên hệ CN_x000D_
+2. Inverter của KH gặp sụ cố báo đỏ, hiện cảnh báo, nhà KH đang không có điện để sử dụng_x000D_
 3. KH cần CN liên hệ và hỗ trợ gấp</t>
         </is>
       </c>
@@ -42552,13 +42554,13 @@
       </c>
       <c r="Q241" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R241" t="inlineStr">
         <is>
-          <t>KH chưa báo CN
-KH phản ánh hệ thống NLMT lâu lâu hay lỗi, báo lỗi tiếp đất khoảng 1 2 tuần nay
+          <t>KH chưa báo CN_x000D_
+KH phản ánh hệ thống NLMT lâu lâu hay lỗi, báo lỗi tiếp đất khoảng 1 2 tuần nay_x000D_
 Yêu cầu CN cho KT qua ktra cho KH</t>
         </is>
       </c>
@@ -42729,13 +42731,13 @@
       </c>
       <c r="Q242" t="inlineStr">
         <is>
-          <t>Hỗ trợ lắp đặt</t>
+          <t>Tiến độ triển khai</t>
         </is>
       </c>
       <c r="R242" t="inlineStr">
         <is>
-          <t>1. KH chưa liên hệ CN
-2. KH đã nhận được Logger từ ngày 26/07 tuy nhiên chưa được hỗ trợ lắp đặt
+          <t>1. KH chưa liên hệ CN_x000D_
+2. KH đã nhận được Logger từ ngày 26/07 tuy nhiên chưa được hỗ trợ lắp đặt_x000D_
 3. KH cần CN hỗ trợ lắp đặt sớm</t>
         </is>
       </c>
@@ -42906,13 +42908,13 @@
       </c>
       <c r="Q243" t="inlineStr">
         <is>
-          <t>Không kết nối được app/Wifi và không theo dõi được hiệu suất</t>
+          <t>Kết nối hệ thống</t>
         </is>
       </c>
       <c r="R243" t="inlineStr">
         <is>
-          <t>1. KH đã liên hệ CN 
-2. KH đang không theo dõi được hiệu suất HT NLMT trên App, hiện đang báo ngoại tuyến
+          <t>1. KH đã liên hệ CN _x000D_
+2. KH đang không theo dõi được hiệu suất HT NLMT trên App, hiện đang báo ngoại tuyến_x000D_
 3. KH cần CN liên hệ và hỗ trợ sớm</t>
         </is>
       </c>
@@ -43078,7 +43080,7 @@
       </c>
       <c r="Q244" t="inlineStr">
         <is>
-          <t>Liên hệ chậm</t>
+          <t>Liên hệ/tư vấn</t>
         </is>
       </c>
       <c r="R244" t="inlineStr">
@@ -43253,13 +43255,13 @@
       </c>
       <c r="Q245" t="inlineStr">
         <is>
-          <t>Thiết bị vỡ, hỏng, chập cháy</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R245" t="inlineStr">
         <is>
-          <t>1. KH đã báo CN 
-2. KH phản ánh: từ phản ánh trước TT_1783925046228 KT đã có qua kiểm tra và xác định ats bị hư, KT chỉ nói qua kiểm tra bảo hành nhưng chưa đưa ra phương án hay hỗ trợ KH. KH có liên hệ CN là A Tài nhưng CN bảo chuyển công tác
+          <t>1. KH đã báo CN _x000D_
+2. KH phản ánh: từ phản ánh trước TT_1783925046228 KT đã có qua kiểm tra và xác định ats bị hư, KT chỉ nói qua kiểm tra bảo hành nhưng chưa đưa ra phương án hay hỗ trợ KH. KH có liên hệ CN là A Tài nhưng CN bảo chuyển công tác_x000D_
 3. KH yêu cầu: Đưa ra phương án xử lý và hỗ trợ KH khắc phục tình trạng này</t>
         </is>
       </c>
@@ -43425,13 +43427,13 @@
       </c>
       <c r="Q246" t="inlineStr">
         <is>
-          <t>Inverter không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R246" t="inlineStr">
         <is>
-          <t>1. KH chưa báo CN
-2. KH phản ánh: biến tần bị lỗi bình thường là đèn xanh nhưng hôm nay KH lên kiểm tra thì thấy đèn run đang nháy, tiền điện các tháng vừa rồi cũng tăng lên so với các tháng trước
+          <t>1. KH chưa báo CN_x000D_
+2. KH phản ánh: biến tần bị lỗi bình thường là đèn xanh nhưng hôm nay KH lên kiểm tra thì thấy đèn run đang nháy, tiền điện các tháng vừa rồi cũng tăng lên so với các tháng trước_x000D_
 3. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này</t>
         </is>
       </c>
@@ -43597,13 +43599,13 @@
       </c>
       <c r="Q247" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R247" t="inlineStr">
         <is>
-          <t>KH báo KT bạn Tuấn CN 
-KH báo sự cố NLMT bị báo động đỏ, không vào điện
+          <t>KH báo KT bạn Tuấn CN _x000D_
+KH báo sự cố NLMT bị báo động đỏ, không vào điện_x000D_
 Yêu Cầu CN cho KT qua ktra cho KH</t>
         </is>
       </c>
@@ -43774,13 +43776,13 @@
       </c>
       <c r="Q248" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R248" t="inlineStr">
         <is>
-          <t>CN 0985951652 báo sự cố hộ KH
-1. KH phản ánh: hệ thống nlmt ko sản sinh ra điện
+          <t>CN 0985951652 báo sự cố hộ KH_x000D_
+1. KH phản ánh: hệ thống nlmt ko sản sinh ra điện_x000D_
 2. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này</t>
         </is>
       </c>
@@ -43951,13 +43953,13 @@
       </c>
       <c r="Q249" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R249" t="inlineStr">
         <is>
-          <t>CN 0985951652 báo sự cố hộ KH
-1. KH phản ánh: hệ thống nlmt ko ra sản lượng, khả năng pin lưu trữ bị lỗi
+          <t>CN 0985951652 báo sự cố hộ KH_x000D_
+1. KH phản ánh: hệ thống nlmt ko ra sản lượng, khả năng pin lưu trữ bị lỗi_x000D_
 2. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này</t>
         </is>
       </c>
@@ -44128,13 +44130,13 @@
       </c>
       <c r="Q250" t="inlineStr">
         <is>
-          <t>Thiếu thiết bị đi kèm/Lắp đặt sai quy cách</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R250" t="inlineStr">
         <is>
-          <t>1. KH đã báo CN
-2. KH phản ánh: hôm nay bên điện lực có đến kiểm tra thông báo về việc sử dụng điện nlmt thì đến kiểm tra phần tủ điện thì thấy bị rò điện
+          <t>1. KH đã báo CN_x000D_
+2. KH phản ánh: hôm nay bên điện lực có đến kiểm tra thông báo về việc sử dụng điện nlmt thì đến kiểm tra phần tủ điện thì thấy bị rò điện_x000D_
 3. KH yêu cầu: Đề nghị kiểm tra lại tủ điện và có biện pháp đấu nối phù hợp do công ty điện lực phát hiện có rò điện ở tủ điện vào sáng nay (10/8).</t>
         </is>
       </c>
@@ -44305,7 +44307,7 @@
       </c>
       <c r="Q251" t="inlineStr">
         <is>
-          <t>Sau bảo dưỡng thiết bị bị hỏng</t>
+          <t>Chất lượng bảo dưỡng</t>
         </is>
       </c>
       <c r="R251" t="inlineStr">
@@ -44480,13 +44482,13 @@
       </c>
       <c r="Q252" t="inlineStr">
         <is>
-          <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
+          <t>Chất lượng triển khai</t>
         </is>
       </c>
       <c r="R252" t="inlineStr">
         <is>
-          <t>1. KH đã báo CN: A Hào
-2. KH phản ánh: hiệu suất ko đạt yêu cầu tiền điện có giảm nhưng ở mức độ thấp hàng tháng KH vẫn phải đóng thêm tiền cho điện lưới 1tr mấy, KH có nhà trọ và sử dụng đến 8-9h tối là hết
+          <t>1. KH đã báo CN: A Hào_x000D_
+2. KH phản ánh: hiệu suất ko đạt yêu cầu tiền điện có giảm nhưng ở mức độ thấp hàng tháng KH vẫn phải đóng thêm tiền cho điện lưới 1tr mấy, KH có nhà trọ và sử dụng đến 8-9h tối là hết_x000D_
 3. KH yêu cầu: qua kiểm tra, đưa ra phương án xử lý hỗ trợ KH</t>
         </is>
       </c>
@@ -44657,13 +44659,13 @@
       </c>
       <c r="Q253" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R253" t="inlineStr">
         <is>
-          <t>1. KH đã báo CN: a Hoàng
-2. KH phản ánh: khi cúp điện ko chuyển đổi sang điện nlmt để sử dụng
+          <t>1. KH đã báo CN: a Hoàng_x000D_
+2. KH phản ánh: khi cúp điện ko chuyển đổi sang điện nlmt để sử dụng_x000D_
 3. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này</t>
         </is>
       </c>
@@ -44829,7 +44831,7 @@
       </c>
       <c r="Q254" t="inlineStr">
         <is>
-          <t>Tư vấn sản phẩm/dịch vụ</t>
+          <t>Liên hệ/tư vấn</t>
         </is>
       </c>
       <c r="R254" t="inlineStr">
@@ -45004,13 +45006,13 @@
       </c>
       <c r="Q255" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R255" t="inlineStr">
         <is>
-          <t>1. KH chưa báo CN
-2. KH phản ánh: từ tối qua 12h mất điện mà ko thấy có điện nlmt, mất hoàn toàn đến 8h nay cũng ko thấy có
+          <t>1. KH chưa báo CN_x000D_
+2. KH phản ánh: từ tối qua 12h mất điện mà ko thấy có điện nlmt, mất hoàn toàn đến 8h nay cũng ko thấy có_x000D_
 3. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này</t>
         </is>
       </c>
@@ -45181,7 +45183,7 @@
       </c>
       <c r="Q256" t="inlineStr">
         <is>
-          <t>Thiết bị vỡ, hỏng, chập cháy</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R256" t="inlineStr">
@@ -45356,13 +45358,13 @@
       </c>
       <c r="Q257" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R257" t="inlineStr">
         <is>
-          <t>1. KH chưa báo CN
-2. KH phản ánh:pin lưu trữ nạp đầy nhưng khi mất điện lưới ko thấy có xả ra để sử dụng
+          <t>1. KH chưa báo CN_x000D_
+2. KH phản ánh:pin lưu trữ nạp đầy nhưng khi mất điện lưới ko thấy có xả ra để sử dụng_x000D_
 3. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này</t>
         </is>
       </c>
@@ -45533,13 +45535,13 @@
       </c>
       <c r="Q258" t="inlineStr">
         <is>
-          <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
+          <t>Chất lượng triển khai</t>
         </is>
       </c>
       <c r="R258" t="inlineStr">
         <is>
-          <t>1. KH chưa liên hệ CN
-2. Hiện hiệu suất HT NLMT của KH đang bị giảm còn 6-&gt;7kw/h khoảng 1 tháng nay, trước đó hiệu suất đạt 12-&gt;13Kw
+          <t>1. KH chưa liên hệ CN_x000D_
+2. Hiện hiệu suất HT NLMT của KH đang bị giảm còn 6-&gt;7kw/h khoảng 1 tháng nay, trước đó hiệu suất đạt 12-&gt;13Kw_x000D_
 3. KH cần CN liên hệ và kiểm tra sớm cho KH</t>
         </is>
       </c>
@@ -45710,7 +45712,7 @@
       </c>
       <c r="Q259" t="inlineStr">
         <is>
-          <t>Tư vấn sản phẩm/dịch vụ</t>
+          <t>Liên hệ/tư vấn</t>
         </is>
       </c>
       <c r="R259" t="inlineStr">
@@ -45885,13 +45887,13 @@
       </c>
       <c r="Q260" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R260" t="inlineStr">
         <is>
-          <t>1. CN báo sự cố cho KH (0985792828)
-2. KH đang gặp sự cố HT NLMT nhảy ATS và bị mất điện
+          <t>1. CN báo sự cố cho KH (0985792828)_x000D_
+2. KH đang gặp sự cố HT NLMT nhảy ATS và bị mất điện_x000D_
 3. KH cần CN liên hệ và đến hỗ trợ gấp cho KH</t>
         </is>
       </c>
@@ -46062,13 +46064,13 @@
       </c>
       <c r="Q261" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R261" t="inlineStr">
         <is>
-          <t>1. KH chưa liên hệ CN
-2. Biến tần của Kh gặp sự cố và báo lỗi 
+          <t>1. KH chưa liên hệ CN_x000D_
+2. Biến tần của Kh gặp sự cố và báo lỗi _x000D_
 3. KH cần CN liên hệ và đến hỗ trợ sớm do nhà KH là hộ kinh doanh tải nhà phát sinh cao</t>
         </is>
       </c>
@@ -46239,13 +46241,13 @@
       </c>
       <c r="Q262" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R262" t="inlineStr">
         <is>
-          <t>1. KH chưa liên hệ CN
-2. Hiện nhà KH đang mất điện lưới, HT NLMT của KH không hoạt động, 
+          <t>1. KH chưa liên hệ CN_x000D_
+2. Hiện nhà KH đang mất điện lưới, HT NLMT của KH không hoạt động, _x000D_
 3. KH cần CN đến kiểm tra và hô trợ sớm</t>
         </is>
       </c>
@@ -46416,13 +46418,13 @@
       </c>
       <c r="Q263" t="inlineStr">
         <is>
-          <t>Không kết nối được app/Wifi và không theo dõi được hiệu suất</t>
+          <t>Kết nối hệ thống</t>
         </is>
       </c>
       <c r="R263" t="inlineStr">
         <is>
-          <t>KH đã báo CN, anh Thắng lắp đặt
-KH phản ánh app KH báo thiết bị ngoại tuyến, KH k xem được thông tin NLMT
+          <t>KH đã báo CN, anh Thắng lắp đặt_x000D_
+KH phản ánh app KH báo thiết bị ngoại tuyến, KH k xem được thông tin NLMT_x000D_
 Yêu cầu quản lí điều kĩ thuật liên hệ và hỗ trợ KH</t>
         </is>
       </c>
@@ -46593,13 +46595,13 @@
       </c>
       <c r="Q264" t="inlineStr">
         <is>
-          <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
+          <t>Chất lượng triển khai</t>
         </is>
       </c>
       <c r="R264" t="inlineStr">
         <is>
-          <t>1. KH đã liên hệ CN
-2. Từ phản ánh TT_1784626052016 HT NLMT của KH tự đóng, ngắt khi đang sử dụng(giờ cao điểm), Chỉ số điện sản xuất được từ HT NLMT với chỉ số điện lưới và tải nhà có chênh lệch khoảng hơn 100 số trên App
+          <t>1. KH đã liên hệ CN_x000D_
+2. Từ phản ánh TT_1784626052016 HT NLMT của KH tự đóng, ngắt khi đang sử dụng(giờ cao điểm), Chỉ số điện sản xuất được từ HT NLMT với chỉ số điện lưới và tải nhà có chênh lệch khoảng hơn 100 số trên App_x000D_
 3. KH cần CN liên hệ và đến kiểm tra sớm</t>
         </is>
       </c>
@@ -46765,7 +46767,7 @@
       </c>
       <c r="Q265" t="inlineStr">
         <is>
-          <t>Tư vấn sản phẩm/dịch vụ</t>
+          <t>Liên hệ/tư vấn</t>
         </is>
       </c>
       <c r="R265" t="inlineStr">
@@ -46940,7 +46942,7 @@
       </c>
       <c r="Q266" t="inlineStr">
         <is>
-          <t>Đơn bảo dưỡng hết hạn bảo hành</t>
+          <t>Chất lượng bảo dưỡng</t>
         </is>
       </c>
       <c r="R266" t="inlineStr">
@@ -47115,13 +47117,13 @@
       </c>
       <c r="Q267" t="inlineStr">
         <is>
-          <t>Lắp đặt sai quy cách, thiếu vật tư, thiết bị, phụ kiện đi kèm</t>
+          <t>Chất lượng triển khai</t>
         </is>
       </c>
       <c r="R267" t="inlineStr">
         <is>
-          <t>1. KH đã báo CN: A Minh
-2. KH phản ánh: sau khi KH nâng hệ, đang sử dụng điện nlmt có nhiều điện trong pin lưu trữ thì tự nhiên bị sập cả nhà, KH kiểm tra tủ điện ở tầng 1 thì ko thấy aptomat nào bị nhảy cả, 5-6p sau thì lại có điện trở lại. KH đang nghi ngờ phần đấu nối 
+          <t>1. KH đã báo CN: A Minh_x000D_
+2. KH phản ánh: sau khi KH nâng hệ, đang sử dụng điện nlmt có nhiều điện trong pin lưu trữ thì tự nhiên bị sập cả nhà, KH kiểm tra tủ điện ở tầng 1 thì ko thấy aptomat nào bị nhảy cả, 5-6p sau thì lại có điện trở lại. KH đang nghi ngờ phần đấu nối _x000D_
 3. KH yêu cầu: KT qua kiểm tra gấp phần đấu nối, KH đang cảm thấy rất nguy hiểm</t>
         </is>
       </c>
@@ -47292,13 +47294,13 @@
       </c>
       <c r="Q268" t="inlineStr">
         <is>
-          <t>Lỗi kết nối giữa thiết bị và hệ thống theo dõi</t>
+          <t>Kết nối hệ thống</t>
         </is>
       </c>
       <c r="R268" t="inlineStr">
         <is>
-          <t>1. KH chưa báo CN
-2. KH phản ánh: sự cố từ trước TT_1783476150441 KT đã cập nhật phần mềm tuy nhiên giờ KH theo dõi trên app vẫn ko hiển thị % pin lưu trữ 
+          <t>1. KH chưa báo CN_x000D_
+2. KH phản ánh: sự cố từ trước TT_1783476150441 KT đã cập nhật phần mềm tuy nhiên giờ KH theo dõi trên app vẫn ko hiển thị % pin lưu trữ _x000D_
 3. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này</t>
         </is>
       </c>
@@ -47469,7 +47471,7 @@
       </c>
       <c r="Q269" t="inlineStr">
         <is>
-          <t>Đơn bảo dưỡng hết hạn bảo hành</t>
+          <t>Chất lượng bảo dưỡng</t>
         </is>
       </c>
       <c r="R269" t="inlineStr">
@@ -47644,13 +47646,13 @@
       </c>
       <c r="Q270" t="inlineStr">
         <is>
-          <t>Inverter không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R270" t="inlineStr">
         <is>
-          <t>1. KH đã báo CN (KH ko nhớ rõ tên)
-2. KH phản ánh: ivt báo lỗi ko có điện
+          <t>1. KH đã báo CN (KH ko nhớ rõ tên)_x000D_
+2. KH phản ánh: ivt báo lỗi ko có điện_x000D_
 3. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này</t>
         </is>
       </c>
@@ -47821,13 +47823,13 @@
       </c>
       <c r="Q271" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R271" t="inlineStr">
         <is>
-          <t>1. KH đã báo CN: Anh Trường
-2. KH phản ánh: pin lưu trữ tự nhiên hết sạch, trước điều chỉnh là 20% pin là sẽ giữ lại, đèn alarm báo đỏ và KH theo dõi app thì thấy máy phát điện báo lỗi
+          <t>1. KH đã báo CN: Anh Trường_x000D_
+2. KH phản ánh: pin lưu trữ tự nhiên hết sạch, trước điều chỉnh là 20% pin là sẽ giữ lại, đèn alarm báo đỏ và KH theo dõi app thì thấy máy phát điện báo lỗi_x000D_
 3. KH yêu cầu: qua kiểm tr, khắc phục tình trạng này sớm</t>
         </is>
       </c>
@@ -47993,7 +47995,7 @@
       </c>
       <c r="Q272" t="inlineStr">
         <is>
-          <t>Liên hệ / Đặt lịch lại</t>
+          <t>Liên hệ/tư vấn</t>
         </is>
       </c>
       <c r="R272" t="inlineStr">
@@ -48168,13 +48170,13 @@
       </c>
       <c r="Q273" t="inlineStr">
         <is>
-          <t>Thiết bị vỡ, hỏng, chập cháy</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R273" t="inlineStr">
         <is>
-          <t>1. KH đã báo CN: Anh Hà nhưng chuyển công tác
-2. KH phản ánh: vừa hôm nay KH kiểm tra thấy toàn bộ tủ điện bị cháy hết
+          <t>1. KH đã báo CN: Anh Hà nhưng chuyển công tác_x000D_
+2. KH phản ánh: vừa hôm nay KH kiểm tra thấy toàn bộ tủ điện bị cháy hết_x000D_
 3. KH yêu cầu: qua kiểm tra, và đưa ra phương án hỗ trợ, xử lý</t>
         </is>
       </c>
@@ -48345,13 +48347,13 @@
       </c>
       <c r="Q274" t="inlineStr">
         <is>
-          <t>Thiếu thiết bị đi kèm/Lắp đặt sai quy cách</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R274" t="inlineStr">
         <is>
-          <t>1. KH đã báo CN ( KH ko nhớ tên, nhưng được mấy ngày rồi, có hẹn đến xử lý nhưng ko thấy )
-2. KH phản ánh: dàn NLMT ko gia cố và đường dây điện đang bị thòng xuống dưới đường gây nguy hiểm
+          <t>1. KH đã báo CN ( KH ko nhớ tên, nhưng được mấy ngày rồi, có hẹn đến xử lý nhưng ko thấy )_x000D_
+2. KH phản ánh: dàn NLMT ko gia cố và đường dây điện đang bị thòng xuống dưới đường gây nguy hiểm_x000D_
 3. KH yêu cầu: qua kiểm tra, xử lý, khắc phục tình trạng này gấp</t>
         </is>
       </c>
@@ -48522,13 +48524,13 @@
       </c>
       <c r="Q275" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R275" t="inlineStr">
         <is>
-          <t>1. KH chưa báo CN
-2. KH phản ánh" hệ nlmt ko hoạt động, cúp hết điện nguyên khu, có 2 cục pin lưu trữ cũng ko sử dụng được luôn
+          <t>1. KH chưa báo CN_x000D_
+2. KH phản ánh" hệ nlmt ko hoạt động, cúp hết điện nguyên khu, có 2 cục pin lưu trữ cũng ko sử dụng được luôn_x000D_
 3. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này</t>
         </is>
       </c>
@@ -48694,13 +48696,13 @@
       </c>
       <c r="Q276" t="inlineStr">
         <is>
-          <t>Thiết bị vỡ, hỏng, chập cháy</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R276" t="inlineStr">
         <is>
-          <t>1. KH chưa báo CN
-2. KH phản ánh: hôm bữa có mưa dột nay KH lên kiểm tra thì thấy có cọng dây màu xanh trên mái 2 đầu bị đứt, ko biết nối vào đâu, hệ của KH thì vẫn thấy hoạt động bình thường
+          <t>1. KH chưa báo CN_x000D_
+2. KH phản ánh: hôm bữa có mưa dột nay KH lên kiểm tra thì thấy có cọng dây màu xanh trên mái 2 đầu bị đứt, ko biết nối vào đâu, hệ của KH thì vẫn thấy hoạt động bình thường_x000D_
 3. KH yêu cầu: qua kiểm tra xem phần đường dây đấu nối kia có ảnh hưởng đến hiệu suất hay ảnh hưởng đến hệ không</t>
         </is>
       </c>
@@ -48871,13 +48873,13 @@
       </c>
       <c r="Q277" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R277" t="inlineStr">
         <is>
-          <t>1. KH đã báo CN: qua SĐT hotline CN
-2. KH phản ánh: điện nlmt ko hoạt động
+          <t>1. KH đã báo CN: qua SĐT hotline CN_x000D_
+2. KH phản ánh: điện nlmt ko hoạt động_x000D_
 3. KH yêu cầu: qua kiểm tra, khắc phục gấp do KH là hộ kinh doanh</t>
         </is>
       </c>
@@ -49048,14 +49050,14 @@
       </c>
       <c r="Q278" t="inlineStr">
         <is>
-          <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
+          <t>Chất lượng triển khai</t>
         </is>
       </c>
       <c r="R278" t="inlineStr">
         <is>
-          <t>1. KH đã liên hệ chi nhánh
-2. Khung giờ 8h sáng -&gt;10h45 có một chuỗi tấm pin bị giảm hơn 1 nửa hiệu suất so với 2 chuỗi pin còn lại 
-KH có ký hợp đồng và lắp đặt thêm 2 Ăc quy lưu trữ tuy nhiên chưa có thông tin trên App 
+          <t>1. KH đã liên hệ chi nhánh_x000D_
+2. Khung giờ 8h sáng -&gt;10h45 có một chuỗi tấm pin bị giảm hơn 1 nửa hiệu suất so với 2 chuỗi pin còn lại _x000D_
+KH có ký hợp đồng và lắp đặt thêm 2 Ăc quy lưu trữ tuy nhiên chưa có thông tin trên App _x000D_
 3. KH cần CN liên hệ và đến kiểm tra cho KH sớm, hỗ trợ hoàn thiện Hợp đồng bản cứng cho KH</t>
         </is>
       </c>
@@ -49226,13 +49228,13 @@
       </c>
       <c r="Q279" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R279" t="inlineStr">
         <is>
-          <t>1. CN báo sự cố cho KH
-2. Điều hòa của KH đang gặp sự cố rò nước
+          <t>1. CN báo sự cố cho KH_x000D_
+2. Điều hòa của KH đang gặp sự cố rò nước_x000D_
 3. KH cần CN liên hệ và đến hỗ trợ sớm</t>
         </is>
       </c>
@@ -49403,13 +49405,13 @@
       </c>
       <c r="Q280" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R280" t="inlineStr">
         <is>
-          <t>KH chưa báo CN 
-KH phản ánh cầu giao NLMT bị nhảy CP, mới phát hiện sáng nay 
+          <t>KH chưa báo CN _x000D_
+KH phản ánh cầu giao NLMT bị nhảy CP, mới phát hiện sáng nay _x000D_
 Yêu cầu quản lí điều kĩ thuật liên hệ và hỗ trợ KH</t>
         </is>
       </c>
@@ -49580,13 +49582,13 @@
       </c>
       <c r="Q281" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R281" t="inlineStr">
         <is>
-          <t>1. KH đã liên hệ CN
-2. Từ phản ánh TT_1780407262564- Hiện một điều hòa của KH đang gặp sự cố rò nước
+          <t>1. KH đã liên hệ CN_x000D_
+2. Từ phản ánh TT_1780407262564- Hiện một điều hòa của KH đang gặp sự cố rò nước_x000D_
 3. KH cần CN liên hệ và đến kiểm tra sớm</t>
         </is>
       </c>
@@ -49757,13 +49759,13 @@
       </c>
       <c r="Q282" t="inlineStr">
         <is>
-          <t>Thủ tục/giấy tờ/ Hóa đơn/ Hồ sơ lắp đặt</t>
+          <t>Thủ tục/giấy tờ/ Hóa đơn/ Hồ sơ lắp đặt</t>
         </is>
       </c>
       <c r="R282" t="inlineStr">
         <is>
-          <t>1. KH đã liên hệ CN
-2. Hiện KH đã được hỗ trợ hoàn thiện lắp đặt và đưa vào sử dụng một thời gian tuy nhiên KH chưa nhận được Hóa đơn liên quan đên HT NLMT
+          <t>1. KH đã liên hệ CN_x000D_
+2. Hiện KH đã được hỗ trợ hoàn thiện lắp đặt và đưa vào sử dụng một thời gian tuy nhiên KH chưa nhận được Hóa đơn liên quan đên HT NLMT_x000D_
 3. KH cần CN hỗ trợ cung cấp các chứng từ cần thiết sớm</t>
         </is>
       </c>
@@ -49934,13 +49936,13 @@
       </c>
       <c r="Q283" t="inlineStr">
         <is>
-          <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
+          <t>Chất lượng triển khai</t>
         </is>
       </c>
       <c r="R283" t="inlineStr">
         <is>
-          <t>1, KH đã liên hệ CN
-2.Đèn điện trong nhà KH có hiện tượng chập chờn khi KH bắt đầu vào tải nhà, trên App theo dõi hiệu suất NLMT hiển thị bình thường không báo lỗi
+          <t>1, KH đã liên hệ CN_x000D_
+2.Đèn điện trong nhà KH có hiện tượng chập chờn khi KH bắt đầu vào tải nhà, trên App theo dõi hiệu suất NLMT hiển thị bình thường không báo lỗi_x000D_
 3. KH cần CN liên hệ và kiểm tra sớm</t>
         </is>
       </c>
@@ -50111,13 +50113,13 @@
       </c>
       <c r="Q284" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R284" t="inlineStr">
         <is>
-          <t>1. KH đã báo CN: anh Lê Khoa
-2. KH phản ánh: pin lưu trữ 10kw như hôm qua 12h là đầy pin nhưng hôm nay ko có thấy điện vào, cháy đèn xanh và chỉ có thấy đèn đỏ ở pin.
+          <t>1. KH đã báo CN: anh Lê Khoa_x000D_
+2. KH phản ánh: pin lưu trữ 10kw như hôm qua 12h là đầy pin nhưng hôm nay ko có thấy điện vào, cháy đèn xanh và chỉ có thấy đèn đỏ ở pin._x000D_
 3. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này gấp cho KH</t>
         </is>
       </c>
@@ -50283,14 +50285,14 @@
       </c>
       <c r="Q285" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R285" t="inlineStr">
         <is>
-          <t>1. KH đã liên hệ CN
-2. HT NLMT của KH nhảy ATS liên tục khoảng 1 tuân nay, hiệu suất HT NLMT của KH đang có dấu hiệu giảm, trước đó ngày nắng tốt sẽ sản xuất được 12kw tuy nhiên hiện tại tối đa chỉ được 6kw điện
-3. KH cần CN liên hệ và đến hỗ trợ sớm
+          <t>1. KH đã liên hệ CN_x000D_
+2. HT NLMT của KH nhảy ATS liên tục khoảng 1 tuân nay, hiệu suất HT NLMT của KH đang có dấu hiệu giảm, trước đó ngày nắng tốt sẽ sản xuất được 12kw tuy nhiên hiện tại tối đa chỉ được 6kw điện_x000D_
+3. KH cần CN liên hệ và đến hỗ trợ sớm_x000D_
 170301- ĐHG/KD/HDMBLĐ-2025/CNCTPTO-NKT</t>
         </is>
       </c>
@@ -50456,7 +50458,7 @@
       </c>
       <c r="Q286" t="inlineStr">
         <is>
-          <t>Tư vấn sản phẩm/dịch vụ</t>
+          <t>Liên hệ/tư vấn</t>
         </is>
       </c>
       <c r="R286" t="inlineStr">
@@ -50631,13 +50633,13 @@
       </c>
       <c r="Q287" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R287" t="inlineStr">
         <is>
-          <t>1. KH chưa báo CN
-2. KH phản ánh: trước đó phản ánh TT_1785482686581 CN đã khắc phục lỗi ko thấy dòng điện từ trên mái xuống KH sử dụng đúng được 1 hôm qua đến hôm nay lại gặp tình trạng cũ như vậy. Tình trạng đã diễn ra 4,5 lần
+          <t>1. KH chưa báo CN_x000D_
+2. KH phản ánh: trước đó phản ánh TT_1785482686581 CN đã khắc phục lỗi ko thấy dòng điện từ trên mái xuống KH sử dụng đúng được 1 hôm qua đến hôm nay lại gặp tình trạng cũ như vậy. Tình trạng đã diễn ra 4,5 lần_x000D_
 3. KH yêu cầu: khắc phục triệt để tình trạng này giúp KH</t>
         </is>
       </c>
@@ -50808,7 +50810,7 @@
       </c>
       <c r="Q288" t="inlineStr">
         <is>
-          <t>Liên hệ / Đặt lịch lại</t>
+          <t>Liên hệ/tư vấn</t>
         </is>
       </c>
       <c r="R288" t="inlineStr">
@@ -50978,7 +50980,7 @@
       </c>
       <c r="Q289" t="inlineStr">
         <is>
-          <t>Tư vấn sản phẩm/dịch vụ</t>
+          <t>Liên hệ/tư vấn</t>
         </is>
       </c>
       <c r="R289" t="inlineStr">
@@ -51153,12 +51155,12 @@
       </c>
       <c r="Q290" t="inlineStr">
         <is>
-          <t>Cài đặt hệ thống (APP/Mật khẩu)</t>
+          <t>Kết nối hệ thống</t>
         </is>
       </c>
       <c r="R290" t="inlineStr">
         <is>
-          <t>1. KH chưa báo CN
+          <t>1. KH chưa báo CN_x000D_
 2. KH cần hỗ trợ kết nối lại app theo dõi nlmt</t>
         </is>
       </c>
@@ -51329,12 +51331,12 @@
       </c>
       <c r="Q291" t="inlineStr">
         <is>
-          <t>Thủ tục/giấy tờ/ Hóa đơn/ Hồ sơ lắp đặt</t>
+          <t>Thủ tục/giấy tờ/ Hóa đơn/ Hồ sơ lắp đặt</t>
         </is>
       </c>
       <c r="R291" t="inlineStr">
         <is>
-          <t>1. KH đã báo CN
+          <t>1. KH đã báo CN_x000D_
 2. KH cần hỗ trợ gửi lại hóa đơn thanh toán hợp đồng qua đường mail hoangtrungtuyen.nd93@gmail.com, trước có bảo CN hỗ trợ nhưng KH cung cấp sai đường mail</t>
         </is>
       </c>
@@ -51505,13 +51507,13 @@
       </c>
       <c r="Q292" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R292" t="inlineStr">
         <is>
-          <t>1. KH đã báo CN
-2. KH phản ánh: pin lưu trữ 80% theo dõi trên app nhưng ko thấy xả điện ra để sử dụng chỉ thấy có dùng được điện lưới, ở màn hình hiển thị ở cục pin bình thường hiện 2 đèn là alarm và run nhưng hiện tại chỉ thấy đèn alarm đỏ
+          <t>1. KH đã báo CN_x000D_
+2. KH phản ánh: pin lưu trữ 80% theo dõi trên app nhưng ko thấy xả điện ra để sử dụng chỉ thấy có dùng được điện lưới, ở màn hình hiển thị ở cục pin bình thường hiện 2 đèn là alarm và run nhưng hiện tại chỉ thấy đèn alarm đỏ_x000D_
 3. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này</t>
         </is>
       </c>
@@ -51682,12 +51684,12 @@
       </c>
       <c r="Q293" t="inlineStr">
         <is>
-          <t>Thủ tục/giấy tờ/ Hóa đơn/ Hồ sơ lắp đặt</t>
+          <t>Thủ tục/giấy tờ/ Hóa đơn/ Hồ sơ lắp đặt</t>
         </is>
       </c>
       <c r="R293" t="inlineStr">
         <is>
-          <t>1. KH đã báo CN: a Hưng, a Phong
+          <t>1. KH đã báo CN: a Hưng, a Phong_x000D_
 2. KH yêu cầu: cần bản cứng HĐ NLMT, KH theo dõi được trên app AIO nhưng cần in ra bản HĐ cứng</t>
         </is>
       </c>
@@ -51858,13 +51860,13 @@
       </c>
       <c r="Q294" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R294" t="inlineStr">
         <is>
-          <t>1. KH chưa báo CN
-2. KH phản ánh: lỗi pin lưu trữ báo lỗi, báo đỏ, vẫn còn 30% nhưng lại lấy điện lưới
+          <t>1. KH chưa báo CN_x000D_
+2. KH phản ánh: lỗi pin lưu trữ báo lỗi, báo đỏ, vẫn còn 30% nhưng lại lấy điện lưới_x000D_
 3. KH yêu cầu: qua kiểm tra lỗi pin lưu trữ, khắc phục gấp và điều chỉnh lại theo nhu cầu KH sử dụng</t>
         </is>
       </c>
@@ -52035,13 +52037,13 @@
       </c>
       <c r="Q295" t="inlineStr">
         <is>
-          <t>Không kết nối được app/Wifi và không theo dõi được hiệu suất</t>
+          <t>Kết nối hệ thống</t>
         </is>
       </c>
       <c r="R295" t="inlineStr">
         <is>
-          <t>1. KH đã liên hệ CN
-2. KH chưa theo dõi được hiệu suất sản lượng điện tiêu thụ trên App
+          <t>1. KH đã liên hệ CN_x000D_
+2. KH chưa theo dõi được hiệu suất sản lượng điện tiêu thụ trên App_x000D_
 3. KH cần CN liên hệ và hỗ trợ sớm</t>
         </is>
       </c>
@@ -52207,13 +52209,13 @@
       </c>
       <c r="Q296" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R296" t="inlineStr">
         <is>
-          <t>1. KH đã báo CN 
-2. Thang máy KH đang không mở cửa 2 ngày nay (6/8-7/8)
+          <t>1. KH đã báo CN _x000D_
+2. Thang máy KH đang không mở cửa 2 ngày nay (6/8-7/8)_x000D_
 3. Yêu cầu CN hỗ trợ KH</t>
         </is>
       </c>
@@ -52384,13 +52386,13 @@
       </c>
       <c r="Q297" t="inlineStr">
         <is>
-          <t>Không kết nối được app/Wifi và không theo dõi được hiệu suất</t>
+          <t>Kết nối hệ thống</t>
         </is>
       </c>
       <c r="R297" t="inlineStr">
         <is>
-          <t>1. KH đã liên hệ CN
-2. Ngày 05/08 KH nghe có tiếng động lớn trên mái nhà, sau đó hệ thống NLMT mất kết nối với App, KH không theo dõi được hiệu suất 
+          <t>1. KH đã liên hệ CN_x000D_
+2. Ngày 05/08 KH nghe có tiếng động lớn trên mái nhà, sau đó hệ thống NLMT mất kết nối với App, KH không theo dõi được hiệu suất _x000D_
 3. KH cần CN đến kiểm tra và khắc phục sớm</t>
         </is>
       </c>
@@ -52561,7 +52563,7 @@
       </c>
       <c r="Q298" t="inlineStr">
         <is>
-          <t>Sau bảo dưỡng thiết bị bị hỏng</t>
+          <t>Chất lượng bảo dưỡng</t>
         </is>
       </c>
       <c r="R298" t="inlineStr">
@@ -52736,13 +52738,13 @@
       </c>
       <c r="Q299" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R299" t="inlineStr">
         <is>
-          <t>KH đã báo CN 
-Kh phản ánh hệ thống năng lượng mặt trời bị sập không sử dụng được 
+          <t>KH đã báo CN _x000D_
+Kh phản ánh hệ thống năng lượng mặt trời bị sập không sử dụng được _x000D_
 Yêu cầu quản lý điều kĩ thuật liên hệ và hỗ trợ KH</t>
         </is>
       </c>
@@ -52913,13 +52915,13 @@
       </c>
       <c r="Q300" t="inlineStr">
         <is>
-          <t>Thủ tục/giấy tờ/ Hóa đơn/ Hồ sơ lắp đặt</t>
+          <t>Thủ tục/giấy tờ/ Hóa đơn/ Hồ sơ lắp đặt</t>
         </is>
       </c>
       <c r="R300" t="inlineStr">
         <is>
-          <t>1. KH đã liên hệ CN
-2. KH cần CN hỗ trợ chuyển hợp đồng bản cứng cho KH với mục đích lưu giữ
+          <t>1. KH đã liên hệ CN_x000D_
+2. KH cần CN hỗ trợ chuyển hợp đồng bản cứng cho KH với mục đích lưu giữ_x000D_
 3. KH cần CN hỗ trợ sớm</t>
         </is>
       </c>
@@ -53095,7 +53097,7 @@
       </c>
       <c r="R301" t="inlineStr">
         <is>
-          <t>1. KH đã được CN đến chuyển ATS đi bảo hành
+          <t>1. KH đã được CN đến chuyển ATS đi bảo hành_x000D_
 2. KH cần CN cập nhật tiến độ bảo hành, kiểm tra Ắc quy lưu trữ và xử lý sơ bộ cho KH</t>
         </is>
       </c>
@@ -53266,13 +53268,13 @@
       </c>
       <c r="Q302" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R302" t="inlineStr">
         <is>
-          <t>1.  Tủ nguồn ATS của KH có dấu hiệu chập cháy
-2. KH đã liên hệ CN và được hỗ trợ xử lý sơ bộ
+          <t>1.  Tủ nguồn ATS của KH có dấu hiệu chập cháy_x000D_
+2. KH đã liên hệ CN và được hỗ trợ xử lý sơ bộ_x000D_
 3. KH cần CN hỗ trợ khắc phục sớm</t>
         </is>
       </c>
@@ -53438,13 +53440,13 @@
       </c>
       <c r="Q303" t="inlineStr">
         <is>
-          <t>Lắp đặt sai quy cách, thiếu vật tư, thiết bị, phụ kiện đi kèm</t>
+          <t>Chất lượng triển khai</t>
         </is>
       </c>
       <c r="R303" t="inlineStr">
         <is>
-          <t>1. CN tạo sự cố cho KH
-2. Sau khi lắp HT NLMT bị lệch cos phi, dẫn tới bị phạt công suất phản kháng khoảng 3 tháng, Điện lực đã thông tin tới KH nhiều lần
+          <t>1. CN tạo sự cố cho KH_x000D_
+2. Sau khi lắp HT NLMT bị lệch cos phi, dẫn tới bị phạt công suất phản kháng khoảng 3 tháng, Điện lực đã thông tin tới KH nhiều lần_x000D_
 3. KH cần CN liên hệ và đến hỗ trợ sớm</t>
         </is>
       </c>
@@ -53615,13 +53617,13 @@
       </c>
       <c r="Q304" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R304" t="inlineStr">
         <is>
-          <t>CN 0978866677 báo sự cố hộ KH
-1. KH phản ánh: đèn tín hiệu trong ivt nhấp nháy và báo lỗi màu đỏ, ko thấy có ra điện nlmt
+          <t>CN 0978866677 báo sự cố hộ KH_x000D_
+1. KH phản ánh: đèn tín hiệu trong ivt nhấp nháy và báo lỗi màu đỏ, ko thấy có ra điện nlmt_x000D_
 2. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này</t>
         </is>
       </c>
@@ -53792,13 +53794,13 @@
       </c>
       <c r="Q305" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R305" t="inlineStr">
         <is>
-          <t>1. KH đã báo CN: A Hoàng
-2. KH phản ánh: pin lưu trữ nạp vào nhưng ko xả ra, đường dây lắp đặt trên mái bị hắt qua 1 bên do mưa bão, KH không biết có ảnh hưởng gì tới hệ nlmt không
+          <t>1. KH đã báo CN: A Hoàng_x000D_
+2. KH phản ánh: pin lưu trữ nạp vào nhưng ko xả ra, đường dây lắp đặt trên mái bị hắt qua 1 bên do mưa bão, KH không biết có ảnh hưởng gì tới hệ nlmt không_x000D_
 3. KH yêu cầu: qua kiểm tra lại phần đường dây và khắc phục lỗi pin lưu trữ</t>
         </is>
       </c>
@@ -53969,13 +53971,13 @@
       </c>
       <c r="Q306" t="inlineStr">
         <is>
-          <t>Tiến độ triển khai chậm</t>
+          <t>Tiến độ triển khai</t>
         </is>
       </c>
       <c r="R306" t="inlineStr">
         <is>
-          <t>1. KH đã báo CN (KH ko muốn nhắc tên)
-2. KH phản ánh: CN có thống nhất với KH là vào lắp đặt vào hôm nay nhưng đến hiện tại KH ko thấy có thông tin gì, liên lạc CN thì cũng ko được, ko chủ động báo lại cho KH mà dời lịch hẹn đã rất nhiều lần. KH phải bỏ việc ở nhà mà lại ko đúng hẹn, KH rất ko hài lòng về cách làm việc của CN
+          <t>1. KH đã báo CN (KH ko muốn nhắc tên)_x000D_
+2. KH phản ánh: CN có thống nhất với KH là vào lắp đặt vào hôm nay nhưng đến hiện tại KH ko thấy có thông tin gì, liên lạc CN thì cũng ko được, ko chủ động báo lại cho KH mà dời lịch hẹn đã rất nhiều lần. KH phải bỏ việc ở nhà mà lại ko đúng hẹn, KH rất ko hài lòng về cách làm việc của CN_x000D_
 3. KH yêu cầu: CN xuống triển khai lắp đặt cho KH theo đúng cam kết</t>
         </is>
       </c>
@@ -54146,13 +54148,13 @@
       </c>
       <c r="Q307" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R307" t="inlineStr">
         <is>
-          <t>1. KH đã báo KT anh Hải
-2.Hệ thống NLMT không phát ra điện, KH bị sự cố báo sáng 6/8 nhưng chưa được hỗ trợ 
+          <t>1. KH đã báo KT anh Hải_x000D_
+2.Hệ thống NLMT không phát ra điện, KH bị sự cố báo sáng 6/8 nhưng chưa được hỗ trợ _x000D_
 3. Yêu cầu CN hỗ trợ KH</t>
         </is>
       </c>
@@ -54318,7 +54320,7 @@
       </c>
       <c r="Q308" t="inlineStr">
         <is>
-          <t>Liên hệ / Đặt lịch lại</t>
+          <t>Liên hệ/tư vấn</t>
         </is>
       </c>
       <c r="R308" t="inlineStr">
@@ -54493,13 +54495,13 @@
       </c>
       <c r="Q309" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R309" t="inlineStr">
         <is>
-          <t>1. KH đã báo CN
-2. KH phản ánh: ko thấy có điện nlmt, mất điện lưới cũng ko thấy có, pin lưu trữ cũng ko thấy xả điện ra để sử dụng
+          <t>1. KH đã báo CN_x000D_
+2. KH phản ánh: ko thấy có điện nlmt, mất điện lưới cũng ko thấy có, pin lưu trữ cũng ko thấy xả điện ra để sử dụng_x000D_
 3. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này gấp</t>
         </is>
       </c>
@@ -54670,13 +54672,13 @@
       </c>
       <c r="Q310" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R310" t="inlineStr">
         <is>
-          <t>CN Nguyễn Huy Thanh báo sự cố hộ KH qua zalo
-1. KH phản ánh:  báo hệ thống nlmt lỗi, tự lấy điện lưới nạp bình , đã bị lâu ngày.
+          <t>CN Nguyễn Huy Thanh báo sự cố hộ KH qua zalo_x000D_
+1. KH phản ánh:  báo hệ thống nlmt lỗi, tự lấy điện lưới nạp bình , đã bị lâu ngày._x000D_
 2. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này</t>
         </is>
       </c>
@@ -54847,13 +54849,13 @@
       </c>
       <c r="Q311" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R311" t="inlineStr">
         <is>
-          <t>KH chưa báo Cn 
-KH phản ánh:  Đường nối từ trên tầng mái xuống tầng tủ điện bị dẫn nước mưa, hiện đã ngừng hoạt động. Cần bảo hành sớm.
+          <t>KH chưa báo Cn _x000D_
+KH phản ánh:  Đường nối từ trên tầng mái xuống tầng tủ điện bị dẫn nước mưa, hiện đã ngừng hoạt động. Cần bảo hành sớm._x000D_
 Yêu cầu KT qua ktra hỗ trợ KH</t>
         </is>
       </c>
@@ -55024,13 +55026,13 @@
       </c>
       <c r="Q312" t="inlineStr">
         <is>
-          <t>Nghiệp vụ chuyên môn kém</t>
+          <t>Chất lượng triển khai</t>
         </is>
       </c>
       <c r="R312" t="inlineStr">
         <is>
-          <t>1. KH đã báo CN: anh Tùng - nhân viên tư vấn
-2. KH phản ánh: lúc tư vấn KH có trao đổi rõ về nhu cầu cũng như mong muốn của KH là sử dụng điện ban ngày, ko tích điện ban đêm và khi mất điện muốn có điện nlmt để sử dụng, nhưng giờ mất điện lần đầu tiên KH không có điện nlmt để sử dụng. KH có trao đổi với CN là anh Tùng nhưng CN phản hồi là phải thay cục pin và bộ chuyển đổi hết 70tr, KH ko đồng ý với phương án này do tư vấn KH đã trao đổi rõ, CN cũng có hẹn KH trưa nay xuống hỗ trợ nhưng giờ cũng ko thấy đâu. Hệ của KH sử dụng cũng ko đạt được mục đích, điện ko tiết kiệm như KH mong muốn chỉ đạt được 1/3 hiệu suất. Ngoài ra KH cũng ko nhận được bản HĐ cứng
+          <t>1. KH đã báo CN: anh Tùng - nhân viên tư vấn_x000D_
+2. KH phản ánh: lúc tư vấn KH có trao đổi rõ về nhu cầu cũng như mong muốn của KH là sử dụng điện ban ngày, ko tích điện ban đêm và khi mất điện muốn có điện nlmt để sử dụng, nhưng giờ mất điện lần đầu tiên KH không có điện nlmt để sử dụng. KH có trao đổi với CN là anh Tùng nhưng CN phản hồi là phải thay cục pin và bộ chuyển đổi hết 70tr, KH ko đồng ý với phương án này do tư vấn KH đã trao đổi rõ, CN cũng có hẹn KH trưa nay xuống hỗ trợ nhưng giờ cũng ko thấy đâu. Hệ của KH sử dụng cũng ko đạt được mục đích, điện ko tiết kiệm như KH mong muốn chỉ đạt được 1/3 hiệu suất. Ngoài ra KH cũng ko nhận được bản HĐ cứng_x000D_
 3. KH yêu cầu: KH bức xúc và cho rằng đây là lỗi nhân viên tư vấn yêu cầu cung cấp bản HĐ và đưa ra phương án xử lý như nào về TH này</t>
         </is>
       </c>
@@ -55201,7 +55203,7 @@
       </c>
       <c r="Q313" t="inlineStr">
         <is>
-          <t>Tiến độ triển khai chậm</t>
+          <t>Tiến độ triển khai</t>
         </is>
       </c>
       <c r="R313" t="inlineStr">
@@ -55376,13 +55378,13 @@
       </c>
       <c r="Q314" t="inlineStr">
         <is>
-          <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
+          <t>Chất lượng triển khai</t>
         </is>
       </c>
       <c r="R314" t="inlineStr">
         <is>
-          <t>CN 0979707700 báo sự cố hộ KH
-1. KH phản ánh: pin lưu trữ nắng to mà đạt công suất thấp từ sáng tới 3h chiều chỉ đạt được 50% pin, KH cũng theo dõi ít thế này mấy ngày nay rồi
+          <t>CN 0979707700 báo sự cố hộ KH_x000D_
+1. KH phản ánh: pin lưu trữ nắng to mà đạt công suất thấp từ sáng tới 3h chiều chỉ đạt được 50% pin, KH cũng theo dõi ít thế này mấy ngày nay rồi_x000D_
 2. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này</t>
         </is>
       </c>
@@ -55553,13 +55555,13 @@
       </c>
       <c r="Q315" t="inlineStr">
         <is>
-          <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
+          <t>Chất lượng triển khai</t>
         </is>
       </c>
       <c r="R315" t="inlineStr">
         <is>
-          <t>1. KH đã liên hệ CN
-2. KH phản ánh HT NLMT đã lắp đặt và đưa vào sử dụng tuy nhiên hiệu suất chưa đạt yêu cầu, tiền điện KH cần thanh toán vẫn cao, số điện tiêu thụ giảm chưa đáng kể
+          <t>1. KH đã liên hệ CN_x000D_
+2. KH phản ánh HT NLMT đã lắp đặt và đưa vào sử dụng tuy nhiên hiệu suất chưa đạt yêu cầu, tiền điện KH cần thanh toán vẫn cao, số điện tiêu thụ giảm chưa đáng kể_x000D_
 3. KH cần CN đến kiểm tra và giải đáp cho KH</t>
         </is>
       </c>
@@ -55730,13 +55732,13 @@
       </c>
       <c r="Q316" t="inlineStr">
         <is>
-          <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
+          <t>Chất lượng triển khai</t>
         </is>
       </c>
       <c r="R316" t="inlineStr">
         <is>
-          <t>1. KH đã báo bạn Tú 
-2. KH có lắp thêm 2 tấm pin nhưng sau khi lắp thì pin chỉ thu được dưới 50%, điện lưới KH vẫn tăng 1 triệu so với tháng trước. KT đã liên hệ hỗ trợ nhưng chưa triệt để
+          <t>1. KH đã báo bạn Tú _x000D_
+2. KH có lắp thêm 2 tấm pin nhưng sau khi lắp thì pin chỉ thu được dưới 50%, điện lưới KH vẫn tăng 1 triệu so với tháng trước. KT đã liên hệ hỗ trợ nhưng chưa triệt để_x000D_
 3. Yêu cầu CN hỗ trợ KH</t>
         </is>
       </c>
@@ -55907,13 +55909,13 @@
       </c>
       <c r="Q317" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R317" t="inlineStr">
         <is>
-          <t>1. KH đã liên hệ CN
-2. 2 Ắc quy lưu trữ của KH đang gặp sự cố không sạc không xả
+          <t>1. KH đã liên hệ CN_x000D_
+2. 2 Ắc quy lưu trữ của KH đang gặp sự cố không sạc không xả_x000D_
 3. KH cần CN liên hệ và đến hỗ trợ sớm</t>
         </is>
       </c>
@@ -56084,13 +56086,13 @@
       </c>
       <c r="Q318" t="inlineStr">
         <is>
-          <t>Thủ tục/giấy tờ/ Hóa đơn/ Hồ sơ lắp đặt</t>
+          <t>Thủ tục/giấy tờ/ Hóa đơn/ Hồ sơ lắp đặt</t>
         </is>
       </c>
       <c r="R318" t="inlineStr">
         <is>
-          <t>1. KH đã liên hệ CN
-2. KH cần hỗ trợ hoàn thiện chứng từ, hồ sơ của hệ thống NLMT để có thể cung cấp cho bên điện lực trong trường hợp có yêu cầu
+          <t>1. KH đã liên hệ CN_x000D_
+2. KH cần hỗ trợ hoàn thiện chứng từ, hồ sơ của hệ thống NLMT để có thể cung cấp cho bên điện lực trong trường hợp có yêu cầu_x000D_
 3. KH cần CN liên hệ và đến hỗ trợ sớm</t>
         </is>
       </c>
@@ -56261,13 +56263,13 @@
       </c>
       <c r="Q319" t="inlineStr">
         <is>
-          <t>Hướng dẫn, hỗ trợ sử dụng sản phẩm</t>
+          <t>Liên hệ/tư vấn</t>
         </is>
       </c>
       <c r="R319" t="inlineStr">
         <is>
-          <t>1. KH đã liên hệ CN
-2. KH đã lắp đặt HT NLMT tuy nhiên chỉ số điện tiêu dùng không thấy giảm , tiền điện cần thanh toán không có chênh lệch nhiều với thời điểm trước khi lắp đặt HT NLMT
+          <t>1. KH đã liên hệ CN_x000D_
+2. KH đã lắp đặt HT NLMT tuy nhiên chỉ số điện tiêu dùng không thấy giảm , tiền điện cần thanh toán không có chênh lệch nhiều với thời điểm trước khi lắp đặt HT NLMT_x000D_
 3. KH cần CN đến kiểm tra và giải đáp cho KH</t>
         </is>
       </c>
@@ -56433,7 +56435,7 @@
       </c>
       <c r="Q320" t="inlineStr">
         <is>
-          <t>Tư vấn sản phẩm/dịch vụ</t>
+          <t>Liên hệ/tư vấn</t>
         </is>
       </c>
       <c r="R320" t="inlineStr">
@@ -56608,13 +56610,13 @@
       </c>
       <c r="Q321" t="inlineStr">
         <is>
-          <t>Hỗ trợ lắp đặt</t>
+          <t>Tiến độ triển khai</t>
         </is>
       </c>
       <c r="R321" t="inlineStr">
         <is>
-          <t>KH đã báo KT nhưng chưa được hỗ trợ 
-KH báo pin lưu trữ của KH bị hỏng đã tháo mang đi bảo hành và đã được trả về, tuy nhiên KT chưa mang pin lưu trữ đến trả và lắp đặt lại cho KH 
+          <t>KH đã báo KT nhưng chưa được hỗ trợ _x000D_
+KH báo pin lưu trữ của KH bị hỏng đã tháo mang đi bảo hành và đã được trả về, tuy nhiên KT chưa mang pin lưu trữ đến trả và lắp đặt lại cho KH _x000D_
 Yêu cầu CN cho KT qua hỗ trợ lắp đặt lại cho KH</t>
         </is>
       </c>
@@ -56785,13 +56787,13 @@
       </c>
       <c r="Q322" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R322" t="inlineStr">
         <is>
-          <t>CN 0357162662 báo sự cố hộ KH 
-1. KH phản ánh: mưa bị dột mái nhà nlmt 
+          <t>CN 0357162662 báo sự cố hộ KH _x000D_
+1. KH phản ánh: mưa bị dột mái nhà nlmt _x000D_
 2. KH yêu cầu: kiểm tra, và xử lý lại phần thi công</t>
         </is>
       </c>
@@ -56962,7 +56964,7 @@
       </c>
       <c r="Q323" t="inlineStr">
         <is>
-          <t>Liên hệ / Đặt lịch lại</t>
+          <t>Liên hệ/tư vấn</t>
         </is>
       </c>
       <c r="R323" t="inlineStr">
@@ -57137,13 +57139,13 @@
       </c>
       <c r="Q324" t="inlineStr">
         <is>
-          <t>Inverter không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R324" t="inlineStr">
         <is>
-          <t>1. KH đã báo CN: KT Quốc Việt,( CN phản hồi là ko thấy có thông tin HĐ, KH thấy có thể là KH gọi bằng SĐT khác nên CN ko thấy có HĐ )
-2. KH phản ánh: ivt mất kết nối, KH kiểm tra đường truyền mạng thì vẫn thấy bình thường
+          <t>1. KH đã báo CN: KT Quốc Việt,( CN phản hồi là ko thấy có thông tin HĐ, KH thấy có thể là KH gọi bằng SĐT khác nên CN ko thấy có HĐ )_x000D_
+2. KH phản ánh: ivt mất kết nối, KH kiểm tra đường truyền mạng thì vẫn thấy bình thường_x000D_
 3. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này</t>
         </is>
       </c>
@@ -57309,13 +57311,13 @@
       </c>
       <c r="Q325" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R325" t="inlineStr">
         <is>
-          <t>1. KH chưa báo CN
-2. KH phản ánh: cả tháng nay hệ nlmt ko hoạt động
+          <t>1. KH chưa báo CN_x000D_
+2. KH phản ánh: cả tháng nay hệ nlmt ko hoạt động_x000D_
 3. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này</t>
         </is>
       </c>
@@ -57481,12 +57483,12 @@
       </c>
       <c r="Q326" t="inlineStr">
         <is>
-          <t>Liên hệ tư vấn chậm</t>
+          <t>Liên hệ/tư vấn</t>
         </is>
       </c>
       <c r="R326" t="inlineStr">
         <is>
-          <t>KH đã có YCTX phản ánh chưa được bên CN liên hệ tư vấn sản phẩm NLMT cho KH 
+          <t>KH đã có YCTX phản ánh chưa được bên CN liên hệ tư vấn sản phẩm NLMT cho KH _x000D_
 Yêu cầu CN liên hệ và hỗ trợ KH</t>
         </is>
       </c>
@@ -57652,7 +57654,7 @@
       </c>
       <c r="Q327" t="inlineStr">
         <is>
-          <t>Tư vấn sản phẩm/dịch vụ</t>
+          <t>Liên hệ/tư vấn</t>
         </is>
       </c>
       <c r="R327" t="inlineStr">
@@ -57822,7 +57824,7 @@
       </c>
       <c r="Q328" t="inlineStr">
         <is>
-          <t>Tư vấn sản phẩm/dịch vụ</t>
+          <t>Liên hệ/tư vấn</t>
         </is>
       </c>
       <c r="R328" t="inlineStr">
@@ -57997,13 +57999,13 @@
       </c>
       <c r="Q329" t="inlineStr">
         <is>
-          <t>Thủ tục/giấy tờ/ Hóa đơn/ Hồ sơ lắp đặt</t>
+          <t>Thủ tục/giấy tờ/ Hóa đơn/ Hồ sơ lắp đặt</t>
         </is>
       </c>
       <c r="R329" t="inlineStr">
         <is>
-          <t>1. KH chưa báo CN: KH ko còn giữ SĐT liên hệ
-2. KH cần hỗ trợ cung cấp bản hợp đồng cứng để KH lưu lại 
+          <t>1. KH chưa báo CN: KH ko còn giữ SĐT liên hệ_x000D_
+2. KH cần hỗ trợ cung cấp bản hợp đồng cứng để KH lưu lại _x000D_
 *** liên hệ trước SĐT đky HĐ là chị phó hiệu trưởng trường, nếu ko liên hệ được thì liên hệ với SĐT phản ánh 0868731084</t>
         </is>
       </c>
@@ -58174,13 +58176,13 @@
       </c>
       <c r="Q330" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R330" t="inlineStr">
         <is>
-          <t>1. CN báo sự cố cho KH (987251444_
-2. Ắc quy lưu trữ của KH không vào điện
+          <t>1. CN báo sự cố cho KH (987251444__x000D_
+2. Ắc quy lưu trữ của KH không vào điện_x000D_
 3. KH cần CN hỗ trợ khắc phục sớm</t>
         </is>
       </c>
@@ -58351,7 +58353,7 @@
       </c>
       <c r="Q331" t="inlineStr">
         <is>
-          <t>Sau bảo dưỡng thiết bị bị hỏng</t>
+          <t>Chất lượng bảo dưỡng</t>
         </is>
       </c>
       <c r="R331" t="inlineStr">
@@ -58526,13 +58528,13 @@
       </c>
       <c r="Q332" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R332" t="inlineStr">
         <is>
-          <t>1. KH đã báo CN 
-2. KH khi sử dụng điện thì nguồn điện bị chuyển nhảy lung tung giữa điện mặt trời và điện lưới (đang sử dụng năng lượng mặt trời thì hệ thống tự ngắt và chuyển sang điện lưới), ban đêm dung lượng pin lưu trữ vẫn còn nhiều (80% - 90%) nhưng hệ thống vẫn bị nhảy nguồn.
+          <t>1. KH đã báo CN _x000D_
+2. KH khi sử dụng điện thì nguồn điện bị chuyển nhảy lung tung giữa điện mặt trời và điện lưới (đang sử dụng năng lượng mặt trời thì hệ thống tự ngắt và chuyển sang điện lưới), ban đêm dung lượng pin lưu trữ vẫn còn nhiều (80% - 90%) nhưng hệ thống vẫn bị nhảy nguồn._x000D_
 3. Yêu cầu CN hỗ trợ KH</t>
         </is>
       </c>
@@ -58698,13 +58700,13 @@
       </c>
       <c r="Q333" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R333" t="inlineStr">
         <is>
-          <t>1. KH đã liên hệ CN
-2. Hiện trường đang bị mất điện một dãy lớp học, KH đã nhờ thợ điện đến kiểm tra và được thông tin do HT NLMT quá tải dẫn đến cháy cầu dao tổng
+          <t>1. KH đã liên hệ CN_x000D_
+2. Hiện trường đang bị mất điện một dãy lớp học, KH đã nhờ thợ điện đến kiểm tra và được thông tin do HT NLMT quá tải dẫn đến cháy cầu dao tổng_x000D_
 3. KH cần CN đến kiểm tra và khắc phục sớm cho KH</t>
         </is>
       </c>
@@ -58870,7 +58872,7 @@
       </c>
       <c r="Q334" t="inlineStr">
         <is>
-          <t>Tiến độ triển khai chậm</t>
+          <t>Tiến độ triển khai</t>
         </is>
       </c>
       <c r="R334" t="inlineStr">
@@ -59045,7 +59047,7 @@
       </c>
       <c r="Q335" t="inlineStr">
         <is>
-          <t>Sau bảo dưỡng thiết bị bị hỏng</t>
+          <t>Chất lượng bảo dưỡng</t>
         </is>
       </c>
       <c r="R335" t="inlineStr">
@@ -59220,14 +59222,15 @@
       </c>
       <c r="Q336" t="inlineStr">
         <is>
-          <t>Tiến độ triển khai chậm</t>
+          <t>Tiến độ triển khai</t>
         </is>
       </c>
       <c r="R336" t="inlineStr">
         <is>
-          <t>1. KH đã liên hệ CN
-2. KH đã ký hợp đồng NLMT với CNCT và đặt cọc từ tháng 3 tuy nhiên hiện tại chưa được CN hỗ trợ đến lắp đặt và hoàn thiện hệ thống, nhà KH đang trong quá trình xây dựng và đã hoàn thiện đường điện do không đợi được CN
-3. Hiện KH đang cân nhắc việc hủy hợp đồng và yêu cầu hoàn cọc do tiến độ lắp đặt chậm, khi cần liên hệ chi nhánh rất khó khăn, cần CN liên hệ và đến hỗ trợ đề xuất hướng xử lý gấp cho KH
+          <t>1. KH đã liên hệ CN_x000D_
+2. KH đã ký hợp đồng NLMT với CNCT và đặt cọc từ tháng 3 tuy nhiên hiện tại chưa được CN hỗ trợ đến lắp đặt và hoàn thiện hệ thống, nhà KH đang trong quá trình xây dựng và đã hoàn thiện đường điện do không đợi được CN_x000D_
+3. Hiện KH đang cân nhắc việc hủy hợp đồng và yêu cầu hoàn cọc do tiến độ lắp đặt chậm, khi cần liên hệ chi nhánh rất khó khăn, cần CN liên hệ và đến hỗ trợ đề xuất hướng xử lý gấp cho KH_x000D_
+_x000D_
 (Liên hệ KH trước 7h sáng hoặc sau 16h chiều, có thể nhắn tin trao đổi qua Zalo)</t>
         </is>
       </c>
@@ -59398,13 +59401,13 @@
       </c>
       <c r="Q337" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R337" t="inlineStr">
         <is>
-          <t>1. KH đã liên hệ CN
-2. Tủ nguồn NLMT đóng ngắt liên tục vào buổi tối khoảng 2 ngày nay
+          <t>1. KH đã liên hệ CN_x000D_
+2. Tủ nguồn NLMT đóng ngắt liên tục vào buổi tối khoảng 2 ngày nay_x000D_
 3. KH cần CN liên hệ và đến hỗ trợ sớm</t>
         </is>
       </c>
@@ -59575,13 +59578,13 @@
       </c>
       <c r="Q338" t="inlineStr">
         <is>
-          <t>Hướng dẫn, hỗ trợ sử dụng sản phẩm</t>
+          <t>Liên hệ/tư vấn</t>
         </is>
       </c>
       <c r="R338" t="inlineStr">
         <is>
-          <t>1. KH chưa liên hệ CN
-2. KH theo dõi HT NLMT thấy lượng điện sản xuất được và sản lượng tiêu thụ đang không đồng đều, nếu HT NLMT sản xuất được 10Kw điện thì tải nhà sẽ tiêu thụ khoảng 8Kw
+          <t>1. KH chưa liên hệ CN_x000D_
+2. KH theo dõi HT NLMT thấy lượng điện sản xuất được và sản lượng tiêu thụ đang không đồng đều, nếu HT NLMT sản xuất được 10Kw điện thì tải nhà sẽ tiêu thụ khoảng 8Kw_x000D_
 3. KH cần CN liên hệ và giải đáp cho KH</t>
         </is>
       </c>
@@ -59752,13 +59755,13 @@
       </c>
       <c r="Q339" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R339" t="inlineStr">
         <is>
-          <t>KH đã báo CN
-KH phản ánh biến tần không phát được điện  nữa,
+          <t>KH đã báo CN_x000D_
+KH phản ánh biến tần không phát được điện  nữa,_x000D_
 Yêu cầu quản lí điều kĩ thuật liên hệ và hỗ trợ KH</t>
         </is>
       </c>
@@ -59929,13 +59932,13 @@
       </c>
       <c r="Q340" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R340" t="inlineStr">
         <is>
-          <t>1. KH chưa báo CN
-2. KH phản ánh: pin lưu trữ ko nạp điện vào, nguồn điện nlmt chạy lên mái đứng im
+          <t>1. KH chưa báo CN_x000D_
+2. KH phản ánh: pin lưu trữ ko nạp điện vào, nguồn điện nlmt chạy lên mái đứng im_x000D_
 3. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này</t>
         </is>
       </c>
@@ -60106,7 +60109,7 @@
       </c>
       <c r="Q341" t="inlineStr">
         <is>
-          <t>Liên hệ / Đặt lịch lại</t>
+          <t>Liên hệ/tư vấn</t>
         </is>
       </c>
       <c r="R341" t="inlineStr">
@@ -60276,13 +60279,13 @@
       </c>
       <c r="Q342" t="inlineStr">
         <is>
-          <t>Tiến độ triển khai chậm</t>
+          <t>Tiến độ triển khai</t>
         </is>
       </c>
       <c r="R342" t="inlineStr">
         <is>
-          <t>1. KH đã báo CN 
-2. KH chưa được hỗ trợ về việc lắp thang hàng và tiến độ về công trình đang bị chậm nửa năm rồi  KH muốn được đền bù HĐ
+          <t>1. KH đã báo CN _x000D_
+2. KH chưa được hỗ trợ về việc lắp thang hàng và tiến độ về công trình đang bị chậm nửa năm rồi  KH muốn được đền bù HĐ_x000D_
 3. Yêu cầu CN hỗ trợ KH</t>
         </is>
       </c>
@@ -60450,13 +60453,13 @@
       </c>
       <c r="Q343" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R343" t="inlineStr">
         <is>
-          <t>1. KH chưa báo CN
-2. KH phản ánh: điều hòa ko lạnh, bật nhiệt độ rất nhỏ nhưng cũng ko thấy lạnh
+          <t>1. KH chưa báo CN_x000D_
+2. KH phản ánh: điều hòa ko lạnh, bật nhiệt độ rất nhỏ nhưng cũng ko thấy lạnh_x000D_
 3. KH yêu cầu: qua kiểm tra, bảo hành điều hòa cho KH</t>
         </is>
       </c>
@@ -60627,7 +60630,7 @@
       </c>
       <c r="Q344" t="inlineStr">
         <is>
-          <t>Đơn bảo dưỡng hết hạn bảo hành</t>
+          <t>Chất lượng bảo dưỡng</t>
         </is>
       </c>
       <c r="R344" t="inlineStr">
@@ -60797,13 +60800,13 @@
       </c>
       <c r="Q345" t="inlineStr">
         <is>
-          <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
+          <t>Chất lượng triển khai</t>
         </is>
       </c>
       <c r="R345" t="inlineStr">
         <is>
-          <t>1. KH đã báo CN: từ phản ánh trước TT_1784109701554, và a Hào ở Thành Quá
-2. KH phản ánh: phản ánh từ trước xác định tấm pin bị vỡ KH có đặt mua nhưng do thời gian lâu nên CN là a Hào báo KH mua tấm pin ở ngoài, KH đã mua nhưng ko thấy CN tới hỗ trợ lắp. Ngoài ra, hiệu suất cũng ko đạt so với trước, bình thường rơi vào 25-30kw nhưng hiện tại chỉ được tầm 10kw
+          <t>1. KH đã báo CN: từ phản ánh trước TT_1784109701554, và a Hào ở Thành Quá_x000D_
+2. KH phản ánh: phản ánh từ trước xác định tấm pin bị vỡ KH có đặt mua nhưng do thời gian lâu nên CN là a Hào báo KH mua tấm pin ở ngoài, KH đã mua nhưng ko thấy CN tới hỗ trợ lắp. Ngoài ra, hiệu suất cũng ko đạt so với trước, bình thường rơi vào 25-30kw nhưng hiện tại chỉ được tầm 10kw_x000D_
 3. KH yêu cầu: hỗ trợ lắp đặt và kiểm tra lại phần hiệu suất</t>
         </is>
       </c>
@@ -60974,13 +60977,13 @@
       </c>
       <c r="Q346" t="inlineStr">
         <is>
-          <t>Không kết nối được app/Wifi và không theo dõi được hiệu suất</t>
+          <t>Kết nối hệ thống</t>
         </is>
       </c>
       <c r="R346" t="inlineStr">
         <is>
-          <t>1. KH chưa báo CN
-2. KH phản ánh: mất kết nối app theo dõi, mất giám sát
+          <t>1. KH chưa báo CN_x000D_
+2. KH phản ánh: mất kết nối app theo dõi, mất giám sát_x000D_
 3. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này</t>
         </is>
       </c>
@@ -61151,13 +61154,13 @@
       </c>
       <c r="Q347" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R347" t="inlineStr">
         <is>
-          <t>KH báo CN, CN báo gọi TĐ
-KH báo sự cố NLMT khi mất điện không tự đảo át
+          <t>KH báo CN, CN báo gọi TĐ_x000D_
+KH báo sự cố NLMT khi mất điện không tự đảo át_x000D_
 Yêu cầu CN cho KT qua ktra cho KH</t>
         </is>
       </c>
@@ -61328,13 +61331,13 @@
       </c>
       <c r="Q348" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R348" t="inlineStr">
         <is>
-          <t>KH đã báo CN, anh Hoàng 
-KH phản ánh hiện nay hệ thống điện NLMT của KH không phát điện được nữa, mất toàn bộ hệ thống, kiểm tra trên app cũng báo lỗi
+          <t>KH đã báo CN, anh Hoàng _x000D_
+KH phản ánh hiện nay hệ thống điện NLMT của KH không phát điện được nữa, mất toàn bộ hệ thống, kiểm tra trên app cũng báo lỗi_x000D_
 Yêu cầu quản lí điều kĩ thuật liên hệ và hỗ trợ KH</t>
         </is>
       </c>
@@ -61505,13 +61508,13 @@
       </c>
       <c r="Q349" t="inlineStr">
         <is>
-          <t>Hướng dẫn, hỗ trợ sử dụng sản phẩm</t>
+          <t>Liên hệ/tư vấn</t>
         </is>
       </c>
       <c r="R349" t="inlineStr">
         <is>
-          <t>KH chưa báo CN
-KH phản ánh: Tháng này biến tần solax nhà mình báo 501 số điện mà evn báo 630 số điện chênh hơn 100 số mình muốn hỏi vì sao nó lại chênh nhiều tới vậy
+          <t>KH chưa báo CN_x000D_
+KH phản ánh: Tháng này biến tần solax nhà mình báo 501 số điện mà evn báo 630 số điện chênh hơn 100 số mình muốn hỏi vì sao nó lại chênh nhiều tới vậy_x000D_
 Yêu cầu CN cho KT qua ktra hỗ trợ KH</t>
         </is>
       </c>
@@ -61682,13 +61685,13 @@
       </c>
       <c r="Q350" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R350" t="inlineStr">
         <is>
-          <t>1. CN báo sự cố cho KH (981575791)
-2. Tủ nguồn của HT NLMT gặp sự cố không nhảy ATS và mất điện NLMT
+          <t>1. CN báo sự cố cho KH (981575791)_x000D_
+2. Tủ nguồn của HT NLMT gặp sự cố không nhảy ATS và mất điện NLMT_x000D_
 3. KH cần CN đến hỗ trợ sớm</t>
         </is>
       </c>
@@ -61859,7 +61862,7 @@
       </c>
       <c r="Q351" t="inlineStr">
         <is>
-          <t>Đơn bảo dưỡng hết hạn bảo hành</t>
+          <t>Chất lượng bảo dưỡng</t>
         </is>
       </c>
       <c r="R351" t="inlineStr">
@@ -62034,15 +62037,16 @@
       </c>
       <c r="Q352" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R352" t="inlineStr">
         <is>
-          <t>1. KH đã liê hệ CN
-2. Hiện tại HT NLMT đấu dây điện đang bị lệch và có hiện tượng quá tải do chịu tải nhà
-3. KH cần CN liên hệ và đến hỗ trợ 
-khắc phục sớm
+          <t>1. KH đã liê hệ CN_x000D_
+2. Hiện tại HT NLMT đấu dây điện đang bị lệch và có hiện tượng quá tải do chịu tải nhà_x000D_
+3. KH cần CN liên hệ và đến hỗ trợ _x000D_
+khắc phục sớm_x000D_
+_x000D_
 Địa chỉ lắp đặt: Xóm Châu Quang, Xã Quy Hợp, Tỉnh Nghệ An</t>
         </is>
       </c>
@@ -62208,7 +62212,7 @@
       </c>
       <c r="Q353" t="inlineStr">
         <is>
-          <t>Tiến độ triển khai chậm</t>
+          <t>Tiến độ triển khai</t>
         </is>
       </c>
       <c r="R353" t="inlineStr">
@@ -62378,7 +62382,7 @@
       </c>
       <c r="Q354" t="inlineStr">
         <is>
-          <t>Tư vấn sản phẩm/dịch vụ</t>
+          <t>Liên hệ/tư vấn</t>
         </is>
       </c>
       <c r="R354" t="inlineStr">
@@ -62548,13 +62552,13 @@
       </c>
       <c r="Q355" t="inlineStr">
         <is>
-          <t>Hỗ trợ lắp đặt</t>
+          <t>Tiến độ triển khai</t>
         </is>
       </c>
       <c r="R355" t="inlineStr">
         <is>
-          <t>1. KH đã báo CN
-2. Hiện vật tư thiết bị của HT NLMT đã tập kết đủ tại nhà KH tuy nhiên CN chưa hỗ trợ lắp đặt
+          <t>1. KH đã báo CN_x000D_
+2. Hiện vật tư thiết bị của HT NLMT đã tập kết đủ tại nhà KH tuy nhiên CN chưa hỗ trợ lắp đặt_x000D_
 3. KH cần CN đến lắp đặt và hoàn thiện HT NLMT cho KH để có thể phục vụ hoạt động sản xuất kinh doanh</t>
         </is>
       </c>
@@ -62720,7 +62724,7 @@
       </c>
       <c r="Q356" t="inlineStr">
         <is>
-          <t>Liên hệ chậm</t>
+          <t>Liên hệ/tư vấn</t>
         </is>
       </c>
       <c r="R356" t="inlineStr">
@@ -62890,7 +62894,7 @@
       </c>
       <c r="Q357" t="inlineStr">
         <is>
-          <t>Tư vấn sản phẩm/dịch vụ</t>
+          <t>Liên hệ/tư vấn</t>
         </is>
       </c>
       <c r="R357" t="inlineStr">
@@ -63065,13 +63069,13 @@
       </c>
       <c r="Q358" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R358" t="inlineStr">
         <is>
-          <t>1. KH đã liên hệ CN
-2. KH phản ánh Inverter của KH có thể bị ảnh hường bởi sét đánh, hiện không có điện lưới và điện NLMT
+          <t>1. KH đã liên hệ CN_x000D_
+2. KH phản ánh Inverter của KH có thể bị ảnh hường bởi sét đánh, hiện không có điện lưới và điện NLMT_x000D_
 3. KH cần CN liên hệ và đến kiểm tra sớm</t>
         </is>
       </c>
@@ -63237,7 +63241,7 @@
       </c>
       <c r="Q359" t="inlineStr">
         <is>
-          <t>Tư vấn sản phẩm/dịch vụ</t>
+          <t>Liên hệ/tư vấn</t>
         </is>
       </c>
       <c r="R359" t="inlineStr">
@@ -63412,13 +63416,13 @@
       </c>
       <c r="Q360" t="inlineStr">
         <is>
-          <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
+          <t>Chất lượng triển khai</t>
         </is>
       </c>
       <c r="R360" t="inlineStr">
         <is>
-          <t>1. KH đã liên hệ CN
-2. Tiền điện KH cần thanh toán tháng 7 là 1tr8 trong khi trước đó khi chưa lắp đặt HT NLMT chi phí khoảng 2tr1, Ăc quy lưu trữ dù nạp đầy nhưng không đủ dùng
+          <t>1. KH đã liên hệ CN_x000D_
+2. Tiền điện KH cần thanh toán tháng 7 là 1tr8 trong khi trước đó khi chưa lắp đặt HT NLMT chi phí khoảng 2tr1, Ăc quy lưu trữ dù nạp đầy nhưng không đủ dùng_x000D_
 3. KH cần CN đến kiểm tra và giải đáp cho KH</t>
         </is>
       </c>
@@ -63584,13 +63588,13 @@
       </c>
       <c r="Q361" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R361" t="inlineStr">
         <is>
-          <t>1. Kh chưa liên hệ CN
-2. KH có ký hợp đồng bán điện cho phía điện lực, tháng vừa rồi KH không thấy điện lực thanh toán cước cho KH
+          <t>1. Kh chưa liên hệ CN_x000D_
+2. KH có ký hợp đồng bán điện cho phía điện lực, tháng vừa rồi KH không thấy điện lực thanh toán cước cho KH_x000D_
 3. KH cần CN liên hệ và đến kiểm tra sớm</t>
         </is>
       </c>
@@ -63761,13 +63765,13 @@
       </c>
       <c r="Q362" t="inlineStr">
         <is>
-          <t>Không kết nối được app/Wifi và không theo dõi được hiệu suất</t>
+          <t>Kết nối hệ thống</t>
         </is>
       </c>
       <c r="R362" t="inlineStr">
         <is>
-          <t>1. KH chưa báo CN
-2. KH phản ánh: mất kết nối app theo dõi nlmt, KH đã kiểm tra đường mạng, tự tìm hiểu kết nối nhưng vẫn ko được
+          <t>1. KH chưa báo CN_x000D_
+2. KH phản ánh: mất kết nối app theo dõi nlmt, KH đã kiểm tra đường mạng, tự tìm hiểu kết nối nhưng vẫn ko được_x000D_
 3. KH yêu cầu: hỗ trợ KH kết nối lại app theo dõi nlmt</t>
         </is>
       </c>
@@ -63938,7 +63942,7 @@
       </c>
       <c r="Q363" t="inlineStr">
         <is>
-          <t>Đơn bảo dưỡng hết hạn bảo hành</t>
+          <t>Chất lượng bảo dưỡng</t>
         </is>
       </c>
       <c r="R363" t="inlineStr">
@@ -64113,13 +64117,13 @@
       </c>
       <c r="Q364" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R364" t="inlineStr">
         <is>
-          <t>1. KH đã báo CN: A Khương
-2. KH phản ánh: pin lưu trữ đầy nhưng ko xả điện ra để sử dụng
+          <t>1. KH đã báo CN: A Khương_x000D_
+2. KH phản ánh: pin lưu trữ đầy nhưng ko xả điện ra để sử dụng_x000D_
 3. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này</t>
         </is>
       </c>
@@ -64290,13 +64294,13 @@
       </c>
       <c r="Q365" t="inlineStr">
         <is>
-          <t>Hỗ trợ lắp đặt</t>
+          <t>Tiến độ triển khai</t>
         </is>
       </c>
       <c r="R365" t="inlineStr">
         <is>
-          <t>KH đã báo CN 
-KH cần bên mình hỗ trợ nhờ đấu thêm dây điện vào tủ điện 
+          <t>KH đã báo CN _x000D_
+KH cần bên mình hỗ trợ nhờ đấu thêm dây điện vào tủ điện _x000D_
 Yêu cầu CN liên hệ và hỗ trợ KH</t>
         </is>
       </c>
@@ -64467,13 +64471,13 @@
       </c>
       <c r="Q366" t="inlineStr">
         <is>
-          <t>Không kết nối được app/Wifi và không theo dõi được hiệu suất</t>
+          <t>Kết nối hệ thống</t>
         </is>
       </c>
       <c r="R366" t="inlineStr">
         <is>
-          <t>1. KH chưa báo CN
-2. KH phản ánh: mất kết nối app theo dõi, ko xem được hiệu suất
+          <t>1. KH chưa báo CN_x000D_
+2. KH phản ánh: mất kết nối app theo dõi, ko xem được hiệu suất_x000D_
 3. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này</t>
         </is>
       </c>
@@ -64644,14 +64648,14 @@
       </c>
       <c r="Q367" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R367" t="inlineStr">
         <is>
-          <t>1. KH đã báo CN: A Viêt
-2. KH phản ánh: trên phần mềm báo lỗi adapter
-3. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này
+          <t>1. KH đã báo CN: A Viêt_x000D_
+2. KH phản ánh: trên phần mềm báo lỗi adapter_x000D_
+3. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này_x000D_
 ***đ/c sau sáp nhập: Số 30 đường nhật đức, phường bắc giang, tỉnh bắc ninh</t>
         </is>
       </c>
@@ -64822,13 +64826,13 @@
       </c>
       <c r="Q368" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R368" t="inlineStr">
         <is>
-          <t>CN 0977477773 báo sự cố hộ KH
-1. KH phản ánh: cục ats nhảy liên tục, ko sử dụng được điện nlmt
+          <t>CN 0977477773 báo sự cố hộ KH_x000D_
+1. KH phản ánh: cục ats nhảy liên tục, ko sử dụng được điện nlmt_x000D_
 2. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này</t>
         </is>
       </c>
@@ -64999,7 +65003,7 @@
       </c>
       <c r="Q369" t="inlineStr">
         <is>
-          <t>Liên hệ chậm</t>
+          <t>Liên hệ/tư vấn</t>
         </is>
       </c>
       <c r="R369" t="inlineStr">
@@ -65174,13 +65178,13 @@
       </c>
       <c r="Q370" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R370" t="inlineStr">
         <is>
-          <t>1. KH chưa báo CN
-2. KH phản ánh: hệ thống bị mất PV, bị từ hôm qua sáng có nhưng chiều mất còn tối thì ko thấy xả pin, đến hôm nay thì chập chờn lúc có lúc ko
+          <t>1. KH chưa báo CN_x000D_
+2. KH phản ánh: hệ thống bị mất PV, bị từ hôm qua sáng có nhưng chiều mất còn tối thì ko thấy xả pin, đến hôm nay thì chập chờn lúc có lúc ko_x000D_
 3. KH yêu cầu: qua kiểm tra,khắc phục tình trạng này</t>
         </is>
       </c>
@@ -65346,7 +65350,7 @@
       </c>
       <c r="Q371" t="inlineStr">
         <is>
-          <t>Tư vấn sản phẩm/dịch vụ</t>
+          <t>Liên hệ/tư vấn</t>
         </is>
       </c>
       <c r="R371" t="inlineStr">
@@ -65521,13 +65525,13 @@
       </c>
       <c r="Q372" t="inlineStr">
         <is>
-          <t>Inverter không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R372" t="inlineStr">
         <is>
-          <t>1. KH chưa báo CN
-2. KH phản ánh: ivt chỉ sạc vào pin chứ ko xả ra, KH có 2 ivt nhưng chỉ bị 1 cái
+          <t>1. KH chưa báo CN_x000D_
+2. KH phản ánh: ivt chỉ sạc vào pin chứ ko xả ra, KH có 2 ivt nhưng chỉ bị 1 cái_x000D_
 3. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này</t>
         </is>
       </c>
@@ -65693,7 +65697,7 @@
       </c>
       <c r="Q373" t="inlineStr">
         <is>
-          <t>Tư vấn sản phẩm/dịch vụ</t>
+          <t>Liên hệ/tư vấn</t>
         </is>
       </c>
       <c r="R373" t="inlineStr">
@@ -65863,7 +65867,7 @@
       </c>
       <c r="Q374" t="inlineStr">
         <is>
-          <t>Tư vấn sản phẩm/dịch vụ</t>
+          <t>Liên hệ/tư vấn</t>
         </is>
       </c>
       <c r="R374" t="inlineStr">
@@ -66038,13 +66042,13 @@
       </c>
       <c r="Q375" t="inlineStr">
         <is>
-          <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
+          <t>Chất lượng triển khai</t>
         </is>
       </c>
       <c r="R375" t="inlineStr">
         <is>
-          <t>1.KH đã liên hệ CN
-2. Số điện phát sinh 20 ngày Tháng 7 là 1022 số, Tháng 6 chưa sử dụng HT NLMT là 1066 số điện trong khi đó KH đã được hỗ trợ lắp lại Inverter vào ngày 10-11/7, App theo dõi tháng 7 thông tin tạo 275kW điện NLMT trong 20 ngày, sản lượng điện NLMT có nhưng mức chênh lệch không nhiều
+          <t>1.KH đã liên hệ CN_x000D_
+2. Số điện phát sinh 20 ngày Tháng 7 là 1022 số, Tháng 6 chưa sử dụng HT NLMT là 1066 số điện trong khi đó KH đã được hỗ trợ lắp lại Inverter vào ngày 10-11/7, App theo dõi tháng 7 thông tin tạo 275kW điện NLMT trong 20 ngày, sản lượng điện NLMT có nhưng mức chênh lệch không nhiều_x000D_
 3.KH cần CN đến kiểm tra và giải đáp cho KH</t>
         </is>
       </c>
@@ -66215,13 +66219,13 @@
       </c>
       <c r="Q376" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R376" t="inlineStr">
         <is>
-          <t>KH đã báo CN 
-KH phản ánh điện NLMT bị nhảy liên tục giữa điện NLMT và điện lưới, không sử dụng được
+          <t>KH đã báo CN _x000D_
+KH phản ánh điện NLMT bị nhảy liên tục giữa điện NLMT và điện lưới, không sử dụng được_x000D_
 Yêu cầu quản lí điều kĩ thuật liên hệ và hỗ trợ KH</t>
         </is>
       </c>
@@ -66392,13 +66396,13 @@
       </c>
       <c r="Q377" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R377" t="inlineStr">
         <is>
-          <t>1. KH đã liên hệ CN
-2. Inverter của KH hiển thị thông tin không chính xác, HT NLMT tự đóng ngắt liên tục
+          <t>1. KH đã liên hệ CN_x000D_
+2. Inverter của KH hiển thị thông tin không chính xác, HT NLMT tự đóng ngắt liên tục_x000D_
 3.KH cần CN đến hỗ trợ và khắc phục sớm</t>
         </is>
       </c>
@@ -66569,13 +66573,13 @@
       </c>
       <c r="Q378" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R378" t="inlineStr">
         <is>
-          <t>KH chưa báo CN 
-KH phản ánh trên app đang báo lỗi mất điện NLMT và mất ắc quy, bị sáng nay 
+          <t>KH chưa báo CN _x000D_
+KH phản ánh trên app đang báo lỗi mất điện NLMT và mất ắc quy, bị sáng nay _x000D_
 Yêu cầu quản lí điều kĩ thuật liên hệ và hỗ trợ KH</t>
         </is>
       </c>
@@ -66741,13 +66745,13 @@
       </c>
       <c r="Q379" t="inlineStr">
         <is>
-          <t>Hiệu suất sản phẩm kém</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R379" t="inlineStr">
         <is>
-          <t>KH chưa báo CN 
-KH phản ánh hiệu suất sản phẩm kém, tiền điện vẫn tăng 40% so với tháng trước
+          <t>KH chưa báo CN _x000D_
+KH phản ánh hiệu suất sản phẩm kém, tiền điện vẫn tăng 40% so với tháng trước_x000D_
 Yêu cầu quản lí điều kĩ thuật liên hệ và hỗ trợ KH</t>
         </is>
       </c>
@@ -66913,15 +66917,16 @@
       </c>
       <c r="Q380" t="inlineStr">
         <is>
-          <t>Hỗ trợ lắp đặt</t>
+          <t>Tiến độ triển khai</t>
         </is>
       </c>
       <c r="R380" t="inlineStr">
         <is>
-          <t>1. CN hỗ trợ KH
-2. KH hỗ trợ bổ sung tiếp địa cho Ăc quy lưu trữ HT NLMT
-3. KH cần CN đến hỗ trợ sớm cho KH
-Chủ HĐ: Trần Văn Chung
+          <t>1. CN hỗ trợ KH_x000D_
+2. KH hỗ trợ bổ sung tiếp địa cho Ăc quy lưu trữ HT NLMT_x000D_
+3. KH cần CN đến hỗ trợ sớm cho KH_x000D_
+_x000D_
+Chủ HĐ: Trần Văn Chung_x000D_
 Địa chỉ lắp đặt: 385 Trần Nguyên Đán, Phường Trần Hưng Đạo, Thành phố Hải Phòng</t>
         </is>
       </c>
@@ -67087,13 +67092,13 @@
       </c>
       <c r="Q381" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R381" t="inlineStr">
         <is>
-          <t>1. KH chưa liên hệ CN
-2. Hệ thống thang máy của KH đang gặp sự cố không hoạt động
+          <t>1. KH chưa liên hệ CN_x000D_
+2. Hệ thống thang máy của KH đang gặp sự cố không hoạt động_x000D_
 3. KH cần CN đến kiểm tra và khắc phục gấp để có thể phục vụ hoạt động sản xuất kinh doanh</t>
         </is>
       </c>
@@ -67264,13 +67269,13 @@
       </c>
       <c r="Q382" t="inlineStr">
         <is>
-          <t>Hỗ trợ lắp đặt</t>
+          <t>Tiến độ triển khai</t>
         </is>
       </c>
       <c r="R382" t="inlineStr">
         <is>
-          <t>1. KH chưa liên hệ CN
-2. Trước đó CN đến hỗ trợ lắp đặt HT NLMT cho KH mới chỉ đấu 1 công tơ điện cho 1 tầng, nhà KH cần hỗ trợ đấu 2 công tơ
+          <t>1. KH chưa liên hệ CN_x000D_
+2. Trước đó CN đến hỗ trợ lắp đặt HT NLMT cho KH mới chỉ đấu 1 công tơ điện cho 1 tầng, nhà KH cần hỗ trợ đấu 2 công tơ_x000D_
 3. KH cần CN liên hệ và đến hỗ trợ sớm</t>
         </is>
       </c>
@@ -67441,7 +67446,7 @@
       </c>
       <c r="Q383" t="inlineStr">
         <is>
-          <t>Sau bảo dưỡng thiết bị bị hỏng</t>
+          <t>Chất lượng bảo dưỡng</t>
         </is>
       </c>
       <c r="R383" t="inlineStr">
@@ -67616,13 +67621,13 @@
       </c>
       <c r="Q384" t="inlineStr">
         <is>
-          <t>Inverter không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R384" t="inlineStr">
         <is>
-          <t>1. KH đã báo CN: A Hoàng
-2. KH phản ánh: lỗi cục wifi của ivt bị mất kết nối
+          <t>1. KH đã báo CN: A Hoàng_x000D_
+2. KH phản ánh: lỗi cục wifi của ivt bị mất kết nối_x000D_
 3. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này</t>
         </is>
       </c>
@@ -67793,13 +67798,13 @@
       </c>
       <c r="Q385" t="inlineStr">
         <is>
-          <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
+          <t>Chất lượng triển khai</t>
         </is>
       </c>
       <c r="R385" t="inlineStr">
         <is>
-          <t>1. KH chưa báo CN
-2. KH phản ánh: hiệu suất sản phẩm kém so với trước đây KH thấy là điện nlmt đang ko vào, trước ban ngày trời nắng từ 6r-12r điện lưới vào 1kw mà hiện tại điện lưới vào 1kw rưỡi - 2kw
+          <t>1. KH chưa báo CN_x000D_
+2. KH phản ánh: hiệu suất sản phẩm kém so với trước đây KH thấy là điện nlmt đang ko vào, trước ban ngày trời nắng từ 6r-12r điện lưới vào 1kw mà hiện tại điện lưới vào 1kw rưỡi - 2kw_x000D_
 3. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này</t>
         </is>
       </c>
@@ -67970,13 +67975,13 @@
       </c>
       <c r="Q386" t="inlineStr">
         <is>
-          <t>Inverter không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R386" t="inlineStr">
         <is>
-          <t>1. KH chưa báo CN
-2. KH phản ánh: ivt ko hoạt động, ko lên đèn nguồn, theo dõi trên app mất giám sát
+          <t>1. KH chưa báo CN_x000D_
+2. KH phản ánh: ivt ko hoạt động, ko lên đèn nguồn, theo dõi trên app mất giám sát_x000D_
 3. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này</t>
         </is>
       </c>
@@ -68147,7 +68152,7 @@
       </c>
       <c r="Q387" t="inlineStr">
         <is>
-          <t>Đơn bảo dưỡng hết hạn bảo hành</t>
+          <t>Chất lượng bảo dưỡng</t>
         </is>
       </c>
       <c r="R387" t="inlineStr">
@@ -68317,13 +68322,13 @@
       </c>
       <c r="Q388" t="inlineStr">
         <is>
-          <t>Thiết bị vỡ, hỏng, chập cháy</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R388" t="inlineStr">
         <is>
-          <t>1. KH đã báo CN: a Thành
-2. KH phản ánh: trước phản ánh t5 TT_1779705231590 xác định lỗi không đảo át và KH cần thay nhưng chưa thay, giờ bật nguồn lên lại chập. KH có liên hệ CN nhưng 2,3 lần ko thấy 
+          <t>1. KH đã báo CN: a Thành_x000D_
+2. KH phản ánh: trước phản ánh t5 TT_1779705231590 xác định lỗi không đảo át và KH cần thay nhưng chưa thay, giờ bật nguồn lên lại chập. KH có liên hệ CN nhưng 2,3 lần ko thấy _x000D_
 3. KH yêu cầu: đưa ra phương án thay cục nhảy áp cho KH</t>
         </is>
       </c>
@@ -68494,13 +68499,13 @@
       </c>
       <c r="Q389" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R389" t="inlineStr">
         <is>
-          <t>1. KH chưa báo CN
-2. KH phản ánh: trời nắng nhưng ko thấy có điện nlmt vào, KH theo dõi cả trên app lẫn đồng hồ tại nhà
+          <t>1. KH chưa báo CN_x000D_
+2. KH phản ánh: trời nắng nhưng ko thấy có điện nlmt vào, KH theo dõi cả trên app lẫn đồng hồ tại nhà_x000D_
 3. KH yêu cầu: qua kiểm tra xem tình trạng hệ nlmt</t>
         </is>
       </c>
@@ -68666,13 +68671,13 @@
       </c>
       <c r="Q390" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R390" t="inlineStr">
         <is>
-          <t>KH chưa báo CN 
-KH phản ánh nguyên buổi sáng nay nắng to nhưng điện năng lượng mặt trời không nạp vào được 1 số nào 
+          <t>KH chưa báo CN _x000D_
+KH phản ánh nguyên buổi sáng nay nắng to nhưng điện năng lượng mặt trời không nạp vào được 1 số nào _x000D_
 Yêu cầu quản lí điều kĩ thuật liên hệ và hỗ trợ KH</t>
         </is>
       </c>
@@ -68843,13 +68848,13 @@
       </c>
       <c r="Q391" t="inlineStr">
         <is>
-          <t>Hiệu suất sản phẩm kém</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R391" t="inlineStr">
         <is>
-          <t>KH chưa báo CN 
-KH phản ánh hiệu suất kém, tiền điện trước là 7-8tr sau khi lắp không thay đổi, kh theo dõi 3-4 tháng nay 
+          <t>KH chưa báo CN _x000D_
+KH phản ánh hiệu suất kém, tiền điện trước là 7-8tr sau khi lắp không thay đổi, kh theo dõi 3-4 tháng nay _x000D_
 Yêu cầu quản lí điều kĩ thuật liên hệ và hỗ trợ KH</t>
         </is>
       </c>
@@ -69020,13 +69025,13 @@
       </c>
       <c r="Q392" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R392" t="inlineStr">
         <is>
-          <t>KH đã báo CN 
-KH phản ánh hệ thống NLMT đang không sử dụng được khi nhà KH mất điện, đã báo CN nhưng chỉ hỗ trợ từ xa, bị sáng nay
+          <t>KH đã báo CN _x000D_
+KH phản ánh hệ thống NLMT đang không sử dụng được khi nhà KH mất điện, đã báo CN nhưng chỉ hỗ trợ từ xa, bị sáng nay_x000D_
 Yêu cầu quản lí điều kĩ thuật liên hệ và hỗ trợ KH</t>
         </is>
       </c>
@@ -69197,13 +69202,13 @@
       </c>
       <c r="Q393" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R393" t="inlineStr">
         <is>
-          <t>1. KH chưa báo CN
-2. KH phản ánh: trên app pin lưu trữ đầy 100% nhưng ko thấy có xả ra để sử dụng
+          <t>1. KH chưa báo CN_x000D_
+2. KH phản ánh: trên app pin lưu trữ đầy 100% nhưng ko thấy có xả ra để sử dụng_x000D_
 3. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này</t>
         </is>
       </c>
@@ -69374,13 +69379,13 @@
       </c>
       <c r="Q394" t="inlineStr">
         <is>
-          <t>Không kết nối được app/Wifi và không theo dõi được hiệu suất</t>
+          <t>Kết nối hệ thống</t>
         </is>
       </c>
       <c r="R394" t="inlineStr">
         <is>
-          <t>1. KH chưa báo CN
-2. KH phản ánh: KH phản ánh từ TT_1780652537817 là sai lệch lượng điện ở trên app với công tơ của điện lực, trước KT đã điều chỉnh lại bộ đếm đến tháng này vẫn bị gặp tình trạng sai lệch trên app báo 44 số nhưng điện lực báo 129 số, sai lệch nhiều quá 
+          <t>1. KH chưa báo CN_x000D_
+2. KH phản ánh: KH phản ánh từ TT_1780652537817 là sai lệch lượng điện ở trên app với công tơ của điện lực, trước KT đã điều chỉnh lại bộ đếm đến tháng này vẫn bị gặp tình trạng sai lệch trên app báo 44 số nhưng điện lực báo 129 số, sai lệch nhiều quá _x000D_
 3. KH yêu cầu: qua kiểm tra, khắc phục triệt để tình trạng này</t>
         </is>
       </c>
@@ -69551,14 +69556,14 @@
       </c>
       <c r="Q395" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R395" t="inlineStr">
         <is>
-          <t>1. KH đã báo CN: a Phát
-2. KH phản ánh: pin lưu trữ ko nạp vào, alarm báo đỏ
-3. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này
+          <t>1. KH đã báo CN: a Phát_x000D_
+2. KH phản ánh: pin lưu trữ ko nạp vào, alarm báo đỏ_x000D_
+3. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này_x000D_
 đ/c lắp đặt: Ấp 2, Xã Tân Bửu, Huyện Bến Lức, Tỉnh Long An (cũ)</t>
         </is>
       </c>
@@ -69729,7 +69734,7 @@
       </c>
       <c r="Q396" t="inlineStr">
         <is>
-          <t>Đơn bảo dưỡng hết hạn bảo hành</t>
+          <t>Chất lượng bảo dưỡng</t>
         </is>
       </c>
       <c r="R396" t="inlineStr">
@@ -69904,13 +69909,13 @@
       </c>
       <c r="Q397" t="inlineStr">
         <is>
-          <t>Hướng dẫn, hỗ trợ sử dụng sản phẩm</t>
+          <t>Liên hệ/tư vấn</t>
         </is>
       </c>
       <c r="R397" t="inlineStr">
         <is>
-          <t>1. KH đã báo CN: 0969856699 (KH ko lưu tên)
-2. KH phản ánh: KH theo dõi thấy hệ đang ko hề tích điện, có gọi cho CN hướng dẫn KH phải bấm xong rồi mới hiển thị giao diện bình thường gồm 4 nhánh nhưng hiện tại ko hiển thị 2 nhánh còn lại, KH phải chủ động bấm nút tích điện thì mới hiển thị. Có trao đổi với CN nhưng CN bảo KH hiểu sai vấn đề, KH ko đồng ý với cách giải thích của CN
+          <t>1. KH đã báo CN: 0969856699 (KH ko lưu tên)_x000D_
+2. KH phản ánh: KH theo dõi thấy hệ đang ko hề tích điện, có gọi cho CN hướng dẫn KH phải bấm xong rồi mới hiển thị giao diện bình thường gồm 4 nhánh nhưng hiện tại ko hiển thị 2 nhánh còn lại, KH phải chủ động bấm nút tích điện thì mới hiển thị. Có trao đổi với CN nhưng CN bảo KH hiểu sai vấn đề, KH ko đồng ý với cách giải thích của CN_x000D_
 3. KH yêu cầu: qua kiểm tra, hướng dẫn KH sử dụng sản phầm, giải thích cho KH</t>
         </is>
       </c>
@@ -70076,7 +70081,7 @@
       </c>
       <c r="Q398" t="inlineStr">
         <is>
-          <t>Liên hệ chậm</t>
+          <t>Liên hệ/tư vấn</t>
         </is>
       </c>
       <c r="R398" t="inlineStr">
@@ -70251,13 +70256,13 @@
       </c>
       <c r="Q399" t="inlineStr">
         <is>
-          <t>Cài đặt hệ thống (APP/Mật khẩu)</t>
+          <t>Kết nối hệ thống</t>
         </is>
       </c>
       <c r="R399" t="inlineStr">
         <is>
-          <t>1. KH chưa báo CN
-2. KH phản ánh: mất kết nối app
+          <t>1. KH chưa báo CN_x000D_
+2. KH phản ánh: mất kết nối app_x000D_
 3. KH yêu cầu: cài đặt lại app theo dõi nlmt</t>
         </is>
       </c>
@@ -70423,7 +70428,7 @@
       </c>
       <c r="Q400" t="inlineStr">
         <is>
-          <t>Tư vấn sản phẩm/dịch vụ</t>
+          <t>Liên hệ/tư vấn</t>
         </is>
       </c>
       <c r="R400" t="inlineStr">
@@ -70593,13 +70598,13 @@
       </c>
       <c r="Q401" t="inlineStr">
         <is>
-          <t>Camera mờ/không ghi hình được</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R401" t="inlineStr">
         <is>
-          <t>1. KH chưa báo CN
-2. KH phản ánh: hiện tại có 1 camera đang ko nhìn thấy
+          <t>1. KH chưa báo CN_x000D_
+2. KH phản ánh: hiện tại có 1 camera đang ko nhìn thấy_x000D_
 3. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này</t>
         </is>
       </c>
@@ -70770,12 +70775,12 @@
       </c>
       <c r="Q402" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R402" t="inlineStr">
         <is>
-          <t>KH phản ánh : ATS thường bị nhảy, phóng hồ quang dễ gây hỏng thiết bị. khi inverter và ATS BỊ lỗi thì không chuyển qua dùng điện lưới được
+          <t>KH phản ánh : ATS thường bị nhảy, phóng hồ quang dễ gây hỏng thiết bị. khi inverter và ATS BỊ lỗi thì không chuyển qua dùng điện lưới được_x000D_
 (sđt 0937378246 ký HĐ chặn TĐ )</t>
         </is>
       </c>
@@ -70946,13 +70951,13 @@
       </c>
       <c r="Q403" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R403" t="inlineStr">
         <is>
-          <t>KH chưa báo CN 
-KH phản ánh KH theo dõi qua ứng dụng theo dõi trên hệ thống thấy hệ thống của KH không hoạt động 
+          <t>KH chưa báo CN _x000D_
+KH phản ánh KH theo dõi qua ứng dụng theo dõi trên hệ thống thấy hệ thống của KH không hoạt động _x000D_
 Yêu cầu quản lí điều kĩ thuật liên hệ và hỗ trợ KH</t>
         </is>
       </c>
@@ -71123,13 +71128,13 @@
       </c>
       <c r="Q404" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R404" t="inlineStr">
         <is>
-          <t>1. KH đã báo CN
-2. HT NLMT của KH không hoạt động khoảng nửa tháng nay, Tiền điện của KH tăng cao, trên App chỉ số về 0
+          <t>1. KH đã báo CN_x000D_
+2. HT NLMT của KH không hoạt động khoảng nửa tháng nay, Tiền điện của KH tăng cao, trên App chỉ số về 0_x000D_
 3.KH cần CN đến kiểm tra và khắc phục sớm cho KH</t>
         </is>
       </c>
@@ -71300,13 +71305,13 @@
       </c>
       <c r="Q405" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R405" t="inlineStr">
         <is>
-          <t>1. KH đã báo CN, anh Luân bên lắp đặt
-2. hệ thống pin NLMT đầy trên 95% nhưng vẫn lấy điện lưới nhiều trong 15 phút rồi mới chuyển sang chạy từ pin, thường thì có lấy từ mạng lưới có chục giây thôi mà 15 phút như kia là quá lâu 
+          <t>1. KH đã báo CN, anh Luân bên lắp đặt_x000D_
+2. hệ thống pin NLMT đầy trên 95% nhưng vẫn lấy điện lưới nhiều trong 15 phút rồi mới chuyển sang chạy từ pin, thường thì có lấy từ mạng lưới có chục giây thôi mà 15 phút như kia là quá lâu _x000D_
 3. Yêu cầu CN hỗ trợ KH, xem có cấu hình sai đâu không</t>
         </is>
       </c>
@@ -71477,13 +71482,13 @@
       </c>
       <c r="Q406" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R406" t="inlineStr">
         <is>
-          <t>1. CN báo sự cố cho KH (968149087)
-2. KH đang mất điện lưới, Inverter không hoạt động, không có điện NLMT
+          <t>1. CN báo sự cố cho KH (968149087)_x000D_
+2. KH đang mất điện lưới, Inverter không hoạt động, không có điện NLMT_x000D_
 3. KH cần CN đến hỗ trợ khắc phục sớm</t>
         </is>
       </c>
@@ -71649,13 +71654,13 @@
       </c>
       <c r="Q407" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R407" t="inlineStr">
         <is>
-          <t>KH chưa báo CN 
-KH phản ánh từ hôm qua KH kiểm tra trên hệ thống thì thấy được sản phẩm đang không có 2 dây điện dòng không có điện mặc dù vẫn đang hoạt động 
+          <t>KH chưa báo CN _x000D_
+KH phản ánh từ hôm qua KH kiểm tra trên hệ thống thì thấy được sản phẩm đang không có 2 dây điện dòng không có điện mặc dù vẫn đang hoạt động _x000D_
 Yêu cầu quản lí điều kĩ thuật liên hệ và hỗ trợ KH</t>
         </is>
       </c>
@@ -71821,12 +71826,12 @@
       </c>
       <c r="Q408" t="inlineStr">
         <is>
-          <t>Liên hệ chậm</t>
+          <t>Liên hệ/tư vấn</t>
         </is>
       </c>
       <c r="R408" t="inlineStr">
         <is>
-          <t>KH có đơn bảo dưỡng điều hòa phản ánh chưa được kĩ thuật liên hệ và hỗ trợ KH
+          <t>KH có đơn bảo dưỡng điều hòa phản ánh chưa được kĩ thuật liên hệ và hỗ trợ KH_x000D_
 Yêu cầu quản lí điều kĩ thuật liên hệ và hỗ trợ KH</t>
         </is>
       </c>
@@ -71992,12 +71997,12 @@
       </c>
       <c r="Q409" t="inlineStr">
         <is>
-          <t>Liên hệ chậm</t>
+          <t>Liên hệ/tư vấn</t>
         </is>
       </c>
       <c r="R409" t="inlineStr">
         <is>
-          <t>KH phản ánh chưa được KT bên CN liên hệ qua hỗ trợ KH
+          <t>KH phản ánh chưa được KT bên CN liên hệ qua hỗ trợ KH_x000D_
 Yêu cầu quản lí điều kĩ thuật liên hệ và hỗ trợ KH</t>
         </is>
       </c>
@@ -72168,13 +72173,13 @@
       </c>
       <c r="Q410" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R410" t="inlineStr">
         <is>
-          <t>KH đã báo CN 
-KH phản ánh cục ATS bị đảo chiều ( nhảy qua nhảy lại giữa điện lưới và điện NLMT ) 
+          <t>KH đã báo CN _x000D_
+KH phản ánh cục ATS bị đảo chiều ( nhảy qua nhảy lại giữa điện lưới và điện NLMT ) _x000D_
 Yêu cầu quản lí điều kĩ thuật liên hệ và hỗ trợ KH</t>
         </is>
       </c>
@@ -72340,13 +72345,13 @@
       </c>
       <c r="Q411" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R411" t="inlineStr">
         <is>
-          <t>1. KH chưa báo CN
-2. hệ thống NLMT không phát ra điện, KH đã bị 2 ngày nay
+          <t>1. KH chưa báo CN_x000D_
+2. hệ thống NLMT không phát ra điện, KH đã bị 2 ngày nay_x000D_
 3. Yêu cầu CN hỗ trợ KH</t>
         </is>
       </c>
@@ -72512,7 +72517,7 @@
       </c>
       <c r="Q412" t="inlineStr">
         <is>
-          <t>Tư vấn sản phẩm/dịch vụ</t>
+          <t>Liên hệ/tư vấn</t>
         </is>
       </c>
       <c r="R412" t="inlineStr">
@@ -72682,13 +72687,13 @@
       </c>
       <c r="Q413" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R413" t="inlineStr">
         <is>
-          <t>KH chưa báo CN 
-KH phản ánh màn hình LED của KH bị hỏng không sử dụng được, KH không biết nguyên nhân tại sao
+          <t>KH chưa báo CN _x000D_
+KH phản ánh màn hình LED của KH bị hỏng không sử dụng được, KH không biết nguyên nhân tại sao_x000D_
 Yêu cầu CN liên hệ và hỗ trợ KH</t>
         </is>
       </c>
@@ -72859,13 +72864,13 @@
       </c>
       <c r="Q414" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R414" t="inlineStr">
         <is>
-          <t>1. KH đã liên hệ CN
-2. Ắc quy lưu trữ sạc đầy nhưng không xả, trên App theo dõi khi dùng tải nhà cao hơn hiệu suất của HT NLMT không thấy bù điện lưới 
+          <t>1. KH đã liên hệ CN_x000D_
+2. Ắc quy lưu trữ sạc đầy nhưng không xả, trên App theo dõi khi dùng tải nhà cao hơn hiệu suất của HT NLMT không thấy bù điện lưới _x000D_
 3. KH cần CN đến kiêm tra sớm</t>
         </is>
       </c>
@@ -73036,12 +73041,12 @@
       </c>
       <c r="Q415" t="inlineStr">
         <is>
-          <t>Tiến độ triển khai chậm</t>
+          <t>Tiến độ triển khai</t>
         </is>
       </c>
       <c r="R415" t="inlineStr">
         <is>
-          <t>KH đã báo CN 
+          <t>KH đã báo CN _x000D_
 Khách hàng đã ký hợp đồng làm tạm ứng đầy đủ nhưng đến hiện tại vẫn chưa thấy triển khai cho khách hàng</t>
         </is>
       </c>
@@ -73212,13 +73217,13 @@
       </c>
       <c r="Q416" t="inlineStr">
         <is>
-          <t>Tiến độ triển khai chậm</t>
+          <t>Tiến độ triển khai</t>
         </is>
       </c>
       <c r="R416" t="inlineStr">
         <is>
-          <t>KH đã báo CN 
-KH phản ánh hiện chưa được bên Cn liên hệ và hỗ trợ lắp đặt NLMT cho KH 
+          <t>KH đã báo CN _x000D_
+KH phản ánh hiện chưa được bên Cn liên hệ và hỗ trợ lắp đặt NLMT cho KH _x000D_
 Yêu cầu CN liên hệ và hỗ trợ KH</t>
         </is>
       </c>
@@ -73389,13 +73394,13 @@
       </c>
       <c r="Q417" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi sản phẩm/hệ thống</t>
         </is>
       </c>
       <c r="R417" t="inlineStr">
         <is>
-          <t>CN 0978852953 báo sự cố hộ KH 
-1. KH phản ánh: hệ nlmt ko hoạt động, CN đã báo hãng kiểm tra xác định lỗi CB
+          <t>CN 0978852953 báo sự cố hộ KH _x000D_
+1. KH phản ánh: hệ nlmt ko hoạt động, CN đã báo hãng kiểm tra xác định lỗi CB_x000D_
 2. KH yêu cầu: qua kiểm tra, xử lý khắc phục tình trạng này</t>
         </is>
       </c>
@@ -73561,12 +73566,12 @@
       </c>
       <c r="Q418" t="inlineStr">
         <is>
-          <t>Tiến độ triển khai chậm</t>
+          <t>Tiến độ triển khai</t>
         </is>
       </c>
       <c r="R418" t="inlineStr">
         <is>
-          <t>KH đã báo CN 
+          <t>KH đã báo CN _x000D_
 KH  đã ký hợp đồng và tạm ứng nhưng đến thời điểm hiện tại vẫn chưa thấy Viettel triển khai lắp đặt</t>
         </is>
       </c>

--- a/data/5.R_pakh_hoan_thanh.xlsx
+++ b/data/5.R_pakh_hoan_thanh.xlsx
@@ -721,7 +721,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI2">
@@ -898,7 +898,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Đăng</t>
         </is>
       </c>
       <c r="AI3">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Đăng</t>
         </is>
       </c>
       <c r="AI4">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI5">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI6">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI7">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Đăng</t>
         </is>
       </c>
       <c r="AI8">
@@ -1939,7 +1939,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI9">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI10">
@@ -2295,7 +2295,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI11">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI12">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Đăng</t>
         </is>
       </c>
       <c r="AI13">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Đăng</t>
         </is>
       </c>
       <c r="AI14">
@@ -2985,7 +2985,7 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI15">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI16">
@@ -3330,7 +3330,7 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI17">
@@ -3500,7 +3500,7 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI18">
@@ -3667,7 +3667,7 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI19">
@@ -3841,7 +3841,7 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Đăng</t>
         </is>
       </c>
       <c r="AI20">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI21">
@@ -4184,7 +4184,7 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI22">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI23">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI24">
@@ -4714,7 +4714,7 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI25">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI26">
@@ -5058,7 +5058,7 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI27">
@@ -5234,7 +5234,7 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI28">
@@ -5401,7 +5401,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Đăng</t>
         </is>
       </c>
       <c r="AI29">
@@ -5578,7 +5578,7 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI30">
@@ -5752,7 +5752,7 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI31">
@@ -5928,7 +5928,7 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI32">
@@ -6103,7 +6103,7 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Đăng</t>
         </is>
       </c>
       <c r="AI33">
@@ -6280,7 +6280,7 @@
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI34">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
+          <t>Đăng</t>
         </is>
       </c>
       <c r="AI35">
@@ -6627,7 +6627,7 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI36">
@@ -6797,7 +6797,7 @@
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI37">
@@ -6974,7 +6974,7 @@
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI38">
@@ -7151,7 +7151,7 @@
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI39">
@@ -7328,7 +7328,7 @@
       </c>
       <c r="AH40" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI40">
@@ -7505,7 +7505,7 @@
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI41">
@@ -7682,7 +7682,7 @@
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI42">
@@ -7852,7 +7852,7 @@
       </c>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI43">
@@ -8029,7 +8029,7 @@
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Đăng</t>
         </is>
       </c>
       <c r="AI44">
@@ -8206,7 +8206,7 @@
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI45">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI46">
@@ -8555,7 +8555,7 @@
       </c>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Đăng</t>
         </is>
       </c>
       <c r="AI47">
@@ -8731,7 +8731,7 @@
       </c>
       <c r="AH48" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI48">
@@ -8908,7 +8908,7 @@
       </c>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI49">
@@ -9085,7 +9085,7 @@
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI50">
@@ -9259,7 +9259,7 @@
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI51">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="AH52" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI52">
@@ -9607,7 +9607,7 @@
       </c>
       <c r="AH53" t="inlineStr">
         <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI53">
@@ -9774,7 +9774,7 @@
       </c>
       <c r="AH54" t="inlineStr">
         <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI54">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Đăng</t>
         </is>
       </c>
       <c r="AI55">
@@ -10116,7 +10116,7 @@
       </c>
       <c r="AH56" t="inlineStr">
         <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI56">
@@ -10293,7 +10293,7 @@
       </c>
       <c r="AH57" t="inlineStr">
         <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI57">
@@ -10470,7 +10470,7 @@
       </c>
       <c r="AH58" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI58">
@@ -10644,7 +10644,7 @@
       </c>
       <c r="AH59" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI59">
@@ -10821,7 +10821,7 @@
       </c>
       <c r="AH60" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Đăng</t>
         </is>
       </c>
       <c r="AI60">
@@ -10999,7 +10999,7 @@
       </c>
       <c r="AH61" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI61">
@@ -11176,7 +11176,7 @@
       </c>
       <c r="AH62" t="inlineStr">
         <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI62">
@@ -11348,7 +11348,7 @@
       </c>
       <c r="AH63" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI63">
@@ -11523,7 +11523,7 @@
       </c>
       <c r="AH64" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI64">
@@ -11698,7 +11698,7 @@
       </c>
       <c r="AH65" t="inlineStr">
         <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI65">
@@ -11867,7 +11867,7 @@
       </c>
       <c r="AH66" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI66">
@@ -12042,7 +12042,7 @@
       </c>
       <c r="AH67" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI67">
@@ -12219,7 +12219,7 @@
       </c>
       <c r="AH68" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI68">
@@ -12389,7 +12389,7 @@
       </c>
       <c r="AH69" t="inlineStr">
         <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI69">
@@ -12563,7 +12563,7 @@
       </c>
       <c r="AH70" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI70">
@@ -12737,7 +12737,7 @@
       </c>
       <c r="AH71" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI71">
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AH72" t="inlineStr">
         <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI72">
@@ -13091,7 +13091,7 @@
       </c>
       <c r="AH73" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI73">
@@ -13268,7 +13268,7 @@
       </c>
       <c r="AH74" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI74">
@@ -13446,7 +13446,7 @@
       </c>
       <c r="AH75" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI75">
@@ -13623,7 +13623,7 @@
       </c>
       <c r="AH76" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI76">
@@ -13801,7 +13801,7 @@
       </c>
       <c r="AH77" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI77">
@@ -13976,7 +13976,7 @@
       </c>
       <c r="AH78" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Đăng</t>
         </is>
       </c>
       <c r="AI78">
@@ -14153,7 +14153,7 @@
       </c>
       <c r="AH79" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI79">
@@ -14330,7 +14330,7 @@
       </c>
       <c r="AH80" t="inlineStr">
         <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI80">
@@ -14507,7 +14507,7 @@
       </c>
       <c r="AH81" t="inlineStr">
         <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI81">
@@ -14684,7 +14684,7 @@
       </c>
       <c r="AH82" t="inlineStr">
         <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI82">
@@ -14860,7 +14860,7 @@
       </c>
       <c r="AH83" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI83">
@@ -15036,7 +15036,7 @@
       </c>
       <c r="AH84" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI84">
@@ -15213,7 +15213,7 @@
       </c>
       <c r="AH85" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI85">
@@ -15382,7 +15382,7 @@
       </c>
       <c r="AH86" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI86">
@@ -15559,7 +15559,7 @@
       </c>
       <c r="AH87" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI87">
@@ -15736,7 +15736,7 @@
       </c>
       <c r="AH88" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI88">
@@ -15906,7 +15906,7 @@
       </c>
       <c r="AH89" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI89">
@@ -16077,7 +16077,7 @@
       </c>
       <c r="AH90" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI90">
@@ -16254,7 +16254,7 @@
       </c>
       <c r="AH91" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Đăng</t>
         </is>
       </c>
       <c r="AI91">
@@ -16431,7 +16431,7 @@
       </c>
       <c r="AH92" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI92">
@@ -16608,7 +16608,7 @@
       </c>
       <c r="AH93" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI93">
@@ -16785,7 +16785,7 @@
       </c>
       <c r="AH94" t="inlineStr">
         <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI94">
@@ -16960,7 +16960,7 @@
       </c>
       <c r="AH95" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI95">
@@ -17136,7 +17136,7 @@
       </c>
       <c r="AH96" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI96">
@@ -17313,7 +17313,7 @@
       </c>
       <c r="AH97" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI97">
@@ -17488,7 +17488,7 @@
       </c>
       <c r="AH98" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI98">
@@ -17665,7 +17665,7 @@
       </c>
       <c r="AH99" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI99">
@@ -17835,7 +17835,7 @@
       </c>
       <c r="AH100" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đăng</t>
         </is>
       </c>
       <c r="AI100">
@@ -18009,7 +18009,7 @@
       </c>
       <c r="AH101" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI101">
@@ -18179,7 +18179,7 @@
       </c>
       <c r="AH102" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI102">
@@ -18356,7 +18356,7 @@
       </c>
       <c r="AH103" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI103">
@@ -18533,7 +18533,7 @@
       </c>
       <c r="AH104" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI104">
@@ -18708,7 +18708,7 @@
       </c>
       <c r="AH105" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI105">
@@ -18885,7 +18885,7 @@
       </c>
       <c r="AH106" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đăng</t>
         </is>
       </c>
       <c r="AI106">
@@ -19055,7 +19055,7 @@
       </c>
       <c r="AH107" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI107">
@@ -19232,7 +19232,7 @@
       </c>
       <c r="AH108" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI108">
@@ -19409,7 +19409,7 @@
       </c>
       <c r="AH109" t="inlineStr">
         <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI109">
@@ -19581,7 +19581,7 @@
       </c>
       <c r="AH110" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI110">
@@ -19758,7 +19758,7 @@
       </c>
       <c r="AH111" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Đăng</t>
         </is>
       </c>
       <c r="AI111">
@@ -19933,7 +19933,7 @@
       </c>
       <c r="AH112" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI112">
@@ -20110,7 +20110,7 @@
       </c>
       <c r="AH113" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI113">
@@ -20280,7 +20280,7 @@
       </c>
       <c r="AH114" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI114">
@@ -20457,7 +20457,7 @@
       </c>
       <c r="AH115" t="inlineStr">
         <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI115">
@@ -20631,7 +20631,7 @@
       </c>
       <c r="AH116" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Đăng</t>
         </is>
       </c>
       <c r="AI116">
@@ -20808,7 +20808,7 @@
       </c>
       <c r="AH117" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI117">
@@ -20979,7 +20979,7 @@
       </c>
       <c r="AH118" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI118">
@@ -21155,7 +21155,7 @@
       </c>
       <c r="AH119" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI119">
@@ -21332,7 +21332,7 @@
       </c>
       <c r="AH120" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI120">
@@ -21509,7 +21509,7 @@
       </c>
       <c r="AH121" t="inlineStr">
         <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI121">
@@ -21683,7 +21683,7 @@
       </c>
       <c r="AH122" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI122">
@@ -21860,7 +21860,7 @@
       </c>
       <c r="AH123" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI123">
@@ -22034,7 +22034,7 @@
       </c>
       <c r="AH124" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI124">
@@ -22206,7 +22206,7 @@
       </c>
       <c r="AH125" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI125">
@@ -22383,7 +22383,7 @@
       </c>
       <c r="AH126" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Đăng</t>
         </is>
       </c>
       <c r="AI126">
@@ -22553,7 +22553,7 @@
       </c>
       <c r="AH127" t="inlineStr">
         <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI127">
@@ -22730,7 +22730,7 @@
       </c>
       <c r="AH128" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI128">
@@ -22907,7 +22907,7 @@
       </c>
       <c r="AH129" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI129">
@@ -23084,7 +23084,7 @@
       </c>
       <c r="AH130" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI130">
@@ -23261,7 +23261,7 @@
       </c>
       <c r="AH131" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI131">
@@ -23431,7 +23431,7 @@
       </c>
       <c r="AH132" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI132">
@@ -23608,7 +23608,7 @@
       </c>
       <c r="AH133" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI133">
@@ -23785,7 +23785,7 @@
       </c>
       <c r="AH134" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI134">
@@ -23957,7 +23957,7 @@
       </c>
       <c r="AH135" t="inlineStr">
         <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
+          <t>Đăng</t>
         </is>
       </c>
       <c r="AI135">
@@ -24134,7 +24134,7 @@
       </c>
       <c r="AH136" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI136">
@@ -24312,7 +24312,7 @@
       </c>
       <c r="AH137" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI137">
@@ -24489,7 +24489,7 @@
       </c>
       <c r="AH138" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI138">
@@ -24666,7 +24666,7 @@
       </c>
       <c r="AH139" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI139">
@@ -24836,7 +24836,7 @@
       </c>
       <c r="AH140" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI140">
@@ -25011,7 +25011,7 @@
       </c>
       <c r="AH141" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI141">
@@ -25183,7 +25183,7 @@
       </c>
       <c r="AH142" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI142">
@@ -25355,7 +25355,7 @@
       </c>
       <c r="AH143" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Đăng</t>
         </is>
       </c>
       <c r="AI143">
@@ -25527,7 +25527,7 @@
       </c>
       <c r="AH144" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI144">
@@ -25704,7 +25704,7 @@
       </c>
       <c r="AH145" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI145">
@@ -25881,7 +25881,7 @@
       </c>
       <c r="AH146" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đăng</t>
         </is>
       </c>
       <c r="AI146">
@@ -26058,7 +26058,7 @@
       </c>
       <c r="AH147" t="inlineStr">
         <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI147">
@@ -26235,7 +26235,7 @@
       </c>
       <c r="AH148" t="inlineStr">
         <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI148">
@@ -26412,7 +26412,7 @@
       </c>
       <c r="AH149" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI149">
@@ -26589,7 +26589,7 @@
       </c>
       <c r="AH150" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Đăng</t>
         </is>
       </c>
       <c r="AI150">
@@ -26766,7 +26766,7 @@
       </c>
       <c r="AH151" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI151">
@@ -26943,7 +26943,7 @@
       </c>
       <c r="AH152" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI152">
@@ -27120,7 +27120,7 @@
       </c>
       <c r="AH153" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI153">
@@ -27295,7 +27295,7 @@
       </c>
       <c r="AH154" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI154">
@@ -27465,7 +27465,7 @@
       </c>
       <c r="AH155" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI155">
@@ -27635,7 +27635,7 @@
       </c>
       <c r="AH156" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đăng</t>
         </is>
       </c>
       <c r="AI156">
@@ -27805,7 +27805,7 @@
       </c>
       <c r="AH157" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI157">
@@ -27982,7 +27982,7 @@
       </c>
       <c r="AH158" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI158">
@@ -28152,7 +28152,7 @@
       </c>
       <c r="AH159" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI159">
@@ -28323,7 +28323,7 @@
       </c>
       <c r="AH160" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI160">
@@ -28493,7 +28493,7 @@
       </c>
       <c r="AH161" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI161">
@@ -28667,7 +28667,7 @@
       </c>
       <c r="AH162" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI162">
@@ -28842,7 +28842,7 @@
       </c>
       <c r="AH163" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI163">
@@ -29017,7 +29017,7 @@
       </c>
       <c r="AH164" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI164">
@@ -29187,7 +29187,7 @@
       </c>
       <c r="AH165" t="inlineStr">
         <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI165">
@@ -29357,7 +29357,7 @@
       </c>
       <c r="AH166" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Đăng</t>
         </is>
       </c>
       <c r="AI166">
@@ -29529,7 +29529,7 @@
       </c>
       <c r="AH167" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI167">
@@ -29703,7 +29703,7 @@
       </c>
       <c r="AH168" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đăng</t>
         </is>
       </c>
       <c r="AI168">
@@ -29880,7 +29880,7 @@
       </c>
       <c r="AH169" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI169">
@@ -30057,7 +30057,7 @@
       </c>
       <c r="AH170" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Đăng</t>
         </is>
       </c>
       <c r="AI170">
@@ -30234,7 +30234,7 @@
       </c>
       <c r="AH171" t="inlineStr">
         <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI171">
@@ -30409,7 +30409,7 @@
       </c>
       <c r="AH172" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI172">
@@ -30586,7 +30586,7 @@
       </c>
       <c r="AH173" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI173">
@@ -30764,7 +30764,7 @@
       </c>
       <c r="AH174" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI174">
@@ -30941,7 +30941,7 @@
       </c>
       <c r="AH175" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI175">
@@ -31118,7 +31118,7 @@
       </c>
       <c r="AH176" t="inlineStr">
         <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI176">
@@ -31288,7 +31288,7 @@
       </c>
       <c r="AH177" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI177">
@@ -31463,7 +31463,7 @@
       </c>
       <c r="AH178" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI178">
@@ -31633,7 +31633,7 @@
       </c>
       <c r="AH179" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI179">
@@ -31803,7 +31803,7 @@
       </c>
       <c r="AH180" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Đăng</t>
         </is>
       </c>
       <c r="AI180">
@@ -31980,7 +31980,7 @@
       </c>
       <c r="AH181" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI181">
@@ -32150,7 +32150,7 @@
       </c>
       <c r="AH182" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI182">
@@ -32320,7 +32320,7 @@
       </c>
       <c r="AH183" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI183">
@@ -32490,7 +32490,7 @@
       </c>
       <c r="AH184" t="inlineStr">
         <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI184">
@@ -32667,7 +32667,7 @@
       </c>
       <c r="AH185" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI185">
@@ -32842,7 +32842,7 @@
       </c>
       <c r="AH186" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI186">
@@ -33012,7 +33012,7 @@
       </c>
       <c r="AH187" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI187">
@@ -33186,7 +33186,7 @@
       </c>
       <c r="AH188" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI188">
@@ -33361,7 +33361,7 @@
       </c>
       <c r="AH189" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI189">
@@ -33539,7 +33539,7 @@
       </c>
       <c r="AH190" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI190">
@@ -33714,7 +33714,7 @@
       </c>
       <c r="AH191" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI191">
@@ -33891,7 +33891,7 @@
       </c>
       <c r="AH192" t="inlineStr">
         <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI192">
@@ -34061,7 +34061,7 @@
       </c>
       <c r="AH193" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI193">
@@ -34238,7 +34238,7 @@
       </c>
       <c r="AH194" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI194">
@@ -34415,7 +34415,7 @@
       </c>
       <c r="AH195" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI195">
@@ -34587,7 +34587,7 @@
       </c>
       <c r="AH196" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI196">
@@ -34764,7 +34764,7 @@
       </c>
       <c r="AH197" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI197">
@@ -34941,7 +34941,7 @@
       </c>
       <c r="AH198" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI198">
@@ -35118,7 +35118,7 @@
       </c>
       <c r="AH199" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI199">
@@ -35288,7 +35288,7 @@
       </c>
       <c r="AH200" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI200">
@@ -35465,7 +35465,7 @@
       </c>
       <c r="AH201" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI201">
@@ -35642,7 +35642,7 @@
       </c>
       <c r="AH202" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI202">
@@ -35817,7 +35817,7 @@
       </c>
       <c r="AH203" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI203">
@@ -35994,7 +35994,7 @@
       </c>
       <c r="AH204" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI204">
@@ -36171,7 +36171,7 @@
       </c>
       <c r="AH205" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI205">
@@ -36348,7 +36348,7 @@
       </c>
       <c r="AH206" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Đăng</t>
         </is>
       </c>
       <c r="AI206">
@@ -36525,7 +36525,7 @@
       </c>
       <c r="AH207" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI207">
@@ -36700,7 +36700,7 @@
       </c>
       <c r="AH208" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI208">
@@ -36877,7 +36877,7 @@
       </c>
       <c r="AH209" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Đăng</t>
         </is>
       </c>
       <c r="AI209">
@@ -37047,7 +37047,7 @@
       </c>
       <c r="AH210" t="inlineStr">
         <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI210">
@@ -37224,7 +37224,7 @@
       </c>
       <c r="AH211" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI211">
@@ -37401,7 +37401,7 @@
       </c>
       <c r="AH212" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI212">
@@ -37573,7 +37573,7 @@
       </c>
       <c r="AH213" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI213">
@@ -37750,7 +37750,7 @@
       </c>
       <c r="AH214" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI214">
@@ -37927,7 +37927,7 @@
       </c>
       <c r="AH215" t="inlineStr">
         <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI215">
@@ -38104,7 +38104,7 @@
       </c>
       <c r="AH216" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI216">
@@ -38281,7 +38281,7 @@
       </c>
       <c r="AH217" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI217">
@@ -38458,7 +38458,7 @@
       </c>
       <c r="AH218" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI218">
@@ -38628,7 +38628,7 @@
       </c>
       <c r="AH219" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI219">
@@ -38805,7 +38805,7 @@
       </c>
       <c r="AH220" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Đăng</t>
         </is>
       </c>
       <c r="AI220">
@@ -38982,7 +38982,7 @@
       </c>
       <c r="AH221" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI221">
@@ -39154,7 +39154,7 @@
       </c>
       <c r="AH222" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI222">
@@ -39331,7 +39331,7 @@
       </c>
       <c r="AH223" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đăng</t>
         </is>
       </c>
       <c r="AI223">
@@ -39508,7 +39508,7 @@
       </c>
       <c r="AH224" t="inlineStr">
         <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI224">
@@ -39685,7 +39685,7 @@
       </c>
       <c r="AH225" t="inlineStr">
         <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI225">
@@ -39856,7 +39856,7 @@
       </c>
       <c r="AH226" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI226">
@@ -40033,7 +40033,7 @@
       </c>
       <c r="AH227" t="inlineStr">
         <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI227">
@@ -40208,7 +40208,7 @@
       </c>
       <c r="AH228" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI228">
@@ -40378,7 +40378,7 @@
       </c>
       <c r="AH229" t="inlineStr">
         <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI229">
@@ -40555,7 +40555,7 @@
       </c>
       <c r="AH230" t="inlineStr">
         <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI230">
@@ -40727,7 +40727,7 @@
       </c>
       <c r="AH231" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI231">
@@ -40904,7 +40904,7 @@
       </c>
       <c r="AH232" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI232">
@@ -41081,7 +41081,7 @@
       </c>
       <c r="AH233" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI233">
@@ -41258,7 +41258,7 @@
       </c>
       <c r="AH234" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI234">
@@ -41435,7 +41435,7 @@
       </c>
       <c r="AH235" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI235">
@@ -41610,7 +41610,7 @@
       </c>
       <c r="AH236" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI236">
@@ -41785,7 +41785,7 @@
       </c>
       <c r="AH237" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI237">
@@ -41961,7 +41961,7 @@
       </c>
       <c r="AH238" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI238">
@@ -42138,7 +42138,7 @@
       </c>
       <c r="AH239" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI239">
@@ -42310,7 +42310,7 @@
       </c>
       <c r="AH240" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI240">
@@ -42487,7 +42487,7 @@
       </c>
       <c r="AH241" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI241">
@@ -42664,7 +42664,7 @@
       </c>
       <c r="AH242" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Đăng</t>
         </is>
       </c>
       <c r="AI242">
@@ -42841,7 +42841,7 @@
       </c>
       <c r="AH243" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI243">
@@ -43018,7 +43018,7 @@
       </c>
       <c r="AH244" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Đăng</t>
         </is>
       </c>
       <c r="AI244">
@@ -43195,7 +43195,7 @@
       </c>
       <c r="AH245" t="inlineStr">
         <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI245">
@@ -43367,7 +43367,7 @@
       </c>
       <c r="AH246" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Đăng</t>
         </is>
       </c>
       <c r="AI246">
@@ -43544,7 +43544,7 @@
       </c>
       <c r="AH247" t="inlineStr">
         <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI247">
@@ -43714,7 +43714,7 @@
       </c>
       <c r="AH248" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI248">
@@ -43891,7 +43891,7 @@
       </c>
       <c r="AH249" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI249">
@@ -44061,7 +44061,7 @@
       </c>
       <c r="AH250" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI250">
@@ -44233,7 +44233,7 @@
       </c>
       <c r="AH251" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Đăng</t>
         </is>
       </c>
       <c r="AI251">
@@ -44408,7 +44408,7 @@
       </c>
       <c r="AH252" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI252">
@@ -44584,7 +44584,7 @@
       </c>
       <c r="AH253" t="inlineStr">
         <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI253">
@@ -44761,7 +44761,7 @@
       </c>
       <c r="AH254" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI254">
@@ -44933,7 +44933,7 @@
       </c>
       <c r="AH255" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI255">
@@ -45110,7 +45110,7 @@
       </c>
       <c r="AH256" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI256">
@@ -45287,7 +45287,7 @@
       </c>
       <c r="AH257" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI257">
@@ -45466,7 +45466,7 @@
       </c>
       <c r="AH258" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI258">
@@ -45643,7 +45643,7 @@
       </c>
       <c r="AH259" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI259">
@@ -45820,7 +45820,7 @@
       </c>
       <c r="AH260" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI260">
@@ -45997,7 +45997,7 @@
       </c>
       <c r="AH261" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI261">
@@ -46174,7 +46174,7 @@
       </c>
       <c r="AH262" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI262">
@@ -46351,7 +46351,7 @@
       </c>
       <c r="AH263" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI263">
@@ -46523,7 +46523,7 @@
       </c>
       <c r="AH264" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI264">
@@ -46700,7 +46700,7 @@
       </c>
       <c r="AH265" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI265">
@@ -46877,7 +46877,7 @@
       </c>
       <c r="AH266" t="inlineStr">
         <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
+          <t>Đăng</t>
         </is>
       </c>
       <c r="AI266">
@@ -47052,7 +47052,7 @@
       </c>
       <c r="AH267" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI267">
@@ -47229,7 +47229,7 @@
       </c>
       <c r="AH268" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI268">
@@ -47406,7 +47406,7 @@
       </c>
       <c r="AH269" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI269">
@@ -47583,7 +47583,7 @@
       </c>
       <c r="AH270" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI270">
@@ -47758,7 +47758,7 @@
       </c>
       <c r="AH271" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI271">
@@ -47934,7 +47934,7 @@
       </c>
       <c r="AH272" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI272">
@@ -48107,7 +48107,7 @@
       </c>
       <c r="AH273" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI273">
@@ -48285,7 +48285,7 @@
       </c>
       <c r="AH274" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Đăng</t>
         </is>
       </c>
       <c r="AI274">
@@ -48462,7 +48462,7 @@
       </c>
       <c r="AH275" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI275">
@@ -48639,7 +48639,7 @@
       </c>
       <c r="AH276" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI276">
@@ -48814,7 +48814,7 @@
       </c>
       <c r="AH277" t="inlineStr">
         <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI277">
@@ -48991,7 +48991,7 @@
       </c>
       <c r="AH278" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI278">
@@ -49168,7 +49168,7 @@
       </c>
       <c r="AH279" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI279">
@@ -49338,7 +49338,7 @@
       </c>
       <c r="AH280" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI280">
@@ -49510,7 +49510,7 @@
       </c>
       <c r="AH281" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI281">
@@ -49685,7 +49685,7 @@
       </c>
       <c r="AH282" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI282">
@@ -49862,7 +49862,7 @@
       </c>
       <c r="AH283" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI283">
@@ -50037,7 +50037,7 @@
       </c>
       <c r="AH284" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI284">
@@ -50214,7 +50214,7 @@
       </c>
       <c r="AH285" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI285">
@@ -50391,7 +50391,7 @@
       </c>
       <c r="AH286" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI286">
@@ -50566,7 +50566,7 @@
       </c>
       <c r="AH287" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI287">
@@ -50738,7 +50738,7 @@
       </c>
       <c r="AH288" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI288">
@@ -50913,7 +50913,7 @@
       </c>
       <c r="AH289" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI289">
@@ -51090,7 +51090,7 @@
       </c>
       <c r="AH290" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI290">
@@ -51265,7 +51265,7 @@
       </c>
       <c r="AH291" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI291">
@@ -51442,7 +51442,7 @@
       </c>
       <c r="AH292" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI292">
@@ -51619,7 +51619,7 @@
       </c>
       <c r="AH293" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI293">
@@ -51794,7 +51794,7 @@
       </c>
       <c r="AH294" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI294">
@@ -51969,7 +51969,7 @@
       </c>
       <c r="AH295" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI295">
@@ -52146,7 +52146,7 @@
       </c>
       <c r="AH296" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI296">
@@ -52323,7 +52323,7 @@
       </c>
       <c r="AH297" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI297">
@@ -52500,7 +52500,7 @@
       </c>
       <c r="AH298" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI298">
@@ -52677,7 +52677,7 @@
       </c>
       <c r="AH299" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI299">
@@ -52847,7 +52847,7 @@
       </c>
       <c r="AH300" t="inlineStr">
         <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI300">
@@ -53024,7 +53024,7 @@
       </c>
       <c r="AH301" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI301">
@@ -53196,7 +53196,7 @@
       </c>
       <c r="AH302" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI302">
@@ -53368,7 +53368,7 @@
       </c>
       <c r="AH303" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI303">
@@ -53545,7 +53545,7 @@
       </c>
       <c r="AH304" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI304">
@@ -53722,7 +53722,7 @@
       </c>
       <c r="AH305" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI305">
@@ -53899,7 +53899,7 @@
       </c>
       <c r="AH306" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI306">
@@ -54074,7 +54074,7 @@
       </c>
       <c r="AH307" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI307">
@@ -54251,7 +54251,7 @@
       </c>
       <c r="AH308" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI308">
@@ -54428,7 +54428,7 @@
       </c>
       <c r="AH309" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI309">
@@ -54598,7 +54598,7 @@
       </c>
       <c r="AH310" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI310">
@@ -54775,7 +54775,7 @@
       </c>
       <c r="AH311" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI311">
@@ -54950,7 +54950,7 @@
       </c>
       <c r="AH312" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI312">
@@ -55127,7 +55127,7 @@
       </c>
       <c r="AH313" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI313">
@@ -55304,7 +55304,7 @@
       </c>
       <c r="AH314" t="inlineStr">
         <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI314">
@@ -55479,7 +55479,7 @@
       </c>
       <c r="AH315" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI315">
@@ -55656,7 +55656,7 @@
       </c>
       <c r="AH316" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI316">
@@ -55833,7 +55833,7 @@
       </c>
       <c r="AH317" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI317">
@@ -56010,7 +56010,7 @@
       </c>
       <c r="AH318" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI318">
@@ -56187,7 +56187,7 @@
       </c>
       <c r="AH319" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI319">
@@ -56364,7 +56364,7 @@
       </c>
       <c r="AH320" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI320">
@@ -56534,7 +56534,7 @@
       </c>
       <c r="AH321" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI321">
@@ -56709,7 +56709,7 @@
       </c>
       <c r="AH322" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI322">
@@ -56886,7 +56886,7 @@
       </c>
       <c r="AH323" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI323">
@@ -57063,7 +57063,7 @@
       </c>
       <c r="AH324" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI324">
@@ -57238,7 +57238,7 @@
       </c>
       <c r="AH325" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI325">
@@ -57415,7 +57415,7 @@
       </c>
       <c r="AH326" t="inlineStr">
         <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI326">
@@ -57592,7 +57592,7 @@
       </c>
       <c r="AH327" t="inlineStr">
         <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI327">
@@ -57762,7 +57762,7 @@
       </c>
       <c r="AH328" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI328">
@@ -57939,7 +57939,7 @@
       </c>
       <c r="AH329" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đăng</t>
         </is>
       </c>
       <c r="AI329">
@@ -58116,7 +58116,7 @@
       </c>
       <c r="AH330" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Đăng</t>
         </is>
       </c>
       <c r="AI330">
@@ -58293,7 +58293,7 @@
       </c>
       <c r="AH331" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI331">
@@ -58465,7 +58465,7 @@
       </c>
       <c r="AH332" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI332">
@@ -58642,7 +58642,7 @@
       </c>
       <c r="AH333" t="inlineStr">
         <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI333">
@@ -58820,7 +58820,7 @@
       </c>
       <c r="AH334" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Đăng</t>
         </is>
       </c>
       <c r="AI334">
@@ -58997,7 +58997,7 @@
       </c>
       <c r="AH335" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI335">
@@ -59174,7 +59174,7 @@
       </c>
       <c r="AH336" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI336">
@@ -59351,7 +59351,7 @@
       </c>
       <c r="AH337" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Đăng</t>
         </is>
       </c>
       <c r="AI337">
@@ -59528,7 +59528,7 @@
       </c>
       <c r="AH338" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI338">
@@ -59705,7 +59705,7 @@
       </c>
       <c r="AH339" t="inlineStr">
         <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI339">
@@ -59882,7 +59882,7 @@
       </c>
       <c r="AH340" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI340">
@@ -60055,7 +60055,7 @@
       </c>
       <c r="AH341" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI341">
@@ -60225,7 +60225,7 @@
       </c>
       <c r="AH342" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI342">
@@ -60402,7 +60402,7 @@
       </c>
       <c r="AH343" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Đăng</t>
         </is>
       </c>
       <c r="AI343">
@@ -60577,7 +60577,7 @@
       </c>
       <c r="AH344" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI344">
@@ -60747,7 +60747,7 @@
       </c>
       <c r="AH345" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI345">
@@ -60923,7 +60923,7 @@
       </c>
       <c r="AH346" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI346">
@@ -61099,7 +61099,7 @@
       </c>
       <c r="AH347" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI347">
@@ -61276,7 +61276,7 @@
       </c>
       <c r="AH348" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI348">
@@ -61452,7 +61452,7 @@
       </c>
       <c r="AH349" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI349">
@@ -61629,7 +61629,7 @@
       </c>
       <c r="AH350" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI350">
@@ -61806,7 +61806,7 @@
       </c>
       <c r="AH351" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI351">
@@ -61978,7 +61978,7 @@
       </c>
       <c r="AH352" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Đăng</t>
         </is>
       </c>
       <c r="AI352">
@@ -62155,7 +62155,7 @@
       </c>
       <c r="AH353" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Đăng</t>
         </is>
       </c>
       <c r="AI353">
@@ -62330,7 +62330,7 @@
       </c>
       <c r="AH354" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đăng</t>
         </is>
       </c>
       <c r="AI354">
@@ -62507,7 +62507,7 @@
       </c>
       <c r="AH355" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đăng</t>
         </is>
       </c>
       <c r="AI355">
@@ -62684,7 +62684,7 @@
       </c>
       <c r="AH356" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI356">
@@ -62860,7 +62860,7 @@
       </c>
       <c r="AH357" t="inlineStr">
         <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI357">
@@ -63037,7 +63037,7 @@
       </c>
       <c r="AH358" t="inlineStr">
         <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI358">
@@ -63209,7 +63209,7 @@
       </c>
       <c r="AH359" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI359">
@@ -63386,7 +63386,7 @@
       </c>
       <c r="AH360" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Đăng</t>
         </is>
       </c>
       <c r="AI360">
@@ -63563,7 +63563,7 @@
       </c>
       <c r="AH361" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI361">
@@ -63740,7 +63740,7 @@
       </c>
       <c r="AH362" t="inlineStr">
         <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI362">
@@ -63917,7 +63917,7 @@
       </c>
       <c r="AH363" t="inlineStr">
         <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI363">
@@ -64087,7 +64087,7 @@
       </c>
       <c r="AH364" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI364">
@@ -64264,7 +64264,7 @@
       </c>
       <c r="AH365" t="inlineStr">
         <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI365">
@@ -64441,7 +64441,7 @@
       </c>
       <c r="AH366" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI366">
@@ -64618,7 +64618,7 @@
       </c>
       <c r="AH367" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI367">
@@ -64795,7 +64795,7 @@
       </c>
       <c r="AH368" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI368">
@@ -64970,7 +64970,7 @@
       </c>
       <c r="AH369" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI369">
@@ -65147,7 +65147,7 @@
       </c>
       <c r="AH370" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI370">
@@ -65324,7 +65324,7 @@
       </c>
       <c r="AH371" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI371">
@@ -65501,7 +65501,7 @@
       </c>
       <c r="AH372" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI372">
@@ -65678,7 +65678,7 @@
       </c>
       <c r="AH373" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI373">
@@ -65855,7 +65855,7 @@
       </c>
       <c r="AH374" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI374">
@@ -66032,7 +66032,7 @@
       </c>
       <c r="AH375" t="inlineStr">
         <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI375">
@@ -66202,7 +66202,7 @@
       </c>
       <c r="AH376" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI376">
@@ -66379,7 +66379,7 @@
       </c>
       <c r="AH377" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI377">
@@ -66556,7 +66556,7 @@
       </c>
       <c r="AH378" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI378">
@@ -66731,7 +66731,7 @@
       </c>
       <c r="AH379" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI379">
@@ -66908,7 +66908,7 @@
       </c>
       <c r="AH380" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI380">
@@ -67080,7 +67080,7 @@
       </c>
       <c r="AH381" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI381">
@@ -67251,7 +67251,7 @@
       </c>
       <c r="AH382" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI382">
@@ -67421,7 +67421,7 @@
       </c>
       <c r="AH383" t="inlineStr">
         <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI383">
@@ -67591,7 +67591,7 @@
       </c>
       <c r="AH384" t="inlineStr">
         <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI384">
@@ -67768,7 +67768,7 @@
       </c>
       <c r="AH385" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đăng</t>
         </is>
       </c>
       <c r="AI385">
@@ -67945,7 +67945,7 @@
       </c>
       <c r="AH386" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI386">
@@ -68120,7 +68120,7 @@
       </c>
       <c r="AH387" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI387">
@@ -68297,7 +68297,7 @@
       </c>
       <c r="AH388" t="inlineStr">
         <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI388">
@@ -68469,7 +68469,7 @@
       </c>
       <c r="AH389" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Đăng</t>
         </is>
       </c>
       <c r="AI389">
@@ -68639,7 +68639,7 @@
       </c>
       <c r="AH390" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI390">
@@ -68814,7 +68814,7 @@
       </c>
       <c r="AH391" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI391">
@@ -68992,7 +68992,7 @@
       </c>
       <c r="AH392" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Đăng</t>
         </is>
       </c>
       <c r="AI392">
@@ -69169,7 +69169,7 @@
       </c>
       <c r="AH393" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI393">
@@ -69346,7 +69346,7 @@
       </c>
       <c r="AH394" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI394">
@@ -69523,7 +69523,7 @@
       </c>
       <c r="AH395" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI395">
@@ -69700,7 +69700,7 @@
       </c>
       <c r="AH396" t="inlineStr">
         <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI396">
@@ -69875,7 +69875,7 @@
       </c>
       <c r="AH397" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI397">
@@ -70044,7 +70044,7 @@
       </c>
       <c r="AH398" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI398">
@@ -70221,7 +70221,7 @@
       </c>
       <c r="AH399" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI399">
@@ -70396,7 +70396,7 @@
       </c>
       <c r="AH400" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI400">
@@ -70568,7 +70568,7 @@
       </c>
       <c r="AH401" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI401">
@@ -70745,7 +70745,7 @@
       </c>
       <c r="AH402" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI402">
@@ -70922,7 +70922,7 @@
       </c>
       <c r="AH403" t="inlineStr">
         <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI403">
@@ -71099,7 +71099,7 @@
       </c>
       <c r="AH404" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI404">
@@ -71276,7 +71276,7 @@
       </c>
       <c r="AH405" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI405">
@@ -71453,7 +71453,7 @@
       </c>
       <c r="AH406" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI406">
@@ -71628,7 +71628,7 @@
       </c>
       <c r="AH407" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI407">
@@ -71807,7 +71807,7 @@
       </c>
       <c r="AH408" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI408">
@@ -71977,7 +71977,7 @@
       </c>
       <c r="AH409" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI409">
@@ -72147,7 +72147,7 @@
       </c>
       <c r="AH410" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Đăng</t>
         </is>
       </c>
       <c r="AI410">
@@ -72319,7 +72319,7 @@
       </c>
       <c r="AH411" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI411">
@@ -72489,7 +72489,7 @@
       </c>
       <c r="AH412" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI412">
@@ -72664,7 +72664,7 @@
       </c>
       <c r="AH413" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI413">
@@ -72841,7 +72841,7 @@
       </c>
       <c r="AH414" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI414">
@@ -73011,7 +73011,7 @@
       </c>
       <c r="AH415" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI415">
@@ -73188,7 +73188,7 @@
       </c>
       <c r="AH416" t="inlineStr">
         <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI416">
@@ -73360,7 +73360,7 @@
       </c>
       <c r="AH417" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI417">
@@ -73537,7 +73537,7 @@
       </c>
       <c r="AH418" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI418">
@@ -73712,7 +73712,7 @@
       </c>
       <c r="AH419" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI419">
@@ -73889,7 +73889,7 @@
       </c>
       <c r="AH420" t="inlineStr">
         <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI420">
@@ -74066,7 +74066,7 @@
       </c>
       <c r="AH421" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI421">
@@ -74243,7 +74243,7 @@
       </c>
       <c r="AH422" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Đăng</t>
         </is>
       </c>
       <c r="AI422">
@@ -74421,7 +74421,7 @@
       </c>
       <c r="AH423" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI423">
@@ -74598,7 +74598,7 @@
       </c>
       <c r="AH424" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI424">
@@ -74773,7 +74773,7 @@
       </c>
       <c r="AH425" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI425">
@@ -74950,7 +74950,7 @@
       </c>
       <c r="AH426" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI426">
@@ -75120,7 +75120,7 @@
       </c>
       <c r="AH427" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đăng</t>
         </is>
       </c>
       <c r="AI427">
@@ -75297,7 +75297,7 @@
       </c>
       <c r="AH428" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI428">
@@ -75467,7 +75467,7 @@
       </c>
       <c r="AH429" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI429">
@@ -75637,7 +75637,7 @@
       </c>
       <c r="AH430" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI430">
@@ -75814,7 +75814,7 @@
       </c>
       <c r="AH431" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI431">
@@ -75991,7 +75991,7 @@
       </c>
       <c r="AH432" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI432">
@@ -76168,7 +76168,7 @@
       </c>
       <c r="AH433" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đăng</t>
         </is>
       </c>
       <c r="AI433">
@@ -76345,7 +76345,7 @@
       </c>
       <c r="AH434" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI434">
@@ -76517,7 +76517,7 @@
       </c>
       <c r="AH435" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI435">
@@ -76691,7 +76691,7 @@
       </c>
       <c r="AH436" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI436">
@@ -76863,7 +76863,7 @@
       </c>
       <c r="AH437" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Đăng</t>
         </is>
       </c>
       <c r="AI437">
@@ -77040,7 +77040,7 @@
       </c>
       <c r="AH438" t="inlineStr">
         <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI438">
@@ -77215,7 +77215,7 @@
       </c>
       <c r="AH439" t="inlineStr">
         <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI439">
@@ -77392,7 +77392,7 @@
       </c>
       <c r="AH440" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI440">
@@ -77569,7 +77569,7 @@
       </c>
       <c r="AH441" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Đăng</t>
         </is>
       </c>
       <c r="AI441">
@@ -77746,7 +77746,7 @@
       </c>
       <c r="AH442" t="inlineStr">
         <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI442">
@@ -77921,7 +77921,7 @@
       </c>
       <c r="AH443" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI443">
@@ -78093,7 +78093,7 @@
       </c>
       <c r="AH444" t="inlineStr">
         <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI444">
@@ -78270,7 +78270,7 @@
       </c>
       <c r="AH445" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI445">
@@ -78442,7 +78442,7 @@
       </c>
       <c r="AH446" t="inlineStr">
         <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI446">
@@ -78619,7 +78619,7 @@
       </c>
       <c r="AH447" t="inlineStr">
         <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI447">
@@ -78796,7 +78796,7 @@
       </c>
       <c r="AH448" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đăng</t>
         </is>
       </c>
       <c r="AI448">
@@ -78973,7 +78973,7 @@
       </c>
       <c r="AH449" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI449">
@@ -79150,7 +79150,7 @@
       </c>
       <c r="AH450" t="inlineStr">
         <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI450">
@@ -79328,7 +79328,7 @@
       </c>
       <c r="AH451" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI451">
@@ -79503,7 +79503,7 @@
       </c>
       <c r="AH452" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI452">
@@ -79680,7 +79680,7 @@
       </c>
       <c r="AH453" t="inlineStr">
         <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI453">
@@ -79850,7 +79850,7 @@
       </c>
       <c r="AH454" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI454">
@@ -80027,7 +80027,7 @@
       </c>
       <c r="AH455" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI455">
@@ -80197,7 +80197,7 @@
       </c>
       <c r="AH456" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI456">
@@ -80369,7 +80369,7 @@
       </c>
       <c r="AH457" t="inlineStr">
         <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI457">
@@ -80545,7 +80545,7 @@
       </c>
       <c r="AH458" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI458">
@@ -80722,7 +80722,7 @@
       </c>
       <c r="AH459" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI459">
@@ -80899,7 +80899,7 @@
       </c>
       <c r="AH460" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI460">
@@ -81076,7 +81076,7 @@
       </c>
       <c r="AH461" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI461">
@@ -81253,7 +81253,7 @@
       </c>
       <c r="AH462" t="inlineStr">
         <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI462">
@@ -81425,7 +81425,7 @@
       </c>
       <c r="AH463" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI463">
@@ -81596,7 +81596,7 @@
       </c>
       <c r="AH464" t="inlineStr">
         <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI464">
@@ -81767,7 +81767,7 @@
       </c>
       <c r="AH465" t="inlineStr">
         <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
+          <t>Đăng</t>
         </is>
       </c>
       <c r="AI465">
@@ -81944,7 +81944,7 @@
       </c>
       <c r="AH466" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI466">
@@ -82116,7 +82116,7 @@
       </c>
       <c r="AH467" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI467">
@@ -82286,7 +82286,7 @@
       </c>
       <c r="AH468" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI468">
@@ -82458,7 +82458,7 @@
       </c>
       <c r="AH469" t="inlineStr">
         <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI469">
@@ -82635,7 +82635,7 @@
       </c>
       <c r="AH470" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI470">
@@ -82811,7 +82811,7 @@
       </c>
       <c r="AH471" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI471">
@@ -82988,7 +82988,7 @@
       </c>
       <c r="AH472" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AI472">
@@ -83165,7 +83165,7 @@
       </c>
       <c r="AH473" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đăng</t>
         </is>
       </c>
       <c r="AI473">
@@ -83336,7 +83336,7 @@
       </c>
       <c r="AH474" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AI474">

--- a/data/5.R_pakh_hoan_thanh.xlsx
+++ b/data/5.R_pakh_hoan_thanh.xlsx
@@ -705,11 +705,11 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N - 1</t>
         </is>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
@@ -884,11 +884,11 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N - 1</t>
         </is>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
@@ -1039,12 +1039,12 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Trần Trọng Hiếu</t>
+          <t>Võ Trọng Đức</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>69197</t>
+          <t>293804</t>
         </is>
       </c>
       <c r="AA4" s="3">
@@ -1058,11 +1058,11 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N - 1</t>
         </is>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
@@ -1237,11 +1237,11 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N - 1</t>
         </is>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
@@ -1416,11 +1416,11 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N - 1</t>
         </is>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
@@ -1595,11 +1595,11 @@
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N - 1</t>
         </is>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
@@ -1773,11 +1773,11 @@
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N - 1</t>
         </is>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Bình thường</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1950,13 +1950,8 @@
       <c r="AC9">
         <v>4</v>
       </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>N - 1</t>
-        </is>
-      </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
@@ -2120,7 +2115,7 @@
         </is>
       </c>
       <c r="Z10" s="2">
-        <v>46259.53819444445</v>
+        <v>46259.85763888889</v>
       </c>
       <c r="AA10" s="3">
         <v>46259</v>
@@ -2131,13 +2126,8 @@
       <c r="AC10">
         <v>4</v>
       </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>N - 1</t>
-        </is>
-      </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
@@ -2155,10 +2145,10 @@
         </is>
       </c>
       <c r="AI10">
-        <v>4.383333333333334</v>
+        <v>8.466388888888888</v>
       </c>
       <c r="AJ10">
-        <v>0.1826388888888889</v>
+        <v>0.3527662037037037</v>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
@@ -2166,7 +2156,7 @@
         </is>
       </c>
       <c r="AL10">
-        <v>19.61638888888889</v>
+        <v>11.94972222222222</v>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
@@ -2315,13 +2305,8 @@
       <c r="AC11">
         <v>4</v>
       </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>N - 1</t>
-        </is>
-      </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
@@ -2496,13 +2481,8 @@
       <c r="AC12">
         <v>4</v>
       </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>N - 1</t>
-        </is>
-      </c>
       <c r="AE12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
@@ -2644,16 +2624,16 @@
         <v>46258.67222222222</v>
       </c>
       <c r="U13" s="2">
-        <v>46259.67222222222</v>
+        <v>46259.85763888889</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>Đang tiến hành</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -2665,6 +2645,9 @@
         <is>
           <t>182255</t>
         </is>
+      </c>
+      <c r="Z13" s="2">
+        <v>46259.70902777778</v>
       </c>
       <c r="AA13" s="3">
         <v>46258</v>
@@ -2675,13 +2658,8 @@
       <c r="AC13">
         <v>4</v>
       </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>N - 1</t>
-        </is>
-      </c>
       <c r="AE13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
@@ -2699,10 +2677,10 @@
         </is>
       </c>
       <c r="AI13">
-        <v>0</v>
+        <v>24.86611111111111</v>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1.036087962962963</v>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
@@ -2710,11 +2688,11 @@
         </is>
       </c>
       <c r="AL13">
-        <v>-1</v>
+        <v>3.566666666666667</v>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="AN13" s="3">
@@ -2857,13 +2835,8 @@
       <c r="AC14">
         <v>4</v>
       </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>N - 1</t>
-        </is>
-      </c>
       <c r="AE14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
@@ -3039,13 +3012,8 @@
       <c r="AC15">
         <v>4</v>
       </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>N - 1</t>
-        </is>
-      </c>
       <c r="AE15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
@@ -3214,13 +3182,8 @@
       <c r="AC16">
         <v>4</v>
       </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>N - 1</t>
-        </is>
-      </c>
       <c r="AE16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
@@ -3376,12 +3339,12 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Lê Duy Tuấn</t>
+          <t>Khương Văn Độ</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>293859</t>
+          <t>450945</t>
         </is>
       </c>
       <c r="AA17" s="3">
@@ -3395,11 +3358,11 @@
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N - 1</t>
         </is>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
@@ -3545,12 +3508,12 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>Đang tiến hành</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -3562,6 +3525,9 @@
         <is>
           <t>428467</t>
         </is>
+      </c>
+      <c r="Z18" s="2">
+        <v>46259.82638888889</v>
       </c>
       <c r="AA18" s="3">
         <v>46259</v>
@@ -3574,11 +3540,11 @@
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N - 1</t>
         </is>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
@@ -3596,10 +3562,10 @@
         </is>
       </c>
       <c r="AI18">
-        <v>0</v>
+        <v>1.849722222222222</v>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>0.07707175925925926</v>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
@@ -3607,11 +3573,11 @@
         </is>
       </c>
       <c r="AL18">
-        <v>-1</v>
+        <v>19.31638888888889</v>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="AN18" s="3">
@@ -3755,11 +3721,11 @@
       </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N - 1</t>
         </is>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
@@ -3937,11 +3903,11 @@
       </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N - 1</t>
         </is>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
@@ -4119,11 +4085,11 @@
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N - 1</t>
         </is>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
@@ -4301,11 +4267,11 @@
       </c>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N - 1</t>
         </is>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
@@ -4480,13 +4446,8 @@
       <c r="AC23">
         <v>4</v>
       </c>
-      <c r="AD23" t="inlineStr">
-        <is>
-          <t>N - 1</t>
-        </is>
-      </c>
       <c r="AE23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
@@ -4662,13 +4623,8 @@
       <c r="AC24">
         <v>4</v>
       </c>
-      <c r="AD24" t="inlineStr">
-        <is>
-          <t>N - 1</t>
-        </is>
-      </c>
       <c r="AE24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
@@ -4836,13 +4792,8 @@
       <c r="AC25">
         <v>4</v>
       </c>
-      <c r="AD25" t="inlineStr">
-        <is>
-          <t>N - 1</t>
-        </is>
-      </c>
       <c r="AE25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
@@ -5018,13 +4969,8 @@
       <c r="AC26">
         <v>4</v>
       </c>
-      <c r="AD26" t="inlineStr">
-        <is>
-          <t>N - 1</t>
-        </is>
-      </c>
       <c r="AE26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
@@ -5201,13 +5147,8 @@
       <c r="AC27">
         <v>4</v>
       </c>
-      <c r="AD27" t="inlineStr">
-        <is>
-          <t>N - 1</t>
-        </is>
-      </c>
       <c r="AE27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
@@ -5384,13 +5325,8 @@
       <c r="AC28">
         <v>4</v>
       </c>
-      <c r="AD28" t="inlineStr">
-        <is>
-          <t>N - 1</t>
-        </is>
-      </c>
       <c r="AE28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
@@ -5566,13 +5502,8 @@
       <c r="AC29">
         <v>4</v>
       </c>
-      <c r="AD29" t="inlineStr">
-        <is>
-          <t>N - 1</t>
-        </is>
-      </c>
       <c r="AE29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
@@ -5748,13 +5679,8 @@
       <c r="AC30">
         <v>4</v>
       </c>
-      <c r="AD30" t="inlineStr">
-        <is>
-          <t>N - 1</t>
-        </is>
-      </c>
       <c r="AE30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
@@ -5930,13 +5856,8 @@
       <c r="AC31">
         <v>4</v>
       </c>
-      <c r="AD31" t="inlineStr">
-        <is>
-          <t>N - 1</t>
-        </is>
-      </c>
       <c r="AE31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
@@ -6106,13 +6027,8 @@
       <c r="AC32">
         <v>4</v>
       </c>
-      <c r="AD32" t="inlineStr">
-        <is>
-          <t>N - 1</t>
-        </is>
-      </c>
       <c r="AE32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
@@ -6288,13 +6204,8 @@
       <c r="AC33">
         <v>4</v>
       </c>
-      <c r="AD33" t="inlineStr">
-        <is>
-          <t>N - 1</t>
-        </is>
-      </c>
       <c r="AE33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF33" t="inlineStr">
         <is>
@@ -6470,13 +6381,8 @@
       <c r="AC34">
         <v>4</v>
       </c>
-      <c r="AD34" t="inlineStr">
-        <is>
-          <t>N - 1</t>
-        </is>
-      </c>
       <c r="AE34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF34" t="inlineStr">
         <is>
@@ -6647,13 +6553,8 @@
       <c r="AC35">
         <v>4</v>
       </c>
-      <c r="AD35" t="inlineStr">
-        <is>
-          <t>N - 1</t>
-        </is>
-      </c>
       <c r="AE35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF35" t="inlineStr">
         <is>
@@ -6830,7 +6731,7 @@
         <v>4</v>
       </c>
       <c r="AE36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF36" t="inlineStr">
         <is>
@@ -7002,7 +6903,7 @@
         <v>4</v>
       </c>
       <c r="AE37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF37" t="inlineStr">
         <is>
@@ -7179,7 +7080,7 @@
         <v>4</v>
       </c>
       <c r="AE38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF38" t="inlineStr">
         <is>
@@ -7349,7 +7250,7 @@
         <v>4</v>
       </c>
       <c r="AE39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF39" t="inlineStr">
         <is>
@@ -7524,7 +7425,7 @@
         <v>4</v>
       </c>
       <c r="AE40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF40" t="inlineStr">
         <is>
@@ -7701,7 +7602,7 @@
         <v>4</v>
       </c>
       <c r="AE41">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF41" t="inlineStr">
         <is>
@@ -7847,7 +7748,7 @@
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>Hoàn thành</t>
+          <t>Đóng</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
@@ -7878,7 +7779,7 @@
         <v>4</v>
       </c>
       <c r="AE42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF42" t="inlineStr">
         <is>
@@ -8050,7 +7951,7 @@
         <v>4</v>
       </c>
       <c r="AE43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF43" t="inlineStr">
         <is>
@@ -8227,7 +8128,7 @@
         <v>4</v>
       </c>
       <c r="AE44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF44" t="inlineStr">
         <is>
@@ -8404,7 +8305,7 @@
         <v>4</v>
       </c>
       <c r="AE45">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF45" t="inlineStr">
         <is>
@@ -8555,7 +8456,7 @@
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>Trong hạn</t>
+          <t>Sắp quá hạn</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
@@ -8578,7 +8479,7 @@
         <v>4</v>
       </c>
       <c r="AE46">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF46" t="inlineStr">
         <is>
@@ -8752,7 +8653,7 @@
         <v>4</v>
       </c>
       <c r="AE47">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF47" t="inlineStr">
         <is>
@@ -8922,7 +8823,7 @@
         <v>4</v>
       </c>
       <c r="AE48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF48" t="inlineStr">
         <is>
@@ -9097,7 +8998,7 @@
         <v>4</v>
       </c>
       <c r="AE49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF49" t="inlineStr">
         <is>
@@ -9274,7 +9175,7 @@
         <v>4</v>
       </c>
       <c r="AE50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF50" t="inlineStr">
         <is>
@@ -9451,7 +9352,7 @@
         <v>4</v>
       </c>
       <c r="AE51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF51" t="inlineStr">
         <is>
@@ -9622,7 +9523,7 @@
         <v>4</v>
       </c>
       <c r="AE52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF52" t="inlineStr">
         <is>
@@ -9773,7 +9674,7 @@
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>Trong hạn</t>
+          <t>Sắp quá hạn</t>
         </is>
       </c>
       <c r="X53" t="inlineStr">
@@ -9796,7 +9697,7 @@
         <v>4</v>
       </c>
       <c r="AE53">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF53" t="inlineStr">
         <is>
@@ -9966,7 +9867,7 @@
         <v>4</v>
       </c>
       <c r="AE54">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF54" t="inlineStr">
         <is>
@@ -10136,7 +10037,7 @@
         <v>4</v>
       </c>
       <c r="AE55">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF55" t="inlineStr">
         <is>
@@ -10313,7 +10214,7 @@
         <v>4</v>
       </c>
       <c r="AE56">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF56" t="inlineStr">
         <is>
@@ -10483,7 +10384,7 @@
         <v>4</v>
       </c>
       <c r="AE57">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF57" t="inlineStr">
         <is>
@@ -10659,7 +10560,7 @@
         <v>3</v>
       </c>
       <c r="AE58">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF58" t="inlineStr">
         <is>
@@ -10836,7 +10737,7 @@
         <v>3</v>
       </c>
       <c r="AE59">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF59" t="inlineStr">
         <is>
@@ -11012,7 +10913,7 @@
         <v>3</v>
       </c>
       <c r="AE60">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF60" t="inlineStr">
         <is>
@@ -11189,7 +11090,7 @@
         <v>3</v>
       </c>
       <c r="AE61">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF61" t="inlineStr">
         <is>
@@ -11359,7 +11260,7 @@
         <v>3</v>
       </c>
       <c r="AE62">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF62" t="inlineStr">
         <is>
@@ -11536,7 +11437,7 @@
         <v>4</v>
       </c>
       <c r="AE63">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF63" t="inlineStr">
         <is>
@@ -11712,7 +11613,7 @@
         <v>4</v>
       </c>
       <c r="AE64">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF64" t="inlineStr">
         <is>
@@ -11882,7 +11783,7 @@
         <v>4</v>
       </c>
       <c r="AE65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF65" t="inlineStr">
         <is>
@@ -12059,7 +11960,7 @@
         <v>4</v>
       </c>
       <c r="AE66">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF66" t="inlineStr">
         <is>
@@ -12236,7 +12137,7 @@
         <v>4</v>
       </c>
       <c r="AE67">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF67" t="inlineStr">
         <is>
@@ -12412,7 +12313,7 @@
         <v>4</v>
       </c>
       <c r="AE68">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF68" t="inlineStr">
         <is>
@@ -12587,7 +12488,7 @@
         <v>4</v>
       </c>
       <c r="AE69">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF69" t="inlineStr">
         <is>
@@ -12764,7 +12665,7 @@
         <v>3</v>
       </c>
       <c r="AE70">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF70" t="inlineStr">
         <is>
@@ -12938,7 +12839,7 @@
         <v>3</v>
       </c>
       <c r="AE71">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF71" t="inlineStr">
         <is>
@@ -13114,7 +13015,7 @@
         <v>3</v>
       </c>
       <c r="AE72">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF72" t="inlineStr">
         <is>
@@ -13284,7 +13185,7 @@
         <v>3</v>
       </c>
       <c r="AE73">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF73" t="inlineStr">
         <is>
@@ -13461,7 +13362,7 @@
         <v>3</v>
       </c>
       <c r="AE74">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF74" t="inlineStr">
         <is>
@@ -13638,7 +13539,7 @@
         <v>3</v>
       </c>
       <c r="AE75">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF75" t="inlineStr">
         <is>
@@ -13815,7 +13716,7 @@
         <v>3</v>
       </c>
       <c r="AE76">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF76" t="inlineStr">
         <is>
@@ -13992,7 +13893,7 @@
         <v>3</v>
       </c>
       <c r="AE77">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF77" t="inlineStr">
         <is>
@@ -14169,7 +14070,7 @@
         <v>3</v>
       </c>
       <c r="AE78">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF78" t="inlineStr">
         <is>
@@ -14339,7 +14240,7 @@
         <v>3</v>
       </c>
       <c r="AE79">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF79" t="inlineStr">
         <is>
@@ -14516,7 +14417,7 @@
         <v>3</v>
       </c>
       <c r="AE80">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF80" t="inlineStr">
         <is>
@@ -14693,7 +14594,7 @@
         <v>3</v>
       </c>
       <c r="AE81">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF81" t="inlineStr">
         <is>
@@ -14865,7 +14766,7 @@
         <v>3</v>
       </c>
       <c r="AE82">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF82" t="inlineStr">
         <is>
@@ -15042,7 +14943,7 @@
         <v>3</v>
       </c>
       <c r="AE83">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF83" t="inlineStr">
         <is>
@@ -15218,7 +15119,7 @@
         <v>3</v>
       </c>
       <c r="AE84">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF84" t="inlineStr">
         <is>
@@ -15395,7 +15296,7 @@
         <v>3</v>
       </c>
       <c r="AE85">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF85" t="inlineStr">
         <is>
@@ -15572,7 +15473,7 @@
         <v>3</v>
       </c>
       <c r="AE86">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF86" t="inlineStr">
         <is>
@@ -15749,7 +15650,7 @@
         <v>3</v>
       </c>
       <c r="AE87">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF87" t="inlineStr">
         <is>
@@ -15919,7 +15820,7 @@
         <v>3</v>
       </c>
       <c r="AE88">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF88" t="inlineStr">
         <is>
@@ -16097,7 +15998,7 @@
         <v>3</v>
       </c>
       <c r="AE89">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF89" t="inlineStr">
         <is>
@@ -16267,7 +16168,7 @@
         <v>3</v>
       </c>
       <c r="AE90">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF90" t="inlineStr">
         <is>
@@ -16437,7 +16338,7 @@
         <v>3</v>
       </c>
       <c r="AE91">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF91" t="inlineStr">
         <is>
@@ -16609,7 +16510,7 @@
         <v>3</v>
       </c>
       <c r="AE92">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF92" t="inlineStr">
         <is>
@@ -16786,7 +16687,7 @@
         <v>3</v>
       </c>
       <c r="AE93">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF93" t="inlineStr">
         <is>
@@ -16963,7 +16864,7 @@
         <v>3</v>
       </c>
       <c r="AE94">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF94" t="inlineStr">
         <is>
@@ -17109,12 +17010,12 @@
       </c>
       <c r="V95" t="inlineStr">
         <is>
-          <t>Đang tiến hành</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="W95" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="X95" t="inlineStr">
@@ -17126,6 +17027,9 @@
         <is>
           <t>7721</t>
         </is>
+      </c>
+      <c r="Z95" s="2">
+        <v>46260.30208333333</v>
       </c>
       <c r="AA95" s="3">
         <v>46255</v>
@@ -17137,7 +17041,7 @@
         <v>3</v>
       </c>
       <c r="AE95">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF95" t="inlineStr">
         <is>
@@ -17155,10 +17059,10 @@
         </is>
       </c>
       <c r="AI95">
-        <v>0</v>
+        <v>70.0825</v>
       </c>
       <c r="AJ95">
-        <v>0</v>
+        <v>2.920104166666667</v>
       </c>
       <c r="AK95" t="inlineStr">
         <is>
@@ -17166,11 +17070,11 @@
         </is>
       </c>
       <c r="AL95">
-        <v>-1</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="AN95" s="3">
@@ -17314,7 +17218,7 @@
         <v>3</v>
       </c>
       <c r="AE96">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF96" t="inlineStr">
         <is>
@@ -17492,7 +17396,7 @@
         <v>3</v>
       </c>
       <c r="AE97">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF97" t="inlineStr">
         <is>
@@ -17669,7 +17573,7 @@
         <v>3</v>
       </c>
       <c r="AE98">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF98" t="inlineStr">
         <is>
@@ -17841,7 +17745,7 @@
         <v>3</v>
       </c>
       <c r="AE99">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF99" t="inlineStr">
         <is>
@@ -18016,7 +17920,7 @@
         <v>3</v>
       </c>
       <c r="AE100">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF100" t="inlineStr">
         <is>
@@ -18191,7 +18095,7 @@
         <v>3</v>
       </c>
       <c r="AE101">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF101" t="inlineStr">
         <is>
@@ -18363,7 +18267,7 @@
         <v>3</v>
       </c>
       <c r="AE102">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF102" t="inlineStr">
         <is>
@@ -18538,7 +18442,7 @@
         <v>3</v>
       </c>
       <c r="AE103">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF103" t="inlineStr">
         <is>
@@ -18715,7 +18619,7 @@
         <v>3</v>
       </c>
       <c r="AE104">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF104" t="inlineStr">
         <is>
@@ -18885,7 +18789,7 @@
         <v>3</v>
       </c>
       <c r="AE105">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF105" t="inlineStr">
         <is>
@@ -19062,7 +18966,7 @@
         <v>3</v>
       </c>
       <c r="AE106">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF106" t="inlineStr">
         <is>
@@ -19239,7 +19143,7 @@
         <v>3</v>
       </c>
       <c r="AE107">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF107" t="inlineStr">
         <is>
@@ -19416,7 +19320,7 @@
         <v>3</v>
       </c>
       <c r="AE108">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF108" t="inlineStr">
         <is>
@@ -19593,7 +19497,7 @@
         <v>3</v>
       </c>
       <c r="AE109">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF109" t="inlineStr">
         <is>
@@ -19770,7 +19674,7 @@
         <v>3</v>
       </c>
       <c r="AE110">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF110" t="inlineStr">
         <is>
@@ -19948,7 +19852,7 @@
         <v>3</v>
       </c>
       <c r="AE111">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF111" t="inlineStr">
         <is>
@@ -20125,7 +20029,7 @@
         <v>3</v>
       </c>
       <c r="AE112">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF112" t="inlineStr">
         <is>
@@ -20303,7 +20207,7 @@
         <v>3</v>
       </c>
       <c r="AE113">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF113" t="inlineStr">
         <is>
@@ -20478,7 +20382,7 @@
         <v>3</v>
       </c>
       <c r="AE114">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF114" t="inlineStr">
         <is>
@@ -20655,7 +20559,7 @@
         <v>3</v>
       </c>
       <c r="AE115">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF115" t="inlineStr">
         <is>
@@ -20832,7 +20736,7 @@
         <v>3</v>
       </c>
       <c r="AE116">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF116" t="inlineStr">
         <is>
@@ -21009,7 +20913,7 @@
         <v>3</v>
       </c>
       <c r="AE117">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF117" t="inlineStr">
         <is>
@@ -21186,7 +21090,7 @@
         <v>3</v>
       </c>
       <c r="AE118">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF118" t="inlineStr">
         <is>
@@ -21362,7 +21266,7 @@
         <v>3</v>
       </c>
       <c r="AE119">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF119" t="inlineStr">
         <is>
@@ -21538,7 +21442,7 @@
         <v>3</v>
       </c>
       <c r="AE120">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF120" t="inlineStr">
         <is>
@@ -21715,7 +21619,7 @@
         <v>3</v>
       </c>
       <c r="AE121">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF121" t="inlineStr">
         <is>
@@ -21861,7 +21765,7 @@
       </c>
       <c r="W122" t="inlineStr">
         <is>
-          <t>Trong hạn</t>
+          <t>Sắp quá hạn</t>
         </is>
       </c>
       <c r="X122" t="inlineStr">
@@ -21884,7 +21788,7 @@
         <v>3</v>
       </c>
       <c r="AE122">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF122" t="inlineStr">
         <is>
@@ -22061,7 +21965,7 @@
         <v>3</v>
       </c>
       <c r="AE123">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF123" t="inlineStr">
         <is>
@@ -22238,7 +22142,7 @@
         <v>3</v>
       </c>
       <c r="AE124">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF124" t="inlineStr">
         <is>
@@ -22408,7 +22312,7 @@
         <v>3</v>
       </c>
       <c r="AE125">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF125" t="inlineStr">
         <is>
@@ -22579,7 +22483,7 @@
         <v>3</v>
       </c>
       <c r="AE126">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF126" t="inlineStr">
         <is>
@@ -22756,7 +22660,7 @@
         <v>3</v>
       </c>
       <c r="AE127">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF127" t="inlineStr">
         <is>
@@ -22933,7 +22837,7 @@
         <v>3</v>
       </c>
       <c r="AE128">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF128" t="inlineStr">
         <is>
@@ -23110,7 +23014,7 @@
         <v>3</v>
       </c>
       <c r="AE129">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF129" t="inlineStr">
         <is>
@@ -23287,7 +23191,7 @@
         <v>3</v>
       </c>
       <c r="AE130">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF130" t="inlineStr">
         <is>
@@ -23462,7 +23366,7 @@
         <v>3</v>
       </c>
       <c r="AE131">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF131" t="inlineStr">
         <is>
@@ -23638,7 +23542,7 @@
         <v>3</v>
       </c>
       <c r="AE132">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF132" t="inlineStr">
         <is>
@@ -23815,7 +23719,7 @@
         <v>3</v>
       </c>
       <c r="AE133">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF133" t="inlineStr">
         <is>
@@ -23990,7 +23894,7 @@
         <v>3</v>
       </c>
       <c r="AE134">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF134" t="inlineStr">
         <is>
@@ -24167,7 +24071,7 @@
         <v>3</v>
       </c>
       <c r="AE135">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF135" t="inlineStr">
         <is>
@@ -24337,7 +24241,7 @@
         <v>3</v>
       </c>
       <c r="AE136">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF136" t="inlineStr">
         <is>
@@ -24511,7 +24415,7 @@
         <v>3</v>
       </c>
       <c r="AE137">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF137" t="inlineStr">
         <is>
@@ -24681,7 +24585,7 @@
         <v>3</v>
       </c>
       <c r="AE138">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF138" t="inlineStr">
         <is>
@@ -24858,7 +24762,7 @@
         <v>3</v>
       </c>
       <c r="AE139">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF139" t="inlineStr">
         <is>
@@ -25035,7 +24939,7 @@
         <v>3</v>
       </c>
       <c r="AE140">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF140" t="inlineStr">
         <is>
@@ -25212,7 +25116,7 @@
         <v>3</v>
       </c>
       <c r="AE141">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF141" t="inlineStr">
         <is>
@@ -25382,7 +25286,7 @@
         <v>3</v>
       </c>
       <c r="AE142">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF142" t="inlineStr">
         <is>
@@ -25559,7 +25463,7 @@
         <v>3</v>
       </c>
       <c r="AE143">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF143" t="inlineStr">
         <is>
@@ -25736,7 +25640,7 @@
         <v>3</v>
       </c>
       <c r="AE144">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF144" t="inlineStr">
         <is>
@@ -25885,7 +25789,7 @@
       </c>
       <c r="W145" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Quá hạn</t>
         </is>
       </c>
       <c r="X145" t="inlineStr">
@@ -25908,7 +25812,7 @@
         <v>3</v>
       </c>
       <c r="AE145">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF145" t="inlineStr">
         <is>
@@ -26085,7 +25989,7 @@
         <v>3</v>
       </c>
       <c r="AE146">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF146" t="inlineStr">
         <is>
@@ -26260,7 +26164,7 @@
         <v>3</v>
       </c>
       <c r="AE147">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF147" t="inlineStr">
         <is>
@@ -26437,7 +26341,7 @@
         <v>3</v>
       </c>
       <c r="AE148">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF148" t="inlineStr">
         <is>
@@ -26607,7 +26511,7 @@
         <v>3</v>
       </c>
       <c r="AE149">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF149" t="inlineStr">
         <is>
@@ -26784,7 +26688,7 @@
         <v>3</v>
       </c>
       <c r="AE150">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF150" t="inlineStr">
         <is>
@@ -26961,7 +26865,7 @@
         <v>3</v>
       </c>
       <c r="AE151">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF151" t="inlineStr">
         <is>
@@ -27138,7 +27042,7 @@
         <v>3</v>
       </c>
       <c r="AE152">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF152" t="inlineStr">
         <is>
@@ -27309,7 +27213,7 @@
         <v>3</v>
       </c>
       <c r="AE153">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF153" t="inlineStr">
         <is>
@@ -27485,7 +27389,7 @@
         <v>3</v>
       </c>
       <c r="AE154">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF154" t="inlineStr">
         <is>
@@ -27662,7 +27566,7 @@
         <v>3</v>
       </c>
       <c r="AE155">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF155" t="inlineStr">
         <is>
@@ -27839,7 +27743,7 @@
         <v>3</v>
       </c>
       <c r="AE156">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF156" t="inlineStr">
         <is>
@@ -28013,7 +27917,7 @@
         <v>3</v>
       </c>
       <c r="AE157">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF157" t="inlineStr">
         <is>
@@ -28190,7 +28094,7 @@
         <v>3</v>
       </c>
       <c r="AE158">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF158" t="inlineStr">
         <is>
@@ -28364,7 +28268,7 @@
         <v>3</v>
       </c>
       <c r="AE159">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF159" t="inlineStr">
         <is>
@@ -28536,7 +28440,7 @@
         <v>3</v>
       </c>
       <c r="AE160">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF160" t="inlineStr">
         <is>
@@ -28713,7 +28617,7 @@
         <v>3</v>
       </c>
       <c r="AE161">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF161" t="inlineStr">
         <is>
@@ -28883,7 +28787,7 @@
         <v>3</v>
       </c>
       <c r="AE162">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF162" t="inlineStr">
         <is>
@@ -29060,7 +28964,7 @@
         <v>3</v>
       </c>
       <c r="AE163">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF163" t="inlineStr">
         <is>
@@ -29237,7 +29141,7 @@
         <v>3</v>
       </c>
       <c r="AE164">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF164" t="inlineStr">
         <is>
@@ -29414,7 +29318,7 @@
         <v>3</v>
       </c>
       <c r="AE165">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF165" t="inlineStr">
         <is>
@@ -29591,7 +29495,7 @@
         <v>3</v>
       </c>
       <c r="AE166">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF166" t="inlineStr">
         <is>
@@ -29761,7 +29665,7 @@
         <v>3</v>
       </c>
       <c r="AE167">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF167" t="inlineStr">
         <is>
@@ -29938,7 +29842,7 @@
         <v>3</v>
       </c>
       <c r="AE168">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF168" t="inlineStr">
         <is>
@@ -30115,7 +30019,7 @@
         <v>3</v>
       </c>
       <c r="AE169">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF169" t="inlineStr">
         <is>
@@ -30287,7 +30191,7 @@
         <v>3</v>
       </c>
       <c r="AE170">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF170" t="inlineStr">
         <is>
@@ -30464,7 +30368,7 @@
         <v>3</v>
       </c>
       <c r="AE171">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF171" t="inlineStr">
         <is>
@@ -30642,7 +30546,7 @@
         <v>3</v>
       </c>
       <c r="AE172">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF172" t="inlineStr">
         <is>
@@ -30819,7 +30723,7 @@
         <v>3</v>
       </c>
       <c r="AE173">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF173" t="inlineStr">
         <is>
@@ -30996,7 +30900,7 @@
         <v>3</v>
       </c>
       <c r="AE174">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF174" t="inlineStr">
         <is>
@@ -31166,7 +31070,7 @@
         <v>3</v>
       </c>
       <c r="AE175">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF175" t="inlineStr">
         <is>
@@ -31341,7 +31245,7 @@
         <v>3</v>
       </c>
       <c r="AE176">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF176" t="inlineStr">
         <is>
@@ -31518,7 +31422,7 @@
         <v>3</v>
       </c>
       <c r="AE177">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF177" t="inlineStr">
         <is>
@@ -31690,7 +31594,7 @@
         <v>3</v>
       </c>
       <c r="AE178">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF178" t="inlineStr">
         <is>
@@ -31862,7 +31766,7 @@
         <v>3</v>
       </c>
       <c r="AE179">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF179" t="inlineStr">
         <is>
@@ -32039,7 +31943,7 @@
         <v>3</v>
       </c>
       <c r="AE180">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF180" t="inlineStr">
         <is>
@@ -32216,7 +32120,7 @@
         <v>3</v>
       </c>
       <c r="AE181">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF181" t="inlineStr">
         <is>
@@ -32393,7 +32297,7 @@
         <v>3</v>
       </c>
       <c r="AE182">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF182" t="inlineStr">
         <is>
@@ -32570,7 +32474,7 @@
         <v>3</v>
       </c>
       <c r="AE183">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF183" t="inlineStr">
         <is>
@@ -32747,7 +32651,7 @@
         <v>3</v>
       </c>
       <c r="AE184">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF184" t="inlineStr">
         <is>
@@ -32924,7 +32828,7 @@
         <v>3</v>
       </c>
       <c r="AE185">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF185" t="inlineStr">
         <is>
@@ -33101,7 +33005,7 @@
         <v>3</v>
       </c>
       <c r="AE186">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF186" t="inlineStr">
         <is>
@@ -33278,7 +33182,7 @@
         <v>3</v>
       </c>
       <c r="AE187">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF187" t="inlineStr">
         <is>
@@ -33455,7 +33359,7 @@
         <v>3</v>
       </c>
       <c r="AE188">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF188" t="inlineStr">
         <is>
@@ -33630,7 +33534,7 @@
         <v>3</v>
       </c>
       <c r="AE189">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF189" t="inlineStr">
         <is>
@@ -33800,7 +33704,7 @@
         <v>3</v>
       </c>
       <c r="AE190">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF190" t="inlineStr">
         <is>
@@ -33970,7 +33874,7 @@
         <v>3</v>
       </c>
       <c r="AE191">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF191" t="inlineStr">
         <is>
@@ -34140,7 +34044,7 @@
         <v>3</v>
       </c>
       <c r="AE192">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF192" t="inlineStr">
         <is>
@@ -34317,7 +34221,7 @@
         <v>3</v>
       </c>
       <c r="AE193">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF193" t="inlineStr">
         <is>
@@ -34487,7 +34391,7 @@
         <v>3</v>
       </c>
       <c r="AE194">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF194" t="inlineStr">
         <is>
@@ -34658,7 +34562,7 @@
         <v>3</v>
       </c>
       <c r="AE195">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF195" t="inlineStr">
         <is>
@@ -34828,7 +34732,7 @@
         <v>3</v>
       </c>
       <c r="AE196">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF196" t="inlineStr">
         <is>
@@ -35002,7 +34906,7 @@
         <v>3</v>
       </c>
       <c r="AE197">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF197" t="inlineStr">
         <is>
@@ -35177,7 +35081,7 @@
         <v>3</v>
       </c>
       <c r="AE198">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF198" t="inlineStr">
         <is>
@@ -35352,7 +35256,7 @@
         <v>3</v>
       </c>
       <c r="AE199">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF199" t="inlineStr">
         <is>
@@ -35522,7 +35426,7 @@
         <v>3</v>
       </c>
       <c r="AE200">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF200" t="inlineStr">
         <is>
@@ -35692,7 +35596,7 @@
         <v>3</v>
       </c>
       <c r="AE201">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF201" t="inlineStr">
         <is>
@@ -35864,7 +35768,7 @@
         <v>3</v>
       </c>
       <c r="AE202">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF202" t="inlineStr">
         <is>
@@ -36038,7 +35942,7 @@
         <v>3</v>
       </c>
       <c r="AE203">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF203" t="inlineStr">
         <is>
@@ -36215,7 +36119,7 @@
         <v>3</v>
       </c>
       <c r="AE204">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF204" t="inlineStr">
         <is>
@@ -36392,7 +36296,7 @@
         <v>3</v>
       </c>
       <c r="AE205">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF205" t="inlineStr">
         <is>
@@ -36569,7 +36473,7 @@
         <v>3</v>
       </c>
       <c r="AE206">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF206" t="inlineStr">
         <is>
@@ -36744,7 +36648,7 @@
         <v>2</v>
       </c>
       <c r="AE207">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF207" t="inlineStr">
         <is>
@@ -36921,7 +36825,7 @@
         <v>2</v>
       </c>
       <c r="AE208">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF208" t="inlineStr">
         <is>
@@ -37100,7 +37004,7 @@
         <v>2</v>
       </c>
       <c r="AE209">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF209" t="inlineStr">
         <is>
@@ -37277,7 +37181,7 @@
         <v>3</v>
       </c>
       <c r="AE210">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF210" t="inlineStr">
         <is>
@@ -37454,7 +37358,7 @@
         <v>3</v>
       </c>
       <c r="AE211">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF211" t="inlineStr">
         <is>
@@ -37624,7 +37528,7 @@
         <v>3</v>
       </c>
       <c r="AE212">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF212" t="inlineStr">
         <is>
@@ -37799,7 +37703,7 @@
         <v>3</v>
       </c>
       <c r="AE213">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF213" t="inlineStr">
         <is>
@@ -37974,7 +37878,7 @@
         <v>3</v>
       </c>
       <c r="AE214">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF214" t="inlineStr">
         <is>
@@ -38144,7 +38048,7 @@
         <v>3</v>
       </c>
       <c r="AE215">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF215" t="inlineStr">
         <is>
@@ -38321,7 +38225,7 @@
         <v>3</v>
       </c>
       <c r="AE216">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF216" t="inlineStr">
         <is>
@@ -38491,7 +38395,7 @@
         <v>2</v>
       </c>
       <c r="AE217">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF217" t="inlineStr">
         <is>
@@ -38661,7 +38565,7 @@
         <v>2</v>
       </c>
       <c r="AE218">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF218" t="inlineStr">
         <is>
@@ -38831,7 +38735,7 @@
         <v>2</v>
       </c>
       <c r="AE219">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF219" t="inlineStr">
         <is>
@@ -39008,7 +38912,7 @@
         <v>2</v>
       </c>
       <c r="AE220">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF220" t="inlineStr">
         <is>
@@ -39183,7 +39087,7 @@
         <v>2</v>
       </c>
       <c r="AE221">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF221" t="inlineStr">
         <is>
@@ -39353,7 +39257,7 @@
         <v>2</v>
       </c>
       <c r="AE222">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF222" t="inlineStr">
         <is>
@@ -39527,7 +39431,7 @@
         <v>2</v>
       </c>
       <c r="AE223">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF223" t="inlineStr">
         <is>
@@ -39702,7 +39606,7 @@
         <v>2</v>
       </c>
       <c r="AE224">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF224" t="inlineStr">
         <is>
@@ -39880,7 +39784,7 @@
         <v>2</v>
       </c>
       <c r="AE225">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF225" t="inlineStr">
         <is>
@@ -40055,7 +39959,7 @@
         <v>2</v>
       </c>
       <c r="AE226">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF226" t="inlineStr">
         <is>
@@ -40232,7 +40136,7 @@
         <v>2</v>
       </c>
       <c r="AE227">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF227" t="inlineStr">
         <is>
@@ -40402,7 +40306,7 @@
         <v>2</v>
       </c>
       <c r="AE228">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF228" t="inlineStr">
         <is>
@@ -40579,7 +40483,7 @@
         <v>2</v>
       </c>
       <c r="AE229">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF229" t="inlineStr">
         <is>
@@ -40756,7 +40660,7 @@
         <v>2</v>
       </c>
       <c r="AE230">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF230" t="inlineStr">
         <is>
@@ -40928,7 +40832,7 @@
         <v>2</v>
       </c>
       <c r="AE231">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF231" t="inlineStr">
         <is>
@@ -41105,7 +41009,7 @@
         <v>2</v>
       </c>
       <c r="AE232">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF232" t="inlineStr">
         <is>
@@ -41282,7 +41186,7 @@
         <v>2</v>
       </c>
       <c r="AE233">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF233" t="inlineStr">
         <is>
@@ -41459,7 +41363,7 @@
         <v>2</v>
       </c>
       <c r="AE234">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF234" t="inlineStr">
         <is>
@@ -41629,7 +41533,7 @@
         <v>2</v>
       </c>
       <c r="AE235">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF235" t="inlineStr">
         <is>
@@ -41775,7 +41679,7 @@
       </c>
       <c r="V236" t="inlineStr">
         <is>
-          <t>Đang tiến hành</t>
+          <t>Đóng</t>
         </is>
       </c>
       <c r="W236" t="inlineStr">
@@ -41806,7 +41710,7 @@
         <v>2</v>
       </c>
       <c r="AE236">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF236" t="inlineStr">
         <is>
@@ -41983,7 +41887,7 @@
         <v>2</v>
       </c>
       <c r="AE237">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF237" t="inlineStr">
         <is>
@@ -42158,7 +42062,7 @@
         <v>2</v>
       </c>
       <c r="AE238">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF238" t="inlineStr">
         <is>
@@ -42335,7 +42239,7 @@
         <v>2</v>
       </c>
       <c r="AE239">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF239" t="inlineStr">
         <is>
@@ -42512,7 +42416,7 @@
         <v>2</v>
       </c>
       <c r="AE240">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF240" t="inlineStr">
         <is>
@@ -42689,7 +42593,7 @@
         <v>2</v>
       </c>
       <c r="AE241">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF241" t="inlineStr">
         <is>
@@ -42866,7 +42770,7 @@
         <v>2</v>
       </c>
       <c r="AE242">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF242" t="inlineStr">
         <is>
@@ -43041,7 +42945,7 @@
         <v>2</v>
       </c>
       <c r="AE243">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF243" t="inlineStr">
         <is>
@@ -43218,7 +43122,7 @@
         <v>2</v>
       </c>
       <c r="AE244">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF244" t="inlineStr">
         <is>
@@ -43388,7 +43292,7 @@
         <v>2</v>
       </c>
       <c r="AE245">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF245" t="inlineStr">
         <is>
@@ -43565,7 +43469,7 @@
         <v>2</v>
       </c>
       <c r="AE246">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF246" t="inlineStr">
         <is>
@@ -43742,7 +43646,7 @@
         <v>2</v>
       </c>
       <c r="AE247">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF247" t="inlineStr">
         <is>
@@ -43919,7 +43823,7 @@
         <v>2</v>
       </c>
       <c r="AE248">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF248" t="inlineStr">
         <is>
@@ -44096,7 +44000,7 @@
         <v>2</v>
       </c>
       <c r="AE249">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF249" t="inlineStr">
         <is>
@@ -44273,7 +44177,7 @@
         <v>2</v>
       </c>
       <c r="AE250">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF250" t="inlineStr">
         <is>
@@ -44450,7 +44354,7 @@
         <v>2</v>
       </c>
       <c r="AE251">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF251" t="inlineStr">
         <is>
@@ -44627,7 +44531,7 @@
         <v>2</v>
       </c>
       <c r="AE252">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF252" t="inlineStr">
         <is>
@@ -44804,7 +44708,7 @@
         <v>2</v>
       </c>
       <c r="AE253">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF253" t="inlineStr">
         <is>
@@ -44974,7 +44878,7 @@
         <v>2</v>
       </c>
       <c r="AE254">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF254" t="inlineStr">
         <is>
@@ -45151,7 +45055,7 @@
         <v>2</v>
       </c>
       <c r="AE255">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF255" t="inlineStr">
         <is>
@@ -45328,7 +45232,7 @@
         <v>2</v>
       </c>
       <c r="AE256">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF256" t="inlineStr">
         <is>
@@ -45500,7 +45404,7 @@
         <v>2</v>
       </c>
       <c r="AE257">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF257" t="inlineStr">
         <is>
@@ -45677,7 +45581,7 @@
         <v>2</v>
       </c>
       <c r="AE258">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF258" t="inlineStr">
         <is>
@@ -45854,7 +45758,7 @@
         <v>2</v>
       </c>
       <c r="AE259">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF259" t="inlineStr">
         <is>
@@ -46031,7 +45935,7 @@
         <v>2</v>
       </c>
       <c r="AE260">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF260" t="inlineStr">
         <is>
@@ -46202,7 +46106,7 @@
         <v>2</v>
       </c>
       <c r="AE261">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF261" t="inlineStr">
         <is>
@@ -46379,7 +46283,7 @@
         <v>2</v>
       </c>
       <c r="AE262">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF262" t="inlineStr">
         <is>
@@ -46554,7 +46458,7 @@
         <v>2</v>
       </c>
       <c r="AE263">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF263" t="inlineStr">
         <is>
@@ -46724,7 +46628,7 @@
         <v>2</v>
       </c>
       <c r="AE264">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF264" t="inlineStr">
         <is>
@@ -46901,7 +46805,7 @@
         <v>2</v>
       </c>
       <c r="AE265">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF265" t="inlineStr">
         <is>
@@ -47073,7 +46977,7 @@
         <v>2</v>
       </c>
       <c r="AE266">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF266" t="inlineStr">
         <is>
@@ -47250,7 +47154,7 @@
         <v>2</v>
       </c>
       <c r="AE267">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF267" t="inlineStr">
         <is>
@@ -47427,7 +47331,7 @@
         <v>2</v>
       </c>
       <c r="AE268">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF268" t="inlineStr">
         <is>
@@ -47604,7 +47508,7 @@
         <v>2</v>
       </c>
       <c r="AE269">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF269" t="inlineStr">
         <is>
@@ -47781,7 +47685,7 @@
         <v>2</v>
       </c>
       <c r="AE270">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF270" t="inlineStr">
         <is>
@@ -47956,7 +47860,7 @@
         <v>2</v>
       </c>
       <c r="AE271">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AF271" t="inlineStr">
         <is>
@@ -48131,7 +48035,7 @@
         <v>2</v>
       </c>
       <c r="AE272">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AF272" t="inlineStr">
         <is>
@@ -48307,7 +48211,7 @@
         <v>2</v>
       </c>
       <c r="AE273">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AF273" t="inlineStr">
         <is>
@@ -48484,7 +48388,7 @@
         <v>2</v>
       </c>
       <c r="AE274">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AF274" t="inlineStr">
         <is>
@@ -48656,7 +48560,7 @@
         <v>2</v>
       </c>
       <c r="AE275">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AF275" t="inlineStr">
         <is>
@@ -48833,7 +48737,7 @@
         <v>2</v>
       </c>
       <c r="AE276">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AF276" t="inlineStr">
         <is>
@@ -49010,7 +48914,7 @@
         <v>2</v>
       </c>
       <c r="AE277">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AF277" t="inlineStr">
         <is>
@@ -49187,7 +49091,7 @@
         <v>2</v>
       </c>
       <c r="AE278">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AF278" t="inlineStr">
         <is>
@@ -49364,7 +49268,7 @@
         <v>2</v>
       </c>
       <c r="AE279">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AF279" t="inlineStr">
         <is>
@@ -49541,7 +49445,7 @@
         <v>2</v>
       </c>
       <c r="AE280">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AF280" t="inlineStr">
         <is>
@@ -49713,7 +49617,7 @@
         <v>2</v>
       </c>
       <c r="AE281">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF281" t="inlineStr">
         <is>
@@ -49890,7 +49794,7 @@
         <v>2</v>
       </c>
       <c r="AE282">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF282" t="inlineStr">
         <is>
@@ -50060,7 +49964,7 @@
         <v>2</v>
       </c>
       <c r="AE283">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF283" t="inlineStr">
         <is>
@@ -50237,7 +50141,7 @@
         <v>2</v>
       </c>
       <c r="AE284">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AF284" t="inlineStr">
         <is>
@@ -50407,7 +50311,7 @@
         <v>2</v>
       </c>
       <c r="AE285">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AF285" t="inlineStr">
         <is>
@@ -50579,7 +50483,7 @@
         <v>2</v>
       </c>
       <c r="AE286">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AF286" t="inlineStr">
         <is>
@@ -50754,7 +50658,7 @@
         <v>2</v>
       </c>
       <c r="AE287">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AF287" t="inlineStr">
         <is>
@@ -50930,7 +50834,7 @@
         <v>2</v>
       </c>
       <c r="AE288">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AF288" t="inlineStr">
         <is>
@@ -51107,7 +51011,7 @@
         <v>2</v>
       </c>
       <c r="AE289">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AF289" t="inlineStr">
         <is>
@@ -51279,7 +51183,7 @@
         <v>2</v>
       </c>
       <c r="AE290">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AF290" t="inlineStr">
         <is>
@@ -51456,7 +51360,7 @@
         <v>2</v>
       </c>
       <c r="AE291">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AF291" t="inlineStr">
         <is>
@@ -51602,7 +51506,7 @@
       </c>
       <c r="V292" t="inlineStr">
         <is>
-          <t>Đang tiến hành</t>
+          <t>Đóng</t>
         </is>
       </c>
       <c r="W292" t="inlineStr">
@@ -51621,7 +51525,7 @@
         </is>
       </c>
       <c r="Z292" s="2">
-        <v>46247.36597222222</v>
+        <v>46259.71875</v>
       </c>
       <c r="AA292" s="3">
         <v>46246</v>
@@ -51633,7 +51537,7 @@
         <v>2</v>
       </c>
       <c r="AE292">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AF292" t="inlineStr">
         <is>
@@ -51651,10 +51555,10 @@
         </is>
       </c>
       <c r="AI292">
-        <v>23.58305555555555</v>
+        <v>223.7972222222222</v>
       </c>
       <c r="AJ292">
-        <v>0.9826273148148147</v>
+        <v>9.32488425925926</v>
       </c>
       <c r="AK292" t="inlineStr">
         <is>
@@ -51662,7 +51566,7 @@
         </is>
       </c>
       <c r="AL292">
-        <v>279.2133333333334</v>
+        <v>78.74888888888889</v>
       </c>
       <c r="AM292" t="inlineStr">
         <is>
@@ -51812,7 +51716,7 @@
         <v>2</v>
       </c>
       <c r="AE293">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AF293" t="inlineStr">
         <is>
@@ -51989,7 +51893,7 @@
         <v>2</v>
       </c>
       <c r="AE294">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AF294" t="inlineStr">
         <is>
@@ -52166,7 +52070,7 @@
         <v>2</v>
       </c>
       <c r="AE295">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AF295" t="inlineStr">
         <is>
@@ -52343,7 +52247,7 @@
         <v>2</v>
       </c>
       <c r="AE296">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AF296" t="inlineStr">
         <is>
@@ -52520,7 +52424,7 @@
         <v>2</v>
       </c>
       <c r="AE297">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AF297" t="inlineStr">
         <is>
@@ -52697,7 +52601,7 @@
         <v>2</v>
       </c>
       <c r="AE298">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AF298" t="inlineStr">
         <is>
@@ -52869,7 +52773,7 @@
         <v>2</v>
       </c>
       <c r="AE299">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AF299" t="inlineStr">
         <is>
@@ -53046,7 +52950,7 @@
         <v>2</v>
       </c>
       <c r="AE300">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AF300" t="inlineStr">
         <is>
@@ -53223,7 +53127,7 @@
         <v>2</v>
       </c>
       <c r="AE301">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AF301" t="inlineStr">
         <is>
@@ -53398,7 +53302,7 @@
         <v>2</v>
       </c>
       <c r="AE302">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AF302" t="inlineStr">
         <is>
@@ -53575,7 +53479,7 @@
         <v>2</v>
       </c>
       <c r="AE303">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AF303" t="inlineStr">
         <is>
@@ -53752,7 +53656,7 @@
         <v>2</v>
       </c>
       <c r="AE304">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AF304" t="inlineStr">
         <is>
@@ -53929,7 +53833,7 @@
         <v>2</v>
       </c>
       <c r="AE305">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AF305" t="inlineStr">
         <is>
@@ -54104,7 +54008,7 @@
         <v>2</v>
       </c>
       <c r="AE306">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AF306" t="inlineStr">
         <is>
@@ -54280,7 +54184,7 @@
         <v>2</v>
       </c>
       <c r="AE307">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AF307" t="inlineStr">
         <is>
@@ -54453,7 +54357,7 @@
         <v>2</v>
       </c>
       <c r="AE308">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AF308" t="inlineStr">
         <is>
@@ -54631,7 +54535,7 @@
         <v>2</v>
       </c>
       <c r="AE309">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AF309" t="inlineStr">
         <is>
@@ -54808,7 +54712,7 @@
         <v>2</v>
       </c>
       <c r="AE310">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AF310" t="inlineStr">
         <is>
@@ -54985,7 +54889,7 @@
         <v>2</v>
       </c>
       <c r="AE311">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AF311" t="inlineStr">
         <is>
@@ -55160,7 +55064,7 @@
         <v>2</v>
       </c>
       <c r="AE312">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AF312" t="inlineStr">
         <is>
@@ -55337,7 +55241,7 @@
         <v>2</v>
       </c>
       <c r="AE313">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF313" t="inlineStr">
         <is>
@@ -55514,7 +55418,7 @@
         <v>2</v>
       </c>
       <c r="AE314">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF314" t="inlineStr">
         <is>
@@ -55684,7 +55588,7 @@
         <v>2</v>
       </c>
       <c r="AE315">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF315" t="inlineStr">
         <is>
@@ -55856,7 +55760,7 @@
         <v>2</v>
       </c>
       <c r="AE316">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AF316" t="inlineStr">
         <is>
@@ -56031,7 +55935,7 @@
         <v>2</v>
       </c>
       <c r="AE317">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AF317" t="inlineStr">
         <is>
@@ -56209,7 +56113,7 @@
         <v>2</v>
       </c>
       <c r="AE318">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF318" t="inlineStr">
         <is>
@@ -56384,7 +56288,7 @@
         <v>2</v>
       </c>
       <c r="AE319">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF319" t="inlineStr">
         <is>
@@ -56561,7 +56465,7 @@
         <v>2</v>
       </c>
       <c r="AE320">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF320" t="inlineStr">
         <is>
@@ -56738,7 +56642,7 @@
         <v>2</v>
       </c>
       <c r="AE321">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF321" t="inlineStr">
         <is>
@@ -56913,7 +56817,7 @@
         <v>2</v>
       </c>
       <c r="AE322">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF322" t="inlineStr">
         <is>
@@ -57085,7 +56989,7 @@
         <v>2</v>
       </c>
       <c r="AE323">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF323" t="inlineStr">
         <is>
@@ -57260,7 +57164,7 @@
         <v>2</v>
       </c>
       <c r="AE324">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF324" t="inlineStr">
         <is>
@@ -57437,7 +57341,7 @@
         <v>2</v>
       </c>
       <c r="AE325">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF325" t="inlineStr">
         <is>
@@ -57612,7 +57516,7 @@
         <v>2</v>
       </c>
       <c r="AE326">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF326" t="inlineStr">
         <is>
@@ -57789,7 +57693,7 @@
         <v>2</v>
       </c>
       <c r="AE327">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF327" t="inlineStr">
         <is>
@@ -57966,7 +57870,7 @@
         <v>2</v>
       </c>
       <c r="AE328">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF328" t="inlineStr">
         <is>
@@ -58141,7 +58045,7 @@
         <v>2</v>
       </c>
       <c r="AE329">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF329" t="inlineStr">
         <is>
@@ -58316,7 +58220,7 @@
         <v>2</v>
       </c>
       <c r="AE330">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF330" t="inlineStr">
         <is>
@@ -58493,7 +58397,7 @@
         <v>2</v>
       </c>
       <c r="AE331">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF331" t="inlineStr">
         <is>
@@ -58670,7 +58574,7 @@
         <v>2</v>
       </c>
       <c r="AE332">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF332" t="inlineStr">
         <is>
@@ -58847,7 +58751,7 @@
         <v>2</v>
       </c>
       <c r="AE333">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF333" t="inlineStr">
         <is>
@@ -59024,7 +58928,7 @@
         <v>2</v>
       </c>
       <c r="AE334">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF334" t="inlineStr">
         <is>
@@ -59194,7 +59098,7 @@
         <v>2</v>
       </c>
       <c r="AE335">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF335" t="inlineStr">
         <is>
@@ -59371,7 +59275,7 @@
         <v>2</v>
       </c>
       <c r="AE336">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF336" t="inlineStr">
         <is>
@@ -59543,7 +59447,7 @@
         <v>2</v>
       </c>
       <c r="AE337">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF337" t="inlineStr">
         <is>
@@ -59715,7 +59619,7 @@
         <v>2</v>
       </c>
       <c r="AE338">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF338" t="inlineStr">
         <is>
@@ -59892,7 +59796,7 @@
         <v>2</v>
       </c>
       <c r="AE339">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF339" t="inlineStr">
         <is>
@@ -60069,7 +59973,7 @@
         <v>2</v>
       </c>
       <c r="AE340">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF340" t="inlineStr">
         <is>
@@ -60246,7 +60150,7 @@
         <v>2</v>
       </c>
       <c r="AE341">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF341" t="inlineStr">
         <is>
@@ -60421,7 +60325,7 @@
         <v>2</v>
       </c>
       <c r="AE342">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF342" t="inlineStr">
         <is>
@@ -60598,7 +60502,7 @@
         <v>2</v>
       </c>
       <c r="AE343">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF343" t="inlineStr">
         <is>
@@ -60775,7 +60679,7 @@
         <v>2</v>
       </c>
       <c r="AE344">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF344" t="inlineStr">
         <is>
@@ -60945,7 +60849,7 @@
         <v>2</v>
       </c>
       <c r="AE345">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF345" t="inlineStr">
         <is>
@@ -61122,7 +61026,7 @@
         <v>2</v>
       </c>
       <c r="AE346">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF346" t="inlineStr">
         <is>
@@ -61297,7 +61201,7 @@
         <v>2</v>
       </c>
       <c r="AE347">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF347" t="inlineStr">
         <is>
@@ -61474,7 +61378,7 @@
         <v>2</v>
       </c>
       <c r="AE348">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF348" t="inlineStr">
         <is>
@@ -61651,7 +61555,7 @@
         <v>2</v>
       </c>
       <c r="AE349">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF349" t="inlineStr">
         <is>
@@ -61826,7 +61730,7 @@
         <v>2</v>
       </c>
       <c r="AE350">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF350" t="inlineStr">
         <is>
@@ -62003,7 +61907,7 @@
         <v>2</v>
       </c>
       <c r="AE351">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF351" t="inlineStr">
         <is>
@@ -62180,7 +62084,7 @@
         <v>2</v>
       </c>
       <c r="AE352">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF352" t="inlineStr">
         <is>
@@ -62357,7 +62261,7 @@
         <v>2</v>
       </c>
       <c r="AE353">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF353" t="inlineStr">
         <is>
@@ -62534,7 +62438,7 @@
         <v>2</v>
       </c>
       <c r="AE354">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF354" t="inlineStr">
         <is>
@@ -62711,7 +62615,7 @@
         <v>2</v>
       </c>
       <c r="AE355">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF355" t="inlineStr">
         <is>
@@ -62881,7 +62785,7 @@
         <v>2</v>
       </c>
       <c r="AE356">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF356" t="inlineStr">
         <is>
@@ -63056,7 +62960,7 @@
         <v>2</v>
       </c>
       <c r="AE357">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF357" t="inlineStr">
         <is>
@@ -63233,7 +63137,7 @@
         <v>2</v>
       </c>
       <c r="AE358">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF358" t="inlineStr">
         <is>
@@ -63410,7 +63314,7 @@
         <v>2</v>
       </c>
       <c r="AE359">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF359" t="inlineStr">
         <is>
@@ -63585,7 +63489,7 @@
         <v>2</v>
       </c>
       <c r="AE360">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF360" t="inlineStr">
         <is>
@@ -63762,7 +63666,7 @@
         <v>2</v>
       </c>
       <c r="AE361">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF361" t="inlineStr">
         <is>
@@ -63939,7 +63843,7 @@
         <v>2</v>
       </c>
       <c r="AE362">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF362" t="inlineStr">
         <is>
@@ -64109,7 +64013,7 @@
         <v>2</v>
       </c>
       <c r="AE363">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF363" t="inlineStr">
         <is>
@@ -64286,7 +64190,7 @@
         <v>2</v>
       </c>
       <c r="AE364">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF364" t="inlineStr">
         <is>
@@ -64463,7 +64367,7 @@
         <v>2</v>
       </c>
       <c r="AE365">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF365" t="inlineStr">
         <is>
@@ -64640,7 +64544,7 @@
         <v>2</v>
       </c>
       <c r="AE366">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF366" t="inlineStr">
         <is>
@@ -64812,7 +64716,7 @@
         <v>1</v>
       </c>
       <c r="AE367">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF367" t="inlineStr">
         <is>
@@ -64989,7 +64893,7 @@
         <v>1</v>
       </c>
       <c r="AE368">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF368" t="inlineStr">
         <is>
@@ -65167,7 +65071,7 @@
         <v>1</v>
       </c>
       <c r="AE369">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF369" t="inlineStr">
         <is>
@@ -65344,7 +65248,7 @@
         <v>1</v>
       </c>
       <c r="AE370">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF370" t="inlineStr">
         <is>
@@ -65521,7 +65425,7 @@
         <v>2</v>
       </c>
       <c r="AE371">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF371" t="inlineStr">
         <is>
@@ -65698,7 +65602,7 @@
         <v>2</v>
       </c>
       <c r="AE372">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF372" t="inlineStr">
         <is>
@@ -65875,7 +65779,7 @@
         <v>2</v>
       </c>
       <c r="AE373">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF373" t="inlineStr">
         <is>
@@ -66052,7 +65956,7 @@
         <v>2</v>
       </c>
       <c r="AE374">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF374" t="inlineStr">
         <is>
@@ -66229,7 +66133,7 @@
         <v>2</v>
       </c>
       <c r="AE375">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF375" t="inlineStr">
         <is>
@@ -66402,7 +66306,7 @@
         <v>2</v>
       </c>
       <c r="AE376">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF376" t="inlineStr">
         <is>
@@ -66572,7 +66476,7 @@
         <v>2</v>
       </c>
       <c r="AE377">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF377" t="inlineStr">
         <is>
@@ -66749,7 +66653,7 @@
         <v>2</v>
       </c>
       <c r="AE378">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF378" t="inlineStr">
         <is>
@@ -66924,7 +66828,7 @@
         <v>2</v>
       </c>
       <c r="AE379">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF379" t="inlineStr">
         <is>
@@ -67094,7 +66998,7 @@
         <v>2</v>
       </c>
       <c r="AE380">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF380" t="inlineStr">
         <is>
@@ -67270,7 +67174,7 @@
         <v>2</v>
       </c>
       <c r="AE381">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF381" t="inlineStr">
         <is>
@@ -67446,7 +67350,7 @@
         <v>2</v>
       </c>
       <c r="AE382">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF382" t="inlineStr">
         <is>
@@ -67623,7 +67527,7 @@
         <v>1</v>
       </c>
       <c r="AE383">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF383" t="inlineStr">
         <is>
@@ -67799,7 +67703,7 @@
         <v>1</v>
       </c>
       <c r="AE384">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF384" t="inlineStr">
         <is>
@@ -67976,7 +67880,7 @@
         <v>1</v>
       </c>
       <c r="AE385">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF385" t="inlineStr">
         <is>
@@ -68153,7 +68057,7 @@
         <v>1</v>
       </c>
       <c r="AE386">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF386" t="inlineStr">
         <is>
@@ -68325,7 +68229,7 @@
         <v>1</v>
       </c>
       <c r="AE387">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF387" t="inlineStr">
         <is>
@@ -68502,7 +68406,7 @@
         <v>1</v>
       </c>
       <c r="AE388">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF388" t="inlineStr">
         <is>
@@ -68677,7 +68581,7 @@
         <v>1</v>
       </c>
       <c r="AE389">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF389" t="inlineStr">
         <is>
@@ -68854,7 +68758,7 @@
         <v>1</v>
       </c>
       <c r="AE390">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF390" t="inlineStr">
         <is>
@@ -69031,7 +68935,7 @@
         <v>1</v>
       </c>
       <c r="AE391">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF391" t="inlineStr">
         <is>
@@ -69207,7 +69111,7 @@
         <v>1</v>
       </c>
       <c r="AE392">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AF392" t="inlineStr">
         <is>
@@ -69384,7 +69288,7 @@
         <v>1</v>
       </c>
       <c r="AE393">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AF393" t="inlineStr">
         <is>
@@ -69556,7 +69460,7 @@
         <v>1</v>
       </c>
       <c r="AE394">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AF394" t="inlineStr">
         <is>
@@ -69733,7 +69637,7 @@
         <v>1</v>
       </c>
       <c r="AE395">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AF395" t="inlineStr">
         <is>
@@ -69910,7 +69814,7 @@
         <v>1</v>
       </c>
       <c r="AE396">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AF396" t="inlineStr">
         <is>
@@ -70087,7 +69991,7 @@
         <v>1</v>
       </c>
       <c r="AE397">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AF397" t="inlineStr">
         <is>
@@ -70264,7 +70168,7 @@
         <v>1</v>
       </c>
       <c r="AE398">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AF398" t="inlineStr">
         <is>
@@ -70434,7 +70338,7 @@
         <v>1</v>
       </c>
       <c r="AE399">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AF399" t="inlineStr">
         <is>
@@ -70611,7 +70515,7 @@
         <v>1</v>
       </c>
       <c r="AE400">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AF400" t="inlineStr">
         <is>
@@ -70788,7 +70692,7 @@
         <v>1</v>
       </c>
       <c r="AE401">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AF401" t="inlineStr">
         <is>
@@ -70965,7 +70869,7 @@
         <v>1</v>
       </c>
       <c r="AE402">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AF402" t="inlineStr">
         <is>
@@ -71142,7 +71046,7 @@
         <v>1</v>
       </c>
       <c r="AE403">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AF403" t="inlineStr">
         <is>
@@ -71317,7 +71221,7 @@
         <v>1</v>
       </c>
       <c r="AE404">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF404" t="inlineStr">
         <is>
@@ -71494,7 +71398,7 @@
         <v>1</v>
       </c>
       <c r="AE405">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF405" t="inlineStr">
         <is>
@@ -71671,7 +71575,7 @@
         <v>1</v>
       </c>
       <c r="AE406">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF406" t="inlineStr">
         <is>
@@ -71848,7 +71752,7 @@
         <v>1</v>
       </c>
       <c r="AE407">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF407" t="inlineStr">
         <is>
@@ -72025,7 +71929,7 @@
         <v>1</v>
       </c>
       <c r="AE408">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AF408" t="inlineStr">
         <is>
@@ -72202,7 +72106,7 @@
         <v>1</v>
       </c>
       <c r="AE409">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AF409" t="inlineStr">
         <is>
@@ -72379,7 +72283,7 @@
         <v>1</v>
       </c>
       <c r="AE410">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AF410" t="inlineStr">
         <is>
@@ -72549,7 +72453,7 @@
         <v>1</v>
       </c>
       <c r="AE411">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AF411" t="inlineStr">
         <is>
@@ -72726,7 +72630,7 @@
         <v>1</v>
       </c>
       <c r="AE412">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AF412" t="inlineStr">
         <is>
@@ -72903,7 +72807,7 @@
         <v>1</v>
       </c>
       <c r="AE413">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AF413" t="inlineStr">
         <is>
@@ -73078,7 +72982,7 @@
         <v>1</v>
       </c>
       <c r="AE414">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AF414" t="inlineStr">
         <is>
@@ -73255,7 +73159,7 @@
         <v>1</v>
       </c>
       <c r="AE415">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AF415" t="inlineStr">
         <is>
@@ -73427,7 +73331,7 @@
         <v>1</v>
       </c>
       <c r="AE416">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AF416" t="inlineStr">
         <is>
@@ -73598,7 +73502,7 @@
         <v>1</v>
       </c>
       <c r="AE417">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AF417" t="inlineStr">
         <is>
@@ -73768,7 +73672,7 @@
         <v>1</v>
       </c>
       <c r="AE418">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AF418" t="inlineStr">
         <is>
@@ -73938,7 +73842,7 @@
         <v>1</v>
       </c>
       <c r="AE419">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AF419" t="inlineStr">
         <is>
@@ -74115,7 +74019,7 @@
         <v>1</v>
       </c>
       <c r="AE420">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF420" t="inlineStr">
         <is>
@@ -74292,7 +74196,7 @@
         <v>1</v>
       </c>
       <c r="AE421">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF421" t="inlineStr">
         <is>
@@ -74467,7 +74371,7 @@
         <v>1</v>
       </c>
       <c r="AE422">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF422" t="inlineStr">
         <is>
@@ -74644,7 +74548,7 @@
         <v>1</v>
       </c>
       <c r="AE423">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF423" t="inlineStr">
         <is>
@@ -74816,7 +74720,7 @@
         <v>1</v>
       </c>
       <c r="AE424">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF424" t="inlineStr">
         <is>
@@ -74991,7 +74895,7 @@
         <v>1</v>
       </c>
       <c r="AE425">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF425" t="inlineStr">
         <is>
@@ -75170,7 +75074,7 @@
         <v>1</v>
       </c>
       <c r="AE426">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF426" t="inlineStr">
         <is>
@@ -75347,7 +75251,7 @@
         <v>1</v>
       </c>
       <c r="AE427">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AF427" t="inlineStr">
         <is>
@@ -75524,7 +75428,7 @@
         <v>1</v>
       </c>
       <c r="AE428">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AF428" t="inlineStr">
         <is>
@@ -75701,7 +75605,7 @@
         <v>1</v>
       </c>
       <c r="AE429">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AF429" t="inlineStr">
         <is>
@@ -75878,7 +75782,7 @@
         <v>1</v>
       </c>
       <c r="AE430">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AF430" t="inlineStr">
         <is>
@@ -76053,7 +75957,7 @@
         <v>1</v>
       </c>
       <c r="AE431">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AF431" t="inlineStr">
         <is>
@@ -76222,7 +76126,7 @@
         <v>1</v>
       </c>
       <c r="AE432">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AF432" t="inlineStr">
         <is>
@@ -76399,7 +76303,7 @@
         <v>1</v>
       </c>
       <c r="AE433">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AF433" t="inlineStr">
         <is>
@@ -76574,7 +76478,7 @@
         <v>1</v>
       </c>
       <c r="AE434">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AF434" t="inlineStr">
         <is>
@@ -76746,7 +76650,7 @@
         <v>1</v>
       </c>
       <c r="AE435">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AF435" t="inlineStr">
         <is>
@@ -76923,7 +76827,7 @@
         <v>1</v>
       </c>
       <c r="AE436">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AF436" t="inlineStr">
         <is>
@@ -77100,7 +77004,7 @@
         <v>1</v>
       </c>
       <c r="AE437">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AF437" t="inlineStr">
         <is>
@@ -77277,7 +77181,7 @@
         <v>1</v>
       </c>
       <c r="AE438">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AF438" t="inlineStr">
         <is>
@@ -77454,7 +77358,7 @@
         <v>1</v>
       </c>
       <c r="AE439">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF439" t="inlineStr">
         <is>
@@ -77631,7 +77535,7 @@
         <v>1</v>
       </c>
       <c r="AE440">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF440" t="inlineStr">
         <is>
@@ -77806,7 +77710,7 @@
         <v>1</v>
       </c>
       <c r="AE441">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF441" t="inlineStr">
         <is>
@@ -77986,7 +77890,7 @@
         <v>1</v>
       </c>
       <c r="AE442">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF442" t="inlineStr">
         <is>
@@ -78156,7 +78060,7 @@
         <v>1</v>
       </c>
       <c r="AE443">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF443" t="inlineStr">
         <is>
@@ -78326,7 +78230,7 @@
         <v>1</v>
       </c>
       <c r="AE444">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF444" t="inlineStr">
         <is>
@@ -78498,7 +78402,7 @@
         <v>1</v>
       </c>
       <c r="AE445">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF445" t="inlineStr">
         <is>
@@ -78673,7 +78577,7 @@
         <v>1</v>
       </c>
       <c r="AE446">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF446" t="inlineStr">
         <is>
@@ -78850,7 +78754,7 @@
         <v>1</v>
       </c>
       <c r="AE447">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AF447" t="inlineStr">
         <is>
@@ -79020,7 +78924,7 @@
         <v>1</v>
       </c>
       <c r="AE448">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AF448" t="inlineStr">
         <is>
@@ -79197,7 +79101,7 @@
         <v>1</v>
       </c>
       <c r="AE449">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AF449" t="inlineStr">
         <is>
@@ -79369,7 +79273,7 @@
         <v>1</v>
       </c>
       <c r="AE450">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AF450" t="inlineStr">
         <is>
@@ -79546,7 +79450,7 @@
         <v>1</v>
       </c>
       <c r="AE451">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AF451" t="inlineStr">
         <is>
@@ -79721,7 +79625,7 @@
         <v>1</v>
       </c>
       <c r="AE452">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AF452" t="inlineStr">
         <is>
@@ -79898,7 +79802,7 @@
         <v>1</v>
       </c>
       <c r="AE453">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AF453" t="inlineStr">
         <is>
@@ -80075,7 +79979,7 @@
         <v>1</v>
       </c>
       <c r="AE454">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AF454" t="inlineStr">
         <is>
@@ -80252,7 +80156,7 @@
         <v>1</v>
       </c>
       <c r="AE455">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AF455" t="inlineStr">
         <is>
@@ -80430,7 +80334,7 @@
         <v>1</v>
       </c>
       <c r="AE456">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AF456" t="inlineStr">
         <is>
@@ -80607,7 +80511,7 @@
         <v>1</v>
       </c>
       <c r="AE457">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AF457" t="inlineStr">
         <is>
@@ -80782,7 +80686,7 @@
         <v>1</v>
       </c>
       <c r="AE458">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AF458" t="inlineStr">
         <is>
@@ -80959,7 +80863,7 @@
         <v>1</v>
       </c>
       <c r="AE459">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF459" t="inlineStr">
         <is>
@@ -81129,7 +81033,7 @@
         <v>1</v>
       </c>
       <c r="AE460">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF460" t="inlineStr">
         <is>
@@ -81306,7 +81210,7 @@
         <v>1</v>
       </c>
       <c r="AE461">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF461" t="inlineStr">
         <is>
@@ -81476,7 +81380,7 @@
         <v>1</v>
       </c>
       <c r="AE462">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF462" t="inlineStr">
         <is>
@@ -81646,7 +81550,7 @@
         <v>1</v>
       </c>
       <c r="AE463">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF463" t="inlineStr">
         <is>
@@ -81823,7 +81727,7 @@
         <v>1</v>
       </c>
       <c r="AE464">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF464" t="inlineStr">
         <is>
@@ -82000,7 +81904,7 @@
         <v>1</v>
       </c>
       <c r="AE465">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF465" t="inlineStr">
         <is>
@@ -82177,7 +82081,7 @@
         <v>1</v>
       </c>
       <c r="AE466">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF466" t="inlineStr">
         <is>
@@ -82354,7 +82258,7 @@
         <v>1</v>
       </c>
       <c r="AE467">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF467" t="inlineStr">
         <is>
@@ -82526,7 +82430,7 @@
         <v>1</v>
       </c>
       <c r="AE468">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF468" t="inlineStr">
         <is>
@@ -82701,7 +82605,7 @@
         <v>1</v>
       </c>
       <c r="AE469">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF469" t="inlineStr">
         <is>
@@ -82873,7 +82777,7 @@
         <v>1</v>
       </c>
       <c r="AE470">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF470" t="inlineStr">
         <is>
@@ -83050,7 +82954,7 @@
         <v>1</v>
       </c>
       <c r="AE471">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF471" t="inlineStr">
         <is>
@@ -83225,7 +83129,7 @@
         <v>1</v>
       </c>
       <c r="AE472">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF472" t="inlineStr">
         <is>
@@ -83402,7 +83306,7 @@
         <v>1</v>
       </c>
       <c r="AE473">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF473" t="inlineStr">
         <is>
@@ -83579,7 +83483,7 @@
         <v>1</v>
       </c>
       <c r="AE474">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF474" t="inlineStr">
         <is>
@@ -83756,7 +83660,7 @@
         <v>1</v>
       </c>
       <c r="AE475">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF475" t="inlineStr">
         <is>
@@ -83931,7 +83835,7 @@
         <v>1</v>
       </c>
       <c r="AE476">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF476" t="inlineStr">
         <is>
@@ -84103,7 +84007,7 @@
         <v>1</v>
       </c>
       <c r="AE477">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF477" t="inlineStr">
         <is>
@@ -84280,7 +84184,7 @@
         <v>1</v>
       </c>
       <c r="AE478">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF478" t="inlineStr">
         <is>
@@ -84452,7 +84356,7 @@
         <v>1</v>
       </c>
       <c r="AE479">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF479" t="inlineStr">
         <is>
@@ -84629,7 +84533,7 @@
         <v>1</v>
       </c>
       <c r="AE480">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF480" t="inlineStr">
         <is>
@@ -84806,7 +84710,7 @@
         <v>1</v>
       </c>
       <c r="AE481">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF481" t="inlineStr">
         <is>
@@ -84983,7 +84887,7 @@
         <v>1</v>
       </c>
       <c r="AE482">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AF482" t="inlineStr">
         <is>
@@ -85160,7 +85064,7 @@
         <v>1</v>
       </c>
       <c r="AE483">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AF483" t="inlineStr">
         <is>
@@ -85338,7 +85242,7 @@
         <v>1</v>
       </c>
       <c r="AE484">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF484" t="inlineStr">
         <is>
@@ -85513,7 +85417,7 @@
         <v>1</v>
       </c>
       <c r="AE485">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF485" t="inlineStr">
         <is>
@@ -85690,7 +85594,7 @@
         <v>1</v>
       </c>
       <c r="AE486">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF486" t="inlineStr">
         <is>
@@ -85860,7 +85764,7 @@
         <v>1</v>
       </c>
       <c r="AE487">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF487" t="inlineStr">
         <is>
@@ -86037,7 +85941,7 @@
         <v>1</v>
       </c>
       <c r="AE488">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF488" t="inlineStr">
         <is>
@@ -86207,7 +86111,7 @@
         <v>1</v>
       </c>
       <c r="AE489">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF489" t="inlineStr">
         <is>
@@ -86379,7 +86283,7 @@
         <v>1</v>
       </c>
       <c r="AE490">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF490" t="inlineStr">
         <is>
@@ -86555,7 +86459,7 @@
         <v>1</v>
       </c>
       <c r="AE491">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF491" t="inlineStr">
         <is>
@@ -86732,7 +86636,7 @@
         <v>1</v>
       </c>
       <c r="AE492">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF492" t="inlineStr">
         <is>
@@ -86909,7 +86813,7 @@
         <v>1</v>
       </c>
       <c r="AE493">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF493" t="inlineStr">
         <is>
@@ -87086,7 +86990,7 @@
         <v>1</v>
       </c>
       <c r="AE494">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF494" t="inlineStr">
         <is>
@@ -87263,7 +87167,7 @@
         <v>1</v>
       </c>
       <c r="AE495">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF495" t="inlineStr">
         <is>
@@ -87435,7 +87339,7 @@
         <v>1</v>
       </c>
       <c r="AE496">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF496" t="inlineStr">
         <is>
@@ -87606,7 +87510,7 @@
         <v>1</v>
       </c>
       <c r="AE497">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF497" t="inlineStr">
         <is>
@@ -87777,7 +87681,7 @@
         <v>1</v>
       </c>
       <c r="AE498">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF498" t="inlineStr">
         <is>
@@ -87954,7 +87858,7 @@
         <v>1</v>
       </c>
       <c r="AE499">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF499" t="inlineStr">
         <is>
@@ -88126,7 +88030,7 @@
         <v>1</v>
       </c>
       <c r="AE500">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF500" t="inlineStr">
         <is>
@@ -88296,7 +88200,7 @@
         <v>1</v>
       </c>
       <c r="AE501">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF501" t="inlineStr">
         <is>
@@ -88468,7 +88372,7 @@
         <v>1</v>
       </c>
       <c r="AE502">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF502" t="inlineStr">
         <is>
@@ -88645,7 +88549,7 @@
         <v>1</v>
       </c>
       <c r="AE503">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF503" t="inlineStr">
         <is>
@@ -88821,7 +88725,7 @@
         <v>1</v>
       </c>
       <c r="AE504">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF504" t="inlineStr">
         <is>
@@ -88998,7 +88902,7 @@
         <v>1</v>
       </c>
       <c r="AE505">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF505" t="inlineStr">
         <is>
@@ -89175,7 +89079,7 @@
         <v>1</v>
       </c>
       <c r="AE506">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF506" t="inlineStr">
         <is>
@@ -89346,7 +89250,7 @@
         <v>1</v>
       </c>
       <c r="AE507">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF507" t="inlineStr">
         <is>
